--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -562,12 +562,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -577,7 +577,7 @@
         <v>34.16</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>216</v>
@@ -589,12 +589,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -604,7 +604,7 @@
         <v>34.16</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>216</v>
@@ -940,34 +940,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>119</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>155</v>
+        <v>545</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>145</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BIKE.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -982,7 +982,7 @@
         <v>25</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>755</v>
+        <v>605</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>775</v>
@@ -994,12 +994,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1009,24 +1009,24 @@
         <v>25</v>
       </c>
       <c r="E21" s="3" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>1375</v>
-      </c>
       <c r="G21" s="3" t="n">
-        <v>1375</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>BIKE.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1036,24 +1036,24 @@
         <v>25</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>153.7625885009766</v>
+        <v>755</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>290</v>
+        <v>775</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>290</v>
+        <v>775</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1063,24 +1063,24 @@
         <v>25</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>605</v>
+        <v>505</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>775</v>
+        <v>505</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>775</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1090,24 +1090,24 @@
         <v>25</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>414.3801616703698</v>
+        <v>153.7625885009766</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>545</v>
+        <v>290</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>545</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1117,24 +1117,24 @@
         <v>25</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>505</v>
+        <v>1200</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>505</v>
+        <v>1375</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>505</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MLPT.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -1144,51 +1144,51 @@
         <v>25</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1425</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1625</v>
+        <v>975</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1625</v>
+        <v>975</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1190</v>
+        <v>165</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1200</v>
+        <v>202</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EKAD.JK</t>
+          <t>MLPT.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1198,51 +1198,51 @@
         <v>25</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>300</v>
+        <v>1425</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>300</v>
+        <v>1625</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>300</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>SAFE.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>165</v>
+        <v>550</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>202</v>
+        <v>615</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>200</v>
+        <v>615</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAFE.JK</t>
+          <t>EKAD.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1252,51 +1252,51 @@
         <v>25</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>615</v>
+        <v>300</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>615</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>119</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>975</v>
+        <v>155</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>975</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NICK.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1306,24 +1306,24 @@
         <v>24.92</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1540</v>
+        <v>3210</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1930</v>
+        <v>4010</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1930</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>NICK.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1333,24 +1333,24 @@
         <v>24.92</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>3210</v>
+        <v>1540</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4010</v>
+        <v>1930</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4010</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1360,24 +1360,24 @@
         <v>24.9</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2580</v>
+        <v>1445</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1387,24 +1387,24 @@
         <v>24.9</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1445</v>
+        <v>2580</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>SMMT.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1414,13 +1414,13 @@
         <v>24.88</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1170</v>
+        <v>2110</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1255</v>
+        <v>2610</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1255</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="37">
@@ -1453,12 +1453,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SMMT.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1468,67 +1468,67 @@
         <v>24.88</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2110</v>
+        <v>1170</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2610</v>
+        <v>1255</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2610</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>24.85</v>
+        <v>29.7</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>4114.81103515625</v>
+        <v>167</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4120</v>
+        <v>214</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4120</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>29.7</v>
+        <v>24.85</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>167</v>
+        <v>4114.81103515625</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>214</v>
+        <v>4120</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>206</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="41">
@@ -1642,12 +1642,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>ASLI.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -1657,24 +1657,24 @@
         <v>24.76</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>525</v>
+        <v>228</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ASLI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -1684,13 +1684,13 @@
         <v>24.76</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>228</v>
+        <v>525</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
     </row>
     <row r="47">
@@ -1939,12 +1939,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FUJI.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -1954,7 +1954,7 @@
         <v>24.62</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>324</v>
@@ -1966,12 +1966,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>FUJI.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -1981,7 +1981,7 @@
         <v>24.62</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>324</v>
@@ -3044,12 +3044,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -3059,24 +3059,24 @@
         <v>19.75</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>17150</v>
+        <v>5950</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>19400</v>
+        <v>7125</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>19400</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -3086,13 +3086,13 @@
         <v>19.75</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>5950</v>
+        <v>17150</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>7125</v>
+        <v>19400</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>7125</v>
+        <v>19400</v>
       </c>
     </row>
     <row r="99">
@@ -4529,55 +4529,55 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MDIA.JK</t>
+          <t>ERAA.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>30.77</v>
+        <v>17.31</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>106</v>
+        <v>515</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>136</v>
+        <v>610</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>119</v>
+        <v>595</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ERAA.JK</t>
+          <t>MDIA.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>17.31</v>
+        <v>30.77</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>515</v>
+        <v>106</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>610</v>
+        <v>136</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>595</v>
+        <v>119</v>
       </c>
     </row>
     <row r="154">
@@ -4934,55 +4934,55 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ELIT.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>13.79</v>
+        <v>15.17</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>13.79</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>236</v>
+        <v>2800</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>264</v>
+        <v>3340</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>264</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>ELIT.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>15.17</v>
+        <v>13.79</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>13.79</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>2800</v>
+        <v>236</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>3340</v>
+        <v>264</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>3300</v>
+        <v>264</v>
       </c>
     </row>
     <row r="169">
@@ -5015,55 +5015,55 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>17.27</v>
+        <v>20</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>13.64</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>550</v>
+        <v>220</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>645</v>
+        <v>264</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>625</v>
+        <v>250</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>20</v>
+        <v>17.27</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>13.64</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>220</v>
+        <v>550</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>264</v>
+        <v>645</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
     </row>
     <row r="172">
@@ -5744,55 +5744,55 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>CBPE.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>20.62</v>
+        <v>23.76</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>160</v>
+        <v>525</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>193</v>
+        <v>625</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>179</v>
+        <v>565</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CBPE.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>23.76</v>
+        <v>20.62</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>525</v>
+        <v>160</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>625</v>
+        <v>193</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>565</v>
+        <v>179</v>
       </c>
     </row>
     <row r="199">
@@ -5879,55 +5879,55 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>11.61</v>
+        <v>13.39</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>218</v>
+        <v>2270</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>250</v>
+        <v>2540</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>13.39</v>
+        <v>11.61</v>
       </c>
       <c r="D203" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>2270</v>
+        <v>218</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>2540</v>
+        <v>250</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>2500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="204">
@@ -6230,55 +6230,55 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>BIPP.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>23.81</v>
+        <v>14.73</v>
       </c>
       <c r="D215" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>64</v>
+        <v>1955</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>78</v>
+        <v>2220</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>70</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>BIPP.JK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>14.73</v>
+        <v>23.81</v>
       </c>
       <c r="D216" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>1955</v>
+        <v>64</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>2220</v>
+        <v>78</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>2150</v>
+        <v>70</v>
       </c>
     </row>
     <row r="217">
@@ -6392,55 +6392,55 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>DOOH.JK</t>
+          <t>ASGR.JK</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>21.09</v>
+        <v>18.83</v>
       </c>
       <c r="D221" s="2" t="n">
         <v>10.88</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>304</v>
+        <v>1890</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>356</v>
+        <v>2240</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>326</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ASGR.JK</t>
+          <t>DOOH.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>18.83</v>
+        <v>21.09</v>
       </c>
       <c r="D222" s="2" t="n">
         <v>10.88</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>1890</v>
+        <v>304</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>2240</v>
+        <v>356</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>2090</v>
+        <v>326</v>
       </c>
     </row>
     <row r="223">
@@ -6689,55 +6689,55 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>BEST.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>14.29</v>
+        <v>11.61</v>
       </c>
       <c r="D232" s="2" t="n">
         <v>10.32</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>128</v>
+        <v>780</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>144</v>
+        <v>865</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>139</v>
+        <v>855</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>BEST.JK</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>11.61</v>
+        <v>14.29</v>
       </c>
       <c r="D233" s="2" t="n">
         <v>10.32</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>780</v>
+        <v>128</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>865</v>
+        <v>144</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>855</v>
+        <v>139</v>
       </c>
     </row>
     <row r="234">
@@ -6905,25 +6905,25 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C240" s="2" t="n">
-        <v>14.68</v>
+        <v>21.1</v>
       </c>
       <c r="D240" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>545</v>
+        <v>495.4545288085938</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>625</v>
+        <v>660</v>
       </c>
       <c r="G240" s="3" t="n">
         <v>600</v>
@@ -6932,25 +6932,25 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C241" s="2" t="n">
-        <v>21.1</v>
+        <v>14.68</v>
       </c>
       <c r="D241" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E241" s="3" t="n">
-        <v>495.4545288085938</v>
+        <v>545</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>660</v>
+        <v>625</v>
       </c>
       <c r="G241" s="3" t="n">
         <v>600</v>
@@ -6986,28 +6986,28 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>APEX.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C243" s="2" t="n">
-        <v>12.67</v>
+        <v>16.36</v>
       </c>
       <c r="D243" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>150</v>
+        <v>224</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>165</v>
+        <v>242</v>
       </c>
     </row>
     <row r="244">
@@ -7040,28 +7040,28 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>APEX.JK</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C245" s="2" t="n">
-        <v>16.36</v>
+        <v>12.67</v>
       </c>
       <c r="D245" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E245" s="3" t="n">
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>256</v>
+        <v>169</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>242</v>
+        <v>165</v>
       </c>
     </row>
     <row r="246">
@@ -7337,55 +7337,55 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C256" s="2" t="n">
-        <v>27.41</v>
+        <v>15.78</v>
       </c>
       <c r="D256" s="2" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>135</v>
+        <v>492</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>172</v>
+        <v>565</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>148</v>
+        <v>535</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>BKDP.JK</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C257" s="2" t="n">
-        <v>15.78</v>
+        <v>27.41</v>
       </c>
       <c r="D257" s="2" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="E257" s="3" t="n">
-        <v>492</v>
+        <v>135</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>565</v>
+        <v>172</v>
       </c>
       <c r="G257" s="3" t="n">
-        <v>535</v>
+        <v>148</v>
       </c>
     </row>
     <row r="258">
@@ -7823,55 +7823,55 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C274" s="2" t="n">
-        <v>23.23</v>
+        <v>22.73</v>
       </c>
       <c r="D274" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E274" s="3" t="n">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="F274" s="3" t="n">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="G274" s="3" t="n">
-        <v>108</v>
+        <v>192</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C275" s="2" t="n">
-        <v>22.73</v>
+        <v>23.23</v>
       </c>
       <c r="D275" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E275" s="3" t="n">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="F275" s="3" t="n">
-        <v>216</v>
+        <v>122</v>
       </c>
       <c r="G275" s="3" t="n">
-        <v>192</v>
+        <v>108</v>
       </c>
     </row>
     <row r="276">
@@ -8255,55 +8255,55 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>ARKO.JK</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>12.86</v>
+        <v>12.38</v>
       </c>
       <c r="D290" s="2" t="n">
         <v>8.57</v>
       </c>
       <c r="E290" s="3" t="n">
-        <v>136</v>
+        <v>5275</v>
       </c>
       <c r="F290" s="3" t="n">
-        <v>158</v>
+        <v>5900</v>
       </c>
       <c r="G290" s="3" t="n">
-        <v>152</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ARKO.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>12.38</v>
+        <v>12.86</v>
       </c>
       <c r="D291" s="2" t="n">
         <v>8.57</v>
       </c>
       <c r="E291" s="3" t="n">
-        <v>5275</v>
+        <v>136</v>
       </c>
       <c r="F291" s="3" t="n">
-        <v>5900</v>
+        <v>158</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>5700</v>
+        <v>152</v>
       </c>
     </row>
     <row r="292">
@@ -8444,190 +8444,190 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>11.11</v>
+        <v>10.19</v>
       </c>
       <c r="D297" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E297" s="3" t="n">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="F297" s="3" t="n">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>78</v>
+        <v>117</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>HGII.JK</t>
+          <t>BKDP.JK</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>27.27</v>
+        <v>12.5</v>
       </c>
       <c r="D298" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E298" s="3" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F298" s="3" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>HGII.JK</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C299" s="2" t="n">
-        <v>11.67</v>
+        <v>27.27</v>
       </c>
       <c r="D299" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E299" s="3" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="F299" s="3" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>SSTM.JK</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C300" s="2" t="n">
-        <v>19.05</v>
+        <v>22.92</v>
       </c>
       <c r="D300" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E300" s="3" t="n">
-        <v>169</v>
+        <v>555</v>
       </c>
       <c r="F300" s="3" t="n">
-        <v>200</v>
+        <v>590</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>182</v>
+        <v>520</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C301" s="2" t="n">
-        <v>12.5</v>
+        <v>19.05</v>
       </c>
       <c r="D301" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E301" s="3" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="F301" s="3" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>156</v>
+        <v>182</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>SSTM.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C302" s="2" t="n">
-        <v>22.92</v>
+        <v>11.11</v>
       </c>
       <c r="D302" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E302" s="3" t="n">
-        <v>555</v>
+        <v>73</v>
       </c>
       <c r="F302" s="3" t="n">
-        <v>590</v>
+        <v>80</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>520</v>
+        <v>78</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C303" s="2" t="n">
-        <v>10.19</v>
+        <v>11.67</v>
       </c>
       <c r="D303" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E303" s="3" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F303" s="3" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="304">
@@ -8930,82 +8930,82 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>LPCK.JK</t>
+          <t>SWID.JK</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>16.52</v>
+        <v>28.7</v>
       </c>
       <c r="D315" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E315" s="3" t="n">
-        <v>590</v>
+        <v>116</v>
       </c>
       <c r="F315" s="3" t="n">
-        <v>670</v>
+        <v>148</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>620</v>
+        <v>124</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>LPCK.JK</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>12.17</v>
+        <v>16.52</v>
       </c>
       <c r="D316" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E316" s="3" t="n">
-        <v>230</v>
+        <v>590</v>
       </c>
       <c r="F316" s="3" t="n">
-        <v>258</v>
+        <v>670</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>248</v>
+        <v>620</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>SWID.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>28.7</v>
+        <v>12.17</v>
       </c>
       <c r="D317" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E317" s="3" t="n">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="F317" s="3" t="n">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>124</v>
+        <v>248</v>
       </c>
     </row>
     <row r="318">
@@ -9119,55 +9119,55 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>LPPS.JK</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>16.35</v>
+        <v>15.38</v>
       </c>
       <c r="D322" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E322" s="3" t="n">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="G322" s="3" t="n">
-        <v>112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>LPPS.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>15.38</v>
+        <v>16.35</v>
       </c>
       <c r="D323" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E323" s="3" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="F323" s="3" t="n">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="324">
@@ -9335,55 +9335,55 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>23.46</v>
+        <v>10.05</v>
       </c>
       <c r="D330" s="2" t="n">
         <v>7.41</v>
       </c>
       <c r="E330" s="3" t="n">
-        <v>161</v>
+        <v>372</v>
       </c>
       <c r="F330" s="3" t="n">
-        <v>200</v>
+        <v>416</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>174</v>
+        <v>406</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>10.05</v>
+        <v>23.46</v>
       </c>
       <c r="D331" s="2" t="n">
         <v>7.41</v>
       </c>
       <c r="E331" s="3" t="n">
-        <v>372</v>
+        <v>161</v>
       </c>
       <c r="F331" s="3" t="n">
-        <v>416</v>
+        <v>200</v>
       </c>
       <c r="G331" s="3" t="n">
-        <v>406</v>
+        <v>174</v>
       </c>
     </row>
     <row r="332">
@@ -9605,55 +9605,55 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>FIRE.JK</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>22.86</v>
+        <v>22.32</v>
       </c>
       <c r="D340" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E340" s="3" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="F340" s="3" t="n">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="G340" s="3" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>FIRE.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>22.32</v>
+        <v>22.86</v>
       </c>
       <c r="D341" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E341" s="3" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="342">
@@ -9767,82 +9767,82 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>BRNA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>15.5</v>
+        <v>12.4</v>
       </c>
       <c r="D346" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E346" s="3" t="n">
-        <v>660</v>
+        <v>134</v>
       </c>
       <c r="F346" s="3" t="n">
-        <v>745</v>
+        <v>145</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>690</v>
+        <v>138</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>BRNA.JK</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>17.44</v>
+        <v>15.5</v>
       </c>
       <c r="D347" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E347" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>660</v>
       </c>
       <c r="F347" s="3" t="n">
-        <v>101</v>
+        <v>745</v>
       </c>
       <c r="G347" s="3" t="n">
-        <v>92</v>
+        <v>690</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>12.4</v>
+        <v>17.44</v>
       </c>
       <c r="D348" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E348" s="3" t="n">
-        <v>134</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="G348" s="3" t="n">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="349">
@@ -10334,55 +10334,55 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>NAIK.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
-        <v>11.96</v>
+        <v>23.29</v>
       </c>
       <c r="D367" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E367" s="3" t="n">
-        <v>92</v>
+        <v>3000</v>
       </c>
       <c r="F367" s="3" t="n">
-        <v>103</v>
+        <v>3970</v>
       </c>
       <c r="G367" s="3" t="n">
-        <v>98</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>NAIK.JK</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>23.29</v>
+        <v>11.96</v>
       </c>
       <c r="D368" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E368" s="3" t="n">
-        <v>3000</v>
+        <v>92</v>
       </c>
       <c r="F368" s="3" t="n">
-        <v>3970</v>
+        <v>103</v>
       </c>
       <c r="G368" s="3" t="n">
-        <v>3430</v>
+        <v>98</v>
       </c>
     </row>
     <row r="369">
@@ -10523,52 +10523,52 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="D374" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E374" s="3" t="n">
-        <v>236</v>
+        <v>66</v>
       </c>
       <c r="F374" s="3" t="n">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="G374" s="3" t="n">
-        <v>238</v>
+        <v>68</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>25</v>
+        <v>10.94</v>
       </c>
       <c r="D375" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E375" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F375" s="3" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G375" s="3" t="n">
         <v>68</v>
@@ -10577,28 +10577,28 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>10.94</v>
+        <v>12.5</v>
       </c>
       <c r="D376" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E376" s="3" t="n">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="F376" s="3" t="n">
-        <v>71</v>
+        <v>252</v>
       </c>
       <c r="G376" s="3" t="n">
-        <v>68</v>
+        <v>238</v>
       </c>
     </row>
     <row r="377">
@@ -10685,55 +10685,55 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>10.43</v>
+        <v>14.78</v>
       </c>
       <c r="D380" s="2" t="n">
         <v>6.09</v>
       </c>
       <c r="E380" s="3" t="n">
-        <v>117</v>
+        <v>232</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>127</v>
+        <v>264</v>
       </c>
       <c r="G380" s="3" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>14.78</v>
+        <v>10.43</v>
       </c>
       <c r="D381" s="2" t="n">
         <v>6.09</v>
       </c>
       <c r="E381" s="3" t="n">
-        <v>232</v>
+        <v>117</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>264</v>
+        <v>127</v>
       </c>
       <c r="G381" s="3" t="n">
-        <v>244</v>
+        <v>122</v>
       </c>
     </row>
     <row r="382">
@@ -11063,82 +11063,82 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>KOPI.JK</t>
+          <t>SEMA.JK</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>20.19</v>
+        <v>15.38</v>
       </c>
       <c r="D394" s="2" t="n">
         <v>5.77</v>
       </c>
       <c r="E394" s="3" t="n">
-        <v>210</v>
+        <v>105</v>
       </c>
       <c r="F394" s="3" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="G394" s="3" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>KOPI.JK</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>25</v>
+        <v>20.19</v>
       </c>
       <c r="D395" s="2" t="n">
         <v>5.77</v>
       </c>
       <c r="E395" s="3" t="n">
-        <v>1095</v>
+        <v>210</v>
       </c>
       <c r="F395" s="3" t="n">
-        <v>1300</v>
+        <v>250</v>
       </c>
       <c r="G395" s="3" t="n">
-        <v>1100</v>
+        <v>220</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>SEMA.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>15.38</v>
+        <v>25</v>
       </c>
       <c r="D396" s="2" t="n">
         <v>5.77</v>
       </c>
       <c r="E396" s="3" t="n">
-        <v>105</v>
+        <v>1095</v>
       </c>
       <c r="F396" s="3" t="n">
-        <v>120</v>
+        <v>1300</v>
       </c>
       <c r="G396" s="3" t="n">
-        <v>110</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="397">
@@ -11279,55 +11279,55 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>SWID.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>17.76</v>
+        <v>12.15</v>
       </c>
       <c r="D402" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E402" s="3" t="n">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="F402" s="3" t="n">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="G402" s="3" t="n">
-        <v>113</v>
+        <v>226</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>KOKA.JK</t>
+          <t>SWID.JK</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>12.15</v>
+        <v>17.76</v>
       </c>
       <c r="D403" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E403" s="3" t="n">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="F403" s="3" t="n">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="G403" s="3" t="n">
-        <v>226</v>
+        <v>113</v>
       </c>
     </row>
     <row r="404">
@@ -11711,55 +11711,55 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>BIPP.JK</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>17.5</v>
+        <v>13.33</v>
       </c>
       <c r="D418" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E418" s="3" t="n">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="F418" s="3" t="n">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="G418" s="3" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>BIPP.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>13.33</v>
+        <v>17.5</v>
       </c>
       <c r="D419" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E419" s="3" t="n">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="F419" s="3" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="G419" s="3" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
     </row>
     <row r="420">
@@ -12089,25 +12089,25 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>10.69</v>
+        <v>12.21</v>
       </c>
       <c r="D432" s="2" t="n">
         <v>4.58</v>
       </c>
       <c r="E432" s="3" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F432" s="3" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G432" s="3" t="n">
         <v>274</v>
@@ -12116,25 +12116,25 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>12.21</v>
+        <v>10.69</v>
       </c>
       <c r="D433" s="2" t="n">
         <v>4.58</v>
       </c>
       <c r="E433" s="3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G433" s="3" t="n">
         <v>274</v>
@@ -12197,25 +12197,25 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C436" s="2" t="n">
-        <v>11.61</v>
+        <v>10.97</v>
       </c>
       <c r="D436" s="2" t="n">
         <v>4.52</v>
       </c>
       <c r="E436" s="3" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F436" s="3" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G436" s="3" t="n">
         <v>162</v>
@@ -12224,25 +12224,25 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C437" s="2" t="n">
-        <v>10.97</v>
+        <v>11.61</v>
       </c>
       <c r="D437" s="2" t="n">
         <v>4.52</v>
       </c>
       <c r="E437" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F437" s="3" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G437" s="3" t="n">
         <v>162</v>
@@ -12251,55 +12251,55 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C438" s="2" t="n">
-        <v>10.53</v>
+        <v>20.49</v>
       </c>
       <c r="D438" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E438" s="3" t="n">
-        <v>266</v>
+        <v>2470</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>294</v>
+        <v>2940</v>
       </c>
       <c r="G438" s="3" t="n">
-        <v>278</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C439" s="2" t="n">
-        <v>20.49</v>
+        <v>10.53</v>
       </c>
       <c r="D439" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E439" s="3" t="n">
-        <v>2470</v>
+        <v>266</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>2940</v>
+        <v>294</v>
       </c>
       <c r="G439" s="3" t="n">
-        <v>2550</v>
+        <v>278</v>
       </c>
     </row>
     <row r="440">
@@ -12467,55 +12467,55 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>MBTO.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C446" s="2" t="n">
-        <v>12.17</v>
+        <v>13.04</v>
       </c>
       <c r="D446" s="2" t="n">
         <v>4.35</v>
       </c>
       <c r="E446" s="3" t="n">
-        <v>115</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F446" s="3" t="n">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="G446" s="3" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>MBTO.JK</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C447" s="2" t="n">
-        <v>13.04</v>
+        <v>12.17</v>
       </c>
       <c r="D447" s="2" t="n">
         <v>4.35</v>
       </c>
       <c r="E447" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>115</v>
       </c>
       <c r="F447" s="3" t="n">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="G447" s="3" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="448">
@@ -12548,55 +12548,55 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C449" s="2" t="n">
-        <v>12.86</v>
+        <v>11.66</v>
       </c>
       <c r="D449" s="2" t="n">
         <v>4.29</v>
       </c>
       <c r="E449" s="3" t="n">
-        <v>71</v>
+        <v>815</v>
       </c>
       <c r="F449" s="3" t="n">
-        <v>79</v>
+        <v>910</v>
       </c>
       <c r="G449" s="3" t="n">
-        <v>73</v>
+        <v>850</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C450" s="2" t="n">
-        <v>11.66</v>
+        <v>12.86</v>
       </c>
       <c r="D450" s="2" t="n">
         <v>4.29</v>
       </c>
       <c r="E450" s="3" t="n">
-        <v>815</v>
+        <v>71</v>
       </c>
       <c r="F450" s="3" t="n">
-        <v>910</v>
+        <v>79</v>
       </c>
       <c r="G450" s="3" t="n">
-        <v>850</v>
+        <v>73</v>
       </c>
     </row>
     <row r="451">
@@ -12683,55 +12683,55 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C454" s="2" t="n">
-        <v>25</v>
+        <v>10.42</v>
       </c>
       <c r="D454" s="2" t="n">
         <v>4.17</v>
       </c>
       <c r="E454" s="3" t="n">
-        <v>480</v>
+        <v>96</v>
       </c>
       <c r="F454" s="3" t="n">
-        <v>600</v>
+        <v>106</v>
       </c>
       <c r="G454" s="3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C455" s="2" t="n">
-        <v>10.42</v>
+        <v>25</v>
       </c>
       <c r="D455" s="2" t="n">
         <v>4.17</v>
       </c>
       <c r="E455" s="3" t="n">
-        <v>96</v>
+        <v>480</v>
       </c>
       <c r="F455" s="3" t="n">
-        <v>106</v>
+        <v>600</v>
       </c>
       <c r="G455" s="3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="456">
@@ -12764,25 +12764,25 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C457" s="2" t="n">
-        <v>10.67</v>
+        <v>17.33</v>
       </c>
       <c r="D457" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E457" s="3" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F457" s="3" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G457" s="3" t="n">
         <v>78</v>
@@ -12791,25 +12791,25 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C458" s="2" t="n">
-        <v>17.33</v>
+        <v>10.67</v>
       </c>
       <c r="D458" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E458" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F458" s="3" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G458" s="3" t="n">
         <v>78</v>
@@ -13682,25 +13682,25 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>VRNA.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C491" s="2" t="n">
-        <v>26.26</v>
+        <v>34.34</v>
       </c>
       <c r="D491" s="2" t="n">
         <v>3.03</v>
       </c>
       <c r="E491" s="3" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F491" s="3" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G491" s="3" t="n">
         <v>102</v>
@@ -13709,25 +13709,25 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>VRNA.JK</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C492" s="2" t="n">
-        <v>34.34</v>
+        <v>26.26</v>
       </c>
       <c r="D492" s="2" t="n">
         <v>3.03</v>
       </c>
       <c r="E492" s="3" t="n">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="F492" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G492" s="3" t="n">
         <v>102</v>
@@ -13736,55 +13736,55 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C493" s="2" t="n">
-        <v>14.71</v>
+        <v>17.65</v>
       </c>
       <c r="D493" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E493" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="F493" s="3" t="n">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="G493" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C494" s="2" t="n">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
       <c r="D494" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E494" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="F494" s="3" t="n">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="G494" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
     </row>
     <row r="495">
@@ -13979,55 +13979,55 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>CRAB.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C502" s="2" t="n">
-        <v>17.59</v>
+        <v>16.7</v>
       </c>
       <c r="D502" s="2" t="n">
         <v>2.78</v>
       </c>
       <c r="E502" s="3" t="n">
-        <v>218</v>
+        <v>5200</v>
       </c>
       <c r="F502" s="3" t="n">
-        <v>254</v>
+        <v>5450</v>
       </c>
       <c r="G502" s="3" t="n">
-        <v>222</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>CRAB.JK</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C503" s="2" t="n">
-        <v>16.7</v>
+        <v>17.59</v>
       </c>
       <c r="D503" s="2" t="n">
         <v>2.78</v>
       </c>
       <c r="E503" s="3" t="n">
-        <v>5200</v>
+        <v>218</v>
       </c>
       <c r="F503" s="3" t="n">
-        <v>5450</v>
+        <v>254</v>
       </c>
       <c r="G503" s="3" t="n">
-        <v>4800</v>
+        <v>222</v>
       </c>
     </row>
     <row r="504">
@@ -14114,55 +14114,55 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C507" s="2" t="n">
-        <v>14.58</v>
+        <v>10.39</v>
       </c>
       <c r="D507" s="2" t="n">
         <v>2.6</v>
       </c>
       <c r="E507" s="3" t="n">
-        <v>1065</v>
+        <v>72.38636016845703</v>
       </c>
       <c r="F507" s="3" t="n">
-        <v>1100</v>
+        <v>85</v>
       </c>
       <c r="G507" s="3" t="n">
-        <v>985</v>
+        <v>79</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C508" s="2" t="n">
-        <v>10.39</v>
+        <v>14.58</v>
       </c>
       <c r="D508" s="2" t="n">
         <v>2.6</v>
       </c>
       <c r="E508" s="3" t="n">
-        <v>72.38636016845703</v>
+        <v>1065</v>
       </c>
       <c r="F508" s="3" t="n">
-        <v>85</v>
+        <v>1100</v>
       </c>
       <c r="G508" s="3" t="n">
-        <v>79</v>
+        <v>985</v>
       </c>
     </row>
     <row r="509">
@@ -14330,55 +14330,55 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>LABA.JK</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C515" s="2" t="n">
-        <v>17.44</v>
+        <v>14.73</v>
       </c>
       <c r="D515" s="2" t="n">
         <v>2.33</v>
       </c>
       <c r="E515" s="3" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="F515" s="3" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="G515" s="3" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>LABA.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C516" s="2" t="n">
-        <v>14.73</v>
+        <v>17.44</v>
       </c>
       <c r="D516" s="2" t="n">
         <v>2.33</v>
       </c>
       <c r="E516" s="3" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="F516" s="3" t="n">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="G516" s="3" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
     </row>
     <row r="517">
@@ -14411,109 +14411,109 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C518" s="2" t="n">
-        <v>20.69</v>
+        <v>15.21</v>
       </c>
       <c r="D518" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="E518" s="3" t="n">
-        <v>99</v>
+        <v>1085</v>
       </c>
       <c r="F518" s="3" t="n">
-        <v>105</v>
+        <v>1250</v>
       </c>
       <c r="G518" s="3" t="n">
-        <v>89</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C519" s="2" t="n">
-        <v>15.21</v>
+        <v>20.69</v>
       </c>
       <c r="D519" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="E519" s="3" t="n">
-        <v>1085</v>
+        <v>99</v>
       </c>
       <c r="F519" s="3" t="n">
-        <v>1250</v>
+        <v>105</v>
       </c>
       <c r="G519" s="3" t="n">
-        <v>1110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>INAI.JK</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C520" s="2" t="n">
-        <v>12.36</v>
+        <v>13.48</v>
       </c>
       <c r="D520" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E520" s="3" t="n">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="F520" s="3" t="n">
-        <v>100</v>
+        <v>202</v>
       </c>
       <c r="G520" s="3" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>INAI.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C521" s="2" t="n">
-        <v>13.48</v>
+        <v>12.36</v>
       </c>
       <c r="D521" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E521" s="3" t="n">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F521" s="3" t="n">
-        <v>202</v>
+        <v>100</v>
       </c>
       <c r="G521" s="3" t="n">
-        <v>182</v>
+        <v>91</v>
       </c>
     </row>
     <row r="522">
@@ -14816,25 +14816,25 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>DOSS.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C533" s="2" t="n">
-        <v>19.38</v>
+        <v>15.62</v>
       </c>
       <c r="D533" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="E533" s="3" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="F533" s="3" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G533" s="3" t="n">
         <v>163</v>
@@ -14843,25 +14843,25 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>DOSS.JK</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C534" s="2" t="n">
-        <v>15.62</v>
+        <v>19.38</v>
       </c>
       <c r="D534" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="E534" s="3" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F534" s="3" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G534" s="3" t="n">
         <v>163</v>
@@ -15167,55 +15167,55 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>LAND.JK</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C546" s="2" t="n">
-        <v>11.83</v>
+        <v>11.29</v>
       </c>
       <c r="D546" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E546" s="3" t="n">
-        <v>181.15625</v>
+        <v>62</v>
       </c>
       <c r="F546" s="3" t="n">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="G546" s="3" t="n">
-        <v>189</v>
+        <v>63</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>LAND.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C547" s="2" t="n">
-        <v>11.29</v>
+        <v>11.83</v>
       </c>
       <c r="D547" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E547" s="3" t="n">
-        <v>62</v>
+        <v>181.15625</v>
       </c>
       <c r="F547" s="3" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="G547" s="3" t="n">
-        <v>63</v>
+        <v>189</v>
       </c>
     </row>
     <row r="548">
@@ -15410,55 +15410,55 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C555" s="2" t="n">
-        <v>15.38</v>
+        <v>19.87</v>
       </c>
       <c r="D555" s="2" t="n">
         <v>1.28</v>
       </c>
       <c r="E555" s="3" t="n">
-        <v>79</v>
+        <v>8125</v>
       </c>
       <c r="F555" s="3" t="n">
-        <v>90</v>
+        <v>9350</v>
       </c>
       <c r="G555" s="3" t="n">
-        <v>79</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C556" s="2" t="n">
-        <v>19.87</v>
+        <v>15.38</v>
       </c>
       <c r="D556" s="2" t="n">
         <v>1.28</v>
       </c>
       <c r="E556" s="3" t="n">
-        <v>8125</v>
+        <v>79</v>
       </c>
       <c r="F556" s="3" t="n">
-        <v>9350</v>
+        <v>90</v>
       </c>
       <c r="G556" s="3" t="n">
-        <v>7900</v>
+        <v>79</v>
       </c>
     </row>
     <row r="557">
@@ -15761,82 +15761,82 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>PORT.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C568" s="2" t="n">
-        <v>16.38</v>
+        <v>20</v>
       </c>
       <c r="D568" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E568" s="3" t="n">
-        <v>1015</v>
+        <v>406</v>
       </c>
       <c r="F568" s="3" t="n">
-        <v>1030</v>
+        <v>432</v>
       </c>
       <c r="G568" s="3" t="n">
-        <v>890</v>
+        <v>362</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C569" s="2" t="n">
-        <v>20</v>
+        <v>10.17</v>
       </c>
       <c r="D569" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E569" s="3" t="n">
-        <v>406</v>
+        <v>177</v>
       </c>
       <c r="F569" s="3" t="n">
-        <v>432</v>
+        <v>195</v>
       </c>
       <c r="G569" s="3" t="n">
-        <v>362</v>
+        <v>178</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>PORT.JK</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C570" s="2" t="n">
-        <v>10.17</v>
+        <v>16.38</v>
       </c>
       <c r="D570" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E570" s="3" t="n">
-        <v>177</v>
+        <v>1015</v>
       </c>
       <c r="F570" s="3" t="n">
-        <v>195</v>
+        <v>1030</v>
       </c>
       <c r="G570" s="3" t="n">
-        <v>178</v>
+        <v>890</v>
       </c>
     </row>
     <row r="571">
@@ -15869,55 +15869,55 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C572" s="2" t="n">
-        <v>11.43</v>
+        <v>11.96</v>
       </c>
       <c r="D572" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="E572" s="3" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F572" s="3" t="n">
         <v>468</v>
       </c>
       <c r="G572" s="3" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C573" s="2" t="n">
-        <v>11.96</v>
+        <v>11.43</v>
       </c>
       <c r="D573" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="E573" s="3" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F573" s="3" t="n">
         <v>468</v>
       </c>
       <c r="G573" s="3" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="574">
@@ -16004,109 +16004,109 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>RELI.JK</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C577" s="2" t="n">
-        <v>10.91</v>
+        <v>14.29</v>
       </c>
       <c r="D577" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E577" s="3" t="n">
-        <v>165</v>
+        <v>520</v>
       </c>
       <c r="F577" s="3" t="n">
-        <v>183</v>
+        <v>600</v>
       </c>
       <c r="G577" s="3" t="n">
-        <v>165</v>
+        <v>525</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>PDES.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C578" s="2" t="n">
-        <v>18.01</v>
+        <v>12.87</v>
       </c>
       <c r="D578" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E578" s="3" t="n">
-        <v>424</v>
+        <v>93</v>
       </c>
       <c r="F578" s="3" t="n">
-        <v>498</v>
+        <v>114</v>
       </c>
       <c r="G578" s="3" t="n">
-        <v>422</v>
+        <v>101</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C579" s="2" t="n">
-        <v>12.38</v>
+        <v>17.5</v>
       </c>
       <c r="D579" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E579" s="3" t="n">
-        <v>91.91489410400391</v>
+        <v>163</v>
       </c>
       <c r="F579" s="3" t="n">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="G579" s="3" t="n">
-        <v>105</v>
+        <v>160</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C580" s="2" t="n">
-        <v>28.48</v>
+        <v>12.78</v>
       </c>
       <c r="D580" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E580" s="3" t="n">
-        <v>152</v>
+        <v>2640</v>
       </c>
       <c r="F580" s="3" t="n">
-        <v>194</v>
+        <v>3000</v>
       </c>
       <c r="G580" s="3" t="n">
-        <v>151</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="581">
@@ -16139,163 +16139,163 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C582" s="2" t="n">
-        <v>10.26</v>
+        <v>28.48</v>
       </c>
       <c r="D582" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E582" s="3" t="n">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="F582" s="3" t="n">
-        <v>86</v>
+        <v>194</v>
       </c>
       <c r="G582" s="3" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>MPRO.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C583" s="2" t="n">
-        <v>19.95</v>
+        <v>10.91</v>
       </c>
       <c r="D583" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E583" s="3" t="n">
-        <v>11750</v>
+        <v>165</v>
       </c>
       <c r="F583" s="3" t="n">
-        <v>11875</v>
+        <v>183</v>
       </c>
       <c r="G583" s="3" t="n">
-        <v>9900</v>
+        <v>165</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>MPRO.JK</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C584" s="2" t="n">
-        <v>12.87</v>
+        <v>19.95</v>
       </c>
       <c r="D584" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E584" s="3" t="n">
-        <v>93</v>
+        <v>11750</v>
       </c>
       <c r="F584" s="3" t="n">
-        <v>114</v>
+        <v>11875</v>
       </c>
       <c r="G584" s="3" t="n">
-        <v>101</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C585" s="2" t="n">
-        <v>12.78</v>
+        <v>12.38</v>
       </c>
       <c r="D585" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E585" s="3" t="n">
-        <v>2640</v>
+        <v>91.91489410400391</v>
       </c>
       <c r="F585" s="3" t="n">
-        <v>3000</v>
+        <v>118</v>
       </c>
       <c r="G585" s="3" t="n">
-        <v>2660</v>
+        <v>105</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>RELI.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C586" s="2" t="n">
-        <v>14.29</v>
+        <v>10.26</v>
       </c>
       <c r="D586" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E586" s="3" t="n">
-        <v>520</v>
+        <v>79</v>
       </c>
       <c r="F586" s="3" t="n">
-        <v>600</v>
+        <v>86</v>
       </c>
       <c r="G586" s="3" t="n">
-        <v>525</v>
+        <v>78</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>PDES.JK</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C587" s="2" t="n">
-        <v>17.5</v>
+        <v>18.01</v>
       </c>
       <c r="D587" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E587" s="3" t="n">
-        <v>163</v>
+        <v>424</v>
       </c>
       <c r="F587" s="3" t="n">
-        <v>188</v>
+        <v>498</v>
       </c>
       <c r="G587" s="3" t="n">
-        <v>160</v>
+        <v>422</v>
       </c>
     </row>
     <row r="588">
@@ -17084,12 +17084,12 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C617" s="2" t="n">
@@ -17099,67 +17099,67 @@
         <v>-2.53</v>
       </c>
       <c r="E617" s="3" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="F617" s="3" t="n">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="G617" s="3" t="n">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C618" s="2" t="n">
-        <v>19.62</v>
+        <v>15.19</v>
       </c>
       <c r="D618" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E618" s="3" t="n">
-        <v>910</v>
+        <v>160</v>
       </c>
       <c r="F618" s="3" t="n">
-        <v>945</v>
+        <v>182</v>
       </c>
       <c r="G618" s="3" t="n">
-        <v>770</v>
+        <v>154</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C619" s="2" t="n">
-        <v>15.19</v>
+        <v>19.62</v>
       </c>
       <c r="D619" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E619" s="3" t="n">
-        <v>80</v>
+        <v>910</v>
       </c>
       <c r="F619" s="3" t="n">
-        <v>91</v>
+        <v>945</v>
       </c>
       <c r="G619" s="3" t="n">
-        <v>77</v>
+        <v>770</v>
       </c>
     </row>
     <row r="620">
@@ -17651,16 +17651,16 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C638" s="2" t="n">
-        <v>20.24</v>
+        <v>15.48</v>
       </c>
       <c r="D638" s="2" t="n">
         <v>-4.76</v>
@@ -17669,7 +17669,7 @@
         <v>84</v>
       </c>
       <c r="F638" s="3" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G638" s="3" t="n">
         <v>80</v>
@@ -17678,16 +17678,16 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C639" s="2" t="n">
-        <v>15.48</v>
+        <v>20.24</v>
       </c>
       <c r="D639" s="2" t="n">
         <v>-4.76</v>
@@ -17696,7 +17696,7 @@
         <v>84</v>
       </c>
       <c r="F639" s="3" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G639" s="3" t="n">
         <v>80</v>
@@ -17921,55 +17921,55 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C648" s="2" t="n">
-        <v>21.24</v>
+        <v>13.58</v>
       </c>
       <c r="D648" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1827.910536399762</v>
+        <v>162</v>
       </c>
       <c r="F648" s="3" t="n">
-        <v>1855</v>
+        <v>184</v>
       </c>
       <c r="G648" s="3" t="n">
-        <v>1445</v>
+        <v>153</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C649" s="2" t="n">
-        <v>13.58</v>
+        <v>21.24</v>
       </c>
       <c r="D649" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E649" s="3" t="n">
-        <v>162</v>
+        <v>1827.910536399762</v>
       </c>
       <c r="F649" s="3" t="n">
-        <v>184</v>
+        <v>1855</v>
       </c>
       <c r="G649" s="3" t="n">
-        <v>153</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="650">
@@ -18920,55 +18920,55 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>DMMX.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C685" s="2" t="n">
-        <v>25</v>
+        <v>16.35</v>
       </c>
       <c r="D685" s="2" t="n">
         <v>-12.5</v>
       </c>
       <c r="E685" s="3" t="n">
-        <v>258</v>
+        <v>91</v>
       </c>
       <c r="F685" s="3" t="n">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c r="G685" s="3" t="n">
-        <v>189</v>
+        <v>91</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>DMMX.JK</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C686" s="2" t="n">
-        <v>16.35</v>
+        <v>25</v>
       </c>
       <c r="D686" s="2" t="n">
         <v>-12.5</v>
       </c>
       <c r="E686" s="3" t="n">
-        <v>91</v>
+        <v>258</v>
       </c>
       <c r="F686" s="3" t="n">
-        <v>121</v>
+        <v>270</v>
       </c>
       <c r="G686" s="3" t="n">
-        <v>91</v>
+        <v>189</v>
       </c>
     </row>
     <row r="687">
@@ -19379,82 +19379,82 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C702" s="2" t="n">
-        <v>24.79</v>
+        <v>25</v>
       </c>
       <c r="D702" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E702" s="3" t="n">
-        <v>1510</v>
+        <v>165</v>
       </c>
       <c r="F702" s="3" t="n">
-        <v>1510</v>
+        <v>210</v>
       </c>
       <c r="G702" s="3" t="n">
-        <v>1030</v>
+        <v>143</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C703" s="2" t="n">
-        <v>25</v>
+        <v>14.05</v>
       </c>
       <c r="D703" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E703" s="3" t="n">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="F703" s="3" t="n">
-        <v>210</v>
+        <v>138</v>
       </c>
       <c r="G703" s="3" t="n">
-        <v>143</v>
+        <v>103</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C704" s="2" t="n">
-        <v>14.05</v>
+        <v>24.79</v>
       </c>
       <c r="D704" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E704" s="3" t="n">
-        <v>115</v>
+        <v>1510</v>
       </c>
       <c r="F704" s="3" t="n">
-        <v>138</v>
+        <v>1510</v>
       </c>
       <c r="G704" s="3" t="n">
-        <v>103</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="705">

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -4057,9 +4057,7 @@
       <c r="D134" s="2" t="n">
         <v>16.44</v>
       </c>
-      <c r="E134" s="3" t="n">
-        <v>296</v>
-      </c>
+      <c r="E134" s="3" t="inlineStr"/>
       <c r="F134" s="3" t="n">
         <v>358</v>
       </c>
@@ -9754,9 +9752,7 @@
       <c r="D345" s="2" t="n">
         <v>7.63</v>
       </c>
-      <c r="E345" s="3" t="n">
-        <v>118</v>
-      </c>
+      <c r="E345" s="3" t="inlineStr"/>
       <c r="F345" s="3" t="n">
         <v>134</v>
       </c>
@@ -10267,9 +10263,7 @@
       <c r="D364" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="E364" s="3" t="n">
-        <v>73</v>
-      </c>
+      <c r="E364" s="3" t="inlineStr"/>
       <c r="F364" s="3" t="n">
         <v>86</v>
       </c>
@@ -12778,9 +12772,7 @@
       <c r="D457" s="2" t="n">
         <v>4.79</v>
       </c>
-      <c r="E457" s="3" t="n">
-        <v>3440</v>
-      </c>
+      <c r="E457" s="3" t="inlineStr"/>
       <c r="F457" s="3" t="n">
         <v>4070</v>
       </c>
@@ -13318,9 +13310,7 @@
       <c r="D477" s="2" t="n">
         <v>4.41</v>
       </c>
-      <c r="E477" s="3" t="n">
-        <v>183</v>
-      </c>
+      <c r="E477" s="3" t="inlineStr"/>
       <c r="F477" s="3" t="n">
         <v>183</v>
       </c>
@@ -16855,9 +16845,7 @@
       <c r="D608" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="E608" s="3" t="n">
-        <v>1005</v>
-      </c>
+      <c r="E608" s="3" t="inlineStr"/>
       <c r="F608" s="3" t="n">
         <v>1180</v>
       </c>
@@ -18286,9 +18274,7 @@
       <c r="D661" s="2" t="n">
         <v>-2.42</v>
       </c>
-      <c r="E661" s="3" t="n">
-        <v>890</v>
-      </c>
+      <c r="E661" s="3" t="inlineStr"/>
       <c r="F661" s="3" t="n">
         <v>1025</v>
       </c>
@@ -18502,9 +18488,7 @@
       <c r="D669" s="2" t="n">
         <v>-2.7</v>
       </c>
-      <c r="E669" s="3" t="n">
-        <v>186</v>
-      </c>
+      <c r="E669" s="3" t="inlineStr"/>
       <c r="F669" s="3" t="n">
         <v>208</v>
       </c>
@@ -20473,9 +20457,7 @@
       <c r="D742" s="2" t="n">
         <v>-14.52</v>
       </c>
-      <c r="E742" s="3" t="n">
-        <v>140</v>
-      </c>
+      <c r="E742" s="3" t="inlineStr"/>
       <c r="F742" s="3" t="n">
         <v>148</v>
       </c>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -616,12 +616,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -631,7 +631,7 @@
         <v>34.16</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>216</v>
@@ -643,12 +643,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -658,7 +658,7 @@
         <v>34.16</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>216</v>
@@ -994,12 +994,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1009,51 +1009,51 @@
         <v>25</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>153.7625885009766</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>290</v>
+        <v>975</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>290</v>
+        <v>975</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>505</v>
+        <v>119</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>505</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>505</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BIKE.JK</t>
+          <t>SAFE.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1063,24 +1063,24 @@
         <v>25</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>755</v>
+        <v>550</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>775</v>
+        <v>615</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>775</v>
+        <v>615</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>BIKE.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1090,78 +1090,78 @@
         <v>25</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1190</v>
+        <v>755</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1200</v>
+        <v>775</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1200</v>
+        <v>775</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>119</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>155</v>
+        <v>545</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>145</v>
+        <v>545</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EKAD.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>300</v>
+        <v>165</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MLPT.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -1171,24 +1171,24 @@
         <v>25</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1425</v>
+        <v>153.7625885009766</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1625</v>
+        <v>290</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1625</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>EKAD.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1198,24 +1198,24 @@
         <v>25</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1375</v>
+        <v>300</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1375</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -1225,24 +1225,24 @@
         <v>25</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>1190</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>975</v>
+        <v>1200</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>975</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAFE.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1252,24 +1252,24 @@
         <v>25</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>550</v>
+        <v>605</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>615</v>
+        <v>775</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>615</v>
+        <v>775</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>MLPT.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -1279,51 +1279,51 @@
         <v>25</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>605</v>
+        <v>1425</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>775</v>
+        <v>1625</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>775</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>165</v>
+        <v>1200</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>202</v>
+        <v>1375</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>200</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1333,24 +1333,24 @@
         <v>25</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>414.3801616703698</v>
+        <v>505</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>545</v>
+        <v>505</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>545</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NICK.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1360,24 +1360,24 @@
         <v>24.92</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1540</v>
+        <v>3210</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1930</v>
+        <v>4010</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1930</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>NICK.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1387,24 +1387,24 @@
         <v>24.92</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>3210</v>
+        <v>1540</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4010</v>
+        <v>1930</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>4010</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1414,24 +1414,24 @@
         <v>24.9</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2580</v>
+        <v>1445</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1441,24 +1441,24 @@
         <v>24.9</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1445</v>
+        <v>2580</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1468,24 +1468,24 @@
         <v>24.88</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2170</v>
+        <v>1170</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2510</v>
+        <v>1255</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2510</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SMMT.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1495,24 +1495,24 @@
         <v>24.88</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2110</v>
+        <v>2170</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2610</v>
+        <v>2510</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2610</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>SMMT.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -1522,67 +1522,67 @@
         <v>24.88</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1170</v>
+        <v>2110</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1255</v>
+        <v>2610</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1255</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>29.7</v>
+        <v>24.85</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>167</v>
+        <v>4114.81103515625</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>214</v>
+        <v>4120</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>206</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>24.85</v>
+        <v>29.7</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>4114.81103515625</v>
+        <v>167</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>4120</v>
+        <v>214</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>4120</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43">
@@ -1885,12 +1885,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -1900,24 +1900,24 @@
         <v>24.69</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>404</v>
+        <v>1625</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>404</v>
+        <v>2020</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>404</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -1927,13 +1927,13 @@
         <v>24.69</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1625</v>
+        <v>404</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2020</v>
+        <v>404</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>2020</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56">
@@ -1993,12 +1993,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FUJI.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -2008,7 +2008,7 @@
         <v>24.62</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="F58" s="3" t="n">
         <v>324</v>
@@ -2020,12 +2020,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>FUJI.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -2035,7 +2035,7 @@
         <v>24.62</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>324</v>
@@ -4057,7 +4057,9 @@
       <c r="D134" s="2" t="n">
         <v>16.44</v>
       </c>
-      <c r="E134" s="3" t="inlineStr"/>
+      <c r="E134" s="3" t="n">
+        <v>296</v>
+      </c>
       <c r="F134" s="3" t="n">
         <v>358</v>
       </c>
@@ -6147,55 +6149,55 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>CBPE.JK</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>20.62</v>
+        <v>23.76</v>
       </c>
       <c r="D212" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>160</v>
+        <v>525</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>193</v>
+        <v>625</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>179</v>
+        <v>565</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CBPE.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>23.76</v>
+        <v>20.62</v>
       </c>
       <c r="D213" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>525</v>
+        <v>160</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>625</v>
+        <v>193</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>565</v>
+        <v>179</v>
       </c>
     </row>
     <row r="214">
@@ -6282,55 +6284,55 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>11.61</v>
+        <v>13.39</v>
       </c>
       <c r="D217" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>218</v>
+        <v>2270</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>250</v>
+        <v>2540</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>13.39</v>
+        <v>11.61</v>
       </c>
       <c r="D218" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>2270</v>
+        <v>218</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>2540</v>
+        <v>250</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>2500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="219">
@@ -6606,28 +6608,28 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>BIPP.JK</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
-        <v>12.5</v>
+        <v>23.81</v>
       </c>
       <c r="D229" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>720</v>
+        <v>64</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>810</v>
+        <v>78</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
     </row>
     <row r="230">
@@ -6660,28 +6662,28 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>BIPP.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>23.81</v>
+        <v>12.5</v>
       </c>
       <c r="D231" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>64</v>
+        <v>720</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>78</v>
+        <v>810</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
     </row>
     <row r="232">
@@ -6795,55 +6797,55 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DOOH.JK</t>
+          <t>ASGR.JK</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>21.09</v>
+        <v>18.83</v>
       </c>
       <c r="D236" s="2" t="n">
         <v>10.88</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>304</v>
+        <v>1890</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>356</v>
+        <v>2240</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>326</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ASGR.JK</t>
+          <t>DOOH.JK</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>18.83</v>
+        <v>21.09</v>
       </c>
       <c r="D237" s="2" t="n">
         <v>10.88</v>
       </c>
       <c r="E237" s="3" t="n">
-        <v>1890</v>
+        <v>304</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>2240</v>
+        <v>356</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>2090</v>
+        <v>326</v>
       </c>
     </row>
     <row r="238">
@@ -7092,55 +7094,55 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BEST.JK</t>
+          <t>VKTR.JK</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>14.29</v>
+        <v>11.61</v>
       </c>
       <c r="D247" s="2" t="n">
         <v>10.32</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>128</v>
+        <v>780</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>144</v>
+        <v>865</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>139</v>
+        <v>855</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>VKTR.JK</t>
+          <t>BEST.JK</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C248" s="2" t="n">
-        <v>11.61</v>
+        <v>14.29</v>
       </c>
       <c r="D248" s="2" t="n">
         <v>10.32</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>780</v>
+        <v>128</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>865</v>
+        <v>144</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>855</v>
+        <v>139</v>
       </c>
     </row>
     <row r="249">
@@ -7389,28 +7391,28 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>APEX.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C258" s="2" t="n">
-        <v>12.67</v>
+        <v>16.36</v>
       </c>
       <c r="D258" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E258" s="3" t="n">
-        <v>150</v>
+        <v>224</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>165</v>
+        <v>242</v>
       </c>
     </row>
     <row r="259">
@@ -7443,28 +7445,28 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>APEX.JK</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C260" s="2" t="n">
-        <v>16.36</v>
+        <v>12.67</v>
       </c>
       <c r="D260" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E260" s="3" t="n">
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="F260" s="3" t="n">
-        <v>256</v>
+        <v>169</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>242</v>
+        <v>165</v>
       </c>
     </row>
     <row r="261">
@@ -7740,55 +7742,55 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
-        <v>27.41</v>
+        <v>15.78</v>
       </c>
       <c r="D271" s="2" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="E271" s="3" t="n">
-        <v>135</v>
+        <v>492</v>
       </c>
       <c r="F271" s="3" t="n">
-        <v>172</v>
+        <v>565</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>148</v>
+        <v>535</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>BKDP.JK</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C272" s="2" t="n">
-        <v>15.78</v>
+        <v>27.41</v>
       </c>
       <c r="D272" s="2" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="E272" s="3" t="n">
-        <v>492</v>
+        <v>135</v>
       </c>
       <c r="F272" s="3" t="n">
-        <v>565</v>
+        <v>172</v>
       </c>
       <c r="G272" s="3" t="n">
-        <v>535</v>
+        <v>148</v>
       </c>
     </row>
     <row r="273">
@@ -8226,25 +8228,25 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>23.23</v>
+        <v>11.11</v>
       </c>
       <c r="D289" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E289" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F289" s="3" t="n">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G289" s="3" t="n">
         <v>108</v>
@@ -8253,109 +8255,109 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>22.73</v>
+        <v>23.23</v>
       </c>
       <c r="D290" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E290" s="3" t="n">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="F290" s="3" t="n">
-        <v>216</v>
+        <v>122</v>
       </c>
       <c r="G290" s="3" t="n">
-        <v>192</v>
+        <v>108</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>11.11</v>
+        <v>22.73</v>
       </c>
       <c r="D291" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E291" s="3" t="n">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="F291" s="3" t="n">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>108</v>
+        <v>192</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>INPC.JK</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>10.28</v>
+        <v>10.97</v>
       </c>
       <c r="D292" s="2" t="n">
         <v>9.029999999999999</v>
       </c>
       <c r="E292" s="3" t="n">
-        <v>3220</v>
+        <v>156</v>
       </c>
       <c r="F292" s="3" t="n">
-        <v>3540</v>
+        <v>172</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>3500</v>
+        <v>169</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>INPC.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>10.97</v>
+        <v>10.28</v>
       </c>
       <c r="D293" s="2" t="n">
         <v>9.029999999999999</v>
       </c>
       <c r="E293" s="3" t="n">
-        <v>156</v>
+        <v>3220</v>
       </c>
       <c r="F293" s="3" t="n">
-        <v>172</v>
+        <v>3540</v>
       </c>
       <c r="G293" s="3" t="n">
-        <v>169</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="294">
@@ -8685,55 +8687,55 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>ARKO.JK</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>12.86</v>
+        <v>12.38</v>
       </c>
       <c r="D306" s="2" t="n">
         <v>8.57</v>
       </c>
       <c r="E306" s="3" t="n">
-        <v>136</v>
+        <v>5275</v>
       </c>
       <c r="F306" s="3" t="n">
-        <v>158</v>
+        <v>5900</v>
       </c>
       <c r="G306" s="3" t="n">
-        <v>152</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ARKO.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>12.38</v>
+        <v>12.86</v>
       </c>
       <c r="D307" s="2" t="n">
         <v>8.57</v>
       </c>
       <c r="E307" s="3" t="n">
-        <v>5275</v>
+        <v>136</v>
       </c>
       <c r="F307" s="3" t="n">
-        <v>5900</v>
+        <v>158</v>
       </c>
       <c r="G307" s="3" t="n">
-        <v>5700</v>
+        <v>152</v>
       </c>
     </row>
     <row r="308">
@@ -8874,190 +8876,190 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>SSTM.JK</t>
+          <t>BKDP.JK</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>22.92</v>
+        <v>12.5</v>
       </c>
       <c r="D313" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E313" s="3" t="n">
-        <v>555</v>
+        <v>147</v>
       </c>
       <c r="F313" s="3" t="n">
-        <v>590</v>
+        <v>162</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>520</v>
+        <v>156</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>11.11</v>
+        <v>19.05</v>
       </c>
       <c r="D314" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E314" s="3" t="n">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G314" s="3" t="n">
-        <v>78</v>
+        <v>182</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>SSTM.JK</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>10.19</v>
+        <v>22.92</v>
       </c>
       <c r="D315" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E315" s="3" t="n">
-        <v>109</v>
+        <v>555</v>
       </c>
       <c r="F315" s="3" t="n">
-        <v>119</v>
+        <v>590</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>117</v>
+        <v>520</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>HGII.JK</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>12.5</v>
+        <v>27.27</v>
       </c>
       <c r="D316" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E316" s="3" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F316" s="3" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>11.67</v>
+        <v>10.19</v>
       </c>
       <c r="D317" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E317" s="3" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F317" s="3" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>HGII.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>27.27</v>
+        <v>11.67</v>
       </c>
       <c r="D318" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E318" s="3" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="F318" s="3" t="n">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>19.05</v>
+        <v>11.11</v>
       </c>
       <c r="D319" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E319" s="3" t="n">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="F319" s="3" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G319" s="3" t="n">
-        <v>182</v>
+        <v>78</v>
       </c>
     </row>
     <row r="320">
@@ -9468,55 +9470,55 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>SWID.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C335" s="2" t="n">
-        <v>28.7</v>
+        <v>12.17</v>
       </c>
       <c r="D335" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E335" s="3" t="n">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="F335" s="3" t="n">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>124</v>
+        <v>248</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>SWID.JK</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C336" s="2" t="n">
-        <v>12.17</v>
+        <v>28.7</v>
       </c>
       <c r="D336" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E336" s="3" t="n">
-        <v>230</v>
+        <v>116</v>
       </c>
       <c r="F336" s="3" t="n">
-        <v>258</v>
+        <v>148</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>248</v>
+        <v>124</v>
       </c>
     </row>
     <row r="337">
@@ -9630,82 +9632,82 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>CCSI.JK</t>
+          <t>LPPS.JK</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>23.78</v>
+        <v>15.38</v>
       </c>
       <c r="D341" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E341" s="3" t="n">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>308</v>
+        <v>84</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>LPPS.JK</t>
+          <t>ASLI.JK</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>15.38</v>
+        <v>20.51</v>
       </c>
       <c r="D342" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E342" s="3" t="n">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>90</v>
+        <v>282</v>
       </c>
       <c r="G342" s="3" t="n">
-        <v>84</v>
+        <v>252</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ASLI.JK</t>
+          <t>CCSI.JK</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>20.51</v>
+        <v>23.78</v>
       </c>
       <c r="D343" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E343" s="3" t="n">
-        <v>238</v>
+        <v>294</v>
       </c>
       <c r="F343" s="3" t="n">
-        <v>282</v>
+        <v>354</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>252</v>
+        <v>308</v>
       </c>
     </row>
     <row r="344">
@@ -9752,7 +9754,9 @@
       <c r="D345" s="2" t="n">
         <v>7.63</v>
       </c>
-      <c r="E345" s="3" t="inlineStr"/>
+      <c r="E345" s="3" t="n">
+        <v>118</v>
+      </c>
       <c r="F345" s="3" t="n">
         <v>134</v>
       </c>
@@ -9790,55 +9794,55 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>16.46</v>
+        <v>11.03</v>
       </c>
       <c r="D347" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E347" s="3" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F347" s="3" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="G347" s="3" t="n">
-        <v>85</v>
+        <v>156</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>11.03</v>
+        <v>16.46</v>
       </c>
       <c r="D348" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E348" s="3" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="G348" s="3" t="n">
-        <v>156</v>
+        <v>85</v>
       </c>
     </row>
     <row r="349">
@@ -9925,55 +9929,55 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>10.05</v>
+        <v>23.46</v>
       </c>
       <c r="D352" s="2" t="n">
         <v>7.41</v>
       </c>
       <c r="E352" s="3" t="n">
-        <v>372</v>
+        <v>161</v>
       </c>
       <c r="F352" s="3" t="n">
-        <v>416</v>
+        <v>200</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>406</v>
+        <v>174</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>23.46</v>
+        <v>10.05</v>
       </c>
       <c r="D353" s="2" t="n">
         <v>7.41</v>
       </c>
       <c r="E353" s="3" t="n">
-        <v>161</v>
+        <v>372</v>
       </c>
       <c r="F353" s="3" t="n">
-        <v>200</v>
+        <v>416</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>174</v>
+        <v>406</v>
       </c>
     </row>
     <row r="354">
@@ -10263,7 +10267,9 @@
       <c r="D364" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="E364" s="3" t="inlineStr"/>
+      <c r="E364" s="3" t="n">
+        <v>73</v>
+      </c>
       <c r="F364" s="3" t="n">
         <v>86</v>
       </c>
@@ -10409,28 +10415,28 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>12.4</v>
+        <v>17.44</v>
       </c>
       <c r="D370" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E370" s="3" t="n">
-        <v>134</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="G370" s="3" t="n">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="371">
@@ -10463,28 +10469,28 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
-        <v>17.44</v>
+        <v>12.4</v>
       </c>
       <c r="D372" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E372" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>134</v>
       </c>
       <c r="F372" s="3" t="n">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="G372" s="3" t="n">
-        <v>92</v>
+        <v>138</v>
       </c>
     </row>
     <row r="373">
@@ -10787,82 +10793,82 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ADMG.JK</t>
+          <t>MDIA.JK</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>15.67</v>
+        <v>11.76</v>
       </c>
       <c r="D384" s="2" t="n">
         <v>6.72</v>
       </c>
       <c r="E384" s="3" t="n">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="F384" s="3" t="n">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="G384" s="3" t="n">
-        <v>286</v>
+        <v>127</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>MDIA.JK</t>
+          <t>ADMG.JK</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>11.76</v>
+        <v>15.67</v>
       </c>
       <c r="D385" s="2" t="n">
         <v>6.72</v>
       </c>
       <c r="E385" s="3" t="n">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="F385" s="3" t="n">
-        <v>133</v>
+        <v>310</v>
       </c>
       <c r="G385" s="3" t="n">
-        <v>127</v>
+        <v>286</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>16</v>
+        <v>23.33</v>
       </c>
       <c r="D386" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E386" s="3" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="F386" s="3" t="n">
-        <v>87</v>
+        <v>148</v>
       </c>
       <c r="G386" s="3" t="n">
-        <v>80</v>
+        <v>128</v>
       </c>
     </row>
     <row r="387">
@@ -10895,28 +10901,28 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>23.33</v>
+        <v>16</v>
       </c>
       <c r="D388" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E388" s="3" t="n">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="F388" s="3" t="n">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="G388" s="3" t="n">
-        <v>128</v>
+        <v>80</v>
       </c>
     </row>
     <row r="389">
@@ -10976,55 +10982,55 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>NAIK.JK</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>23.29</v>
+        <v>11.96</v>
       </c>
       <c r="D391" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E391" s="3" t="n">
-        <v>3000</v>
+        <v>92</v>
       </c>
       <c r="F391" s="3" t="n">
-        <v>3970</v>
+        <v>103</v>
       </c>
       <c r="G391" s="3" t="n">
-        <v>3430</v>
+        <v>98</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>NAIK.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>11.96</v>
+        <v>23.29</v>
       </c>
       <c r="D392" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E392" s="3" t="n">
-        <v>92</v>
+        <v>3000</v>
       </c>
       <c r="F392" s="3" t="n">
-        <v>103</v>
+        <v>3970</v>
       </c>
       <c r="G392" s="3" t="n">
-        <v>98</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="393">
@@ -11327,55 +11333,55 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>MERI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C404" s="2" t="n">
-        <v>18.58</v>
+        <v>29.9</v>
       </c>
       <c r="D404" s="2" t="n">
         <v>6.19</v>
       </c>
       <c r="E404" s="3" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F404" s="3" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G404" s="3" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>MERI.JK</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C405" s="2" t="n">
-        <v>29.9</v>
+        <v>18.58</v>
       </c>
       <c r="D405" s="2" t="n">
         <v>6.19</v>
       </c>
       <c r="E405" s="3" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F405" s="3" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G405" s="3" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="406">
@@ -12083,109 +12089,109 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>SWID.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>17.76</v>
+        <v>12.15</v>
       </c>
       <c r="D432" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E432" s="3" t="n">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="F432" s="3" t="n">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="G432" s="3" t="n">
-        <v>113</v>
+        <v>226</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>KOKA.JK</t>
+          <t>SWID.JK</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>12.15</v>
+        <v>17.76</v>
       </c>
       <c r="D433" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E433" s="3" t="n">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="G433" s="3" t="n">
-        <v>226</v>
+        <v>113</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>SOTS.JK</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>15.87</v>
+        <v>17.46</v>
       </c>
       <c r="D434" s="2" t="n">
         <v>5.56</v>
       </c>
       <c r="E434" s="3" t="n">
-        <v>133</v>
+        <v>645</v>
       </c>
       <c r="F434" s="3" t="n">
-        <v>146</v>
+        <v>740</v>
       </c>
       <c r="G434" s="3" t="n">
-        <v>133</v>
+        <v>665</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>SOTS.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>17.46</v>
+        <v>15.87</v>
       </c>
       <c r="D435" s="2" t="n">
         <v>5.56</v>
       </c>
       <c r="E435" s="3" t="n">
-        <v>645</v>
+        <v>133</v>
       </c>
       <c r="F435" s="3" t="n">
-        <v>740</v>
+        <v>146</v>
       </c>
       <c r="G435" s="3" t="n">
-        <v>665</v>
+        <v>133</v>
       </c>
     </row>
     <row r="436">
@@ -12542,55 +12548,55 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>BIPP.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C449" s="2" t="n">
-        <v>13.33</v>
+        <v>17.5</v>
       </c>
       <c r="D449" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E449" s="3" t="n">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="F449" s="3" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="G449" s="3" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>BIPP.JK</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C450" s="2" t="n">
-        <v>17.5</v>
+        <v>13.33</v>
       </c>
       <c r="D450" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E450" s="3" t="n">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="F450" s="3" t="n">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="G450" s="3" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
     </row>
     <row r="451">
@@ -12772,7 +12778,9 @@
       <c r="D457" s="2" t="n">
         <v>4.79</v>
       </c>
-      <c r="E457" s="3" t="inlineStr"/>
+      <c r="E457" s="3" t="n">
+        <v>3440</v>
+      </c>
       <c r="F457" s="3" t="n">
         <v>4070</v>
       </c>
@@ -12837,55 +12845,55 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>NAIK.JK</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C460" s="2" t="n">
-        <v>13.33</v>
+        <v>14.12</v>
       </c>
       <c r="D460" s="2" t="n">
         <v>4.71</v>
       </c>
       <c r="E460" s="3" t="n">
-        <v>2750</v>
+        <v>87</v>
       </c>
       <c r="F460" s="3" t="n">
-        <v>2890</v>
+        <v>97</v>
       </c>
       <c r="G460" s="3" t="n">
-        <v>2670</v>
+        <v>89</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>NAIK.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C461" s="2" t="n">
-        <v>14.12</v>
+        <v>13.33</v>
       </c>
       <c r="D461" s="2" t="n">
         <v>4.71</v>
       </c>
       <c r="E461" s="3" t="n">
-        <v>87</v>
+        <v>2750</v>
       </c>
       <c r="F461" s="3" t="n">
-        <v>97</v>
+        <v>2890</v>
       </c>
       <c r="G461" s="3" t="n">
-        <v>89</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="462">
@@ -13053,28 +13061,28 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C468" s="2" t="n">
-        <v>11.61</v>
+        <v>19.77</v>
       </c>
       <c r="D468" s="2" t="n">
         <v>4.52</v>
       </c>
       <c r="E468" s="3" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="F468" s="3" t="n">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="G468" s="3" t="n">
-        <v>162</v>
+        <v>185</v>
       </c>
     </row>
     <row r="469">
@@ -13107,82 +13115,82 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C470" s="2" t="n">
-        <v>19.77</v>
+        <v>11.61</v>
       </c>
       <c r="D470" s="2" t="n">
         <v>4.52</v>
       </c>
       <c r="E470" s="3" t="n">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="F470" s="3" t="n">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="G470" s="3" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C471" s="2" t="n">
-        <v>20.49</v>
+        <v>10.53</v>
       </c>
       <c r="D471" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E471" s="3" t="n">
-        <v>2470</v>
+        <v>266</v>
       </c>
       <c r="F471" s="3" t="n">
-        <v>2940</v>
+        <v>294</v>
       </c>
       <c r="G471" s="3" t="n">
-        <v>2550</v>
+        <v>278</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C472" s="2" t="n">
-        <v>10.53</v>
+        <v>20.49</v>
       </c>
       <c r="D472" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E472" s="3" t="n">
-        <v>266</v>
+        <v>2470</v>
       </c>
       <c r="F472" s="3" t="n">
-        <v>294</v>
+        <v>2940</v>
       </c>
       <c r="G472" s="3" t="n">
-        <v>278</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="473">
@@ -13310,7 +13318,9 @@
       <c r="D477" s="2" t="n">
         <v>4.41</v>
       </c>
-      <c r="E477" s="3" t="inlineStr"/>
+      <c r="E477" s="3" t="n">
+        <v>183</v>
+      </c>
       <c r="F477" s="3" t="n">
         <v>183</v>
       </c>
@@ -13456,55 +13466,55 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C483" s="2" t="n">
-        <v>12.86</v>
+        <v>11.66</v>
       </c>
       <c r="D483" s="2" t="n">
         <v>4.29</v>
       </c>
       <c r="E483" s="3" t="n">
-        <v>71</v>
+        <v>815</v>
       </c>
       <c r="F483" s="3" t="n">
-        <v>79</v>
+        <v>910</v>
       </c>
       <c r="G483" s="3" t="n">
-        <v>73</v>
+        <v>850</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C484" s="2" t="n">
-        <v>11.66</v>
+        <v>12.86</v>
       </c>
       <c r="D484" s="2" t="n">
         <v>4.29</v>
       </c>
       <c r="E484" s="3" t="n">
-        <v>815</v>
+        <v>71</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>910</v>
+        <v>79</v>
       </c>
       <c r="G484" s="3" t="n">
-        <v>850</v>
+        <v>73</v>
       </c>
     </row>
     <row r="485">
@@ -13699,79 +13709,79 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C492" s="2" t="n">
-        <v>15</v>
+        <v>10.67</v>
       </c>
       <c r="D492" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E492" s="3" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="F492" s="3" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="G492" s="3" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C493" s="2" t="n">
-        <v>17.33</v>
+        <v>15</v>
       </c>
       <c r="D493" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E493" s="3" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="F493" s="3" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="G493" s="3" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C494" s="2" t="n">
-        <v>10.67</v>
+        <v>17.33</v>
       </c>
       <c r="D494" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E494" s="3" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F494" s="3" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G494" s="3" t="n">
         <v>78</v>
@@ -14347,55 +14357,55 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>TNCA.JK</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C516" s="2" t="n">
-        <v>17.51</v>
+        <v>11.24</v>
       </c>
       <c r="D516" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E516" s="3" t="n">
-        <v>3180</v>
+        <v>180</v>
       </c>
       <c r="F516" s="3" t="n">
-        <v>3490</v>
+        <v>198</v>
       </c>
       <c r="G516" s="3" t="n">
-        <v>3070</v>
+        <v>184</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>TNCA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C517" s="2" t="n">
-        <v>11.24</v>
+        <v>17.51</v>
       </c>
       <c r="D517" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E517" s="3" t="n">
-        <v>180</v>
+        <v>3180</v>
       </c>
       <c r="F517" s="3" t="n">
-        <v>198</v>
+        <v>3490</v>
       </c>
       <c r="G517" s="3" t="n">
-        <v>184</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="518">
@@ -14482,82 +14492,82 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C521" s="2" t="n">
-        <v>17.21</v>
+        <v>10.66</v>
       </c>
       <c r="D521" s="2" t="n">
         <v>3.28</v>
       </c>
       <c r="E521" s="3" t="n">
-        <v>615</v>
+        <v>246</v>
       </c>
       <c r="F521" s="3" t="n">
-        <v>715</v>
+        <v>270</v>
       </c>
       <c r="G521" s="3" t="n">
-        <v>630</v>
+        <v>252</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C522" s="2" t="n">
-        <v>19.4</v>
+        <v>17.21</v>
       </c>
       <c r="D522" s="2" t="n">
         <v>3.28</v>
       </c>
       <c r="E522" s="3" t="n">
-        <v>1670</v>
+        <v>615</v>
       </c>
       <c r="F522" s="3" t="n">
-        <v>2000</v>
+        <v>715</v>
       </c>
       <c r="G522" s="3" t="n">
-        <v>1730</v>
+        <v>630</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C523" s="2" t="n">
-        <v>10.66</v>
+        <v>19.4</v>
       </c>
       <c r="D523" s="2" t="n">
         <v>3.28</v>
       </c>
       <c r="E523" s="3" t="n">
-        <v>246</v>
+        <v>1670</v>
       </c>
       <c r="F523" s="3" t="n">
-        <v>270</v>
+        <v>2000</v>
       </c>
       <c r="G523" s="3" t="n">
-        <v>252</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="524">
@@ -14590,82 +14600,82 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C525" s="2" t="n">
-        <v>23.66</v>
+        <v>15.48</v>
       </c>
       <c r="D525" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E525" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>850</v>
       </c>
       <c r="F525" s="3" t="n">
-        <v>460</v>
+        <v>895</v>
       </c>
       <c r="G525" s="3" t="n">
-        <v>384</v>
+        <v>800</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C526" s="2" t="n">
-        <v>11.83</v>
+        <v>23.66</v>
       </c>
       <c r="D526" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E526" s="3" t="n">
-        <v>95</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F526" s="3" t="n">
-        <v>104</v>
+        <v>460</v>
       </c>
       <c r="G526" s="3" t="n">
-        <v>96</v>
+        <v>384</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C527" s="2" t="n">
-        <v>15.48</v>
+        <v>11.83</v>
       </c>
       <c r="D527" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E527" s="3" t="n">
-        <v>850</v>
+        <v>95</v>
       </c>
       <c r="F527" s="3" t="n">
-        <v>895</v>
+        <v>104</v>
       </c>
       <c r="G527" s="3" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
     </row>
     <row r="528">
@@ -14779,55 +14789,55 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C532" s="2" t="n">
-        <v>14.71</v>
+        <v>17.65</v>
       </c>
       <c r="D532" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E532" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="F532" s="3" t="n">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="G532" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C533" s="2" t="n">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
       <c r="D533" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E533" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="F533" s="3" t="n">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="G533" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
     </row>
     <row r="534">
@@ -14860,55 +14870,55 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>PBID.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C535" s="2" t="n">
-        <v>10.68</v>
+        <v>11.63</v>
       </c>
       <c r="D535" s="2" t="n">
         <v>2.91</v>
       </c>
       <c r="E535" s="3" t="n">
-        <v>515</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F535" s="3" t="n">
-        <v>570</v>
+        <v>192</v>
       </c>
       <c r="G535" s="3" t="n">
-        <v>530</v>
+        <v>177</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>PBID.JK</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C536" s="2" t="n">
-        <v>11.63</v>
+        <v>10.68</v>
       </c>
       <c r="D536" s="2" t="n">
         <v>2.91</v>
       </c>
       <c r="E536" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>515</v>
       </c>
       <c r="F536" s="3" t="n">
-        <v>192</v>
+        <v>570</v>
       </c>
       <c r="G536" s="3" t="n">
-        <v>177</v>
+        <v>530</v>
       </c>
     </row>
     <row r="537">
@@ -15400,55 +15410,55 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>LABA.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C555" s="2" t="n">
-        <v>14.73</v>
+        <v>17.44</v>
       </c>
       <c r="D555" s="2" t="n">
         <v>2.33</v>
       </c>
       <c r="E555" s="3" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="F555" s="3" t="n">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="G555" s="3" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>LABA.JK</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C556" s="2" t="n">
-        <v>17.44</v>
+        <v>14.73</v>
       </c>
       <c r="D556" s="2" t="n">
         <v>2.33</v>
       </c>
       <c r="E556" s="3" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="F556" s="3" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="G556" s="3" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
     </row>
     <row r="557">
@@ -15535,55 +15545,55 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>INAI.JK</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C560" s="2" t="n">
-        <v>12.36</v>
+        <v>13.48</v>
       </c>
       <c r="D560" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E560" s="3" t="n">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="F560" s="3" t="n">
-        <v>100</v>
+        <v>202</v>
       </c>
       <c r="G560" s="3" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>INAI.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C561" s="2" t="n">
-        <v>13.48</v>
+        <v>12.36</v>
       </c>
       <c r="D561" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E561" s="3" t="n">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F561" s="3" t="n">
-        <v>202</v>
+        <v>100</v>
       </c>
       <c r="G561" s="3" t="n">
-        <v>182</v>
+        <v>91</v>
       </c>
     </row>
     <row r="562">
@@ -15886,25 +15896,25 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>DOSS.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C573" s="2" t="n">
-        <v>19.38</v>
+        <v>15.62</v>
       </c>
       <c r="D573" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="E573" s="3" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="F573" s="3" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G573" s="3" t="n">
         <v>163</v>
@@ -15913,25 +15923,25 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>DOSS.JK</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C574" s="2" t="n">
-        <v>15.62</v>
+        <v>19.38</v>
       </c>
       <c r="D574" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="E574" s="3" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F574" s="3" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G574" s="3" t="n">
         <v>163</v>
@@ -16237,55 +16247,55 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>LAND.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C586" s="2" t="n">
-        <v>11.29</v>
+        <v>11.83</v>
       </c>
       <c r="D586" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E586" s="3" t="n">
-        <v>62</v>
+        <v>181.15625</v>
       </c>
       <c r="F586" s="3" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="G586" s="3" t="n">
-        <v>63</v>
+        <v>189</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>LAND.JK</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C587" s="2" t="n">
-        <v>11.83</v>
+        <v>11.29</v>
       </c>
       <c r="D587" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E587" s="3" t="n">
-        <v>181.15625</v>
+        <v>62</v>
       </c>
       <c r="F587" s="3" t="n">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="G587" s="3" t="n">
-        <v>189</v>
+        <v>63</v>
       </c>
     </row>
     <row r="588">
@@ -16399,55 +16409,55 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>PYFA.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C592" s="2" t="n">
-        <v>13.77</v>
+        <v>24.4</v>
       </c>
       <c r="D592" s="2" t="n">
         <v>1.45</v>
       </c>
       <c r="E592" s="3" t="n">
-        <v>296</v>
+        <v>480</v>
       </c>
       <c r="F592" s="3" t="n">
-        <v>314</v>
+        <v>515</v>
       </c>
       <c r="G592" s="3" t="n">
-        <v>280</v>
+        <v>420</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>PYFA.JK</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C593" s="2" t="n">
-        <v>24.4</v>
+        <v>13.77</v>
       </c>
       <c r="D593" s="2" t="n">
         <v>1.45</v>
       </c>
       <c r="E593" s="3" t="n">
-        <v>480</v>
+        <v>296</v>
       </c>
       <c r="F593" s="3" t="n">
-        <v>515</v>
+        <v>314</v>
       </c>
       <c r="G593" s="3" t="n">
-        <v>420</v>
+        <v>280</v>
       </c>
     </row>
     <row r="594">
@@ -16534,109 +16544,109 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C597" s="2" t="n">
-        <v>15.38</v>
+        <v>19.87</v>
       </c>
       <c r="D597" s="2" t="n">
         <v>1.28</v>
       </c>
       <c r="E597" s="3" t="n">
-        <v>79</v>
+        <v>8125</v>
       </c>
       <c r="F597" s="3" t="n">
-        <v>90</v>
+        <v>9350</v>
       </c>
       <c r="G597" s="3" t="n">
-        <v>79</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C598" s="2" t="n">
-        <v>19.87</v>
+        <v>15.38</v>
       </c>
       <c r="D598" s="2" t="n">
         <v>1.28</v>
       </c>
       <c r="E598" s="3" t="n">
-        <v>8125</v>
+        <v>79</v>
       </c>
       <c r="F598" s="3" t="n">
-        <v>9350</v>
+        <v>90</v>
       </c>
       <c r="G598" s="3" t="n">
-        <v>7900</v>
+        <v>79</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>LPPS.JK</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C599" s="2" t="n">
-        <v>15.94</v>
+        <v>10.13</v>
       </c>
       <c r="D599" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="E599" s="3" t="n">
-        <v>13800</v>
+        <v>79</v>
       </c>
       <c r="F599" s="3" t="n">
-        <v>16000</v>
+        <v>87</v>
       </c>
       <c r="G599" s="3" t="n">
-        <v>13975</v>
+        <v>80</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>LPPS.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C600" s="2" t="n">
-        <v>10.13</v>
+        <v>15.94</v>
       </c>
       <c r="D600" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="E600" s="3" t="n">
-        <v>79</v>
+        <v>13800</v>
       </c>
       <c r="F600" s="3" t="n">
-        <v>87</v>
+        <v>16000</v>
       </c>
       <c r="G600" s="3" t="n">
-        <v>80</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="601">
@@ -16845,7 +16855,9 @@
       <c r="D608" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="E608" s="3" t="inlineStr"/>
+      <c r="E608" s="3" t="n">
+        <v>1005</v>
+      </c>
       <c r="F608" s="3" t="n">
         <v>1180</v>
       </c>
@@ -16910,55 +16922,55 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>PORT.JK</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C611" s="2" t="n">
-        <v>10.17</v>
+        <v>16.38</v>
       </c>
       <c r="D611" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E611" s="3" t="n">
-        <v>177</v>
+        <v>1015</v>
       </c>
       <c r="F611" s="3" t="n">
-        <v>195</v>
+        <v>1030</v>
       </c>
       <c r="G611" s="3" t="n">
-        <v>178</v>
+        <v>890</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>PORT.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C612" s="2" t="n">
-        <v>16.38</v>
+        <v>10.17</v>
       </c>
       <c r="D612" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E612" s="3" t="n">
-        <v>1015</v>
+        <v>177</v>
       </c>
       <c r="F612" s="3" t="n">
-        <v>1030</v>
+        <v>195</v>
       </c>
       <c r="G612" s="3" t="n">
-        <v>890</v>
+        <v>178</v>
       </c>
     </row>
     <row r="613">
@@ -17018,70 +17030,70 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C615" s="2" t="n">
-        <v>11.43</v>
+        <v>11.96</v>
       </c>
       <c r="D615" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="E615" s="3" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F615" s="3" t="n">
         <v>468</v>
       </c>
       <c r="G615" s="3" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C616" s="2" t="n">
-        <v>11.96</v>
+        <v>11.43</v>
       </c>
       <c r="D616" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="E616" s="3" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F616" s="3" t="n">
         <v>468</v>
       </c>
       <c r="G616" s="3" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C617" s="2" t="n">
-        <v>27.33</v>
+        <v>28.48</v>
       </c>
       <c r="D617" s="2" t="n">
         <v>0</v>
@@ -17090,361 +17102,361 @@
         <v>152</v>
       </c>
       <c r="F617" s="3" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G617" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ISEA.JK</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C618" s="2" t="n">
-        <v>10.76</v>
+        <v>11.25</v>
       </c>
       <c r="D618" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E618" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>82</v>
       </c>
       <c r="F618" s="3" t="n">
-        <v>3500</v>
+        <v>89</v>
       </c>
       <c r="G618" s="3" t="n">
-        <v>3160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>RELI.JK</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C619" s="2" t="n">
-        <v>12.87</v>
+        <v>14.29</v>
       </c>
       <c r="D619" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E619" s="3" t="n">
-        <v>93</v>
+        <v>520</v>
       </c>
       <c r="F619" s="3" t="n">
-        <v>114</v>
+        <v>600</v>
       </c>
       <c r="G619" s="3" t="n">
-        <v>101</v>
+        <v>525</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C620" s="2" t="n">
-        <v>28.48</v>
+        <v>10.61</v>
       </c>
       <c r="D620" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E620" s="3" t="n">
-        <v>152</v>
+        <v>67</v>
       </c>
       <c r="F620" s="3" t="n">
-        <v>194</v>
+        <v>73</v>
       </c>
       <c r="G620" s="3" t="n">
-        <v>151</v>
+        <v>66</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C621" s="2" t="n">
-        <v>10.26</v>
+        <v>12.38</v>
       </c>
       <c r="D621" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E621" s="3" t="n">
-        <v>79</v>
+        <v>91.91489410400391</v>
       </c>
       <c r="F621" s="3" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="G621" s="3" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>PDES.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C622" s="2" t="n">
-        <v>18.01</v>
+        <v>12.78</v>
       </c>
       <c r="D622" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E622" s="3" t="n">
-        <v>424</v>
+        <v>2640</v>
       </c>
       <c r="F622" s="3" t="n">
-        <v>498</v>
+        <v>3000</v>
       </c>
       <c r="G622" s="3" t="n">
-        <v>422</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>RELI.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C623" s="2" t="n">
-        <v>14.29</v>
+        <v>27.33</v>
       </c>
       <c r="D623" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E623" s="3" t="n">
-        <v>520</v>
+        <v>152</v>
       </c>
       <c r="F623" s="3" t="n">
-        <v>600</v>
+        <v>191</v>
       </c>
       <c r="G623" s="3" t="n">
-        <v>525</v>
+        <v>150</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>PDES.JK</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C624" s="2" t="n">
-        <v>12.78</v>
+        <v>18.01</v>
       </c>
       <c r="D624" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E624" s="3" t="n">
-        <v>2640</v>
+        <v>424</v>
       </c>
       <c r="F624" s="3" t="n">
-        <v>3000</v>
+        <v>498</v>
       </c>
       <c r="G624" s="3" t="n">
-        <v>2660</v>
+        <v>422</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>ISEA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C625" s="2" t="n">
-        <v>11.25</v>
+        <v>10.76</v>
       </c>
       <c r="D625" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E625" s="3" t="n">
-        <v>82</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F625" s="3" t="n">
-        <v>89</v>
+        <v>3500</v>
       </c>
       <c r="G625" s="3" t="n">
-        <v>80</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C626" s="2" t="n">
-        <v>10.61</v>
+        <v>10.26</v>
       </c>
       <c r="D626" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E626" s="3" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F626" s="3" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="G626" s="3" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C627" s="2" t="n">
-        <v>17.5</v>
+        <v>10.91</v>
       </c>
       <c r="D627" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E627" s="3" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F627" s="3" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G627" s="3" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>MPRO.JK</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C628" s="2" t="n">
-        <v>12.38</v>
+        <v>19.95</v>
       </c>
       <c r="D628" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E628" s="3" t="n">
-        <v>91.91489410400391</v>
+        <v>11750</v>
       </c>
       <c r="F628" s="3" t="n">
-        <v>118</v>
+        <v>11875</v>
       </c>
       <c r="G628" s="3" t="n">
-        <v>105</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C629" s="2" t="n">
-        <v>10.91</v>
+        <v>17.5</v>
       </c>
       <c r="D629" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E629" s="3" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F629" s="3" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G629" s="3" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>MPRO.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C630" s="2" t="n">
-        <v>19.95</v>
+        <v>12.87</v>
       </c>
       <c r="D630" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E630" s="3" t="n">
-        <v>11750</v>
+        <v>93</v>
       </c>
       <c r="F630" s="3" t="n">
-        <v>11875</v>
+        <v>114</v>
       </c>
       <c r="G630" s="3" t="n">
-        <v>9900</v>
+        <v>101</v>
       </c>
     </row>
     <row r="631">
@@ -18274,7 +18286,9 @@
       <c r="D661" s="2" t="n">
         <v>-2.42</v>
       </c>
-      <c r="E661" s="3" t="inlineStr"/>
+      <c r="E661" s="3" t="n">
+        <v>890</v>
+      </c>
       <c r="F661" s="3" t="n">
         <v>1025</v>
       </c>
@@ -18366,55 +18380,55 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C665" s="2" t="n">
-        <v>19.62</v>
+        <v>15.19</v>
       </c>
       <c r="D665" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E665" s="3" t="n">
-        <v>910</v>
+        <v>80</v>
       </c>
       <c r="F665" s="3" t="n">
-        <v>945</v>
+        <v>91</v>
       </c>
       <c r="G665" s="3" t="n">
-        <v>770</v>
+        <v>77</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C666" s="2" t="n">
-        <v>15.19</v>
+        <v>19.62</v>
       </c>
       <c r="D666" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E666" s="3" t="n">
-        <v>80</v>
+        <v>910</v>
       </c>
       <c r="F666" s="3" t="n">
-        <v>91</v>
+        <v>945</v>
       </c>
       <c r="G666" s="3" t="n">
-        <v>77</v>
+        <v>770</v>
       </c>
     </row>
     <row r="667">
@@ -18488,7 +18502,9 @@
       <c r="D669" s="2" t="n">
         <v>-2.7</v>
       </c>
-      <c r="E669" s="3" t="inlineStr"/>
+      <c r="E669" s="3" t="n">
+        <v>186</v>
+      </c>
       <c r="F669" s="3" t="n">
         <v>208</v>
       </c>
@@ -18796,55 +18812,55 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C681" s="2" t="n">
-        <v>18.05</v>
+        <v>19.31</v>
       </c>
       <c r="D681" s="2" t="n">
         <v>-4.14</v>
       </c>
       <c r="E681" s="3" t="n">
-        <v>2700</v>
+        <v>149</v>
       </c>
       <c r="F681" s="3" t="n">
-        <v>3140</v>
+        <v>173</v>
       </c>
       <c r="G681" s="3" t="n">
-        <v>2550</v>
+        <v>139</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C682" s="2" t="n">
-        <v>19.31</v>
+        <v>18.05</v>
       </c>
       <c r="D682" s="2" t="n">
         <v>-4.14</v>
       </c>
       <c r="E682" s="3" t="n">
-        <v>149</v>
+        <v>2700</v>
       </c>
       <c r="F682" s="3" t="n">
-        <v>173</v>
+        <v>3140</v>
       </c>
       <c r="G682" s="3" t="n">
-        <v>139</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="683">
@@ -19174,55 +19190,55 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C695" s="2" t="n">
-        <v>23.53</v>
+        <v>12.63</v>
       </c>
       <c r="D695" s="2" t="n">
         <v>-5.15</v>
       </c>
       <c r="E695" s="3" t="n">
-        <v>700</v>
+        <v>19500</v>
       </c>
       <c r="F695" s="3" t="n">
-        <v>840</v>
+        <v>21850</v>
       </c>
       <c r="G695" s="3" t="n">
-        <v>645</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C696" s="2" t="n">
-        <v>12.63</v>
+        <v>23.53</v>
       </c>
       <c r="D696" s="2" t="n">
         <v>-5.15</v>
       </c>
       <c r="E696" s="3" t="n">
-        <v>19500</v>
+        <v>700</v>
       </c>
       <c r="F696" s="3" t="n">
-        <v>21850</v>
+        <v>840</v>
       </c>
       <c r="G696" s="3" t="n">
-        <v>18400</v>
+        <v>645</v>
       </c>
     </row>
     <row r="697">
@@ -20457,7 +20473,9 @@
       <c r="D742" s="2" t="n">
         <v>-14.52</v>
       </c>
-      <c r="E742" s="3" t="inlineStr"/>
+      <c r="E742" s="3" t="n">
+        <v>140</v>
+      </c>
       <c r="F742" s="3" t="n">
         <v>148</v>
       </c>
@@ -20603,55 +20621,55 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C748" s="2" t="n">
-        <v>19.27</v>
+        <v>24.77</v>
       </c>
       <c r="D748" s="2" t="n">
         <v>-14.68</v>
       </c>
       <c r="E748" s="3" t="n">
-        <v>222</v>
+        <v>1788.388189719142</v>
       </c>
       <c r="F748" s="3" t="n">
-        <v>260</v>
+        <v>2040</v>
       </c>
       <c r="G748" s="3" t="n">
-        <v>186</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C749" s="2" t="n">
-        <v>24.77</v>
+        <v>19.27</v>
       </c>
       <c r="D749" s="2" t="n">
         <v>-14.68</v>
       </c>
       <c r="E749" s="3" t="n">
-        <v>1788.388189719142</v>
+        <v>222</v>
       </c>
       <c r="F749" s="3" t="n">
-        <v>2040</v>
+        <v>260</v>
       </c>
       <c r="G749" s="3" t="n">
-        <v>1395</v>
+        <v>186</v>
       </c>
     </row>
     <row r="750">
@@ -20819,55 +20837,55 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C756" s="2" t="n">
-        <v>24.79</v>
+        <v>14.05</v>
       </c>
       <c r="D756" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E756" s="3" t="n">
-        <v>1510</v>
+        <v>115</v>
       </c>
       <c r="F756" s="3" t="n">
-        <v>1510</v>
+        <v>138</v>
       </c>
       <c r="G756" s="3" t="n">
-        <v>1030</v>
+        <v>103</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C757" s="2" t="n">
-        <v>14.05</v>
+        <v>24.79</v>
       </c>
       <c r="D757" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E757" s="3" t="n">
-        <v>115</v>
+        <v>1510</v>
       </c>
       <c r="F757" s="3" t="n">
-        <v>138</v>
+        <v>1510</v>
       </c>
       <c r="G757" s="3" t="n">
-        <v>103</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="758">

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -508,12 +508,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DPUM.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -535,12 +535,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>DPUM.JK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -589,12 +589,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -604,7 +604,7 @@
         <v>34.33</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>90</v>
@@ -616,12 +616,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -631,7 +631,7 @@
         <v>34.33</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>90</v>
@@ -1021,12 +1021,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MLPT.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1036,24 +1036,24 @@
         <v>25</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1425</v>
+        <v>153.7625885009766</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1625</v>
+        <v>290</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1625</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>BIKE.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1063,51 +1063,51 @@
         <v>25</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1200</v>
+        <v>755</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1375</v>
+        <v>775</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1375</v>
+        <v>775</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>26.25</v>
+        <v>33.62</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>200</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1117,24 +1117,24 @@
         <v>25</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>505</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>505</v>
+        <v>975</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>505</v>
+        <v>975</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>605</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>975</v>
+        <v>775</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>975</v>
+        <v>775</v>
       </c>
     </row>
     <row r="27">
@@ -1183,12 +1183,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1198,78 +1198,78 @@
         <v>25</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>605</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>775</v>
+        <v>545</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>775</v>
+        <v>545</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1190</v>
+        <v>165</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1200</v>
+        <v>202</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>EKAD.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>119</v>
+        <v>300</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>155</v>
+        <v>300</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>145</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>MLPT.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -1279,24 +1279,24 @@
         <v>25</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>414.3801616703698</v>
+        <v>1425</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>545</v>
+        <v>1625</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>545</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BIKE.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1306,24 +1306,24 @@
         <v>25</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>755</v>
+        <v>1190</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>775</v>
+        <v>1200</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>775</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EKAD.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1333,24 +1333,24 @@
         <v>25</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>300</v>
+        <v>505</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>300</v>
+        <v>505</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>300</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1360,13 +1360,13 @@
         <v>25</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>153.7625885009766</v>
+        <v>1200</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>290</v>
+        <v>1375</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>290</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="35">
@@ -1424,12 +1424,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1439,24 +1439,24 @@
         <v>24.9</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2580</v>
+        <v>1445</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1466,24 +1466,24 @@
         <v>24.9</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1445</v>
+        <v>2580</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SMMT.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1493,24 +1493,24 @@
         <v>24.88</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2110</v>
+        <v>2170</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2610</v>
+        <v>2510</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2610</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>SMMT.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -1520,24 +1520,24 @@
         <v>24.88</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1170</v>
+        <v>2110</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1255</v>
+        <v>2610</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1255</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1547,13 +1547,13 @@
         <v>24.88</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2170</v>
+        <v>1170</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2510</v>
+        <v>1255</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2510</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="42">
@@ -1586,55 +1586,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>24.85</v>
+        <v>29.7</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>4114.81103515625</v>
+        <v>167</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>4120</v>
+        <v>214</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>4120</v>
+        <v>206</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>29.7</v>
+        <v>24.85</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>167</v>
+        <v>4114.81103515625</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>214</v>
+        <v>4120</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>206</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="45">
@@ -1775,12 +1775,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>ASLI.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -1790,24 +1790,24 @@
         <v>24.76</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>525</v>
+        <v>228</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ASLI.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -1817,7 +1817,7 @@
         <v>24.76</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>262</v>
@@ -1829,12 +1829,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -1844,13 +1844,13 @@
         <v>24.76</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>214</v>
+        <v>525</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
     </row>
     <row r="53">
@@ -2099,12 +2099,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FUJI.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -2114,7 +2114,7 @@
         <v>24.62</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>324</v>
@@ -2126,12 +2126,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>VOKS.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -2141,7 +2141,7 @@
         <v>24.62</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>324</v>
+        <v>266</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>324</v>
@@ -2153,12 +2153,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VOKS.JK</t>
+          <t>FUJI.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -2168,7 +2168,7 @@
         <v>24.62</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>324</v>
@@ -2288,12 +2288,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BELI.JK</t>
+          <t>SAPX.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -2303,7 +2303,7 @@
         <v>24.54</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>406</v>
@@ -2315,12 +2315,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SAPX.JK</t>
+          <t>BELI.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -2330,7 +2330,7 @@
         <v>24.54</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>406</v>
@@ -3650,7 +3650,9 @@
       <c r="D119" s="2" t="n">
         <v>18.78</v>
       </c>
-      <c r="E119" s="3" t="inlineStr"/>
+      <c r="E119" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="F119" s="3" t="n">
         <v>260</v>
       </c>
@@ -4471,55 +4473,55 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>SLIS.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>25</v>
+        <v>29.55</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>15.91</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>1320</v>
+        <v>92</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>1650</v>
+        <v>114</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>1530</v>
+        <v>102</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SLIS.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>29.55</v>
+        <v>25</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>15.91</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>92</v>
+        <v>1320</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>114</v>
+        <v>1650</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>102</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="152">
@@ -4768,55 +4770,55 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FITT.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>24.62</v>
+        <v>30.77</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>15.38</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>408</v>
+        <v>77</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>486</v>
+        <v>102</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>450</v>
+        <v>90</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>FITT.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>30.77</v>
+        <v>24.62</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>15.38</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>102</v>
+        <v>486</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
     </row>
     <row r="163">
@@ -5227,28 +5229,28 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>MDIA.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>21.4</v>
+        <v>30.77</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>2200</v>
+        <v>106</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>2610</v>
+        <v>136</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>2460</v>
+        <v>119</v>
       </c>
     </row>
     <row r="179">
@@ -5281,28 +5283,28 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MDIA.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>30.77</v>
+        <v>21.4</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>106</v>
+        <v>2200</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>136</v>
+        <v>2610</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>119</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="181">
@@ -5632,109 +5634,109 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>ELIT.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>15.17</v>
+        <v>13.79</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>13.79</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>2800</v>
+        <v>236</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>3340</v>
+        <v>264</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>3300</v>
+        <v>264</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ELIT.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>13.79</v>
+        <v>15.17</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>13.79</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>236</v>
+        <v>2800</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>264</v>
+        <v>3340</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>264</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>24.9</v>
+        <v>14.88</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>13.69</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>2990</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>3010</v>
+        <v>386</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>2740</v>
+        <v>382</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>14.88</v>
+        <v>24.9</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>13.69</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>2990</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>386</v>
+        <v>3010</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>382</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="197">
@@ -6253,55 +6255,55 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>15.53</v>
+        <v>14.56</v>
       </c>
       <c r="D216" s="2" t="n">
         <v>12.62</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>515</v>
+        <v>210</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>595</v>
+        <v>236</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>580</v>
+        <v>232</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>14.56</v>
+        <v>15.53</v>
       </c>
       <c r="D217" s="2" t="n">
         <v>12.62</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>210</v>
+        <v>515</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>236</v>
+        <v>595</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>232</v>
+        <v>580</v>
       </c>
     </row>
     <row r="218">
@@ -6334,55 +6336,55 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>20.31</v>
+        <v>14.06</v>
       </c>
       <c r="D219" s="2" t="n">
         <v>12.5</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>308</v>
+        <v>146</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>288</v>
+        <v>144</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>14.06</v>
+        <v>20.31</v>
       </c>
       <c r="D220" s="2" t="n">
         <v>12.5</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>146</v>
+        <v>308</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>144</v>
+        <v>288</v>
       </c>
     </row>
     <row r="221">
@@ -6415,55 +6417,55 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>12.32</v>
+        <v>14.49</v>
       </c>
       <c r="D222" s="2" t="n">
         <v>12.32</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>690</v>
+        <v>138</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>775</v>
+        <v>158</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>775</v>
+        <v>155</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>14.49</v>
+        <v>12.32</v>
       </c>
       <c r="D223" s="2" t="n">
         <v>12.32</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>138</v>
+        <v>690</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>158</v>
+        <v>775</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>155</v>
+        <v>775</v>
       </c>
     </row>
     <row r="224">
@@ -6847,55 +6849,55 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>11.61</v>
+        <v>13.39</v>
       </c>
       <c r="D238" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>218</v>
+        <v>2270</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>250</v>
+        <v>2540</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>13.39</v>
+        <v>11.61</v>
       </c>
       <c r="D239" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>2270</v>
+        <v>218</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>2540</v>
+        <v>250</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>2500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="240">
@@ -7090,55 +7092,55 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>11.79</v>
+        <v>14.36</v>
       </c>
       <c r="D247" s="2" t="n">
         <v>11.28</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>5100</v>
+        <v>398</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>5500</v>
+        <v>446</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>5475</v>
+        <v>434</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C248" s="2" t="n">
-        <v>14.36</v>
+        <v>11.79</v>
       </c>
       <c r="D248" s="2" t="n">
         <v>11.28</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>398</v>
+        <v>5100</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>446</v>
+        <v>5500</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>434</v>
+        <v>5475</v>
       </c>
     </row>
     <row r="249">
@@ -7198,55 +7200,55 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>WAPO.JK</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C251" s="2" t="n">
-        <v>23.28</v>
+        <v>18.1</v>
       </c>
       <c r="D251" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="E251" s="3" t="n">
-        <v>119</v>
+        <v>226</v>
       </c>
       <c r="F251" s="3" t="n">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="G251" s="3" t="n">
-        <v>129</v>
+        <v>258</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>WAPO.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C252" s="2" t="n">
-        <v>18.1</v>
+        <v>23.28</v>
       </c>
       <c r="D252" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="E252" s="3" t="n">
-        <v>226</v>
+        <v>119</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>274</v>
+        <v>143</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>258</v>
+        <v>129</v>
       </c>
     </row>
     <row r="253">
@@ -7333,55 +7335,55 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>BIPP.JK</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C256" s="2" t="n">
-        <v>12.5</v>
+        <v>23.81</v>
       </c>
       <c r="D256" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>720</v>
+        <v>64</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>810</v>
+        <v>78</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BIPP.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C257" s="2" t="n">
-        <v>23.81</v>
+        <v>12.5</v>
       </c>
       <c r="D257" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E257" s="3" t="n">
-        <v>64</v>
+        <v>720</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>78</v>
+        <v>810</v>
       </c>
       <c r="G257" s="3" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
     </row>
     <row r="258">
@@ -8035,25 +8037,25 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>21.1</v>
+        <v>14.68</v>
       </c>
       <c r="D282" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E282" s="3" t="n">
-        <v>495.4545288085938</v>
+        <v>545</v>
       </c>
       <c r="F282" s="3" t="n">
-        <v>660</v>
+        <v>625</v>
       </c>
       <c r="G282" s="3" t="n">
         <v>600</v>
@@ -8062,25 +8064,25 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>14.68</v>
+        <v>10.09</v>
       </c>
       <c r="D283" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E283" s="3" t="n">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="F283" s="3" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G283" s="3" t="n">
         <v>600</v>
@@ -8089,25 +8091,25 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>10.09</v>
+        <v>21.1</v>
       </c>
       <c r="D284" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E284" s="3" t="n">
-        <v>535</v>
+        <v>495.4545288085938</v>
       </c>
       <c r="F284" s="3" t="n">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="G284" s="3" t="n">
         <v>600</v>
@@ -8116,7 +8118,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>TKIM.JK</t>
+          <t>APEX.JK</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8125,25 +8127,25 @@
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>10.77</v>
+        <v>12.67</v>
       </c>
       <c r="D285" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E285" s="3" t="n">
-        <v>6850</v>
+        <v>150</v>
       </c>
       <c r="F285" s="3" t="n">
-        <v>7200</v>
+        <v>169</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>7150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>APEX.JK</t>
+          <t>TKIM.JK</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8152,19 +8154,19 @@
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>12.67</v>
+        <v>10.77</v>
       </c>
       <c r="D286" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E286" s="3" t="n">
-        <v>150</v>
+        <v>6850</v>
       </c>
       <c r="F286" s="3" t="n">
-        <v>169</v>
+        <v>7200</v>
       </c>
       <c r="G286" s="3" t="n">
-        <v>165</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="287">
@@ -8683,55 +8685,55 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>PGLI.JK</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>11.72</v>
+        <v>11.46</v>
       </c>
       <c r="D306" s="2" t="n">
         <v>9.380000000000001</v>
       </c>
       <c r="E306" s="3" t="n">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="F306" s="3" t="n">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="G306" s="3" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>PGLI.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>11.46</v>
+        <v>11.72</v>
       </c>
       <c r="D307" s="2" t="n">
         <v>9.380000000000001</v>
       </c>
       <c r="E307" s="3" t="n">
-        <v>191</v>
+        <v>128</v>
       </c>
       <c r="F307" s="3" t="n">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="G307" s="3" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
     </row>
     <row r="308">
@@ -9007,25 +9009,25 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>23.23</v>
+        <v>11.11</v>
       </c>
       <c r="D318" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E318" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F318" s="3" t="n">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G318" s="3" t="n">
         <v>108</v>
@@ -9061,25 +9063,25 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>11.11</v>
+        <v>23.23</v>
       </c>
       <c r="D320" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E320" s="3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F320" s="3" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G320" s="3" t="n">
         <v>108</v>
@@ -9088,55 +9090,55 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>INPC.JK</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>10.28</v>
+        <v>10.97</v>
       </c>
       <c r="D321" s="2" t="n">
         <v>9.029999999999999</v>
       </c>
       <c r="E321" s="3" t="n">
-        <v>3220</v>
+        <v>156</v>
       </c>
       <c r="F321" s="3" t="n">
-        <v>3540</v>
+        <v>172</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3500</v>
+        <v>169</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>INPC.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>10.97</v>
+        <v>10.28</v>
       </c>
       <c r="D322" s="2" t="n">
         <v>9.029999999999999</v>
       </c>
       <c r="E322" s="3" t="n">
-        <v>156</v>
+        <v>3220</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>172</v>
+        <v>3540</v>
       </c>
       <c r="G322" s="3" t="n">
-        <v>169</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="323">
@@ -9736,28 +9738,28 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>HGII.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>27.27</v>
+        <v>11.11</v>
       </c>
       <c r="D345" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E345" s="3" t="n">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="F345" s="3" t="n">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>143</v>
+        <v>78</v>
       </c>
     </row>
     <row r="346">
@@ -9790,109 +9792,109 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>BKDP.JK</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>19.05</v>
+        <v>12.5</v>
       </c>
       <c r="D347" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E347" s="3" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="F347" s="3" t="n">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="G347" s="3" t="n">
-        <v>182</v>
+        <v>156</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>HGII.JK</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>11.67</v>
+        <v>27.27</v>
       </c>
       <c r="D348" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E348" s="3" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="G348" s="3" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>12.5</v>
+        <v>19.05</v>
       </c>
       <c r="D349" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E349" s="3" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="F349" s="3" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>156</v>
+        <v>182</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>11.11</v>
+        <v>11.67</v>
       </c>
       <c r="D350" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E350" s="3" t="n">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="G350" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
     </row>
     <row r="351">
@@ -10357,82 +10359,82 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>SWID.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>28.7</v>
+        <v>12.17</v>
       </c>
       <c r="D368" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E368" s="3" t="n">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="F368" s="3" t="n">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="G368" s="3" t="n">
-        <v>124</v>
+        <v>248</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>LPCK.JK</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>12.17</v>
+        <v>16.52</v>
       </c>
       <c r="D369" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E369" s="3" t="n">
-        <v>230</v>
+        <v>590</v>
       </c>
       <c r="F369" s="3" t="n">
-        <v>258</v>
+        <v>670</v>
       </c>
       <c r="G369" s="3" t="n">
-        <v>248</v>
+        <v>620</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>LPCK.JK</t>
+          <t>SWID.JK</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>16.52</v>
+        <v>28.7</v>
       </c>
       <c r="D370" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E370" s="3" t="n">
-        <v>590</v>
+        <v>116</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>670</v>
+        <v>148</v>
       </c>
       <c r="G370" s="3" t="n">
-        <v>620</v>
+        <v>124</v>
       </c>
     </row>
     <row r="371">
@@ -10546,28 +10548,28 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CCSI.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>23.78</v>
+        <v>16.35</v>
       </c>
       <c r="D375" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E375" s="3" t="n">
-        <v>294</v>
+        <v>106</v>
       </c>
       <c r="F375" s="3" t="n">
-        <v>354</v>
+        <v>121</v>
       </c>
       <c r="G375" s="3" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
     </row>
     <row r="376">
@@ -10627,82 +10629,82 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>CCSI.JK</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>16.35</v>
+        <v>23.78</v>
       </c>
       <c r="D378" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E378" s="3" t="n">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="F378" s="3" t="n">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="G378" s="3" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>MPIX.JK</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>12.98</v>
+        <v>13.56</v>
       </c>
       <c r="D379" s="2" t="n">
         <v>7.63</v>
       </c>
       <c r="E379" s="3" t="n">
-        <v>264</v>
+        <v>118</v>
       </c>
       <c r="F379" s="3" t="n">
-        <v>296</v>
+        <v>134</v>
       </c>
       <c r="G379" s="3" t="n">
-        <v>282</v>
+        <v>127</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>MPIX.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>13.56</v>
+        <v>12.98</v>
       </c>
       <c r="D380" s="2" t="n">
         <v>7.63</v>
       </c>
       <c r="E380" s="3" t="n">
-        <v>118</v>
+        <v>264</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="G380" s="3" t="n">
-        <v>127</v>
+        <v>282</v>
       </c>
     </row>
     <row r="381">
@@ -10735,55 +10737,55 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>11.03</v>
+        <v>16.46</v>
       </c>
       <c r="D382" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E382" s="3" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="F382" s="3" t="n">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="G382" s="3" t="n">
-        <v>156</v>
+        <v>85</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>16.46</v>
+        <v>11.03</v>
       </c>
       <c r="D383" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E383" s="3" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="G383" s="3" t="n">
-        <v>85</v>
+        <v>156</v>
       </c>
     </row>
     <row r="384">
@@ -11167,55 +11169,55 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>FIRE.JK</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>22.86</v>
+        <v>22.32</v>
       </c>
       <c r="D398" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E398" s="3" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="F398" s="3" t="n">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="G398" s="3" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>FIRE.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>22.32</v>
+        <v>22.86</v>
       </c>
       <c r="D399" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E399" s="3" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="F399" s="3" t="n">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="G399" s="3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="400">
@@ -11302,25 +11304,25 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>DPUM.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D403" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E403" s="3" t="n">
-        <v>100</v>
+        <v>99.03620169095905</v>
       </c>
       <c r="F403" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G403" s="3" t="n">
         <v>107</v>
@@ -11329,25 +11331,25 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>DPUM.JK</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C404" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D404" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E404" s="3" t="n">
-        <v>99.03620169095905</v>
+        <v>100</v>
       </c>
       <c r="F404" s="3" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G404" s="3" t="n">
         <v>107</v>
@@ -11383,55 +11385,55 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>12.4</v>
+        <v>17.44</v>
       </c>
       <c r="D406" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E406" s="3" t="n">
-        <v>134</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F406" s="3" t="n">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="G406" s="3" t="n">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C407" s="2" t="n">
-        <v>17.44</v>
+        <v>12.4</v>
       </c>
       <c r="D407" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E407" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>134</v>
       </c>
       <c r="F407" s="3" t="n">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="G407" s="3" t="n">
-        <v>92</v>
+        <v>138</v>
       </c>
     </row>
     <row r="408">
@@ -11842,28 +11844,28 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>ISEA.JK</t>
+          <t>PTSN.JK</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>25.33</v>
+        <v>11.11</v>
       </c>
       <c r="D423" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E423" s="3" t="n">
-        <v>77</v>
+        <v>452</v>
       </c>
       <c r="F423" s="3" t="n">
-        <v>94</v>
+        <v>500</v>
       </c>
       <c r="G423" s="3" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
     </row>
     <row r="424">
@@ -11896,52 +11898,52 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>PTSN.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>11.11</v>
+        <v>16</v>
       </c>
       <c r="D425" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E425" s="3" t="n">
-        <v>452</v>
+        <v>74</v>
       </c>
       <c r="F425" s="3" t="n">
-        <v>500</v>
+        <v>87</v>
       </c>
       <c r="G425" s="3" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ISEA.JK</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>16</v>
+        <v>25.33</v>
       </c>
       <c r="D426" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E426" s="3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F426" s="3" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G426" s="3" t="n">
         <v>80</v>
@@ -12004,55 +12006,55 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>NAIK.JK</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>23.29</v>
+        <v>11.96</v>
       </c>
       <c r="D429" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E429" s="3" t="n">
-        <v>3000</v>
+        <v>92</v>
       </c>
       <c r="F429" s="3" t="n">
-        <v>3970</v>
+        <v>103</v>
       </c>
       <c r="G429" s="3" t="n">
-        <v>3430</v>
+        <v>98</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>NAIK.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>11.96</v>
+        <v>23.29</v>
       </c>
       <c r="D430" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E430" s="3" t="n">
-        <v>92</v>
+        <v>3000</v>
       </c>
       <c r="F430" s="3" t="n">
-        <v>103</v>
+        <v>3970</v>
       </c>
       <c r="G430" s="3" t="n">
-        <v>98</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="431">
@@ -12274,28 +12276,28 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C439" s="2" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="D439" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E439" s="3" t="n">
-        <v>236</v>
+        <v>66</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="G439" s="3" t="n">
-        <v>238</v>
+        <v>68</v>
       </c>
     </row>
     <row r="440">
@@ -12328,28 +12330,28 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C441" s="2" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="D441" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E441" s="3" t="n">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="F441" s="3" t="n">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="G441" s="3" t="n">
-        <v>68</v>
+        <v>238</v>
       </c>
     </row>
     <row r="442">
@@ -12652,55 +12654,55 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>DAAZ.JK</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C453" s="2" t="n">
-        <v>11.92</v>
+        <v>21.63</v>
       </c>
       <c r="D453" s="2" t="n">
         <v>5.96</v>
       </c>
       <c r="E453" s="3" t="n">
-        <v>151</v>
+        <v>1615</v>
       </c>
       <c r="F453" s="3" t="n">
-        <v>169</v>
+        <v>1940</v>
       </c>
       <c r="G453" s="3" t="n">
-        <v>160</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>DAAZ.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C454" s="2" t="n">
-        <v>21.63</v>
+        <v>11.92</v>
       </c>
       <c r="D454" s="2" t="n">
         <v>5.96</v>
       </c>
       <c r="E454" s="3" t="n">
-        <v>1615</v>
+        <v>151</v>
       </c>
       <c r="F454" s="3" t="n">
-        <v>1940</v>
+        <v>169</v>
       </c>
       <c r="G454" s="3" t="n">
-        <v>1690</v>
+        <v>160</v>
       </c>
     </row>
     <row r="455">
@@ -12909,7 +12911,9 @@
       <c r="D462" s="2" t="n">
         <v>5.77</v>
       </c>
-      <c r="E462" s="3" t="inlineStr"/>
+      <c r="E462" s="3" t="n">
+        <v>105</v>
+      </c>
       <c r="F462" s="3" t="n">
         <v>120</v>
       </c>
@@ -13217,109 +13221,109 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>KOKA.JK</t>
+          <t>SWID.JK</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C474" s="2" t="n">
-        <v>12.15</v>
+        <v>17.76</v>
       </c>
       <c r="D474" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E474" s="3" t="n">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="F474" s="3" t="n">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="G474" s="3" t="n">
-        <v>226</v>
+        <v>113</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>SWID.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C475" s="2" t="n">
-        <v>17.76</v>
+        <v>12.15</v>
       </c>
       <c r="D475" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E475" s="3" t="n">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="F475" s="3" t="n">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="G475" s="3" t="n">
-        <v>113</v>
+        <v>226</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>SOTS.JK</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C476" s="2" t="n">
-        <v>15.87</v>
+        <v>17.46</v>
       </c>
       <c r="D476" s="2" t="n">
         <v>5.56</v>
       </c>
       <c r="E476" s="3" t="n">
-        <v>133</v>
+        <v>645</v>
       </c>
       <c r="F476" s="3" t="n">
-        <v>146</v>
+        <v>740</v>
       </c>
       <c r="G476" s="3" t="n">
-        <v>133</v>
+        <v>665</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>SOTS.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C477" s="2" t="n">
-        <v>17.46</v>
+        <v>15.87</v>
       </c>
       <c r="D477" s="2" t="n">
         <v>5.56</v>
       </c>
       <c r="E477" s="3" t="n">
-        <v>645</v>
+        <v>133</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>740</v>
+        <v>146</v>
       </c>
       <c r="G477" s="3" t="n">
-        <v>665</v>
+        <v>133</v>
       </c>
     </row>
     <row r="478">
@@ -13487,55 +13491,55 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>FITT.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C484" s="2" t="n">
-        <v>12.44</v>
+        <v>11.58</v>
       </c>
       <c r="D484" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E484" s="3" t="n">
-        <v>424</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>470</v>
+        <v>106</v>
       </c>
       <c r="G484" s="3" t="n">
-        <v>440</v>
+        <v>100</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>FITT.JK</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C485" s="2" t="n">
-        <v>11.58</v>
+        <v>12.44</v>
       </c>
       <c r="D485" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E485" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>424</v>
       </c>
       <c r="F485" s="3" t="n">
-        <v>106</v>
+        <v>470</v>
       </c>
       <c r="G485" s="3" t="n">
-        <v>100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="486">
@@ -13634,7 +13638,9 @@
       <c r="D489" s="2" t="n">
         <v>5.13</v>
       </c>
-      <c r="E489" s="3" t="inlineStr"/>
+      <c r="E489" s="3" t="n">
+        <v>236</v>
+      </c>
       <c r="F489" s="3" t="n">
         <v>282</v>
       </c>
@@ -14320,25 +14326,25 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C515" s="2" t="n">
-        <v>11.61</v>
+        <v>10.97</v>
       </c>
       <c r="D515" s="2" t="n">
         <v>4.52</v>
       </c>
       <c r="E515" s="3" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F515" s="3" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G515" s="3" t="n">
         <v>162</v>
@@ -14347,25 +14353,25 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C516" s="2" t="n">
-        <v>10.97</v>
+        <v>11.61</v>
       </c>
       <c r="D516" s="2" t="n">
         <v>4.52</v>
       </c>
       <c r="E516" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F516" s="3" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G516" s="3" t="n">
         <v>162</v>
@@ -14374,55 +14380,55 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C517" s="2" t="n">
-        <v>20.49</v>
+        <v>10.53</v>
       </c>
       <c r="D517" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E517" s="3" t="n">
-        <v>2470</v>
+        <v>266</v>
       </c>
       <c r="F517" s="3" t="n">
-        <v>2940</v>
+        <v>294</v>
       </c>
       <c r="G517" s="3" t="n">
-        <v>2550</v>
+        <v>278</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C518" s="2" t="n">
-        <v>10.53</v>
+        <v>20.49</v>
       </c>
       <c r="D518" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E518" s="3" t="n">
-        <v>266</v>
+        <v>2470</v>
       </c>
       <c r="F518" s="3" t="n">
-        <v>294</v>
+        <v>2940</v>
       </c>
       <c r="G518" s="3" t="n">
-        <v>278</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="519">
@@ -14482,55 +14488,55 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>KKES.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C521" s="2" t="n">
-        <v>32.22</v>
+        <v>13.33</v>
       </c>
       <c r="D521" s="2" t="n">
         <v>4.44</v>
       </c>
       <c r="E521" s="3" t="n">
-        <v>86</v>
+        <v>270</v>
       </c>
       <c r="F521" s="3" t="n">
-        <v>119</v>
+        <v>306</v>
       </c>
       <c r="G521" s="3" t="n">
-        <v>94</v>
+        <v>282</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>KKES.JK</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C522" s="2" t="n">
-        <v>13.33</v>
+        <v>32.22</v>
       </c>
       <c r="D522" s="2" t="n">
         <v>4.44</v>
       </c>
       <c r="E522" s="3" t="n">
-        <v>270</v>
+        <v>86</v>
       </c>
       <c r="F522" s="3" t="n">
-        <v>306</v>
+        <v>119</v>
       </c>
       <c r="G522" s="3" t="n">
-        <v>282</v>
+        <v>94</v>
       </c>
     </row>
     <row r="523">
@@ -14590,55 +14596,55 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>POLI.JK</t>
+          <t>ARII.JK</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C525" s="2" t="n">
-        <v>20.88</v>
+        <v>10.06</v>
       </c>
       <c r="D525" s="2" t="n">
         <v>4.4</v>
       </c>
       <c r="E525" s="3" t="n">
-        <v>895</v>
+        <v>324</v>
       </c>
       <c r="F525" s="3" t="n">
-        <v>1100</v>
+        <v>350</v>
       </c>
       <c r="G525" s="3" t="n">
-        <v>950</v>
+        <v>332</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>ARII.JK</t>
+          <t>POLI.JK</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C526" s="2" t="n">
-        <v>10.06</v>
+        <v>20.88</v>
       </c>
       <c r="D526" s="2" t="n">
         <v>4.4</v>
       </c>
       <c r="E526" s="3" t="n">
-        <v>324</v>
+        <v>895</v>
       </c>
       <c r="F526" s="3" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="G526" s="3" t="n">
-        <v>332</v>
+        <v>950</v>
       </c>
     </row>
     <row r="527">
@@ -14752,77 +14758,79 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C531" s="2" t="n">
-        <v>11.66</v>
+        <v>12.86</v>
       </c>
       <c r="D531" s="2" t="n">
         <v>4.29</v>
       </c>
       <c r="E531" s="3" t="n">
-        <v>815</v>
+        <v>71</v>
       </c>
       <c r="F531" s="3" t="n">
-        <v>910</v>
+        <v>79</v>
       </c>
       <c r="G531" s="3" t="n">
-        <v>850</v>
+        <v>73</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C532" s="2" t="n">
-        <v>12.86</v>
+        <v>11.66</v>
       </c>
       <c r="D532" s="2" t="n">
         <v>4.29</v>
       </c>
       <c r="E532" s="3" t="n">
-        <v>71</v>
+        <v>815</v>
       </c>
       <c r="F532" s="3" t="n">
-        <v>79</v>
+        <v>910</v>
       </c>
       <c r="G532" s="3" t="n">
-        <v>73</v>
+        <v>850</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>SEMA.JK</t>
+          <t>OPMS.JK</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C533" s="2" t="n">
-        <v>14.53</v>
+        <v>19.66</v>
       </c>
       <c r="D533" s="2" t="n">
         <v>4.27</v>
       </c>
-      <c r="E533" s="3" t="inlineStr"/>
+      <c r="E533" s="3" t="n">
+        <v>118</v>
+      </c>
       <c r="F533" s="3" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G533" s="3" t="n">
         <v>122</v>
@@ -14831,25 +14839,25 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>OPMS.JK</t>
+          <t>SEMA.JK</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C534" s="2" t="n">
-        <v>19.66</v>
+        <v>14.53</v>
       </c>
       <c r="D534" s="2" t="n">
         <v>4.27</v>
       </c>
       <c r="E534" s="3" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F534" s="3" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G534" s="3" t="n">
         <v>122</v>
@@ -14912,55 +14920,55 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C537" s="2" t="n">
-        <v>10.42</v>
+        <v>25</v>
       </c>
       <c r="D537" s="2" t="n">
         <v>4.17</v>
       </c>
       <c r="E537" s="3" t="n">
-        <v>96</v>
+        <v>480</v>
       </c>
       <c r="F537" s="3" t="n">
-        <v>106</v>
+        <v>600</v>
       </c>
       <c r="G537" s="3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C538" s="2" t="n">
-        <v>25</v>
+        <v>10.42</v>
       </c>
       <c r="D538" s="2" t="n">
         <v>4.17</v>
       </c>
       <c r="E538" s="3" t="n">
-        <v>480</v>
+        <v>96</v>
       </c>
       <c r="F538" s="3" t="n">
-        <v>600</v>
+        <v>106</v>
       </c>
       <c r="G538" s="3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="539">
@@ -15020,79 +15028,79 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C541" s="2" t="n">
-        <v>17.33</v>
+        <v>15</v>
       </c>
       <c r="D541" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E541" s="3" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="F541" s="3" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="G541" s="3" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C542" s="2" t="n">
-        <v>15</v>
+        <v>10.67</v>
       </c>
       <c r="D542" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E542" s="3" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="F542" s="3" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="G542" s="3" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C543" s="2" t="n">
-        <v>10.67</v>
+        <v>17.33</v>
       </c>
       <c r="D543" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E543" s="3" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F543" s="3" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G543" s="3" t="n">
         <v>78</v>
@@ -15533,55 +15541,55 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>MPIX.JK</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C560" s="2" t="n">
-        <v>15.52</v>
+        <v>12.07</v>
       </c>
       <c r="D560" s="2" t="n">
         <v>3.45</v>
       </c>
       <c r="E560" s="3" t="n">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="F560" s="3" t="n">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="G560" s="3" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>MPIX.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C561" s="2" t="n">
-        <v>12.07</v>
+        <v>15.52</v>
       </c>
       <c r="D561" s="2" t="n">
         <v>3.45</v>
       </c>
       <c r="E561" s="3" t="n">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="F561" s="3" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="G561" s="3" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="562">
@@ -15722,55 +15730,55 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>TNCA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C567" s="2" t="n">
-        <v>11.24</v>
+        <v>17.51</v>
       </c>
       <c r="D567" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E567" s="3" t="n">
-        <v>180</v>
+        <v>3180</v>
       </c>
       <c r="F567" s="3" t="n">
-        <v>198</v>
+        <v>3490</v>
       </c>
       <c r="G567" s="3" t="n">
-        <v>184</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>TNCA.JK</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C568" s="2" t="n">
-        <v>17.51</v>
+        <v>11.24</v>
       </c>
       <c r="D568" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E568" s="3" t="n">
-        <v>3180</v>
+        <v>180</v>
       </c>
       <c r="F568" s="3" t="n">
-        <v>3490</v>
+        <v>198</v>
       </c>
       <c r="G568" s="3" t="n">
-        <v>3070</v>
+        <v>184</v>
       </c>
     </row>
     <row r="569">
@@ -15992,28 +16000,28 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C577" s="2" t="n">
-        <v>23.66</v>
+        <v>11.83</v>
       </c>
       <c r="D577" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E577" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>95</v>
       </c>
       <c r="F577" s="3" t="n">
-        <v>460</v>
+        <v>104</v>
       </c>
       <c r="G577" s="3" t="n">
-        <v>384</v>
+        <v>96</v>
       </c>
     </row>
     <row r="578">
@@ -16046,28 +16054,28 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C579" s="2" t="n">
-        <v>11.83</v>
+        <v>23.66</v>
       </c>
       <c r="D579" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E579" s="3" t="n">
-        <v>95</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F579" s="3" t="n">
-        <v>104</v>
+        <v>460</v>
       </c>
       <c r="G579" s="3" t="n">
-        <v>96</v>
+        <v>384</v>
       </c>
     </row>
     <row r="580">
@@ -16289,55 +16297,55 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>PBID.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C588" s="2" t="n">
-        <v>10.68</v>
+        <v>11.63</v>
       </c>
       <c r="D588" s="2" t="n">
         <v>2.91</v>
       </c>
       <c r="E588" s="3" t="n">
-        <v>515</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F588" s="3" t="n">
-        <v>570</v>
+        <v>192</v>
       </c>
       <c r="G588" s="3" t="n">
-        <v>530</v>
+        <v>177</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>PBID.JK</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C589" s="2" t="n">
-        <v>11.63</v>
+        <v>10.68</v>
       </c>
       <c r="D589" s="2" t="n">
         <v>2.91</v>
       </c>
       <c r="E589" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>515</v>
       </c>
       <c r="F589" s="3" t="n">
-        <v>192</v>
+        <v>570</v>
       </c>
       <c r="G589" s="3" t="n">
-        <v>177</v>
+        <v>530</v>
       </c>
     </row>
     <row r="590">
@@ -16397,55 +16405,55 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C592" s="2" t="n">
-        <v>12.15</v>
+        <v>11.89</v>
       </c>
       <c r="D592" s="2" t="n">
         <v>2.8</v>
       </c>
       <c r="E592" s="3" t="n">
-        <v>109</v>
+        <v>286.4117805325255</v>
       </c>
       <c r="F592" s="3" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="G592" s="3" t="n">
-        <v>110</v>
+        <v>294</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C593" s="2" t="n">
-        <v>11.89</v>
+        <v>12.15</v>
       </c>
       <c r="D593" s="2" t="n">
         <v>2.8</v>
       </c>
       <c r="E593" s="3" t="n">
-        <v>286.4117805325255</v>
+        <v>109</v>
       </c>
       <c r="F593" s="3" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="G593" s="3" t="n">
-        <v>294</v>
+        <v>110</v>
       </c>
     </row>
     <row r="594">
@@ -16586,109 +16594,109 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C599" s="2" t="n">
-        <v>14.58</v>
+        <v>10.39</v>
       </c>
       <c r="D599" s="2" t="n">
         <v>2.6</v>
       </c>
       <c r="E599" s="3" t="n">
-        <v>1065</v>
+        <v>72.38636016845703</v>
       </c>
       <c r="F599" s="3" t="n">
-        <v>1100</v>
+        <v>85</v>
       </c>
       <c r="G599" s="3" t="n">
-        <v>985</v>
+        <v>79</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C600" s="2" t="n">
-        <v>10.39</v>
+        <v>14.58</v>
       </c>
       <c r="D600" s="2" t="n">
         <v>2.6</v>
       </c>
       <c r="E600" s="3" t="n">
-        <v>72.38636016845703</v>
+        <v>1065</v>
       </c>
       <c r="F600" s="3" t="n">
-        <v>85</v>
+        <v>1100</v>
       </c>
       <c r="G600" s="3" t="n">
-        <v>79</v>
+        <v>985</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C601" s="2" t="n">
-        <v>17.95</v>
+        <v>17.09</v>
       </c>
       <c r="D601" s="2" t="n">
         <v>2.56</v>
       </c>
       <c r="E601" s="3" t="n">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="F601" s="3" t="n">
-        <v>92</v>
+        <v>274</v>
       </c>
       <c r="G601" s="3" t="n">
-        <v>80</v>
+        <v>240</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C602" s="2" t="n">
-        <v>17.09</v>
+        <v>17.95</v>
       </c>
       <c r="D602" s="2" t="n">
         <v>2.56</v>
       </c>
       <c r="E602" s="3" t="n">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="F602" s="3" t="n">
-        <v>274</v>
+        <v>92</v>
       </c>
       <c r="G602" s="3" t="n">
-        <v>240</v>
+        <v>80</v>
       </c>
     </row>
     <row r="603">
@@ -16856,55 +16864,55 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>LABA.JK</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C609" s="2" t="n">
-        <v>17.44</v>
+        <v>14.73</v>
       </c>
       <c r="D609" s="2" t="n">
         <v>2.33</v>
       </c>
       <c r="E609" s="3" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="F609" s="3" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="G609" s="3" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>LABA.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C610" s="2" t="n">
-        <v>14.73</v>
+        <v>17.44</v>
       </c>
       <c r="D610" s="2" t="n">
         <v>2.33</v>
       </c>
       <c r="E610" s="3" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="F610" s="3" t="n">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="G610" s="3" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
     </row>
     <row r="611">
@@ -16937,109 +16945,109 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C612" s="2" t="n">
-        <v>15.21</v>
+        <v>20.69</v>
       </c>
       <c r="D612" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="E612" s="3" t="n">
-        <v>1085</v>
+        <v>99</v>
       </c>
       <c r="F612" s="3" t="n">
-        <v>1250</v>
+        <v>105</v>
       </c>
       <c r="G612" s="3" t="n">
-        <v>1110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C613" s="2" t="n">
-        <v>20.69</v>
+        <v>15.21</v>
       </c>
       <c r="D613" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="E613" s="3" t="n">
-        <v>99</v>
+        <v>1085</v>
       </c>
       <c r="F613" s="3" t="n">
-        <v>105</v>
+        <v>1250</v>
       </c>
       <c r="G613" s="3" t="n">
-        <v>89</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>INAI.JK</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C614" s="2" t="n">
-        <v>12.36</v>
+        <v>13.48</v>
       </c>
       <c r="D614" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E614" s="3" t="n">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="F614" s="3" t="n">
-        <v>100</v>
+        <v>202</v>
       </c>
       <c r="G614" s="3" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>INAI.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C615" s="2" t="n">
-        <v>13.48</v>
+        <v>12.36</v>
       </c>
       <c r="D615" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E615" s="3" t="n">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F615" s="3" t="n">
-        <v>202</v>
+        <v>100</v>
       </c>
       <c r="G615" s="3" t="n">
-        <v>182</v>
+        <v>91</v>
       </c>
     </row>
     <row r="616">
@@ -17207,25 +17215,25 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C622" s="2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D622" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E622" s="3" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F622" s="3" t="n">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="G622" s="3" t="n">
         <v>204</v>
@@ -17234,25 +17242,25 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C623" s="2" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D623" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E623" s="3" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F623" s="3" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="G623" s="3" t="n">
         <v>204</v>
@@ -17342,25 +17350,25 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>DOSS.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C627" s="2" t="n">
-        <v>19.38</v>
+        <v>15.62</v>
       </c>
       <c r="D627" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="E627" s="3" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="F627" s="3" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G627" s="3" t="n">
         <v>163</v>
@@ -17369,25 +17377,25 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>DOSS.JK</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C628" s="2" t="n">
-        <v>15.62</v>
+        <v>19.38</v>
       </c>
       <c r="D628" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="E628" s="3" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F628" s="3" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G628" s="3" t="n">
         <v>163</v>
@@ -17693,109 +17701,109 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>LAND.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C640" s="2" t="n">
-        <v>11.29</v>
+        <v>11.83</v>
       </c>
       <c r="D640" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E640" s="3" t="n">
-        <v>62</v>
+        <v>181.15625</v>
       </c>
       <c r="F640" s="3" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="G640" s="3" t="n">
-        <v>63</v>
+        <v>189</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>LAND.JK</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C641" s="2" t="n">
-        <v>11.83</v>
+        <v>11.29</v>
       </c>
       <c r="D641" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E641" s="3" t="n">
-        <v>181.15625</v>
+        <v>62</v>
       </c>
       <c r="F641" s="3" t="n">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="G641" s="3" t="n">
-        <v>189</v>
+        <v>63</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>TFAS.JK</t>
+          <t>MCAS.JK</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C642" s="2" t="n">
-        <v>11.79</v>
+        <v>16.92</v>
       </c>
       <c r="D642" s="2" t="n">
         <v>1.54</v>
       </c>
       <c r="E642" s="3" t="n">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="F642" s="3" t="n">
-        <v>218</v>
+        <v>304</v>
       </c>
       <c r="G642" s="3" t="n">
-        <v>198</v>
+        <v>264</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>MCAS.JK</t>
+          <t>TFAS.JK</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C643" s="2" t="n">
-        <v>16.92</v>
+        <v>11.79</v>
       </c>
       <c r="D643" s="2" t="n">
         <v>1.54</v>
       </c>
       <c r="E643" s="3" t="n">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="F643" s="3" t="n">
-        <v>304</v>
+        <v>218</v>
       </c>
       <c r="G643" s="3" t="n">
-        <v>264</v>
+        <v>198</v>
       </c>
     </row>
     <row r="644">
@@ -18071,55 +18079,55 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>LPPS.JK</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C654" s="2" t="n">
-        <v>15.94</v>
+        <v>10.13</v>
       </c>
       <c r="D654" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="E654" s="3" t="n">
-        <v>13800</v>
+        <v>79</v>
       </c>
       <c r="F654" s="3" t="n">
-        <v>16000</v>
+        <v>87</v>
       </c>
       <c r="G654" s="3" t="n">
-        <v>13975</v>
+        <v>80</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>LPPS.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C655" s="2" t="n">
-        <v>10.13</v>
+        <v>15.94</v>
       </c>
       <c r="D655" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="E655" s="3" t="n">
-        <v>79</v>
+        <v>13800</v>
       </c>
       <c r="F655" s="3" t="n">
-        <v>87</v>
+        <v>16000</v>
       </c>
       <c r="G655" s="3" t="n">
-        <v>80</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="656">
@@ -18395,55 +18403,55 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>PORT.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C666" s="2" t="n">
-        <v>16.38</v>
+        <v>10.17</v>
       </c>
       <c r="D666" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E666" s="3" t="n">
-        <v>1015</v>
+        <v>177</v>
       </c>
       <c r="F666" s="3" t="n">
-        <v>1030</v>
+        <v>195</v>
       </c>
       <c r="G666" s="3" t="n">
-        <v>890</v>
+        <v>178</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>PORT.JK</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C667" s="2" t="n">
-        <v>10.17</v>
+        <v>16.38</v>
       </c>
       <c r="D667" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E667" s="3" t="n">
-        <v>177</v>
+        <v>1015</v>
       </c>
       <c r="F667" s="3" t="n">
-        <v>195</v>
+        <v>1030</v>
       </c>
       <c r="G667" s="3" t="n">
-        <v>178</v>
+        <v>890</v>
       </c>
     </row>
     <row r="668">
@@ -18557,7 +18565,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -18566,235 +18574,235 @@
         </is>
       </c>
       <c r="C672" s="2" t="n">
-        <v>28.48</v>
+        <v>10.76</v>
       </c>
       <c r="D672" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E672" s="3" t="n">
-        <v>152</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F672" s="3" t="n">
-        <v>194</v>
+        <v>3500</v>
       </c>
       <c r="G672" s="3" t="n">
-        <v>151</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>ISEA.JK</t>
+          <t>PDES.JK</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C673" s="2" t="n">
-        <v>11.25</v>
+        <v>18.01</v>
       </c>
       <c r="D673" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E673" s="3" t="n">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="F673" s="3" t="n">
-        <v>89</v>
+        <v>498</v>
       </c>
       <c r="G673" s="3" t="n">
-        <v>80</v>
+        <v>422</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>MPRO.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C674" s="2" t="n">
-        <v>19.95</v>
+        <v>27.33</v>
       </c>
       <c r="D674" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E674" s="3" t="n">
-        <v>11750</v>
+        <v>152</v>
       </c>
       <c r="F674" s="3" t="n">
-        <v>11875</v>
+        <v>191</v>
       </c>
       <c r="G674" s="3" t="n">
-        <v>9900</v>
+        <v>150</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C675" s="2" t="n">
-        <v>10.76</v>
+        <v>10.91</v>
       </c>
       <c r="D675" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E675" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>165</v>
       </c>
       <c r="F675" s="3" t="n">
-        <v>3500</v>
+        <v>183</v>
       </c>
       <c r="G675" s="3" t="n">
-        <v>3160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C676" s="2" t="n">
-        <v>12.38</v>
+        <v>17.5</v>
       </c>
       <c r="D676" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E676" s="3" t="n">
-        <v>91.91489410400391</v>
+        <v>163</v>
       </c>
       <c r="F676" s="3" t="n">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="G676" s="3" t="n">
-        <v>105</v>
+        <v>160</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C677" s="2" t="n">
-        <v>10.26</v>
+        <v>28.48</v>
       </c>
       <c r="D677" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E677" s="3" t="n">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="F677" s="3" t="n">
-        <v>86</v>
+        <v>194</v>
       </c>
       <c r="G677" s="3" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C678" s="2" t="n">
-        <v>17.5</v>
+        <v>12.78</v>
       </c>
       <c r="D678" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E678" s="3" t="n">
-        <v>163</v>
+        <v>2640</v>
       </c>
       <c r="F678" s="3" t="n">
-        <v>188</v>
+        <v>3000</v>
       </c>
       <c r="G678" s="3" t="n">
-        <v>160</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>RELI.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C679" s="2" t="n">
-        <v>14.29</v>
+        <v>10.61</v>
       </c>
       <c r="D679" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E679" s="3" t="n">
-        <v>520</v>
+        <v>67</v>
       </c>
       <c r="F679" s="3" t="n">
-        <v>600</v>
+        <v>73</v>
       </c>
       <c r="G679" s="3" t="n">
-        <v>525</v>
+        <v>66</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>AISA.JK</t>
+          <t>RELI.JK</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C680" s="2" t="n">
-        <v>12.9</v>
+        <v>14.29</v>
       </c>
       <c r="D680" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E680" s="3" t="n">
-        <v>128</v>
+        <v>520</v>
       </c>
       <c r="F680" s="3" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="G680" s="3" t="n">
-        <v>124</v>
+        <v>525</v>
       </c>
     </row>
     <row r="681">
@@ -18827,190 +18835,190 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C682" s="2" t="n">
-        <v>10.91</v>
+        <v>12.87</v>
       </c>
       <c r="D682" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E682" s="3" t="n">
-        <v>165</v>
+        <v>93</v>
       </c>
       <c r="F682" s="3" t="n">
-        <v>183</v>
+        <v>114</v>
       </c>
       <c r="G682" s="3" t="n">
-        <v>165</v>
+        <v>101</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C683" s="2" t="n">
-        <v>17.65</v>
+        <v>10.26</v>
       </c>
       <c r="D683" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E683" s="3" t="n">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="F683" s="3" t="n">
-        <v>200</v>
+        <v>86</v>
       </c>
       <c r="G683" s="3" t="n">
-        <v>170</v>
+        <v>78</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ISEA.JK</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C684" s="2" t="n">
-        <v>12.87</v>
+        <v>11.25</v>
       </c>
       <c r="D684" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E684" s="3" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F684" s="3" t="n">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="G684" s="3" t="n">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>MPRO.JK</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C685" s="2" t="n">
-        <v>12.78</v>
+        <v>19.95</v>
       </c>
       <c r="D685" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E685" s="3" t="n">
-        <v>2640</v>
+        <v>11750</v>
       </c>
       <c r="F685" s="3" t="n">
-        <v>3000</v>
+        <v>11875</v>
       </c>
       <c r="G685" s="3" t="n">
-        <v>2660</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C686" s="2" t="n">
-        <v>10.61</v>
+        <v>17.65</v>
       </c>
       <c r="D686" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E686" s="3" t="n">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="F686" s="3" t="n">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="G686" s="3" t="n">
-        <v>66</v>
+        <v>170</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>AISA.JK</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C687" s="2" t="n">
-        <v>27.33</v>
+        <v>12.9</v>
       </c>
       <c r="D687" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E687" s="3" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="F687" s="3" t="n">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="G687" s="3" t="n">
-        <v>150</v>
+        <v>124</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>PDES.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C688" s="2" t="n">
-        <v>18.01</v>
+        <v>12.38</v>
       </c>
       <c r="D688" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E688" s="3" t="n">
-        <v>424</v>
+        <v>91.91489410400391</v>
       </c>
       <c r="F688" s="3" t="n">
-        <v>498</v>
+        <v>118</v>
       </c>
       <c r="G688" s="3" t="n">
-        <v>422</v>
+        <v>105</v>
       </c>
     </row>
     <row r="689">
@@ -20042,12 +20050,12 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C727" s="2" t="n">
@@ -20057,24 +20065,24 @@
         <v>-2.53</v>
       </c>
       <c r="E727" s="3" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="F727" s="3" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="G727" s="3" t="n">
-        <v>77</v>
+        <v>154</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C728" s="2" t="n">
@@ -20084,13 +20092,13 @@
         <v>-2.53</v>
       </c>
       <c r="E728" s="3" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="F728" s="3" t="n">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="G728" s="3" t="n">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="729">
@@ -20742,16 +20750,16 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C753" s="2" t="n">
-        <v>15.48</v>
+        <v>20.24</v>
       </c>
       <c r="D753" s="2" t="n">
         <v>-4.76</v>
@@ -20760,7 +20768,7 @@
         <v>84</v>
       </c>
       <c r="F753" s="3" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G753" s="3" t="n">
         <v>80</v>
@@ -20769,16 +20777,16 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C754" s="2" t="n">
-        <v>20.24</v>
+        <v>15.48</v>
       </c>
       <c r="D754" s="2" t="n">
         <v>-4.76</v>
@@ -20787,7 +20795,7 @@
         <v>84</v>
       </c>
       <c r="F754" s="3" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G754" s="3" t="n">
         <v>80</v>
@@ -20958,55 +20966,55 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C761" s="2" t="n">
-        <v>23.53</v>
+        <v>12.63</v>
       </c>
       <c r="D761" s="2" t="n">
         <v>-5.15</v>
       </c>
       <c r="E761" s="3" t="n">
-        <v>700</v>
+        <v>19500</v>
       </c>
       <c r="F761" s="3" t="n">
-        <v>840</v>
+        <v>21850</v>
       </c>
       <c r="G761" s="3" t="n">
-        <v>645</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C762" s="2" t="n">
-        <v>12.63</v>
+        <v>23.53</v>
       </c>
       <c r="D762" s="2" t="n">
         <v>-5.15</v>
       </c>
       <c r="E762" s="3" t="n">
-        <v>19500</v>
+        <v>700</v>
       </c>
       <c r="F762" s="3" t="n">
-        <v>21850</v>
+        <v>840</v>
       </c>
       <c r="G762" s="3" t="n">
-        <v>18400</v>
+        <v>645</v>
       </c>
     </row>
     <row r="763">
@@ -21039,55 +21047,55 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C764" s="2" t="n">
-        <v>13.58</v>
+        <v>21.24</v>
       </c>
       <c r="D764" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E764" s="3" t="n">
-        <v>162</v>
+        <v>1827.910536399762</v>
       </c>
       <c r="F764" s="3" t="n">
-        <v>184</v>
+        <v>1855</v>
       </c>
       <c r="G764" s="3" t="n">
-        <v>153</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C765" s="2" t="n">
-        <v>21.24</v>
+        <v>13.58</v>
       </c>
       <c r="D765" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E765" s="3" t="n">
-        <v>1827.910536399762</v>
+        <v>162</v>
       </c>
       <c r="F765" s="3" t="n">
-        <v>1855</v>
+        <v>184</v>
       </c>
       <c r="G765" s="3" t="n">
-        <v>1445</v>
+        <v>153</v>
       </c>
     </row>
     <row r="766">

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -1102,12 +1102,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1117,24 +1117,24 @@
         <v>25</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1190</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1200</v>
+        <v>545</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1200</v>
+        <v>545</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>434</v>
+        <v>153.7625885009766</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>515</v>
+        <v>290</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>515</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27">
@@ -1183,12 +1183,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1198,24 +1198,24 @@
         <v>25</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>605</v>
+        <v>1200</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>775</v>
+        <v>1375</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>775</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -1225,78 +1225,78 @@
         <v>25</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1200</v>
+        <v>605</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1375</v>
+        <v>775</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1375</v>
+        <v>775</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>33.62</v>
+        <v>26.25</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>119</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>975</v>
+        <v>155</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>975</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EKAD.JK</t>
+          <t>SAFE.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1306,19 +1306,19 @@
         <v>25</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>300</v>
+        <v>615</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>300</v>
+        <v>615</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1333,13 +1333,13 @@
         <v>25</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>3310</v>
+        <v>290</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3700</v>
+        <v>350</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>3700</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34">
@@ -1372,12 +1372,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1387,24 +1387,24 @@
         <v>25</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>3040</v>
+        <v>3310</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3600</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1414,24 +1414,24 @@
         <v>25</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>290</v>
+        <v>505</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>350</v>
+        <v>505</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>350</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1441,24 +1441,24 @@
         <v>25</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>153.7625885009766</v>
+        <v>434</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>290</v>
+        <v>515</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>290</v>
+        <v>515</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1468,24 +1468,24 @@
         <v>25</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>414.3801616703698</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>545</v>
+        <v>975</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>545</v>
+        <v>975</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAFE.JK</t>
+          <t>EKAD.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1495,13 +1495,13 @@
         <v>25</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>615</v>
+        <v>300</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>615</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40">
@@ -1534,12 +1534,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1549,51 +1549,51 @@
         <v>25</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>505</v>
+        <v>1190</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>505</v>
+        <v>1200</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>505</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>BLTZ.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>165</v>
+        <v>3040</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>202</v>
+        <v>3600</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>200</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>NICK.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -1603,24 +1603,24 @@
         <v>24.92</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>3210</v>
+        <v>1540</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>4010</v>
+        <v>1930</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>4010</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NICK.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -1630,24 +1630,24 @@
         <v>24.92</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1540</v>
+        <v>3210</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1930</v>
+        <v>4010</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1930</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -1657,24 +1657,24 @@
         <v>24.9</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2580</v>
+        <v>1445</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -1684,13 +1684,13 @@
         <v>24.9</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1445</v>
+        <v>2580</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="47">
@@ -1939,12 +1939,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PGLI.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -1954,24 +1954,24 @@
         <v>24.81</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>2600</v>
+        <v>300</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>3220</v>
+        <v>332</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>3220</v>
+        <v>332</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PGLI.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -1981,24 +1981,24 @@
         <v>24.81</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>300</v>
+        <v>2600</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>332</v>
+        <v>3220</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>332</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IFSH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -2008,24 +2008,24 @@
         <v>24.8</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1555</v>
+        <v>3070</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1560</v>
+        <v>3070</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1560</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>IFSH.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -2035,13 +2035,13 @@
         <v>24.8</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>3070</v>
+        <v>1555</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>3070</v>
+        <v>1560</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3070</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="60">
@@ -2128,12 +2128,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BABY.JK</t>
+          <t>BIKE.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -2143,24 +2143,24 @@
         <v>24.77</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>226</v>
+        <v>2270</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>272</v>
+        <v>2670</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>272</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BIKE.JK</t>
+          <t>BABY.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -2170,13 +2170,13 @@
         <v>24.77</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>2270</v>
+        <v>226</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>2670</v>
+        <v>272</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>2670</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65">
@@ -2209,12 +2209,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ASLI.JK</t>
+          <t>TFCO.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -2224,24 +2224,24 @@
         <v>24.76</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>228</v>
+        <v>1060</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>262</v>
+        <v>1285</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>262</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>ASLI.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -2251,24 +2251,24 @@
         <v>24.76</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>525</v>
+        <v>228</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TFCO.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -2278,13 +2278,13 @@
         <v>24.76</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1060</v>
+        <v>525</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1285</v>
+        <v>655</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1285</v>
+        <v>655</v>
       </c>
     </row>
     <row r="69">
@@ -2398,12 +2398,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -2413,24 +2413,24 @@
         <v>24.69</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>404</v>
+        <v>1625</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>404</v>
+        <v>2020</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>404</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -2440,24 +2440,24 @@
         <v>24.69</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>1625</v>
+        <v>404</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2020</v>
+        <v>404</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2020</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -2467,24 +2467,24 @@
         <v>24.68</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2330</v>
+        <v>760</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2880</v>
+        <v>960</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>BLTZ.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -2494,13 +2494,13 @@
         <v>24.68</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>760</v>
+        <v>2330</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>960</v>
+        <v>2880</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>960</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="77">
@@ -2560,12 +2560,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>FUJI.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -2575,7 +2575,7 @@
         <v>24.62</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>324</v>
@@ -2587,12 +2587,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FUJI.JK</t>
+          <t>VOKS.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -2602,7 +2602,7 @@
         <v>24.62</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F80" s="3" t="n">
         <v>324</v>
@@ -2614,12 +2614,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VOKS.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -2629,7 +2629,7 @@
         <v>24.62</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="F81" s="3" t="n">
         <v>324</v>
@@ -3476,55 +3476,55 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>24.6</v>
+        <v>30.71</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>21.43</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>690</v>
+        <v>143</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>785</v>
+        <v>183</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>765</v>
+        <v>170</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KOKA.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>30.71</v>
+        <v>24.6</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>21.43</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>143</v>
+        <v>690</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>183</v>
+        <v>785</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>170</v>
+        <v>765</v>
       </c>
     </row>
     <row r="115">
@@ -4867,9 +4867,7 @@
       <c r="D164" s="2" t="n">
         <v>17.59</v>
       </c>
-      <c r="E164" s="3" t="n">
-        <v>109</v>
-      </c>
+      <c r="E164" s="3" t="inlineStr"/>
       <c r="F164" s="3" t="n">
         <v>138</v>
       </c>
@@ -5285,55 +5283,55 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SLIS.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>29.55</v>
+        <v>25</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>15.91</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>92</v>
+        <v>1320</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>114</v>
+        <v>1650</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>102</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>SLIS.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>25</v>
+        <v>29.55</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>15.91</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>1320</v>
+        <v>92</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>1650</v>
+        <v>114</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>1530</v>
+        <v>102</v>
       </c>
     </row>
     <row r="182">
@@ -5501,25 +5499,25 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>LUCK.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>26.21</v>
+        <v>28.16</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>15.53</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G188" s="3" t="n">
         <v>119</v>
@@ -5528,25 +5526,25 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LUCK.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>28.16</v>
+        <v>26.21</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>15.53</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G189" s="3" t="n">
         <v>119</v>
@@ -6149,55 +6147,55 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>VICI.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>19.07</v>
+        <v>21.4</v>
       </c>
       <c r="D212" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>1080</v>
+        <v>2200</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>1280</v>
+        <v>2610</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>1230</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>21.4</v>
+        <v>19.07</v>
       </c>
       <c r="D213" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>2200</v>
+        <v>1080</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>2610</v>
+        <v>1280</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>2460</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="214">
@@ -6622,9 +6620,7 @@
       <c r="D229" s="2" t="n">
         <v>13.85</v>
       </c>
-      <c r="E229" s="3" t="n">
-        <v>268</v>
-      </c>
+      <c r="E229" s="3" t="inlineStr"/>
       <c r="F229" s="3" t="n">
         <v>296</v>
       </c>
@@ -6662,109 +6658,109 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>ELIT.JK</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>15.17</v>
+        <v>13.79</v>
       </c>
       <c r="D231" s="2" t="n">
         <v>13.79</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>2800</v>
+        <v>236</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>3340</v>
+        <v>264</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>3300</v>
+        <v>264</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ELIT.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>13.79</v>
+        <v>15.17</v>
       </c>
       <c r="D232" s="2" t="n">
         <v>13.79</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>236</v>
+        <v>2800</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>264</v>
+        <v>3340</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>264</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>24.9</v>
+        <v>14.88</v>
       </c>
       <c r="D233" s="2" t="n">
         <v>13.69</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>2990</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>3010</v>
+        <v>386</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>2740</v>
+        <v>382</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>14.88</v>
+        <v>24.9</v>
       </c>
       <c r="D234" s="2" t="n">
         <v>13.69</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>2990</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>386</v>
+        <v>3010</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>382</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="235">
@@ -7391,55 +7387,55 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C258" s="2" t="n">
-        <v>15.53</v>
+        <v>14.56</v>
       </c>
       <c r="D258" s="2" t="n">
         <v>12.62</v>
       </c>
       <c r="E258" s="3" t="n">
-        <v>515</v>
+        <v>210</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>595</v>
+        <v>236</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>580</v>
+        <v>232</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C259" s="2" t="n">
-        <v>14.56</v>
+        <v>15.53</v>
       </c>
       <c r="D259" s="2" t="n">
         <v>12.62</v>
       </c>
       <c r="E259" s="3" t="n">
-        <v>210</v>
+        <v>515</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>236</v>
+        <v>595</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>232</v>
+        <v>580</v>
       </c>
     </row>
     <row r="260">
@@ -7472,55 +7468,53 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C261" s="2" t="n">
-        <v>14.06</v>
+        <v>20.31</v>
       </c>
       <c r="D261" s="2" t="n">
         <v>12.5</v>
       </c>
       <c r="E261" s="3" t="n">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="F261" s="3" t="n">
-        <v>146</v>
+        <v>308</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>144</v>
+        <v>288</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C262" s="2" t="n">
-        <v>20.31</v>
+        <v>14.06</v>
       </c>
       <c r="D262" s="2" t="n">
         <v>12.5</v>
       </c>
-      <c r="E262" s="3" t="n">
-        <v>258</v>
-      </c>
+      <c r="E262" s="3" t="inlineStr"/>
       <c r="F262" s="3" t="n">
-        <v>308</v>
+        <v>146</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>288</v>
+        <v>144</v>
       </c>
     </row>
     <row r="263">
@@ -7877,55 +7871,55 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>CBPE.JK</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C276" s="2" t="n">
-        <v>20.62</v>
+        <v>23.76</v>
       </c>
       <c r="D276" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="E276" s="3" t="n">
-        <v>160</v>
+        <v>525</v>
       </c>
       <c r="F276" s="3" t="n">
-        <v>193</v>
+        <v>625</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>179</v>
+        <v>565</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CBPE.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>23.76</v>
+        <v>20.62</v>
       </c>
       <c r="D277" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="E277" s="3" t="n">
-        <v>525</v>
+        <v>160</v>
       </c>
       <c r="F277" s="3" t="n">
-        <v>625</v>
+        <v>193</v>
       </c>
       <c r="G277" s="3" t="n">
-        <v>565</v>
+        <v>179</v>
       </c>
     </row>
     <row r="278">
@@ -8039,55 +8033,55 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>13.39</v>
+        <v>11.61</v>
       </c>
       <c r="D282" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E282" s="3" t="n">
-        <v>2270</v>
+        <v>218</v>
       </c>
       <c r="F282" s="3" t="n">
-        <v>2540</v>
+        <v>250</v>
       </c>
       <c r="G282" s="3" t="n">
-        <v>2500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>11.61</v>
+        <v>13.39</v>
       </c>
       <c r="D283" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E283" s="3" t="n">
-        <v>218</v>
+        <v>2270</v>
       </c>
       <c r="F283" s="3" t="n">
-        <v>250</v>
+        <v>2540</v>
       </c>
       <c r="G283" s="3" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="284">
@@ -8417,55 +8411,55 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>WAPO.JK</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>23.28</v>
+        <v>18.1</v>
       </c>
       <c r="D296" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="E296" s="3" t="n">
-        <v>119</v>
+        <v>226</v>
       </c>
       <c r="F296" s="3" t="n">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>129</v>
+        <v>258</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>WAPO.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>18.1</v>
+        <v>23.28</v>
       </c>
       <c r="D297" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="E297" s="3" t="n">
-        <v>226</v>
+        <v>119</v>
       </c>
       <c r="F297" s="3" t="n">
-        <v>274</v>
+        <v>143</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>258</v>
+        <v>129</v>
       </c>
     </row>
     <row r="298">
@@ -8525,28 +8519,28 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>BIPP.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C300" s="2" t="n">
-        <v>23.81</v>
+        <v>12.5</v>
       </c>
       <c r="D300" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E300" s="3" t="n">
-        <v>64</v>
+        <v>720</v>
       </c>
       <c r="F300" s="3" t="n">
-        <v>78</v>
+        <v>810</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
     </row>
     <row r="301">
@@ -8579,28 +8573,28 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>BIPP.JK</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C302" s="2" t="n">
-        <v>12.5</v>
+        <v>23.81</v>
       </c>
       <c r="D302" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E302" s="3" t="n">
-        <v>720</v>
+        <v>64</v>
       </c>
       <c r="F302" s="3" t="n">
-        <v>810</v>
+        <v>78</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
     </row>
     <row r="303">
@@ -8741,55 +8735,55 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ASGR.JK</t>
+          <t>DOOH.JK</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>18.83</v>
+        <v>21.09</v>
       </c>
       <c r="D308" s="2" t="n">
         <v>10.88</v>
       </c>
       <c r="E308" s="3" t="n">
-        <v>1665.468007064892</v>
+        <v>304</v>
       </c>
       <c r="F308" s="3" t="n">
-        <v>2240</v>
+        <v>356</v>
       </c>
       <c r="G308" s="3" t="n">
-        <v>2090</v>
+        <v>326</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>DOOH.JK</t>
+          <t>ASGR.JK</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>21.09</v>
+        <v>18.83</v>
       </c>
       <c r="D309" s="2" t="n">
         <v>10.88</v>
       </c>
       <c r="E309" s="3" t="n">
-        <v>304</v>
+        <v>1665.468007064892</v>
       </c>
       <c r="F309" s="3" t="n">
-        <v>356</v>
+        <v>2240</v>
       </c>
       <c r="G309" s="3" t="n">
-        <v>326</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="310">
@@ -8822,55 +8816,55 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>18.07</v>
+        <v>21.69</v>
       </c>
       <c r="D311" s="2" t="n">
         <v>10.84</v>
       </c>
       <c r="E311" s="3" t="n">
-        <v>332</v>
+        <v>87</v>
       </c>
       <c r="F311" s="3" t="n">
-        <v>392</v>
+        <v>101</v>
       </c>
       <c r="G311" s="3" t="n">
-        <v>368</v>
+        <v>92</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>21.69</v>
+        <v>18.07</v>
       </c>
       <c r="D312" s="2" t="n">
         <v>10.84</v>
       </c>
       <c r="E312" s="3" t="n">
-        <v>87</v>
+        <v>332</v>
       </c>
       <c r="F312" s="3" t="n">
-        <v>101</v>
+        <v>392</v>
       </c>
       <c r="G312" s="3" t="n">
-        <v>92</v>
+        <v>368</v>
       </c>
     </row>
     <row r="313">
@@ -9146,55 +9140,55 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>22.64</v>
+        <v>10.38</v>
       </c>
       <c r="D323" s="2" t="n">
         <v>10.38</v>
       </c>
       <c r="E323" s="3" t="n">
-        <v>106</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F323" s="3" t="n">
-        <v>130</v>
+        <v>585</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>117</v>
+        <v>585</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>10.38</v>
+        <v>22.64</v>
       </c>
       <c r="D324" s="2" t="n">
         <v>10.38</v>
       </c>
       <c r="E324" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>106</v>
       </c>
       <c r="F324" s="3" t="n">
-        <v>585</v>
+        <v>130</v>
       </c>
       <c r="G324" s="3" t="n">
-        <v>585</v>
+        <v>117</v>
       </c>
     </row>
     <row r="325">
@@ -9497,25 +9491,25 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C336" s="2" t="n">
-        <v>10.09</v>
+        <v>21.1</v>
       </c>
       <c r="D336" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E336" s="3" t="n">
-        <v>535</v>
+        <v>495.4545288085938</v>
       </c>
       <c r="F336" s="3" t="n">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="G336" s="3" t="n">
         <v>600</v>
@@ -9524,25 +9518,25 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C337" s="2" t="n">
-        <v>21.1</v>
+        <v>10.09</v>
       </c>
       <c r="D337" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E337" s="3" t="n">
-        <v>495.4545288085938</v>
+        <v>535</v>
       </c>
       <c r="F337" s="3" t="n">
-        <v>660</v>
+        <v>600</v>
       </c>
       <c r="G337" s="3" t="n">
         <v>600</v>
@@ -9578,7 +9572,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>APEX.JK</t>
+          <t>TKIM.JK</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9587,73 +9581,73 @@
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>12.67</v>
+        <v>10.77</v>
       </c>
       <c r="D339" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E339" s="3" t="n">
-        <v>150</v>
+        <v>6850</v>
       </c>
       <c r="F339" s="3" t="n">
-        <v>169</v>
+        <v>7200</v>
       </c>
       <c r="G339" s="3" t="n">
-        <v>165</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>TKIM.JK</t>
+          <t>PPRO.JK</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>10.77</v>
+        <v>30</v>
       </c>
       <c r="D340" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E340" s="3" t="n">
-        <v>6850</v>
+        <v>23</v>
       </c>
       <c r="F340" s="3" t="n">
-        <v>7200</v>
+        <v>26</v>
       </c>
       <c r="G340" s="3" t="n">
-        <v>7150</v>
+        <v>22</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>PPRO.JK</t>
+          <t>APEX.JK</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>30</v>
+        <v>12.67</v>
       </c>
       <c r="D341" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E341" s="3" t="n">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>22</v>
+        <v>165</v>
       </c>
     </row>
     <row r="342">
@@ -9848,55 +9842,55 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>VTNY.JK</t>
+          <t>MOLI.JK</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>11.48</v>
+        <v>11.4</v>
       </c>
       <c r="D349" s="2" t="n">
         <v>9.84</v>
       </c>
       <c r="E349" s="3" t="n">
-        <v>62</v>
+        <v>390</v>
       </c>
       <c r="F349" s="3" t="n">
-        <v>68</v>
+        <v>430</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>67</v>
+        <v>424</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>MOLI.JK</t>
+          <t>VTNY.JK</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>11.4</v>
+        <v>11.48</v>
       </c>
       <c r="D350" s="2" t="n">
         <v>9.84</v>
       </c>
       <c r="E350" s="3" t="n">
-        <v>390</v>
+        <v>62</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>430</v>
+        <v>68</v>
       </c>
       <c r="G350" s="3" t="n">
-        <v>424</v>
+        <v>67</v>
       </c>
     </row>
     <row r="351">
@@ -10388,55 +10382,55 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>WAPO.JK</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>13.95</v>
+        <v>24.81</v>
       </c>
       <c r="D369" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E369" s="3" t="n">
-        <v>20500</v>
+        <v>260</v>
       </c>
       <c r="F369" s="3" t="n">
-        <v>24500</v>
+        <v>322</v>
       </c>
       <c r="G369" s="3" t="n">
-        <v>23500</v>
+        <v>282</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>WAPO.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>24.81</v>
+        <v>13.95</v>
       </c>
       <c r="D370" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E370" s="3" t="n">
-        <v>260</v>
+        <v>20500</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>322</v>
+        <v>24500</v>
       </c>
       <c r="G370" s="3" t="n">
-        <v>282</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="371">
@@ -11171,136 +11165,136 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>MOLI.JK</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>12.86</v>
+        <v>13.14</v>
       </c>
       <c r="D398" s="2" t="n">
         <v>8.57</v>
       </c>
       <c r="E398" s="3" t="n">
-        <v>136</v>
+        <v>360</v>
       </c>
       <c r="F398" s="3" t="n">
-        <v>158</v>
+        <v>396</v>
       </c>
       <c r="G398" s="3" t="n">
-        <v>152</v>
+        <v>380</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>ARKO.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>12.38</v>
+        <v>12.86</v>
       </c>
       <c r="D399" s="2" t="n">
         <v>8.57</v>
       </c>
       <c r="E399" s="3" t="n">
-        <v>5275</v>
+        <v>136</v>
       </c>
       <c r="F399" s="3" t="n">
-        <v>5900</v>
+        <v>158</v>
       </c>
       <c r="G399" s="3" t="n">
-        <v>5700</v>
+        <v>152</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>MOLI.JK</t>
+          <t>ARKO.JK</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
-        <v>13.14</v>
+        <v>12.38</v>
       </c>
       <c r="D400" s="2" t="n">
         <v>8.57</v>
       </c>
       <c r="E400" s="3" t="n">
-        <v>360</v>
+        <v>5275</v>
       </c>
       <c r="F400" s="3" t="n">
-        <v>396</v>
+        <v>5900</v>
       </c>
       <c r="G400" s="3" t="n">
-        <v>380</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
-        <v>16.1</v>
+        <v>10.17</v>
       </c>
       <c r="D401" s="2" t="n">
         <v>8.470000000000001</v>
       </c>
       <c r="E401" s="3" t="n">
-        <v>120</v>
+        <v>248</v>
       </c>
       <c r="F401" s="3" t="n">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="G401" s="3" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>10.17</v>
+        <v>16.1</v>
       </c>
       <c r="D402" s="2" t="n">
         <v>8.470000000000001</v>
       </c>
       <c r="E402" s="3" t="n">
-        <v>248</v>
+        <v>120</v>
       </c>
       <c r="F402" s="3" t="n">
-        <v>260</v>
+        <v>137</v>
       </c>
       <c r="G402" s="3" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
     </row>
     <row r="403">
@@ -11387,55 +11381,55 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>HGII.JK</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>19.05</v>
+        <v>27.27</v>
       </c>
       <c r="D406" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E406" s="3" t="n">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F406" s="3" t="n">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="G406" s="3" t="n">
-        <v>182</v>
+        <v>143</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C407" s="2" t="n">
-        <v>10.19</v>
+        <v>11.67</v>
       </c>
       <c r="D407" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E407" s="3" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F407" s="3" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G407" s="3" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="408">
@@ -11468,136 +11462,136 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>SSTM.JK</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>11.11</v>
+        <v>22.92</v>
       </c>
       <c r="D409" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E409" s="3" t="n">
-        <v>73</v>
+        <v>555</v>
       </c>
       <c r="F409" s="3" t="n">
-        <v>80</v>
+        <v>590</v>
       </c>
       <c r="G409" s="3" t="n">
-        <v>78</v>
+        <v>520</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>12.5</v>
+        <v>19.05</v>
       </c>
       <c r="D410" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E410" s="3" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="F410" s="3" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="G410" s="3" t="n">
-        <v>156</v>
+        <v>182</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>HGII.JK</t>
+          <t>BKDP.JK</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>27.27</v>
+        <v>12.5</v>
       </c>
       <c r="D411" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E411" s="3" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F411" s="3" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G411" s="3" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>11.67</v>
+        <v>10.19</v>
       </c>
       <c r="D412" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E412" s="3" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F412" s="3" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="G412" s="3" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>SSTM.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>22.92</v>
+        <v>11.11</v>
       </c>
       <c r="D413" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E413" s="3" t="n">
-        <v>555</v>
+        <v>73</v>
       </c>
       <c r="F413" s="3" t="n">
-        <v>590</v>
+        <v>80</v>
       </c>
       <c r="G413" s="3" t="n">
-        <v>520</v>
+        <v>78</v>
       </c>
     </row>
     <row r="414">
@@ -11927,79 +11921,79 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>BEKS.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>20</v>
+        <v>18.67</v>
       </c>
       <c r="D426" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E426" s="3" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="F426" s="3" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="G426" s="3" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>BEKS.JK</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>13.33</v>
+        <v>20</v>
       </c>
       <c r="D427" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E427" s="3" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F427" s="3" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="G427" s="3" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>20</v>
+        <v>13.33</v>
       </c>
       <c r="D428" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E428" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F428" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G428" s="3" t="n">
         <v>81</v>
@@ -12008,25 +12002,25 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>18.67</v>
+        <v>20</v>
       </c>
       <c r="D429" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E429" s="3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F429" s="3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G429" s="3" t="n">
         <v>81</v>
@@ -12116,55 +12110,55 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>LPCK.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>16.52</v>
+        <v>12.17</v>
       </c>
       <c r="D433" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E433" s="3" t="n">
-        <v>590</v>
+        <v>230</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>670</v>
+        <v>258</v>
       </c>
       <c r="G433" s="3" t="n">
-        <v>620</v>
+        <v>248</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>LPCK.JK</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>12.17</v>
+        <v>16.52</v>
       </c>
       <c r="D434" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E434" s="3" t="n">
-        <v>230</v>
+        <v>590</v>
       </c>
       <c r="F434" s="3" t="n">
-        <v>258</v>
+        <v>670</v>
       </c>
       <c r="G434" s="3" t="n">
-        <v>248</v>
+        <v>620</v>
       </c>
     </row>
     <row r="435">
@@ -12305,55 +12299,55 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>ASLI.JK</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C440" s="2" t="n">
-        <v>16.35</v>
+        <v>20.51</v>
       </c>
       <c r="D440" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E440" s="3" t="n">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="F440" s="3" t="n">
-        <v>121</v>
+        <v>282</v>
       </c>
       <c r="G440" s="3" t="n">
-        <v>112</v>
+        <v>252</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>CCSI.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C441" s="2" t="n">
-        <v>23.78</v>
+        <v>16.35</v>
       </c>
       <c r="D441" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E441" s="3" t="n">
-        <v>294</v>
+        <v>106</v>
       </c>
       <c r="F441" s="3" t="n">
-        <v>354</v>
+        <v>121</v>
       </c>
       <c r="G441" s="3" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
     </row>
     <row r="442">
@@ -12386,82 +12380,82 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>ASLI.JK</t>
+          <t>CCSI.JK</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C443" s="2" t="n">
-        <v>20.51</v>
+        <v>23.78</v>
       </c>
       <c r="D443" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E443" s="3" t="n">
-        <v>238</v>
+        <v>294</v>
       </c>
       <c r="F443" s="3" t="n">
-        <v>282</v>
+        <v>354</v>
       </c>
       <c r="G443" s="3" t="n">
-        <v>252</v>
+        <v>308</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>MPIX.JK</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C444" s="2" t="n">
-        <v>12.98</v>
+        <v>13.56</v>
       </c>
       <c r="D444" s="2" t="n">
         <v>7.63</v>
       </c>
       <c r="E444" s="3" t="n">
-        <v>264</v>
+        <v>118</v>
       </c>
       <c r="F444" s="3" t="n">
-        <v>296</v>
+        <v>134</v>
       </c>
       <c r="G444" s="3" t="n">
-        <v>282</v>
+        <v>127</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MPIX.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C445" s="2" t="n">
-        <v>13.56</v>
+        <v>12.98</v>
       </c>
       <c r="D445" s="2" t="n">
         <v>7.63</v>
       </c>
       <c r="E445" s="3" t="n">
-        <v>118</v>
+        <v>264</v>
       </c>
       <c r="F445" s="3" t="n">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="G445" s="3" t="n">
-        <v>127</v>
+        <v>282</v>
       </c>
     </row>
     <row r="446">
@@ -12494,55 +12488,55 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C447" s="2" t="n">
-        <v>11.03</v>
+        <v>16.46</v>
       </c>
       <c r="D447" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E447" s="3" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="F447" s="3" t="n">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="G447" s="3" t="n">
-        <v>156</v>
+        <v>85</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C448" s="2" t="n">
-        <v>16.46</v>
+        <v>11.03</v>
       </c>
       <c r="D448" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E448" s="3" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="G448" s="3" t="n">
-        <v>85</v>
+        <v>156</v>
       </c>
     </row>
     <row r="449">
@@ -12980,55 +12974,55 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>FIRE.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C465" s="2" t="n">
-        <v>22.32</v>
+        <v>22.86</v>
       </c>
       <c r="D465" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E465" s="3" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="F465" s="3" t="n">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="G465" s="3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>FIRE.JK</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C466" s="2" t="n">
-        <v>22.86</v>
+        <v>22.32</v>
       </c>
       <c r="D466" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E466" s="3" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="F466" s="3" t="n">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="G466" s="3" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="467">
@@ -13223,55 +13217,55 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>BRNA.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C474" s="2" t="n">
-        <v>15.5</v>
+        <v>17.44</v>
       </c>
       <c r="D474" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E474" s="3" t="n">
-        <v>660</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F474" s="3" t="n">
-        <v>745</v>
+        <v>101</v>
       </c>
       <c r="G474" s="3" t="n">
-        <v>690</v>
+        <v>92</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>BRNA.JK</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C475" s="2" t="n">
-        <v>17.44</v>
+        <v>15.5</v>
       </c>
       <c r="D475" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E475" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>660</v>
       </c>
       <c r="F475" s="3" t="n">
-        <v>101</v>
+        <v>745</v>
       </c>
       <c r="G475" s="3" t="n">
-        <v>92</v>
+        <v>690</v>
       </c>
     </row>
     <row r="476">
@@ -13480,9 +13474,7 @@
       <c r="D483" s="2" t="n">
         <v>6.86</v>
       </c>
-      <c r="E483" s="3" t="n">
-        <v>103</v>
-      </c>
+      <c r="E483" s="3" t="inlineStr"/>
       <c r="F483" s="3" t="n">
         <v>115</v>
       </c>
@@ -13601,109 +13593,109 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C488" s="2" t="n">
-        <v>25.84</v>
+        <v>20.73</v>
       </c>
       <c r="D488" s="2" t="n">
         <v>6.74</v>
       </c>
       <c r="E488" s="3" t="n">
-        <v>91</v>
+        <v>396</v>
       </c>
       <c r="F488" s="3" t="n">
-        <v>112</v>
+        <v>466</v>
       </c>
       <c r="G488" s="3" t="n">
-        <v>95</v>
+        <v>412</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C489" s="2" t="n">
-        <v>20.73</v>
+        <v>25.84</v>
       </c>
       <c r="D489" s="2" t="n">
         <v>6.74</v>
       </c>
       <c r="E489" s="3" t="n">
-        <v>396</v>
+        <v>91</v>
       </c>
       <c r="F489" s="3" t="n">
-        <v>466</v>
+        <v>112</v>
       </c>
       <c r="G489" s="3" t="n">
-        <v>412</v>
+        <v>95</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>ADMG.JK</t>
+          <t>MDIA.JK</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C490" s="2" t="n">
-        <v>15.67</v>
+        <v>11.76</v>
       </c>
       <c r="D490" s="2" t="n">
         <v>6.72</v>
       </c>
       <c r="E490" s="3" t="n">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="F490" s="3" t="n">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="G490" s="3" t="n">
-        <v>286</v>
+        <v>127</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>MDIA.JK</t>
+          <t>ADMG.JK</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C491" s="2" t="n">
-        <v>11.76</v>
+        <v>15.67</v>
       </c>
       <c r="D491" s="2" t="n">
         <v>6.72</v>
       </c>
       <c r="E491" s="3" t="n">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="F491" s="3" t="n">
-        <v>133</v>
+        <v>310</v>
       </c>
       <c r="G491" s="3" t="n">
-        <v>127</v>
+        <v>286</v>
       </c>
     </row>
     <row r="492">
@@ -13763,55 +13755,55 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>PTSN.JK</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C494" s="2" t="n">
-        <v>23.33</v>
+        <v>11.11</v>
       </c>
       <c r="D494" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E494" s="3" t="n">
-        <v>119</v>
+        <v>452</v>
       </c>
       <c r="F494" s="3" t="n">
-        <v>148</v>
+        <v>500</v>
       </c>
       <c r="G494" s="3" t="n">
-        <v>128</v>
+        <v>480</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>PTSN.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C495" s="2" t="n">
-        <v>11.11</v>
+        <v>23.33</v>
       </c>
       <c r="D495" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E495" s="3" t="n">
-        <v>452</v>
+        <v>119</v>
       </c>
       <c r="F495" s="3" t="n">
-        <v>500</v>
+        <v>148</v>
       </c>
       <c r="G495" s="3" t="n">
-        <v>480</v>
+        <v>128</v>
       </c>
     </row>
     <row r="496">
@@ -13871,55 +13863,55 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>NAIK.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C498" s="2" t="n">
-        <v>11.96</v>
+        <v>23.29</v>
       </c>
       <c r="D498" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E498" s="3" t="n">
-        <v>92</v>
+        <v>3000</v>
       </c>
       <c r="F498" s="3" t="n">
-        <v>103</v>
+        <v>3970</v>
       </c>
       <c r="G498" s="3" t="n">
-        <v>98</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>NAIK.JK</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C499" s="2" t="n">
-        <v>23.29</v>
+        <v>11.96</v>
       </c>
       <c r="D499" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E499" s="3" t="n">
-        <v>3000</v>
+        <v>92</v>
       </c>
       <c r="F499" s="3" t="n">
-        <v>3970</v>
+        <v>103</v>
       </c>
       <c r="G499" s="3" t="n">
-        <v>3430</v>
+        <v>98</v>
       </c>
     </row>
     <row r="500">
@@ -14087,25 +14079,25 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C506" s="2" t="n">
-        <v>11.9</v>
+        <v>17.46</v>
       </c>
       <c r="D506" s="2" t="n">
         <v>6.35</v>
       </c>
       <c r="E506" s="3" t="n">
-        <v>127</v>
+        <v>127.4960645988806</v>
       </c>
       <c r="F506" s="3" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G506" s="3" t="n">
         <v>134</v>
@@ -14114,25 +14106,25 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C507" s="2" t="n">
-        <v>17.46</v>
+        <v>11.9</v>
       </c>
       <c r="D507" s="2" t="n">
         <v>6.35</v>
       </c>
       <c r="E507" s="3" t="n">
-        <v>127.4960645988806</v>
+        <v>127</v>
       </c>
       <c r="F507" s="3" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G507" s="3" t="n">
         <v>134</v>
@@ -14195,52 +14187,52 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C510" s="2" t="n">
-        <v>10.94</v>
+        <v>12.5</v>
       </c>
       <c r="D510" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E510" s="3" t="n">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="F510" s="3" t="n">
-        <v>71</v>
+        <v>252</v>
       </c>
       <c r="G510" s="3" t="n">
-        <v>68</v>
+        <v>238</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C511" s="2" t="n">
-        <v>25</v>
+        <v>10.94</v>
       </c>
       <c r="D511" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E511" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F511" s="3" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G511" s="3" t="n">
         <v>68</v>
@@ -14249,28 +14241,28 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C512" s="2" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="D512" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E512" s="3" t="n">
-        <v>236</v>
+        <v>66</v>
       </c>
       <c r="F512" s="3" t="n">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="G512" s="3" t="n">
-        <v>238</v>
+        <v>68</v>
       </c>
     </row>
     <row r="513">
@@ -14519,55 +14511,53 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C522" s="2" t="n">
-        <v>12.03</v>
+        <v>10.53</v>
       </c>
       <c r="D522" s="2" t="n">
         <v>6.02</v>
       </c>
       <c r="E522" s="3" t="n">
-        <v>268</v>
+        <v>133</v>
       </c>
       <c r="F522" s="3" t="n">
-        <v>298</v>
+        <v>147</v>
       </c>
       <c r="G522" s="3" t="n">
-        <v>282</v>
+        <v>141</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C523" s="2" t="n">
-        <v>10.53</v>
+        <v>12.03</v>
       </c>
       <c r="D523" s="2" t="n">
         <v>6.02</v>
       </c>
-      <c r="E523" s="3" t="n">
-        <v>133</v>
-      </c>
+      <c r="E523" s="3" t="inlineStr"/>
       <c r="F523" s="3" t="n">
-        <v>147</v>
+        <v>298</v>
       </c>
       <c r="G523" s="3" t="n">
-        <v>141</v>
+        <v>282</v>
       </c>
     </row>
     <row r="524">
@@ -14681,55 +14671,55 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>SMAR.JK</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C528" s="2" t="n">
-        <v>15.69</v>
+        <v>15.88</v>
       </c>
       <c r="D528" s="2" t="n">
         <v>5.88</v>
       </c>
       <c r="E528" s="3" t="n">
-        <v>103</v>
+        <v>8450</v>
       </c>
       <c r="F528" s="3" t="n">
-        <v>118</v>
+        <v>9850</v>
       </c>
       <c r="G528" s="3" t="n">
-        <v>108</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>SMAR.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C529" s="2" t="n">
-        <v>15.88</v>
+        <v>15.69</v>
       </c>
       <c r="D529" s="2" t="n">
         <v>5.88</v>
       </c>
       <c r="E529" s="3" t="n">
-        <v>8450</v>
+        <v>103</v>
       </c>
       <c r="F529" s="3" t="n">
-        <v>9850</v>
+        <v>118</v>
       </c>
       <c r="G529" s="3" t="n">
-        <v>9000</v>
+        <v>108</v>
       </c>
     </row>
     <row r="530">
@@ -14843,28 +14833,28 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>KOPI.JK</t>
+          <t>SEMA.JK</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C534" s="2" t="n">
-        <v>20.19</v>
+        <v>15.38</v>
       </c>
       <c r="D534" s="2" t="n">
         <v>5.77</v>
       </c>
       <c r="E534" s="3" t="n">
-        <v>210</v>
+        <v>105</v>
       </c>
       <c r="F534" s="3" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="G534" s="3" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
     </row>
     <row r="535">
@@ -14897,28 +14887,28 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>SEMA.JK</t>
+          <t>KOPI.JK</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C536" s="2" t="n">
-        <v>15.38</v>
+        <v>20.19</v>
       </c>
       <c r="D536" s="2" t="n">
         <v>5.77</v>
       </c>
       <c r="E536" s="3" t="n">
-        <v>105</v>
+        <v>210</v>
       </c>
       <c r="F536" s="3" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="G536" s="3" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
     </row>
     <row r="537">
@@ -15005,79 +14995,79 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C540" s="2" t="n">
-        <v>15.43</v>
+        <v>13.33</v>
       </c>
       <c r="D540" s="2" t="n">
         <v>5.71</v>
       </c>
       <c r="E540" s="3" t="n">
-        <v>360</v>
+        <v>1055</v>
       </c>
       <c r="F540" s="3" t="n">
-        <v>404</v>
+        <v>1190</v>
       </c>
       <c r="G540" s="3" t="n">
-        <v>370</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>VICI.JK</t>
+          <t>GGRP.JK</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C541" s="2" t="n">
-        <v>13.33</v>
+        <v>10.29</v>
       </c>
       <c r="D541" s="2" t="n">
         <v>5.71</v>
       </c>
       <c r="E541" s="3" t="n">
-        <v>1055</v>
+        <v>350</v>
       </c>
       <c r="F541" s="3" t="n">
-        <v>1190</v>
+        <v>386</v>
       </c>
       <c r="G541" s="3" t="n">
-        <v>1110</v>
+        <v>370</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>GGRP.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C542" s="2" t="n">
-        <v>10.29</v>
+        <v>15.43</v>
       </c>
       <c r="D542" s="2" t="n">
         <v>5.71</v>
       </c>
       <c r="E542" s="3" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="F542" s="3" t="n">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="G542" s="3" t="n">
         <v>370</v>
@@ -15221,109 +15211,109 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>KOKA.JK</t>
+          <t>SWID.JK</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C548" s="2" t="n">
-        <v>12.15</v>
+        <v>17.76</v>
       </c>
       <c r="D548" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E548" s="3" t="n">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="F548" s="3" t="n">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="G548" s="3" t="n">
-        <v>226</v>
+        <v>113</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>SWID.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C549" s="2" t="n">
-        <v>17.76</v>
+        <v>12.15</v>
       </c>
       <c r="D549" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E549" s="3" t="n">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="F549" s="3" t="n">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="G549" s="3" t="n">
-        <v>113</v>
+        <v>226</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>SOTS.JK</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C550" s="2" t="n">
-        <v>15.87</v>
+        <v>17.46</v>
       </c>
       <c r="D550" s="2" t="n">
         <v>5.56</v>
       </c>
       <c r="E550" s="3" t="n">
-        <v>133</v>
+        <v>645</v>
       </c>
       <c r="F550" s="3" t="n">
-        <v>146</v>
+        <v>740</v>
       </c>
       <c r="G550" s="3" t="n">
-        <v>133</v>
+        <v>665</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>SOTS.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C551" s="2" t="n">
-        <v>17.46</v>
+        <v>15.87</v>
       </c>
       <c r="D551" s="2" t="n">
         <v>5.56</v>
       </c>
       <c r="E551" s="3" t="n">
-        <v>645</v>
+        <v>133</v>
       </c>
       <c r="F551" s="3" t="n">
-        <v>740</v>
+        <v>146</v>
       </c>
       <c r="G551" s="3" t="n">
-        <v>665</v>
+        <v>133</v>
       </c>
     </row>
     <row r="552">
@@ -15491,82 +15481,82 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>FITT.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C558" s="2" t="n">
-        <v>12.44</v>
+        <v>11.58</v>
       </c>
       <c r="D558" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E558" s="3" t="n">
-        <v>424</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F558" s="3" t="n">
-        <v>470</v>
+        <v>106</v>
       </c>
       <c r="G558" s="3" t="n">
-        <v>440</v>
+        <v>100</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>PPRI.JK</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C559" s="2" t="n">
-        <v>11.58</v>
+        <v>22.81</v>
       </c>
       <c r="D559" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E559" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>171</v>
       </c>
       <c r="F559" s="3" t="n">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="G559" s="3" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>PPRI.JK</t>
+          <t>FITT.JK</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C560" s="2" t="n">
-        <v>22.81</v>
+        <v>12.44</v>
       </c>
       <c r="D560" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E560" s="3" t="n">
-        <v>171</v>
+        <v>424</v>
       </c>
       <c r="F560" s="3" t="n">
-        <v>210</v>
+        <v>470</v>
       </c>
       <c r="G560" s="3" t="n">
-        <v>180</v>
+        <v>440</v>
       </c>
     </row>
     <row r="561">
@@ -15653,55 +15643,55 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SEMA.JK</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C564" s="2" t="n">
-        <v>14.36</v>
+        <v>20.51</v>
       </c>
       <c r="D564" s="2" t="n">
         <v>5.13</v>
       </c>
       <c r="E564" s="3" t="n">
-        <v>390</v>
+        <v>236</v>
       </c>
       <c r="F564" s="3" t="n">
-        <v>446</v>
+        <v>282</v>
       </c>
       <c r="G564" s="3" t="n">
-        <v>410</v>
+        <v>246</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>SEMA.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C565" s="2" t="n">
-        <v>20.51</v>
+        <v>14.36</v>
       </c>
       <c r="D565" s="2" t="n">
         <v>5.13</v>
       </c>
       <c r="E565" s="3" t="n">
-        <v>236</v>
+        <v>390</v>
       </c>
       <c r="F565" s="3" t="n">
-        <v>282</v>
+        <v>446</v>
       </c>
       <c r="G565" s="3" t="n">
-        <v>246</v>
+        <v>410</v>
       </c>
     </row>
     <row r="566">
@@ -15734,55 +15724,55 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C567" s="2" t="n">
-        <v>16.55</v>
+        <v>17.65</v>
       </c>
       <c r="D567" s="2" t="n">
         <v>5.04</v>
       </c>
       <c r="E567" s="3" t="n">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="F567" s="3" t="n">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="G567" s="3" t="n">
-        <v>292</v>
+        <v>250</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C568" s="2" t="n">
-        <v>17.65</v>
+        <v>16.55</v>
       </c>
       <c r="D568" s="2" t="n">
         <v>5.04</v>
       </c>
       <c r="E568" s="3" t="n">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="F568" s="3" t="n">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="G568" s="3" t="n">
-        <v>250</v>
+        <v>292</v>
       </c>
     </row>
     <row r="569">
@@ -15869,55 +15859,55 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>MGNA.JK</t>
+          <t>BBSS.JK</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C572" s="2" t="n">
-        <v>10.89</v>
+        <v>15.84</v>
       </c>
       <c r="D572" s="2" t="n">
         <v>4.95</v>
       </c>
       <c r="E572" s="3" t="n">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="F572" s="3" t="n">
-        <v>224</v>
+        <v>117</v>
       </c>
       <c r="G572" s="3" t="n">
-        <v>212</v>
+        <v>106</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>BBSS.JK</t>
+          <t>MGNA.JK</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C573" s="2" t="n">
-        <v>15.84</v>
+        <v>10.89</v>
       </c>
       <c r="D573" s="2" t="n">
         <v>4.95</v>
       </c>
       <c r="E573" s="3" t="n">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="F573" s="3" t="n">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="G573" s="3" t="n">
-        <v>106</v>
+        <v>212</v>
       </c>
     </row>
     <row r="574">
@@ -15950,55 +15940,55 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>BWPT.JK</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C575" s="2" t="n">
-        <v>15.69</v>
+        <v>10.78</v>
       </c>
       <c r="D575" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E575" s="3" t="n">
-        <v>230</v>
+        <v>104</v>
       </c>
       <c r="F575" s="3" t="n">
-        <v>236</v>
+        <v>113</v>
       </c>
       <c r="G575" s="3" t="n">
-        <v>214</v>
+        <v>107</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>BWPT.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C576" s="2" t="n">
-        <v>10.78</v>
+        <v>15.69</v>
       </c>
       <c r="D576" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E576" s="3" t="n">
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="F576" s="3" t="n">
-        <v>113</v>
+        <v>236</v>
       </c>
       <c r="G576" s="3" t="n">
-        <v>107</v>
+        <v>214</v>
       </c>
     </row>
     <row r="577">
@@ -16112,55 +16102,55 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>PURA.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C581" s="2" t="n">
-        <v>14.29</v>
+        <v>22.22</v>
       </c>
       <c r="D581" s="2" t="n">
         <v>4.76</v>
       </c>
       <c r="E581" s="3" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F581" s="3" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="G581" s="3" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>PURA.JK</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C582" s="2" t="n">
-        <v>22.22</v>
+        <v>14.29</v>
       </c>
       <c r="D582" s="2" t="n">
         <v>4.76</v>
       </c>
       <c r="E582" s="3" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="F582" s="3" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G582" s="3" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
     </row>
     <row r="583">
@@ -16355,25 +16345,25 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C590" s="2" t="n">
-        <v>10.69</v>
+        <v>12.21</v>
       </c>
       <c r="D590" s="2" t="n">
         <v>4.58</v>
       </c>
       <c r="E590" s="3" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F590" s="3" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G590" s="3" t="n">
         <v>274</v>
@@ -16382,25 +16372,25 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C591" s="2" t="n">
-        <v>12.21</v>
+        <v>10.69</v>
       </c>
       <c r="D591" s="2" t="n">
         <v>4.58</v>
       </c>
       <c r="E591" s="3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F591" s="3" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G591" s="3" t="n">
         <v>274</v>
@@ -16517,55 +16507,55 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C596" s="2" t="n">
-        <v>10.53</v>
+        <v>20.49</v>
       </c>
       <c r="D596" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E596" s="3" t="n">
-        <v>266</v>
+        <v>2470</v>
       </c>
       <c r="F596" s="3" t="n">
-        <v>294</v>
+        <v>2940</v>
       </c>
       <c r="G596" s="3" t="n">
-        <v>278</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C597" s="2" t="n">
-        <v>20.49</v>
+        <v>10.53</v>
       </c>
       <c r="D597" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E597" s="3" t="n">
-        <v>2470</v>
+        <v>266</v>
       </c>
       <c r="F597" s="3" t="n">
-        <v>2940</v>
+        <v>294</v>
       </c>
       <c r="G597" s="3" t="n">
-        <v>2550</v>
+        <v>278</v>
       </c>
     </row>
     <row r="598">
@@ -16625,55 +16615,55 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>KKES.JK</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C600" s="2" t="n">
-        <v>13.33</v>
+        <v>32.22</v>
       </c>
       <c r="D600" s="2" t="n">
         <v>4.44</v>
       </c>
       <c r="E600" s="3" t="n">
-        <v>270</v>
+        <v>86</v>
       </c>
       <c r="F600" s="3" t="n">
-        <v>306</v>
+        <v>119</v>
       </c>
       <c r="G600" s="3" t="n">
-        <v>282</v>
+        <v>94</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>KKES.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C601" s="2" t="n">
-        <v>32.22</v>
+        <v>13.33</v>
       </c>
       <c r="D601" s="2" t="n">
         <v>4.44</v>
       </c>
       <c r="E601" s="3" t="n">
-        <v>86</v>
+        <v>270</v>
       </c>
       <c r="F601" s="3" t="n">
-        <v>119</v>
+        <v>306</v>
       </c>
       <c r="G601" s="3" t="n">
-        <v>94</v>
+        <v>282</v>
       </c>
     </row>
     <row r="602">
@@ -16733,55 +16723,55 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>ARII.JK</t>
+          <t>POLI.JK</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C604" s="2" t="n">
-        <v>10.06</v>
+        <v>20.88</v>
       </c>
       <c r="D604" s="2" t="n">
         <v>4.4</v>
       </c>
       <c r="E604" s="3" t="n">
-        <v>324</v>
+        <v>895</v>
       </c>
       <c r="F604" s="3" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="G604" s="3" t="n">
-        <v>332</v>
+        <v>950</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>POLI.JK</t>
+          <t>ARII.JK</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C605" s="2" t="n">
-        <v>20.88</v>
+        <v>10.06</v>
       </c>
       <c r="D605" s="2" t="n">
         <v>4.4</v>
       </c>
       <c r="E605" s="3" t="n">
-        <v>895</v>
+        <v>324</v>
       </c>
       <c r="F605" s="3" t="n">
-        <v>1100</v>
+        <v>350</v>
       </c>
       <c r="G605" s="3" t="n">
-        <v>950</v>
+        <v>332</v>
       </c>
     </row>
     <row r="606">
@@ -16814,55 +16804,55 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>MBTO.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C607" s="2" t="n">
-        <v>12.17</v>
+        <v>13.04</v>
       </c>
       <c r="D607" s="2" t="n">
         <v>4.35</v>
       </c>
       <c r="E607" s="3" t="n">
-        <v>115</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F607" s="3" t="n">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="G607" s="3" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>MBTO.JK</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C608" s="2" t="n">
-        <v>13.04</v>
+        <v>12.17</v>
       </c>
       <c r="D608" s="2" t="n">
         <v>4.35</v>
       </c>
       <c r="E608" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>115</v>
       </c>
       <c r="F608" s="3" t="n">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="G608" s="3" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="609">
@@ -16895,79 +16885,79 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C610" s="2" t="n">
-        <v>11.66</v>
+        <v>12.86</v>
       </c>
       <c r="D610" s="2" t="n">
         <v>4.29</v>
       </c>
       <c r="E610" s="3" t="n">
-        <v>815</v>
+        <v>71</v>
       </c>
       <c r="F610" s="3" t="n">
-        <v>910</v>
+        <v>79</v>
       </c>
       <c r="G610" s="3" t="n">
-        <v>850</v>
+        <v>73</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C611" s="2" t="n">
-        <v>12.86</v>
+        <v>11.66</v>
       </c>
       <c r="D611" s="2" t="n">
         <v>4.29</v>
       </c>
       <c r="E611" s="3" t="n">
-        <v>71</v>
+        <v>815</v>
       </c>
       <c r="F611" s="3" t="n">
-        <v>79</v>
+        <v>910</v>
       </c>
       <c r="G611" s="3" t="n">
-        <v>73</v>
+        <v>850</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>SEMA.JK</t>
+          <t>OPMS.JK</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C612" s="2" t="n">
-        <v>14.53</v>
+        <v>19.66</v>
       </c>
       <c r="D612" s="2" t="n">
         <v>4.27</v>
       </c>
       <c r="E612" s="3" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F612" s="3" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G612" s="3" t="n">
         <v>122</v>
@@ -16976,25 +16966,25 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>OPMS.JK</t>
+          <t>SEMA.JK</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C613" s="2" t="n">
-        <v>19.66</v>
+        <v>14.53</v>
       </c>
       <c r="D613" s="2" t="n">
         <v>4.27</v>
       </c>
       <c r="E613" s="3" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F613" s="3" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G613" s="3" t="n">
         <v>122</v>
@@ -17273,55 +17263,55 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>MPRO.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C624" s="2" t="n">
-        <v>20</v>
+        <v>21.78</v>
       </c>
       <c r="D624" s="2" t="n">
         <v>3.96</v>
       </c>
       <c r="E624" s="3" t="n">
-        <v>16650</v>
+        <v>102</v>
       </c>
       <c r="F624" s="3" t="n">
-        <v>16650</v>
+        <v>123</v>
       </c>
       <c r="G624" s="3" t="n">
-        <v>14425</v>
+        <v>105</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>MPRO.JK</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C625" s="2" t="n">
-        <v>21.78</v>
+        <v>20</v>
       </c>
       <c r="D625" s="2" t="n">
         <v>3.96</v>
       </c>
       <c r="E625" s="3" t="n">
-        <v>102</v>
+        <v>16650</v>
       </c>
       <c r="F625" s="3" t="n">
-        <v>123</v>
+        <v>16650</v>
       </c>
       <c r="G625" s="3" t="n">
-        <v>105</v>
+        <v>14425</v>
       </c>
     </row>
     <row r="626">
@@ -17705,55 +17695,55 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>MPIX.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C640" s="2" t="n">
-        <v>12.07</v>
+        <v>15.52</v>
       </c>
       <c r="D640" s="2" t="n">
         <v>3.45</v>
       </c>
       <c r="E640" s="3" t="n">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="F640" s="3" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="G640" s="3" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>MPIX.JK</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C641" s="2" t="n">
-        <v>15.52</v>
+        <v>12.07</v>
       </c>
       <c r="D641" s="2" t="n">
         <v>3.45</v>
       </c>
       <c r="E641" s="3" t="n">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="F641" s="3" t="n">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="G641" s="3" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="642">
@@ -17786,55 +17776,55 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>GUNA.JK</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C643" s="2" t="n">
-        <v>12.45</v>
+        <v>10.23</v>
       </c>
       <c r="D643" s="2" t="n">
         <v>3.41</v>
       </c>
       <c r="E643" s="3" t="n">
-        <v>545</v>
+        <v>178</v>
       </c>
       <c r="F643" s="3" t="n">
-        <v>560</v>
+        <v>194</v>
       </c>
       <c r="G643" s="3" t="n">
-        <v>515</v>
+        <v>182</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>GUNA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C644" s="2" t="n">
-        <v>10.23</v>
+        <v>12.45</v>
       </c>
       <c r="D644" s="2" t="n">
         <v>3.41</v>
       </c>
       <c r="E644" s="3" t="n">
-        <v>178</v>
+        <v>545</v>
       </c>
       <c r="F644" s="3" t="n">
-        <v>194</v>
+        <v>560</v>
       </c>
       <c r="G644" s="3" t="n">
-        <v>182</v>
+        <v>515</v>
       </c>
     </row>
     <row r="645">
@@ -17894,55 +17884,55 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>TNCA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C647" s="2" t="n">
-        <v>11.24</v>
+        <v>17.51</v>
       </c>
       <c r="D647" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E647" s="3" t="n">
-        <v>180</v>
+        <v>3180</v>
       </c>
       <c r="F647" s="3" t="n">
-        <v>198</v>
+        <v>3490</v>
       </c>
       <c r="G647" s="3" t="n">
-        <v>184</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>TNCA.JK</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C648" s="2" t="n">
-        <v>17.51</v>
+        <v>11.24</v>
       </c>
       <c r="D648" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E648" s="3" t="n">
-        <v>3180</v>
+        <v>180</v>
       </c>
       <c r="F648" s="3" t="n">
-        <v>3490</v>
+        <v>198</v>
       </c>
       <c r="G648" s="3" t="n">
-        <v>3070</v>
+        <v>184</v>
       </c>
     </row>
     <row r="649">
@@ -18164,109 +18154,109 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C657" s="2" t="n">
-        <v>23.66</v>
+        <v>15.48</v>
       </c>
       <c r="D657" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E657" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>850</v>
       </c>
       <c r="F657" s="3" t="n">
-        <v>460</v>
+        <v>895</v>
       </c>
       <c r="G657" s="3" t="n">
-        <v>384</v>
+        <v>800</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C658" s="2" t="n">
-        <v>11.83</v>
+        <v>23.66</v>
       </c>
       <c r="D658" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E658" s="3" t="n">
-        <v>95</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F658" s="3" t="n">
-        <v>104</v>
+        <v>460</v>
       </c>
       <c r="G658" s="3" t="n">
-        <v>96</v>
+        <v>384</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C659" s="2" t="n">
-        <v>15.48</v>
+        <v>19.35</v>
       </c>
       <c r="D659" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E659" s="3" t="n">
-        <v>850</v>
+        <v>70</v>
       </c>
       <c r="F659" s="3" t="n">
-        <v>895</v>
+        <v>74</v>
       </c>
       <c r="G659" s="3" t="n">
-        <v>800</v>
+        <v>64</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C660" s="2" t="n">
-        <v>19.35</v>
+        <v>11.83</v>
       </c>
       <c r="D660" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E660" s="3" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F660" s="3" t="n">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="G660" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
     </row>
     <row r="661">
@@ -18326,25 +18316,25 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>VRNA.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C663" s="2" t="n">
-        <v>26.26</v>
+        <v>34.34</v>
       </c>
       <c r="D663" s="2" t="n">
         <v>3.03</v>
       </c>
       <c r="E663" s="3" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F663" s="3" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G663" s="3" t="n">
         <v>102</v>
@@ -18353,25 +18343,25 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>VRNA.JK</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C664" s="2" t="n">
-        <v>34.34</v>
+        <v>26.26</v>
       </c>
       <c r="D664" s="2" t="n">
         <v>3.03</v>
       </c>
       <c r="E664" s="3" t="n">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="F664" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G664" s="3" t="n">
         <v>102</v>
@@ -18407,55 +18397,55 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C666" s="2" t="n">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
       <c r="D666" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E666" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="F666" s="3" t="n">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="G666" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C667" s="2" t="n">
-        <v>14.71</v>
+        <v>17.65</v>
       </c>
       <c r="D667" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E667" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="F667" s="3" t="n">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="G667" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
     </row>
     <row r="668">
@@ -18623,55 +18613,55 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C674" s="2" t="n">
-        <v>12.15</v>
+        <v>11.89</v>
       </c>
       <c r="D674" s="2" t="n">
         <v>2.8</v>
       </c>
       <c r="E674" s="3" t="n">
-        <v>109</v>
+        <v>286.4117805325255</v>
       </c>
       <c r="F674" s="3" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="G674" s="3" t="n">
-        <v>110</v>
+        <v>294</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C675" s="2" t="n">
-        <v>11.89</v>
+        <v>12.15</v>
       </c>
       <c r="D675" s="2" t="n">
         <v>2.8</v>
       </c>
       <c r="E675" s="3" t="n">
-        <v>286.4117805325255</v>
+        <v>109</v>
       </c>
       <c r="F675" s="3" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="G675" s="3" t="n">
-        <v>294</v>
+        <v>110</v>
       </c>
     </row>
     <row r="676">
@@ -18812,55 +18802,55 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C681" s="2" t="n">
-        <v>10.39</v>
+        <v>14.58</v>
       </c>
       <c r="D681" s="2" t="n">
         <v>2.6</v>
       </c>
       <c r="E681" s="3" t="n">
-        <v>72.38636016845703</v>
+        <v>1065</v>
       </c>
       <c r="F681" s="3" t="n">
-        <v>85</v>
+        <v>1100</v>
       </c>
       <c r="G681" s="3" t="n">
-        <v>79</v>
+        <v>985</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C682" s="2" t="n">
-        <v>14.58</v>
+        <v>10.39</v>
       </c>
       <c r="D682" s="2" t="n">
         <v>2.6</v>
       </c>
       <c r="E682" s="3" t="n">
-        <v>1065</v>
+        <v>72.38636016845703</v>
       </c>
       <c r="F682" s="3" t="n">
-        <v>1100</v>
+        <v>85</v>
       </c>
       <c r="G682" s="3" t="n">
-        <v>985</v>
+        <v>79</v>
       </c>
     </row>
     <row r="683">
@@ -18920,55 +18910,55 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>LAND.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C685" s="2" t="n">
-        <v>10.13</v>
+        <v>25</v>
       </c>
       <c r="D685" s="2" t="n">
         <v>2.53</v>
       </c>
       <c r="E685" s="3" t="n">
-        <v>78</v>
+        <v>1975</v>
       </c>
       <c r="F685" s="3" t="n">
-        <v>87</v>
+        <v>1975</v>
       </c>
       <c r="G685" s="3" t="n">
-        <v>81</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>LAND.JK</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C686" s="2" t="n">
-        <v>25</v>
+        <v>10.13</v>
       </c>
       <c r="D686" s="2" t="n">
         <v>2.53</v>
       </c>
       <c r="E686" s="3" t="n">
-        <v>1975</v>
+        <v>78</v>
       </c>
       <c r="F686" s="3" t="n">
-        <v>1975</v>
+        <v>87</v>
       </c>
       <c r="G686" s="3" t="n">
-        <v>1620</v>
+        <v>81</v>
       </c>
     </row>
     <row r="687">
@@ -19163,109 +19153,109 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C694" s="2" t="n">
-        <v>20.69</v>
+        <v>15.21</v>
       </c>
       <c r="D694" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="E694" s="3" t="n">
-        <v>99</v>
+        <v>1085</v>
       </c>
       <c r="F694" s="3" t="n">
-        <v>105</v>
+        <v>1250</v>
       </c>
       <c r="G694" s="3" t="n">
-        <v>89</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C695" s="2" t="n">
-        <v>15.21</v>
+        <v>20.69</v>
       </c>
       <c r="D695" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="E695" s="3" t="n">
-        <v>1085</v>
+        <v>99</v>
       </c>
       <c r="F695" s="3" t="n">
-        <v>1250</v>
+        <v>105</v>
       </c>
       <c r="G695" s="3" t="n">
-        <v>1110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>INAI.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C696" s="2" t="n">
-        <v>13.48</v>
+        <v>12.36</v>
       </c>
       <c r="D696" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E696" s="3" t="n">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F696" s="3" t="n">
-        <v>202</v>
+        <v>100</v>
       </c>
       <c r="G696" s="3" t="n">
-        <v>182</v>
+        <v>91</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>INAI.JK</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C697" s="2" t="n">
-        <v>12.36</v>
+        <v>13.48</v>
       </c>
       <c r="D697" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E697" s="3" t="n">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="F697" s="3" t="n">
-        <v>100</v>
+        <v>202</v>
       </c>
       <c r="G697" s="3" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
     </row>
     <row r="698">
@@ -20052,55 +20042,55 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>TFAS.JK</t>
+          <t>MCAS.JK</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C727" s="2" t="n">
-        <v>11.79</v>
+        <v>16.92</v>
       </c>
       <c r="D727" s="2" t="n">
         <v>1.54</v>
       </c>
       <c r="E727" s="3" t="n">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="F727" s="3" t="n">
-        <v>218</v>
+        <v>304</v>
       </c>
       <c r="G727" s="3" t="n">
-        <v>198</v>
+        <v>264</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>MCAS.JK</t>
+          <t>TFAS.JK</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C728" s="2" t="n">
-        <v>16.92</v>
+        <v>11.79</v>
       </c>
       <c r="D728" s="2" t="n">
         <v>1.54</v>
       </c>
       <c r="E728" s="3" t="n">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="F728" s="3" t="n">
-        <v>304</v>
+        <v>218</v>
       </c>
       <c r="G728" s="3" t="n">
-        <v>264</v>
+        <v>198</v>
       </c>
     </row>
     <row r="729">
@@ -20187,55 +20177,55 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>PYFA.JK</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C732" s="2" t="n">
-        <v>24.4</v>
+        <v>13.77</v>
       </c>
       <c r="D732" s="2" t="n">
         <v>1.45</v>
       </c>
       <c r="E732" s="3" t="n">
-        <v>480</v>
+        <v>296</v>
       </c>
       <c r="F732" s="3" t="n">
-        <v>515</v>
+        <v>314</v>
       </c>
       <c r="G732" s="3" t="n">
-        <v>420</v>
+        <v>280</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>PYFA.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C733" s="2" t="n">
-        <v>13.77</v>
+        <v>24.4</v>
       </c>
       <c r="D733" s="2" t="n">
         <v>1.45</v>
       </c>
       <c r="E733" s="3" t="n">
-        <v>296</v>
+        <v>480</v>
       </c>
       <c r="F733" s="3" t="n">
-        <v>314</v>
+        <v>515</v>
       </c>
       <c r="G733" s="3" t="n">
-        <v>280</v>
+        <v>420</v>
       </c>
     </row>
     <row r="734">
@@ -20376,55 +20366,55 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>LPPS.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C739" s="2" t="n">
-        <v>10.13</v>
+        <v>15.94</v>
       </c>
       <c r="D739" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="E739" s="3" t="n">
-        <v>79</v>
+        <v>13800</v>
       </c>
       <c r="F739" s="3" t="n">
-        <v>87</v>
+        <v>16000</v>
       </c>
       <c r="G739" s="3" t="n">
-        <v>80</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>LPPS.JK</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C740" s="2" t="n">
-        <v>15.94</v>
+        <v>10.13</v>
       </c>
       <c r="D740" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="E740" s="3" t="n">
-        <v>13800</v>
+        <v>79</v>
       </c>
       <c r="F740" s="3" t="n">
-        <v>16000</v>
+        <v>87</v>
       </c>
       <c r="G740" s="3" t="n">
-        <v>13975</v>
+        <v>80</v>
       </c>
     </row>
     <row r="741">
@@ -20727,82 +20717,82 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>PORT.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C752" s="2" t="n">
-        <v>16.38</v>
+        <v>20</v>
       </c>
       <c r="D752" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E752" s="3" t="n">
-        <v>1015</v>
+        <v>406</v>
       </c>
       <c r="F752" s="3" t="n">
-        <v>1030</v>
+        <v>432</v>
       </c>
       <c r="G752" s="3" t="n">
-        <v>890</v>
+        <v>362</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C753" s="2" t="n">
-        <v>20</v>
+        <v>10.17</v>
       </c>
       <c r="D753" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E753" s="3" t="n">
-        <v>406</v>
+        <v>177</v>
       </c>
       <c r="F753" s="3" t="n">
-        <v>432</v>
+        <v>195</v>
       </c>
       <c r="G753" s="3" t="n">
-        <v>362</v>
+        <v>178</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>PORT.JK</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C754" s="2" t="n">
-        <v>10.17</v>
+        <v>16.38</v>
       </c>
       <c r="D754" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E754" s="3" t="n">
-        <v>177</v>
+        <v>1015</v>
       </c>
       <c r="F754" s="3" t="n">
-        <v>195</v>
+        <v>1030</v>
       </c>
       <c r="G754" s="3" t="n">
-        <v>178</v>
+        <v>890</v>
       </c>
     </row>
     <row r="755">
@@ -20835,55 +20825,55 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C756" s="2" t="n">
-        <v>11.96</v>
+        <v>11.43</v>
       </c>
       <c r="D756" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="E756" s="3" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F756" s="3" t="n">
         <v>468</v>
       </c>
       <c r="G756" s="3" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C757" s="2" t="n">
-        <v>11.43</v>
+        <v>11.96</v>
       </c>
       <c r="D757" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="E757" s="3" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F757" s="3" t="n">
         <v>468</v>
       </c>
       <c r="G757" s="3" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="758">
@@ -20916,606 +20906,606 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>MPRO.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C759" s="2" t="n">
-        <v>19.95</v>
+        <v>17.65</v>
       </c>
       <c r="D759" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E759" s="3" t="n">
-        <v>11750</v>
+        <v>181</v>
       </c>
       <c r="F759" s="3" t="n">
-        <v>11875</v>
+        <v>200</v>
       </c>
       <c r="G759" s="3" t="n">
-        <v>9900</v>
+        <v>170</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>PDES.JK</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C760" s="2" t="n">
-        <v>12.87</v>
+        <v>18.01</v>
       </c>
       <c r="D760" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E760" s="3" t="n">
-        <v>93</v>
+        <v>424</v>
       </c>
       <c r="F760" s="3" t="n">
-        <v>114</v>
+        <v>498</v>
       </c>
       <c r="G760" s="3" t="n">
-        <v>101</v>
+        <v>422</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>KREN.JK</t>
+          <t>ISEA.JK</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C761" s="2" t="n">
-        <v>10.53</v>
+        <v>11.25</v>
       </c>
       <c r="D761" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E761" s="3" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="F761" s="3" t="n">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="G761" s="3" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>BTEK.JK</t>
+          <t>AISA.JK</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C762" s="2" t="n">
-        <v>14.29</v>
+        <v>12.9</v>
       </c>
       <c r="D762" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E762" s="3" t="n">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F762" s="3" t="n">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="G762" s="3" t="n">
-        <v>14</v>
+        <v>124</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C763" s="2" t="n">
-        <v>10.26</v>
+        <v>28.48</v>
       </c>
       <c r="D763" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E763" s="3" t="n">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="F763" s="3" t="n">
-        <v>86</v>
+        <v>194</v>
       </c>
       <c r="G763" s="3" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>FISH.JK</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C764" s="2" t="n">
-        <v>27.33</v>
+        <v>13.89</v>
       </c>
       <c r="D764" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E764" s="3" t="n">
-        <v>152</v>
+        <v>760</v>
       </c>
       <c r="F764" s="3" t="n">
-        <v>191</v>
+        <v>820</v>
       </c>
       <c r="G764" s="3" t="n">
-        <v>150</v>
+        <v>720</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>ISEA.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C765" s="2" t="n">
-        <v>11.25</v>
+        <v>12.38</v>
       </c>
       <c r="D765" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E765" s="3" t="n">
-        <v>82</v>
+        <v>91.91489410400391</v>
       </c>
       <c r="F765" s="3" t="n">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="G765" s="3" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>SAFE.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C766" s="2" t="n">
-        <v>12.41</v>
+        <v>12.87</v>
       </c>
       <c r="D766" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E766" s="3" t="n">
-        <v>810</v>
+        <v>93</v>
       </c>
       <c r="F766" s="3" t="n">
-        <v>815</v>
+        <v>114</v>
       </c>
       <c r="G766" s="3" t="n">
-        <v>725</v>
+        <v>101</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>KREN.JK</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C767" s="2" t="n">
-        <v>17.5</v>
+        <v>10.53</v>
       </c>
       <c r="D767" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E767" s="3" t="n">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="F767" s="3" t="n">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="G767" s="3" t="n">
-        <v>160</v>
+        <v>19</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>FISH.JK</t>
+          <t>MPRO.JK</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C768" s="2" t="n">
-        <v>13.89</v>
+        <v>19.95</v>
       </c>
       <c r="D768" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E768" s="3" t="n">
-        <v>760</v>
+        <v>11750</v>
       </c>
       <c r="F768" s="3" t="n">
-        <v>820</v>
+        <v>11875</v>
       </c>
       <c r="G768" s="3" t="n">
-        <v>720</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C769" s="2" t="n">
-        <v>10.61</v>
+        <v>10.26</v>
       </c>
       <c r="D769" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E769" s="3" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F769" s="3" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="G769" s="3" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>TAXI.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C770" s="2" t="n">
-        <v>11.11</v>
+        <v>10.76</v>
       </c>
       <c r="D770" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E770" s="3" t="n">
-        <v>19</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F770" s="3" t="n">
-        <v>20</v>
+        <v>3500</v>
       </c>
       <c r="G770" s="3" t="n">
-        <v>18</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C771" s="2" t="n">
-        <v>12.38</v>
+        <v>10.91</v>
       </c>
       <c r="D771" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E771" s="3" t="n">
-        <v>91.91489410400391</v>
+        <v>165</v>
       </c>
       <c r="F771" s="3" t="n">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="G771" s="3" t="n">
-        <v>105</v>
+        <v>165</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>PDES.JK</t>
+          <t>BEKS.JK</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C772" s="2" t="n">
-        <v>18.01</v>
+        <v>11.11</v>
       </c>
       <c r="D772" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E772" s="3" t="n">
-        <v>424</v>
+        <v>38</v>
       </c>
       <c r="F772" s="3" t="n">
-        <v>498</v>
+        <v>40</v>
       </c>
       <c r="G772" s="3" t="n">
-        <v>422</v>
+        <v>36</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>KREN.JK</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C773" s="2" t="n">
-        <v>28.48</v>
+        <v>26.32</v>
       </c>
       <c r="D773" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E773" s="3" t="n">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="F773" s="3" t="n">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="G773" s="3" t="n">
-        <v>151</v>
+        <v>19</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>AISA.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C774" s="2" t="n">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="D774" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E774" s="3" t="n">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="F774" s="3" t="n">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="G774" s="3" t="n">
-        <v>124</v>
+        <v>66</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>KKES.JK</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C775" s="2" t="n">
-        <v>10.76</v>
+        <v>11.43</v>
       </c>
       <c r="D775" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E775" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>75</v>
       </c>
       <c r="F775" s="3" t="n">
-        <v>3500</v>
+        <v>78</v>
       </c>
       <c r="G775" s="3" t="n">
-        <v>3160</v>
+        <v>70</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>BTEK.JK</t>
+          <t>SAFE.JK</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C776" s="2" t="n">
-        <v>28.57</v>
+        <v>12.41</v>
       </c>
       <c r="D776" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E776" s="3" t="n">
-        <v>17</v>
+        <v>810</v>
       </c>
       <c r="F776" s="3" t="n">
-        <v>18</v>
+        <v>815</v>
       </c>
       <c r="G776" s="3" t="n">
-        <v>14</v>
+        <v>725</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>RELI.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C777" s="2" t="n">
-        <v>14.29</v>
+        <v>12.78</v>
       </c>
       <c r="D777" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E777" s="3" t="n">
-        <v>520</v>
+        <v>2640</v>
       </c>
       <c r="F777" s="3" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="G777" s="3" t="n">
-        <v>525</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C778" s="2" t="n">
-        <v>17.65</v>
+        <v>27.33</v>
       </c>
       <c r="D778" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E778" s="3" t="n">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="F778" s="3" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G778" s="3" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>BTEK.JK</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C779" s="2" t="n">
-        <v>10.91</v>
+        <v>28.57</v>
       </c>
       <c r="D779" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E779" s="3" t="n">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="F779" s="3" t="n">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="G779" s="3" t="n">
-        <v>165</v>
+        <v>14</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>RELI.JK</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C780" s="2" t="n">
-        <v>12.78</v>
+        <v>14.29</v>
       </c>
       <c r="D780" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E780" s="3" t="n">
-        <v>2640</v>
+        <v>520</v>
       </c>
       <c r="F780" s="3" t="n">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="G780" s="3" t="n">
-        <v>2660</v>
+        <v>525</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>BEKS.JK</t>
+          <t>TAXI.JK</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C781" s="2" t="n">
@@ -21525,67 +21515,67 @@
         <v>0</v>
       </c>
       <c r="E781" s="3" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F781" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G781" s="3" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>KKES.JK</t>
+          <t>BTEK.JK</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C782" s="2" t="n">
-        <v>11.43</v>
+        <v>14.29</v>
       </c>
       <c r="D782" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E782" s="3" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="F782" s="3" t="n">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="G782" s="3" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>KREN.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C783" s="2" t="n">
-        <v>26.32</v>
+        <v>17.5</v>
       </c>
       <c r="D783" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E783" s="3" t="n">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="F783" s="3" t="n">
-        <v>24</v>
+        <v>188</v>
       </c>
       <c r="G783" s="3" t="n">
-        <v>19</v>
+        <v>160</v>
       </c>
     </row>
     <row r="784">
@@ -22617,66 +22607,66 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C822" s="2" t="n">
-        <v>15.19</v>
+        <v>19.62</v>
       </c>
       <c r="D822" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E822" s="3" t="n">
-        <v>80</v>
+        <v>910</v>
       </c>
       <c r="F822" s="3" t="n">
-        <v>91</v>
+        <v>945</v>
       </c>
       <c r="G822" s="3" t="n">
-        <v>77</v>
+        <v>770</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C823" s="2" t="n">
-        <v>19.62</v>
+        <v>15.19</v>
       </c>
       <c r="D823" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E823" s="3" t="n">
-        <v>910</v>
+        <v>160</v>
       </c>
       <c r="F823" s="3" t="n">
-        <v>945</v>
+        <v>182</v>
       </c>
       <c r="G823" s="3" t="n">
-        <v>770</v>
+        <v>154</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C824" s="2" t="n">
@@ -22686,13 +22676,13 @@
         <v>-2.53</v>
       </c>
       <c r="E824" s="3" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="F824" s="3" t="n">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="G824" s="3" t="n">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="825">
@@ -22806,55 +22796,55 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>POLA.JK</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C829" s="2" t="n">
-        <v>17.36</v>
+        <v>12.04</v>
       </c>
       <c r="D829" s="2" t="n">
         <v>-2.78</v>
       </c>
       <c r="E829" s="3" t="n">
-        <v>720</v>
+        <v>110</v>
       </c>
       <c r="F829" s="3" t="n">
-        <v>845</v>
+        <v>121</v>
       </c>
       <c r="G829" s="3" t="n">
-        <v>700</v>
+        <v>105</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>POLA.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C830" s="2" t="n">
-        <v>12.04</v>
+        <v>17.36</v>
       </c>
       <c r="D830" s="2" t="n">
         <v>-2.78</v>
       </c>
       <c r="E830" s="3" t="n">
-        <v>110</v>
+        <v>720</v>
       </c>
       <c r="F830" s="3" t="n">
-        <v>121</v>
+        <v>845</v>
       </c>
       <c r="G830" s="3" t="n">
-        <v>105</v>
+        <v>700</v>
       </c>
     </row>
     <row r="831">
@@ -23238,55 +23228,55 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C845" s="2" t="n">
-        <v>18.05</v>
+        <v>19.31</v>
       </c>
       <c r="D845" s="2" t="n">
         <v>-4.14</v>
       </c>
       <c r="E845" s="3" t="n">
-        <v>2700</v>
+        <v>149</v>
       </c>
       <c r="F845" s="3" t="n">
-        <v>3140</v>
+        <v>173</v>
       </c>
       <c r="G845" s="3" t="n">
-        <v>2550</v>
+        <v>139</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C846" s="2" t="n">
-        <v>19.31</v>
+        <v>18.05</v>
       </c>
       <c r="D846" s="2" t="n">
         <v>-4.14</v>
       </c>
       <c r="E846" s="3" t="n">
-        <v>149</v>
+        <v>2700</v>
       </c>
       <c r="F846" s="3" t="n">
-        <v>173</v>
+        <v>3140</v>
       </c>
       <c r="G846" s="3" t="n">
-        <v>139</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="847">
@@ -23481,16 +23471,16 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C854" s="2" t="n">
-        <v>15.48</v>
+        <v>20.24</v>
       </c>
       <c r="D854" s="2" t="n">
         <v>-4.76</v>
@@ -23499,7 +23489,7 @@
         <v>84</v>
       </c>
       <c r="F854" s="3" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G854" s="3" t="n">
         <v>80</v>
@@ -23508,16 +23498,16 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C855" s="2" t="n">
-        <v>20.24</v>
+        <v>15.48</v>
       </c>
       <c r="D855" s="2" t="n">
         <v>-4.76</v>
@@ -23526,7 +23516,7 @@
         <v>84</v>
       </c>
       <c r="F855" s="3" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G855" s="3" t="n">
         <v>80</v>
@@ -23589,55 +23579,55 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>POLA.JK</t>
+          <t>NASA.JK</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C858" s="2" t="n">
-        <v>13.33</v>
+        <v>17.5</v>
       </c>
       <c r="D858" s="2" t="n">
         <v>-5</v>
       </c>
       <c r="E858" s="3" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F858" s="3" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G858" s="3" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>NASA.JK</t>
+          <t>POLA.JK</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C859" s="2" t="n">
-        <v>17.5</v>
+        <v>13.33</v>
       </c>
       <c r="D859" s="2" t="n">
         <v>-5</v>
       </c>
       <c r="E859" s="3" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="F859" s="3" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G859" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="860">
@@ -23805,55 +23795,55 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C866" s="2" t="n">
-        <v>21.24</v>
+        <v>13.58</v>
       </c>
       <c r="D866" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E866" s="3" t="n">
-        <v>1827.910536399762</v>
+        <v>162</v>
       </c>
       <c r="F866" s="3" t="n">
-        <v>1855</v>
+        <v>184</v>
       </c>
       <c r="G866" s="3" t="n">
-        <v>1445</v>
+        <v>153</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C867" s="2" t="n">
-        <v>13.58</v>
+        <v>21.24</v>
       </c>
       <c r="D867" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E867" s="3" t="n">
-        <v>162</v>
+        <v>1827.910536399762</v>
       </c>
       <c r="F867" s="3" t="n">
-        <v>184</v>
+        <v>1855</v>
       </c>
       <c r="G867" s="3" t="n">
-        <v>153</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="868">
@@ -25641,55 +25631,55 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C934" s="2" t="n">
-        <v>19.27</v>
+        <v>24.77</v>
       </c>
       <c r="D934" s="2" t="n">
         <v>-14.68</v>
       </c>
       <c r="E934" s="3" t="n">
-        <v>222</v>
+        <v>1788.388189719142</v>
       </c>
       <c r="F934" s="3" t="n">
-        <v>260</v>
+        <v>2040</v>
       </c>
       <c r="G934" s="3" t="n">
-        <v>186</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C935" s="2" t="n">
-        <v>24.77</v>
+        <v>19.27</v>
       </c>
       <c r="D935" s="2" t="n">
         <v>-14.68</v>
       </c>
       <c r="E935" s="3" t="n">
-        <v>1788.388189719142</v>
+        <v>222</v>
       </c>
       <c r="F935" s="3" t="n">
-        <v>2040</v>
+        <v>260</v>
       </c>
       <c r="G935" s="3" t="n">
-        <v>1395</v>
+        <v>186</v>
       </c>
     </row>
     <row r="936">
@@ -25830,82 +25820,82 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C941" s="2" t="n">
-        <v>14.86</v>
+        <v>15.94</v>
       </c>
       <c r="D941" s="2" t="n">
         <v>-14.86</v>
       </c>
       <c r="E941" s="3" t="n">
-        <v>296</v>
+        <v>2760</v>
       </c>
       <c r="F941" s="3" t="n">
-        <v>340</v>
+        <v>3200</v>
       </c>
       <c r="G941" s="3" t="n">
-        <v>252</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C942" s="2" t="n">
-        <v>15.94</v>
+        <v>14.86</v>
       </c>
       <c r="D942" s="2" t="n">
         <v>-14.86</v>
       </c>
       <c r="E942" s="3" t="n">
-        <v>2760</v>
+        <v>296</v>
       </c>
       <c r="F942" s="3" t="n">
-        <v>3200</v>
+        <v>340</v>
       </c>
       <c r="G942" s="3" t="n">
-        <v>2350</v>
+        <v>252</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C943" s="2" t="n">
-        <v>14.05</v>
+        <v>24.79</v>
       </c>
       <c r="D943" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E943" s="3" t="n">
-        <v>115</v>
+        <v>1510</v>
       </c>
       <c r="F943" s="3" t="n">
-        <v>138</v>
+        <v>1510</v>
       </c>
       <c r="G943" s="3" t="n">
-        <v>103</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="944">
@@ -25938,28 +25928,28 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C945" s="2" t="n">
-        <v>24.79</v>
+        <v>14.05</v>
       </c>
       <c r="D945" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E945" s="3" t="n">
-        <v>1510</v>
+        <v>115</v>
       </c>
       <c r="F945" s="3" t="n">
-        <v>1510</v>
+        <v>138</v>
       </c>
       <c r="G945" s="3" t="n">
-        <v>1030</v>
+        <v>103</v>
       </c>
     </row>
     <row r="946">
@@ -26071,55 +26061,55 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>INTD.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C950" s="2" t="n">
-        <v>12.5</v>
+        <v>13.57</v>
       </c>
       <c r="D950" s="2" t="n">
         <v>-15</v>
       </c>
       <c r="E950" s="3" t="n">
-        <v>320</v>
+        <v>3010</v>
       </c>
       <c r="F950" s="3" t="n">
-        <v>360</v>
+        <v>3180</v>
       </c>
       <c r="G950" s="3" t="n">
-        <v>272</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>INTD.JK</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C951" s="2" t="n">
-        <v>13.57</v>
+        <v>12.5</v>
       </c>
       <c r="D951" s="2" t="n">
         <v>-15</v>
       </c>
       <c r="E951" s="3" t="n">
-        <v>3010</v>
+        <v>320</v>
       </c>
       <c r="F951" s="3" t="n">
-        <v>3180</v>
+        <v>360</v>
       </c>
       <c r="G951" s="3" t="n">
-        <v>2380</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -1102,12 +1102,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1117,51 +1117,51 @@
         <v>25</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>153.7625885009766</v>
+        <v>434</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>290</v>
+        <v>515</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>290</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>165</v>
+        <v>3310</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>202</v>
+        <v>3700</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>200</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>SAFE.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -1171,40 +1171,40 @@
         <v>25</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3680</v>
+        <v>550</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4500</v>
+        <v>615</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4500</v>
+        <v>615</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAFE.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>550</v>
+        <v>119</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>615</v>
+        <v>155</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>615</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29">
@@ -1237,12 +1237,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1252,24 +1252,24 @@
         <v>25</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3040</v>
+        <v>605</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3600</v>
+        <v>775</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3600</v>
+        <v>775</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLPT.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -1279,24 +1279,24 @@
         <v>25</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1425</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1625</v>
+        <v>975</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1625</v>
+        <v>975</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EKAD.JK</t>
+          <t>BLTZ.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1306,24 +1306,24 @@
         <v>25</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>300</v>
+        <v>3680</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>300</v>
+        <v>4500</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>300</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>BLTZ.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1333,24 +1333,24 @@
         <v>25</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1200</v>
+        <v>3040</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1375</v>
+        <v>3600</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1375</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>EKAD.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1360,24 +1360,24 @@
         <v>25</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>505</v>
+        <v>300</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>505</v>
+        <v>300</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>505</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BIKE.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1387,24 +1387,24 @@
         <v>25</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>414.3801616703698</v>
+        <v>755</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>545</v>
+        <v>775</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>545</v>
+        <v>775</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BIKE.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1414,24 +1414,24 @@
         <v>25</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>755</v>
+        <v>153.7625885009766</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>775</v>
+        <v>290</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>775</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1441,51 +1441,51 @@
         <v>25</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1190</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1200</v>
+        <v>545</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1200</v>
+        <v>545</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>3310</v>
+        <v>165</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>3700</v>
+        <v>202</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3700</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1495,51 +1495,51 @@
         <v>25</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>434</v>
+        <v>1200</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>515</v>
+        <v>1375</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>515</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>119</v>
+        <v>505</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>155</v>
+        <v>505</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>145</v>
+        <v>505</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>MLPT.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1549,24 +1549,24 @@
         <v>25</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>605</v>
+        <v>1425</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>775</v>
+        <v>1625</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>775</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -1576,13 +1576,13 @@
         <v>25</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>1190</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>975</v>
+        <v>1200</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>975</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="43">
@@ -1642,12 +1642,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>NICK.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -1657,24 +1657,24 @@
         <v>24.92</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>3210</v>
+        <v>1540</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>4010</v>
+        <v>1930</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>4010</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NICK.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -1684,13 +1684,13 @@
         <v>24.92</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1540</v>
+        <v>3210</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1930</v>
+        <v>4010</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1930</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="47">
@@ -1777,12 +1777,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -1792,24 +1792,24 @@
         <v>24.88</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1170</v>
+        <v>2170</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1255</v>
+        <v>2510</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1255</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>SMMT.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -1819,24 +1819,24 @@
         <v>24.88</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2170</v>
+        <v>2110</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2510</v>
+        <v>2610</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>2510</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SMMT.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -1846,24 +1846,24 @@
         <v>24.88</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>2110</v>
+        <v>1170</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2610</v>
+        <v>1255</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2610</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CCSI.JK</t>
+          <t>ARII.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -1873,24 +1873,24 @@
         <v>24.86</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ARII.JK</t>
+          <t>CCSI.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -1900,13 +1900,13 @@
         <v>24.86</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>452</v>
+        <v>442</v>
       </c>
     </row>
     <row r="55">
@@ -1939,55 +1939,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEMA.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>24.85</v>
+        <v>29.7</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>372</v>
+        <v>167</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>412</v>
+        <v>214</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>412</v>
+        <v>206</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>SEMA.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>29.7</v>
+        <v>24.85</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>167</v>
+        <v>372</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>214</v>
+        <v>412</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>206</v>
+        <v>412</v>
       </c>
     </row>
     <row r="58">
@@ -2020,12 +2020,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PGLI.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -2035,13 +2035,13 @@
         <v>24.81</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>2600</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>3220</v>
+        <v>332</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3220</v>
+        <v>332</v>
       </c>
     </row>
     <row r="60">
@@ -2074,12 +2074,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PGLI.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -2089,13 +2089,13 @@
         <v>24.81</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>300</v>
+        <v>2600</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>332</v>
+        <v>3220</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>332</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="62">
@@ -2236,12 +2236,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BABY.JK</t>
+          <t>BIKE.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -2251,24 +2251,24 @@
         <v>24.77</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>226</v>
+        <v>2270</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>272</v>
+        <v>2670</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>272</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BIKE.JK</t>
+          <t>BABY.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -2278,24 +2278,24 @@
         <v>24.77</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>2270</v>
+        <v>226</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2670</v>
+        <v>272</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>2670</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>ASLI.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -2305,24 +2305,24 @@
         <v>24.76</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>525</v>
+        <v>228</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ASLI.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -2332,7 +2332,7 @@
         <v>24.76</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>262</v>
@@ -2371,12 +2371,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -2386,13 +2386,13 @@
         <v>24.76</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>214</v>
+        <v>525</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
     </row>
     <row r="73">
@@ -2452,12 +2452,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>PTSP.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -2470,21 +2470,21 @@
         <v>1380</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1690</v>
+        <v>1665</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1690</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PTSP.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -2497,10 +2497,10 @@
         <v>1380</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1665</v>
+        <v>1690</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1665</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="77">
@@ -2533,12 +2533,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -2548,24 +2548,24 @@
         <v>24.69</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>404</v>
+        <v>1625</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>404</v>
+        <v>2020</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>404</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -2575,24 +2575,24 @@
         <v>24.69</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>1625</v>
+        <v>404</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2020</v>
+        <v>404</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2020</v>
+        <v>404</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -2602,24 +2602,24 @@
         <v>24.68</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2330</v>
+        <v>760</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2880</v>
+        <v>960</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>BLTZ.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -2629,13 +2629,13 @@
         <v>24.68</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>760</v>
+        <v>2330</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>960</v>
+        <v>2880</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>960</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="82">
@@ -2749,12 +2749,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VOKS.JK</t>
+          <t>FUJI.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -2764,7 +2764,7 @@
         <v>24.62</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F86" s="3" t="n">
         <v>324</v>
@@ -2776,12 +2776,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FUJI.JK</t>
+          <t>VOKS.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -2791,7 +2791,7 @@
         <v>24.62</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F87" s="3" t="n">
         <v>324</v>
@@ -3100,12 +3100,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KDTN.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -3115,24 +3115,24 @@
         <v>24.41</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KDTN.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -3142,13 +3142,13 @@
         <v>24.41</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="101">
@@ -4016,55 +4016,55 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BEKS.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>33.33</v>
+        <v>20</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>20</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>30</v>
+        <v>6550</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>40</v>
+        <v>7800</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>36</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>BEKS.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>20</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>6550</v>
+        <v>30</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>7800</v>
+        <v>40</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>7800</v>
+        <v>36</v>
       </c>
     </row>
     <row r="135">
@@ -4232,12 +4232,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
@@ -4247,24 +4247,24 @@
         <v>19.75</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>17150</v>
+        <v>5950</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>19400</v>
+        <v>7125</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>19400</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
@@ -4274,13 +4274,13 @@
         <v>19.75</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>5950</v>
+        <v>17150</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>7125</v>
+        <v>19400</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>7125</v>
+        <v>19400</v>
       </c>
     </row>
     <row r="143">
@@ -4745,55 +4745,55 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>22.31</v>
+        <v>29.09</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>18.18</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>615</v>
+        <v>123</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>740</v>
+        <v>142</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>715</v>
+        <v>130</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>29.09</v>
+        <v>22.31</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>18.18</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>123</v>
+        <v>615</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>142</v>
+        <v>740</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>130</v>
+        <v>715</v>
       </c>
     </row>
     <row r="162">
@@ -5042,55 +5042,55 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SMAR.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>19.03</v>
+        <v>22.99</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>17.65</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>7175</v>
+        <v>191</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>8600</v>
+        <v>230</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>8500</v>
+        <v>220</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>SMAR.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>22.99</v>
+        <v>19.03</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>17.65</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>191</v>
+        <v>7175</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>230</v>
+        <v>8600</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>220</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="173">
@@ -5110,7 +5110,9 @@
       <c r="D173" s="2" t="n">
         <v>17.59</v>
       </c>
-      <c r="E173" s="3" t="inlineStr"/>
+      <c r="E173" s="3" t="n">
+        <v>109</v>
+      </c>
       <c r="F173" s="3" t="n">
         <v>138</v>
       </c>
@@ -5526,55 +5528,55 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>SLIS.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>25</v>
+        <v>29.55</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>15.91</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>1320</v>
+        <v>92</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>1650</v>
+        <v>114</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>1530</v>
+        <v>102</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SLIS.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>29.55</v>
+        <v>25</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>15.91</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>92</v>
+        <v>1320</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>114</v>
+        <v>1650</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>102</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="191">
@@ -5823,55 +5825,55 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>FITT.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>30.77</v>
+        <v>24.62</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>15.38</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>102</v>
+        <v>486</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FITT.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>24.62</v>
+        <v>30.77</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>15.38</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>408</v>
+        <v>77</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>486</v>
+        <v>102</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>450</v>
+        <v>90</v>
       </c>
     </row>
     <row r="202">
@@ -6012,55 +6014,55 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>MBSS.JK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="D207" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>78</v>
+        <v>3940</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>98</v>
+        <v>4600</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>92</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MBSS.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="D208" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>3940</v>
+        <v>78</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>4600</v>
+        <v>98</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>4600</v>
+        <v>92</v>
       </c>
     </row>
     <row r="209">
@@ -6093,25 +6095,25 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SQMI.JK</t>
+          <t>ZATA.JK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>23.88</v>
+        <v>28.36</v>
       </c>
       <c r="D210" s="2" t="n">
         <v>14.93</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G210" s="3" t="n">
         <v>77</v>
@@ -6120,25 +6122,25 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ZATA.JK</t>
+          <t>SQMI.JK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>28.36</v>
+        <v>23.88</v>
       </c>
       <c r="D211" s="2" t="n">
         <v>14.93</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G211" s="3" t="n">
         <v>77</v>
@@ -6390,82 +6392,82 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>ERAA.JK</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>21.4</v>
+        <v>17.31</v>
       </c>
       <c r="D221" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>2200</v>
+        <v>515</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>2610</v>
+        <v>610</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>2460</v>
+        <v>595</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ERAA.JK</t>
+          <t>MDIA.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>17.31</v>
+        <v>30.77</v>
       </c>
       <c r="D222" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>515</v>
+        <v>106</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>610</v>
+        <v>136</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>595</v>
+        <v>119</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MDIA.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>30.77</v>
+        <v>21.4</v>
       </c>
       <c r="D223" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>106</v>
+        <v>2200</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>136</v>
+        <v>2610</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>119</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="224">
@@ -6863,7 +6865,9 @@
       <c r="D238" s="2" t="n">
         <v>13.85</v>
       </c>
-      <c r="E238" s="3" t="inlineStr"/>
+      <c r="E238" s="3" t="n">
+        <v>268</v>
+      </c>
       <c r="F238" s="3" t="n">
         <v>296</v>
       </c>
@@ -7090,55 +7094,55 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ASGR.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>19.37</v>
+        <v>23.42</v>
       </c>
       <c r="D247" s="2" t="n">
         <v>13.51</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>2291.120024181548</v>
+        <v>228</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>2650</v>
+        <v>274</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>2520</v>
+        <v>252</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>ASGR.JK</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C248" s="2" t="n">
-        <v>23.42</v>
+        <v>19.37</v>
       </c>
       <c r="D248" s="2" t="n">
         <v>13.51</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>228</v>
+        <v>2291.120024181548</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>274</v>
+        <v>2650</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>252</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="249">
@@ -7333,55 +7337,55 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>INTD.JK</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C256" s="2" t="n">
-        <v>20.92</v>
+        <v>16.99</v>
       </c>
       <c r="D256" s="2" t="n">
         <v>13.07</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>1525</v>
+        <v>352</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>1850</v>
+        <v>358</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>1730</v>
+        <v>346</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>INTD.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C257" s="2" t="n">
-        <v>16.99</v>
+        <v>20.92</v>
       </c>
       <c r="D257" s="2" t="n">
         <v>13.07</v>
       </c>
       <c r="E257" s="3" t="n">
-        <v>352</v>
+        <v>1525</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>358</v>
+        <v>1850</v>
       </c>
       <c r="G257" s="3" t="n">
-        <v>346</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="258">
@@ -7630,55 +7634,55 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>15.53</v>
+        <v>14.56</v>
       </c>
       <c r="D267" s="2" t="n">
         <v>12.62</v>
       </c>
       <c r="E267" s="3" t="n">
-        <v>515</v>
+        <v>210</v>
       </c>
       <c r="F267" s="3" t="n">
-        <v>595</v>
+        <v>236</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>580</v>
+        <v>232</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>14.56</v>
+        <v>15.53</v>
       </c>
       <c r="D268" s="2" t="n">
         <v>12.62</v>
       </c>
       <c r="E268" s="3" t="n">
-        <v>210</v>
+        <v>515</v>
       </c>
       <c r="F268" s="3" t="n">
-        <v>236</v>
+        <v>595</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>232</v>
+        <v>580</v>
       </c>
     </row>
     <row r="269">
@@ -7738,53 +7742,55 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>KREN.JK</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
-        <v>14.06</v>
+        <v>18.75</v>
       </c>
       <c r="D271" s="2" t="n">
         <v>12.5</v>
       </c>
-      <c r="E271" s="3" t="inlineStr"/>
+      <c r="E271" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="F271" s="3" t="n">
-        <v>146</v>
+        <v>19</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>144</v>
+        <v>18</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>KREN.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C272" s="2" t="n">
-        <v>18.75</v>
+        <v>14.06</v>
       </c>
       <c r="D272" s="2" t="n">
         <v>12.5</v>
       </c>
       <c r="E272" s="3" t="n">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="F272" s="3" t="n">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="G272" s="3" t="n">
-        <v>18</v>
+        <v>144</v>
       </c>
     </row>
     <row r="273">
@@ -7817,55 +7823,55 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C274" s="2" t="n">
-        <v>12.32</v>
+        <v>14.49</v>
       </c>
       <c r="D274" s="2" t="n">
         <v>12.32</v>
       </c>
       <c r="E274" s="3" t="n">
-        <v>690</v>
+        <v>138</v>
       </c>
       <c r="F274" s="3" t="n">
-        <v>775</v>
+        <v>158</v>
       </c>
       <c r="G274" s="3" t="n">
-        <v>775</v>
+        <v>155</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C275" s="2" t="n">
-        <v>14.49</v>
+        <v>12.32</v>
       </c>
       <c r="D275" s="2" t="n">
         <v>12.32</v>
       </c>
       <c r="E275" s="3" t="n">
-        <v>138</v>
+        <v>690</v>
       </c>
       <c r="F275" s="3" t="n">
-        <v>158</v>
+        <v>775</v>
       </c>
       <c r="G275" s="3" t="n">
-        <v>155</v>
+        <v>775</v>
       </c>
     </row>
     <row r="276">
@@ -8303,55 +8309,55 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>11.61</v>
+        <v>13.39</v>
       </c>
       <c r="D292" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E292" s="3" t="n">
-        <v>218</v>
+        <v>2270</v>
       </c>
       <c r="F292" s="3" t="n">
-        <v>250</v>
+        <v>2540</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>13.39</v>
+        <v>11.61</v>
       </c>
       <c r="D293" s="2" t="n">
         <v>11.61</v>
       </c>
       <c r="E293" s="3" t="n">
-        <v>2270</v>
+        <v>218</v>
       </c>
       <c r="F293" s="3" t="n">
-        <v>2540</v>
+        <v>250</v>
       </c>
       <c r="G293" s="3" t="n">
-        <v>2500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="294">
@@ -8681,55 +8687,55 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>WAPO.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>18.1</v>
+        <v>23.28</v>
       </c>
       <c r="D306" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="E306" s="3" t="n">
-        <v>226</v>
+        <v>119</v>
       </c>
       <c r="F306" s="3" t="n">
-        <v>274</v>
+        <v>143</v>
       </c>
       <c r="G306" s="3" t="n">
-        <v>258</v>
+        <v>129</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>WAPO.JK</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>23.28</v>
+        <v>18.1</v>
       </c>
       <c r="D307" s="2" t="n">
         <v>11.21</v>
       </c>
       <c r="E307" s="3" t="n">
-        <v>119</v>
+        <v>226</v>
       </c>
       <c r="F307" s="3" t="n">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="G307" s="3" t="n">
-        <v>129</v>
+        <v>258</v>
       </c>
     </row>
     <row r="308">
@@ -9005,55 +9011,55 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>DOOH.JK</t>
+          <t>ASGR.JK</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>21.09</v>
+        <v>18.83</v>
       </c>
       <c r="D318" s="2" t="n">
         <v>10.88</v>
       </c>
       <c r="E318" s="3" t="n">
-        <v>304</v>
+        <v>1665.468007064892</v>
       </c>
       <c r="F318" s="3" t="n">
-        <v>356</v>
+        <v>2240</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>326</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ASGR.JK</t>
+          <t>DOOH.JK</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>18.83</v>
+        <v>21.09</v>
       </c>
       <c r="D319" s="2" t="n">
         <v>10.88</v>
       </c>
       <c r="E319" s="3" t="n">
-        <v>1665.468007064892</v>
+        <v>304</v>
       </c>
       <c r="F319" s="3" t="n">
-        <v>2240</v>
+        <v>356</v>
       </c>
       <c r="G319" s="3" t="n">
-        <v>2090</v>
+        <v>326</v>
       </c>
     </row>
     <row r="320">
@@ -9086,55 +9092,55 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>21.69</v>
+        <v>18.07</v>
       </c>
       <c r="D321" s="2" t="n">
         <v>10.84</v>
       </c>
       <c r="E321" s="3" t="n">
-        <v>87</v>
+        <v>332</v>
       </c>
       <c r="F321" s="3" t="n">
-        <v>101</v>
+        <v>392</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>92</v>
+        <v>368</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>18.07</v>
+        <v>21.69</v>
       </c>
       <c r="D322" s="2" t="n">
         <v>10.84</v>
       </c>
       <c r="E322" s="3" t="n">
-        <v>332</v>
+        <v>87</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>392</v>
+        <v>101</v>
       </c>
       <c r="G322" s="3" t="n">
-        <v>368</v>
+        <v>92</v>
       </c>
     </row>
     <row r="323">
@@ -9761,25 +9767,25 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>21.1</v>
+        <v>14.68</v>
       </c>
       <c r="D346" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E346" s="3" t="n">
-        <v>495.4545288085938</v>
+        <v>545</v>
       </c>
       <c r="F346" s="3" t="n">
-        <v>660</v>
+        <v>625</v>
       </c>
       <c r="G346" s="3" t="n">
         <v>600</v>
@@ -9788,25 +9794,25 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>10.09</v>
+        <v>21.1</v>
       </c>
       <c r="D347" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E347" s="3" t="n">
-        <v>535</v>
+        <v>495.4545288085938</v>
       </c>
       <c r="F347" s="3" t="n">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="G347" s="3" t="n">
         <v>600</v>
@@ -9815,25 +9821,25 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>14.68</v>
+        <v>10.09</v>
       </c>
       <c r="D348" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E348" s="3" t="n">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G348" s="3" t="n">
         <v>600</v>
@@ -9842,88 +9848,88 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>TKIM.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>10.77</v>
+        <v>16.36</v>
       </c>
       <c r="D349" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E349" s="3" t="n">
-        <v>6850</v>
+        <v>224</v>
       </c>
       <c r="F349" s="3" t="n">
-        <v>7200</v>
+        <v>256</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>7150</v>
+        <v>242</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>PPRO.JK</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>16.36</v>
+        <v>30</v>
       </c>
       <c r="D350" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E350" s="3" t="n">
-        <v>224</v>
+        <v>23</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>256</v>
+        <v>26</v>
       </c>
       <c r="G350" s="3" t="n">
-        <v>242</v>
+        <v>22</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>PPRO.JK</t>
+          <t>APEX.JK</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>30</v>
+        <v>12.67</v>
       </c>
       <c r="D351" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E351" s="3" t="n">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="F351" s="3" t="n">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>22</v>
+        <v>165</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>APEX.JK</t>
+          <t>TKIM.JK</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9932,19 +9938,19 @@
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>12.67</v>
+        <v>10.77</v>
       </c>
       <c r="D352" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E352" s="3" t="n">
-        <v>150</v>
+        <v>6850</v>
       </c>
       <c r="F352" s="3" t="n">
-        <v>169</v>
+        <v>7200</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>165</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="353">
@@ -10139,55 +10145,55 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>MOLI.JK</t>
+          <t>VTNY.JK</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>11.4</v>
+        <v>11.48</v>
       </c>
       <c r="D360" s="2" t="n">
         <v>9.84</v>
       </c>
       <c r="E360" s="3" t="n">
-        <v>390</v>
+        <v>62</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>430</v>
+        <v>68</v>
       </c>
       <c r="G360" s="3" t="n">
-        <v>424</v>
+        <v>67</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>VTNY.JK</t>
+          <t>MOLI.JK</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>11.48</v>
+        <v>11.4</v>
       </c>
       <c r="D361" s="2" t="n">
         <v>9.84</v>
       </c>
       <c r="E361" s="3" t="n">
-        <v>62</v>
+        <v>390</v>
       </c>
       <c r="F361" s="3" t="n">
-        <v>68</v>
+        <v>430</v>
       </c>
       <c r="G361" s="3" t="n">
-        <v>67</v>
+        <v>424</v>
       </c>
     </row>
     <row r="362">
@@ -10409,55 +10415,55 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>SQMI.JK</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>13.04</v>
+        <v>18.09</v>
       </c>
       <c r="D370" s="2" t="n">
         <v>9.57</v>
       </c>
       <c r="E370" s="3" t="n">
-        <v>580</v>
+        <v>98</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>650</v>
+        <v>111</v>
       </c>
       <c r="G370" s="3" t="n">
-        <v>630</v>
+        <v>103</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>SQMI.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
-        <v>18.09</v>
+        <v>13.04</v>
       </c>
       <c r="D371" s="2" t="n">
         <v>9.57</v>
       </c>
       <c r="E371" s="3" t="n">
-        <v>98</v>
+        <v>580</v>
       </c>
       <c r="F371" s="3" t="n">
-        <v>111</v>
+        <v>650</v>
       </c>
       <c r="G371" s="3" t="n">
-        <v>103</v>
+        <v>630</v>
       </c>
     </row>
     <row r="372">
@@ -10625,25 +10631,25 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>EKAD.JK</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>11.4</v>
+        <v>20.73</v>
       </c>
       <c r="D378" s="2" t="n">
         <v>9.33</v>
       </c>
       <c r="E378" s="3" t="n">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="F378" s="3" t="n">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="G378" s="3" t="n">
         <v>422</v>
@@ -10652,25 +10658,25 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>EKAD.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>20.73</v>
+        <v>11.4</v>
       </c>
       <c r="D379" s="2" t="n">
         <v>9.33</v>
       </c>
       <c r="E379" s="3" t="n">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="F379" s="3" t="n">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="G379" s="3" t="n">
         <v>422</v>
@@ -10679,55 +10685,55 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>WAPO.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>24.81</v>
+        <v>13.95</v>
       </c>
       <c r="D380" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E380" s="3" t="n">
-        <v>260</v>
+        <v>20500</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>322</v>
+        <v>24500</v>
       </c>
       <c r="G380" s="3" t="n">
-        <v>282</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>WAPO.JK</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>13.95</v>
+        <v>24.81</v>
       </c>
       <c r="D381" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E381" s="3" t="n">
-        <v>20500</v>
+        <v>260</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>24500</v>
+        <v>322</v>
       </c>
       <c r="G381" s="3" t="n">
-        <v>23500</v>
+        <v>282</v>
       </c>
     </row>
     <row r="382">
@@ -10868,28 +10874,28 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>22.73</v>
+        <v>11.11</v>
       </c>
       <c r="D387" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E387" s="3" t="n">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="F387" s="3" t="n">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="G387" s="3" t="n">
-        <v>192</v>
+        <v>108</v>
       </c>
     </row>
     <row r="388">
@@ -10922,28 +10928,28 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>11.11</v>
+        <v>22.73</v>
       </c>
       <c r="D389" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E389" s="3" t="n">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="F389" s="3" t="n">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="G389" s="3" t="n">
-        <v>108</v>
+        <v>192</v>
       </c>
     </row>
     <row r="390">
@@ -11300,109 +11306,109 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>WINS.JK</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>15.2</v>
+        <v>15.79</v>
       </c>
       <c r="D403" s="2" t="n">
         <v>8.77</v>
       </c>
       <c r="E403" s="3" t="n">
-        <v>364</v>
+        <v>580</v>
       </c>
       <c r="F403" s="3" t="n">
-        <v>394</v>
+        <v>660</v>
       </c>
       <c r="G403" s="3" t="n">
-        <v>372</v>
+        <v>620</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>WINS.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C404" s="2" t="n">
-        <v>15.79</v>
+        <v>15.2</v>
       </c>
       <c r="D404" s="2" t="n">
         <v>8.77</v>
       </c>
       <c r="E404" s="3" t="n">
-        <v>580</v>
+        <v>364</v>
       </c>
       <c r="F404" s="3" t="n">
-        <v>660</v>
+        <v>394</v>
       </c>
       <c r="G404" s="3" t="n">
-        <v>620</v>
+        <v>372</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>IKAI.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C405" s="2" t="n">
-        <v>21.74</v>
+        <v>10.14</v>
       </c>
       <c r="D405" s="2" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E405" s="3" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="F405" s="3" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G405" s="3" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>IKAI.JK</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>10.14</v>
+        <v>21.74</v>
       </c>
       <c r="D406" s="2" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E406" s="3" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="F406" s="3" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G406" s="3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="407">
@@ -11462,28 +11468,28 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>MOLI.JK</t>
+          <t>ARKO.JK</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>13.14</v>
+        <v>12.38</v>
       </c>
       <c r="D409" s="2" t="n">
         <v>8.57</v>
       </c>
       <c r="E409" s="3" t="n">
-        <v>360</v>
+        <v>5275</v>
       </c>
       <c r="F409" s="3" t="n">
-        <v>396</v>
+        <v>5900</v>
       </c>
       <c r="G409" s="3" t="n">
-        <v>380</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="410">
@@ -11516,28 +11522,28 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ARKO.JK</t>
+          <t>MOLI.JK</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>12.38</v>
+        <v>13.14</v>
       </c>
       <c r="D411" s="2" t="n">
         <v>8.57</v>
       </c>
       <c r="E411" s="3" t="n">
-        <v>5275</v>
+        <v>360</v>
       </c>
       <c r="F411" s="3" t="n">
-        <v>5900</v>
+        <v>396</v>
       </c>
       <c r="G411" s="3" t="n">
-        <v>5700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="412">
@@ -11678,217 +11684,217 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>BKDP.JK</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>11.67</v>
+        <v>12.5</v>
       </c>
       <c r="D417" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E417" s="3" t="n">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="F417" s="3" t="n">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="G417" s="3" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>SSTM.JK</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>19.05</v>
+        <v>22.92</v>
       </c>
       <c r="D418" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E418" s="3" t="n">
-        <v>169</v>
+        <v>555</v>
       </c>
       <c r="F418" s="3" t="n">
-        <v>200</v>
+        <v>590</v>
       </c>
       <c r="G418" s="3" t="n">
-        <v>182</v>
+        <v>520</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>10.19</v>
+        <v>11.11</v>
       </c>
       <c r="D419" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E419" s="3" t="n">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="F419" s="3" t="n">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="G419" s="3" t="n">
-        <v>117</v>
+        <v>78</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>SSTM.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>22.92</v>
+        <v>10.19</v>
       </c>
       <c r="D420" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E420" s="3" t="n">
-        <v>555</v>
+        <v>109</v>
       </c>
       <c r="F420" s="3" t="n">
-        <v>590</v>
+        <v>119</v>
       </c>
       <c r="G420" s="3" t="n">
-        <v>520</v>
+        <v>117</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>HGII.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>27.27</v>
+        <v>11.67</v>
       </c>
       <c r="D421" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E421" s="3" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="F421" s="3" t="n">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="G421" s="3" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>BKSL.JK</t>
+          <t>HGII.JK</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>11.11</v>
+        <v>27.27</v>
       </c>
       <c r="D422" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E422" s="3" t="n">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="F422" s="3" t="n">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="G422" s="3" t="n">
-        <v>78</v>
+        <v>143</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>12.12</v>
+        <v>19.05</v>
       </c>
       <c r="D423" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E423" s="3" t="n">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="F423" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="G423" s="3" t="n">
-        <v>143</v>
+        <v>182</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>12.5</v>
+        <v>12.12</v>
       </c>
       <c r="D424" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E424" s="3" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F424" s="3" t="n">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="G424" s="3" t="n">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="425">
@@ -11948,25 +11954,25 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>GDST.JK</t>
+          <t>SQMI.JK</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>10.31</v>
+        <v>14.43</v>
       </c>
       <c r="D427" s="2" t="n">
         <v>8.25</v>
       </c>
       <c r="E427" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F427" s="3" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G427" s="3" t="n">
         <v>105</v>
@@ -11975,25 +11981,25 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>SQMI.JK</t>
+          <t>GDST.JK</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>14.43</v>
+        <v>10.31</v>
       </c>
       <c r="D428" s="2" t="n">
         <v>8.25</v>
       </c>
       <c r="E428" s="3" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F428" s="3" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G428" s="3" t="n">
         <v>105</v>
@@ -12245,12 +12251,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>BEKS.JK</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C438" s="2" t="n">
@@ -12260,13 +12266,13 @@
         <v>8</v>
       </c>
       <c r="E438" s="3" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G438" s="3" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
     </row>
     <row r="439">
@@ -12299,12 +12305,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>BEKS.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C440" s="2" t="n">
@@ -12314,13 +12320,13 @@
         <v>8</v>
       </c>
       <c r="E440" s="3" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="F440" s="3" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G440" s="3" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="441">
@@ -12407,28 +12413,28 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>LPCK.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C444" s="2" t="n">
-        <v>16.52</v>
+        <v>12.17</v>
       </c>
       <c r="D444" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E444" s="3" t="n">
-        <v>590</v>
+        <v>230</v>
       </c>
       <c r="F444" s="3" t="n">
-        <v>670</v>
+        <v>258</v>
       </c>
       <c r="G444" s="3" t="n">
-        <v>620</v>
+        <v>248</v>
       </c>
     </row>
     <row r="445">
@@ -12461,28 +12467,28 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>LPCK.JK</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C446" s="2" t="n">
-        <v>12.17</v>
+        <v>16.52</v>
       </c>
       <c r="D446" s="2" t="n">
         <v>7.83</v>
       </c>
       <c r="E446" s="3" t="n">
-        <v>230</v>
+        <v>590</v>
       </c>
       <c r="F446" s="3" t="n">
-        <v>258</v>
+        <v>670</v>
       </c>
       <c r="G446" s="3" t="n">
-        <v>248</v>
+        <v>620</v>
       </c>
     </row>
     <row r="447">
@@ -12596,55 +12602,55 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>CCSI.JK</t>
+          <t>ASLI.JK</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C451" s="2" t="n">
-        <v>23.78</v>
+        <v>20.51</v>
       </c>
       <c r="D451" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E451" s="3" t="n">
-        <v>294</v>
+        <v>238</v>
       </c>
       <c r="F451" s="3" t="n">
-        <v>354</v>
+        <v>282</v>
       </c>
       <c r="G451" s="3" t="n">
-        <v>308</v>
+        <v>252</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>ASLI.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C452" s="2" t="n">
-        <v>20.51</v>
+        <v>16.35</v>
       </c>
       <c r="D452" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E452" s="3" t="n">
-        <v>238</v>
+        <v>106</v>
       </c>
       <c r="F452" s="3" t="n">
-        <v>282</v>
+        <v>121</v>
       </c>
       <c r="G452" s="3" t="n">
-        <v>252</v>
+        <v>112</v>
       </c>
     </row>
     <row r="453">
@@ -12677,82 +12683,82 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>CCSI.JK</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C454" s="2" t="n">
-        <v>16.35</v>
+        <v>23.78</v>
       </c>
       <c r="D454" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E454" s="3" t="n">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="F454" s="3" t="n">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="G454" s="3" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>MPIX.JK</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C455" s="2" t="n">
-        <v>12.98</v>
+        <v>13.56</v>
       </c>
       <c r="D455" s="2" t="n">
         <v>7.63</v>
       </c>
       <c r="E455" s="3" t="n">
-        <v>264</v>
+        <v>118</v>
       </c>
       <c r="F455" s="3" t="n">
-        <v>296</v>
+        <v>134</v>
       </c>
       <c r="G455" s="3" t="n">
-        <v>282</v>
+        <v>127</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>MPIX.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C456" s="2" t="n">
-        <v>13.56</v>
+        <v>12.98</v>
       </c>
       <c r="D456" s="2" t="n">
         <v>7.63</v>
       </c>
       <c r="E456" s="3" t="n">
-        <v>118</v>
+        <v>264</v>
       </c>
       <c r="F456" s="3" t="n">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="G456" s="3" t="n">
-        <v>127</v>
+        <v>282</v>
       </c>
     </row>
     <row r="457">
@@ -12785,109 +12791,109 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C458" s="2" t="n">
-        <v>16.46</v>
+        <v>11.03</v>
       </c>
       <c r="D458" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E458" s="3" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F458" s="3" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="G458" s="3" t="n">
-        <v>85</v>
+        <v>156</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C459" s="2" t="n">
-        <v>11.03</v>
+        <v>16.46</v>
       </c>
       <c r="D459" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E459" s="3" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="F459" s="3" t="n">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="G459" s="3" t="n">
-        <v>156</v>
+        <v>85</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>WAPO.JK</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C460" s="2" t="n">
-        <v>18.01</v>
+        <v>18.18</v>
       </c>
       <c r="D460" s="2" t="n">
         <v>7.58</v>
       </c>
       <c r="E460" s="3" t="n">
-        <v>2220</v>
+        <v>143</v>
       </c>
       <c r="F460" s="3" t="n">
-        <v>2490</v>
+        <v>156</v>
       </c>
       <c r="G460" s="3" t="n">
-        <v>2270</v>
+        <v>142</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>WAPO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C461" s="2" t="n">
-        <v>18.18</v>
+        <v>18.01</v>
       </c>
       <c r="D461" s="2" t="n">
         <v>7.58</v>
       </c>
       <c r="E461" s="3" t="n">
-        <v>143</v>
+        <v>2220</v>
       </c>
       <c r="F461" s="3" t="n">
-        <v>156</v>
+        <v>2490</v>
       </c>
       <c r="G461" s="3" t="n">
-        <v>142</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="462">
@@ -12974,55 +12980,55 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C465" s="2" t="n">
-        <v>10.05</v>
+        <v>23.46</v>
       </c>
       <c r="D465" s="2" t="n">
         <v>7.41</v>
       </c>
       <c r="E465" s="3" t="n">
-        <v>372</v>
+        <v>161</v>
       </c>
       <c r="F465" s="3" t="n">
-        <v>416</v>
+        <v>200</v>
       </c>
       <c r="G465" s="3" t="n">
-        <v>406</v>
+        <v>174</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C466" s="2" t="n">
-        <v>23.46</v>
+        <v>10.05</v>
       </c>
       <c r="D466" s="2" t="n">
         <v>7.41</v>
       </c>
       <c r="E466" s="3" t="n">
-        <v>161</v>
+        <v>372</v>
       </c>
       <c r="F466" s="3" t="n">
-        <v>200</v>
+        <v>416</v>
       </c>
       <c r="G466" s="3" t="n">
-        <v>174</v>
+        <v>406</v>
       </c>
     </row>
     <row r="467">
@@ -13271,55 +13277,55 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>FIRE.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C476" s="2" t="n">
-        <v>22.32</v>
+        <v>22.86</v>
       </c>
       <c r="D476" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E476" s="3" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="F476" s="3" t="n">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="G476" s="3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>FIRE.JK</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C477" s="2" t="n">
-        <v>22.86</v>
+        <v>22.32</v>
       </c>
       <c r="D477" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E477" s="3" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="G477" s="3" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="478">
@@ -13487,109 +13493,109 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>BRNA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C484" s="2" t="n">
-        <v>15.5</v>
+        <v>12.4</v>
       </c>
       <c r="D484" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E484" s="3" t="n">
-        <v>660</v>
+        <v>134</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>745</v>
+        <v>145</v>
       </c>
       <c r="G484" s="3" t="n">
-        <v>690</v>
+        <v>138</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>IFSH.JK</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C485" s="2" t="n">
-        <v>12.4</v>
+        <v>16.28</v>
       </c>
       <c r="D485" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E485" s="3" t="n">
-        <v>134</v>
+        <v>2210</v>
       </c>
       <c r="F485" s="3" t="n">
-        <v>145</v>
+        <v>2500</v>
       </c>
       <c r="G485" s="3" t="n">
-        <v>138</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>BRNA.JK</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C486" s="2" t="n">
-        <v>17.44</v>
+        <v>15.5</v>
       </c>
       <c r="D486" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E486" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>660</v>
       </c>
       <c r="F486" s="3" t="n">
-        <v>101</v>
+        <v>745</v>
       </c>
       <c r="G486" s="3" t="n">
-        <v>92</v>
+        <v>690</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>IFSH.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C487" s="2" t="n">
-        <v>16.28</v>
+        <v>17.44</v>
       </c>
       <c r="D487" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E487" s="3" t="n">
-        <v>2210</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F487" s="3" t="n">
-        <v>2500</v>
+        <v>101</v>
       </c>
       <c r="G487" s="3" t="n">
-        <v>2300</v>
+        <v>92</v>
       </c>
     </row>
     <row r="488">
@@ -13703,55 +13709,55 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>PTSP.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C492" s="2" t="n">
-        <v>24.92</v>
+        <v>24.86</v>
       </c>
       <c r="D492" s="2" t="n">
         <v>6.91</v>
       </c>
       <c r="E492" s="3" t="n">
-        <v>1850</v>
+        <v>2260</v>
       </c>
       <c r="F492" s="3" t="n">
-        <v>2080</v>
+        <v>2260</v>
       </c>
       <c r="G492" s="3" t="n">
-        <v>1780</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PTSP.JK</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C493" s="2" t="n">
-        <v>24.86</v>
+        <v>24.92</v>
       </c>
       <c r="D493" s="2" t="n">
         <v>6.91</v>
       </c>
       <c r="E493" s="3" t="n">
-        <v>2260</v>
+        <v>1850</v>
       </c>
       <c r="F493" s="3" t="n">
-        <v>2260</v>
+        <v>2080</v>
       </c>
       <c r="G493" s="3" t="n">
-        <v>1935</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="494">
@@ -13825,7 +13831,9 @@
       <c r="D496" s="2" t="n">
         <v>6.86</v>
       </c>
-      <c r="E496" s="3" t="inlineStr"/>
+      <c r="E496" s="3" t="n">
+        <v>103</v>
+      </c>
       <c r="F496" s="3" t="n">
         <v>115</v>
       </c>
@@ -14052,52 +14060,52 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>PTSN.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C505" s="2" t="n">
-        <v>11.11</v>
+        <v>16</v>
       </c>
       <c r="D505" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E505" s="3" t="n">
-        <v>452</v>
+        <v>74</v>
       </c>
       <c r="F505" s="3" t="n">
-        <v>500</v>
+        <v>87</v>
       </c>
       <c r="G505" s="3" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ISEA.JK</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C506" s="2" t="n">
-        <v>16</v>
+        <v>25.33</v>
       </c>
       <c r="D506" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E506" s="3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F506" s="3" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G506" s="3" t="n">
         <v>80</v>
@@ -14133,28 +14141,28 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>ISEA.JK</t>
+          <t>PTSN.JK</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C508" s="2" t="n">
-        <v>25.33</v>
+        <v>11.11</v>
       </c>
       <c r="D508" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E508" s="3" t="n">
-        <v>77</v>
+        <v>452</v>
       </c>
       <c r="F508" s="3" t="n">
-        <v>94</v>
+        <v>500</v>
       </c>
       <c r="G508" s="3" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
     </row>
     <row r="509">
@@ -14214,55 +14222,55 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>NAIK.JK</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C511" s="2" t="n">
-        <v>23.29</v>
+        <v>11.96</v>
       </c>
       <c r="D511" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E511" s="3" t="n">
-        <v>3000</v>
+        <v>92</v>
       </c>
       <c r="F511" s="3" t="n">
-        <v>3970</v>
+        <v>103</v>
       </c>
       <c r="G511" s="3" t="n">
-        <v>3430</v>
+        <v>98</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>NAIK.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C512" s="2" t="n">
-        <v>11.96</v>
+        <v>23.29</v>
       </c>
       <c r="D512" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E512" s="3" t="n">
-        <v>92</v>
+        <v>3000</v>
       </c>
       <c r="F512" s="3" t="n">
-        <v>103</v>
+        <v>3970</v>
       </c>
       <c r="G512" s="3" t="n">
-        <v>98</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="513">
@@ -14565,25 +14573,25 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C524" s="2" t="n">
-        <v>25</v>
+        <v>10.94</v>
       </c>
       <c r="D524" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E524" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F524" s="3" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G524" s="3" t="n">
         <v>68</v>
@@ -14592,25 +14600,25 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C525" s="2" t="n">
-        <v>10.94</v>
+        <v>25</v>
       </c>
       <c r="D525" s="2" t="n">
         <v>6.25</v>
       </c>
       <c r="E525" s="3" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F525" s="3" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G525" s="3" t="n">
         <v>68</v>
@@ -14727,55 +14735,55 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C530" s="2" t="n">
-        <v>14.78</v>
+        <v>10.43</v>
       </c>
       <c r="D530" s="2" t="n">
         <v>6.09</v>
       </c>
       <c r="E530" s="3" t="n">
-        <v>232</v>
+        <v>117</v>
       </c>
       <c r="F530" s="3" t="n">
-        <v>264</v>
+        <v>127</v>
       </c>
       <c r="G530" s="3" t="n">
-        <v>244</v>
+        <v>122</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C531" s="2" t="n">
-        <v>10.43</v>
+        <v>14.78</v>
       </c>
       <c r="D531" s="2" t="n">
         <v>6.09</v>
       </c>
       <c r="E531" s="3" t="n">
-        <v>117</v>
+        <v>232</v>
       </c>
       <c r="F531" s="3" t="n">
-        <v>127</v>
+        <v>264</v>
       </c>
       <c r="G531" s="3" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
     </row>
     <row r="532">
@@ -14903,7 +14911,9 @@
       <c r="D536" s="2" t="n">
         <v>6.02</v>
       </c>
-      <c r="E536" s="3" t="inlineStr"/>
+      <c r="E536" s="3" t="n">
+        <v>268</v>
+      </c>
       <c r="F536" s="3" t="n">
         <v>298</v>
       </c>
@@ -15184,82 +15194,82 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>SEMA.JK</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C547" s="2" t="n">
-        <v>25</v>
+        <v>15.38</v>
       </c>
       <c r="D547" s="2" t="n">
         <v>5.77</v>
       </c>
       <c r="E547" s="3" t="n">
-        <v>1095</v>
+        <v>105</v>
       </c>
       <c r="F547" s="3" t="n">
-        <v>1300</v>
+        <v>120</v>
       </c>
       <c r="G547" s="3" t="n">
-        <v>1100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>KOPI.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C548" s="2" t="n">
-        <v>20.19</v>
+        <v>25</v>
       </c>
       <c r="D548" s="2" t="n">
         <v>5.77</v>
       </c>
       <c r="E548" s="3" t="n">
-        <v>210</v>
+        <v>1095</v>
       </c>
       <c r="F548" s="3" t="n">
-        <v>250</v>
+        <v>1300</v>
       </c>
       <c r="G548" s="3" t="n">
-        <v>220</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>SEMA.JK</t>
+          <t>KOPI.JK</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C549" s="2" t="n">
-        <v>15.38</v>
+        <v>20.19</v>
       </c>
       <c r="D549" s="2" t="n">
         <v>5.77</v>
       </c>
       <c r="E549" s="3" t="n">
-        <v>105</v>
+        <v>210</v>
       </c>
       <c r="F549" s="3" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="G549" s="3" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
     </row>
     <row r="550">
@@ -15373,55 +15383,55 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C554" s="2" t="n">
-        <v>15.43</v>
+        <v>13.33</v>
       </c>
       <c r="D554" s="2" t="n">
         <v>5.71</v>
       </c>
       <c r="E554" s="3" t="n">
-        <v>360</v>
+        <v>1055</v>
       </c>
       <c r="F554" s="3" t="n">
-        <v>404</v>
+        <v>1190</v>
       </c>
       <c r="G554" s="3" t="n">
-        <v>370</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>VICI.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C555" s="2" t="n">
-        <v>13.33</v>
+        <v>15.43</v>
       </c>
       <c r="D555" s="2" t="n">
         <v>5.71</v>
       </c>
       <c r="E555" s="3" t="n">
-        <v>1055</v>
+        <v>360</v>
       </c>
       <c r="F555" s="3" t="n">
-        <v>1190</v>
+        <v>404</v>
       </c>
       <c r="G555" s="3" t="n">
-        <v>1110</v>
+        <v>370</v>
       </c>
     </row>
     <row r="556">
@@ -15481,16 +15491,16 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>LAJU.JK</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C558" s="2" t="n">
-        <v>22.54</v>
+        <v>16.9</v>
       </c>
       <c r="D558" s="2" t="n">
         <v>5.63</v>
@@ -15499,7 +15509,7 @@
         <v>72</v>
       </c>
       <c r="F558" s="3" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G558" s="3" t="n">
         <v>75</v>
@@ -15508,16 +15518,16 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>LAJU.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C559" s="2" t="n">
-        <v>16.9</v>
+        <v>22.54</v>
       </c>
       <c r="D559" s="2" t="n">
         <v>5.63</v>
@@ -15526,7 +15536,7 @@
         <v>72</v>
       </c>
       <c r="F559" s="3" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G559" s="3" t="n">
         <v>75</v>
@@ -15616,55 +15626,55 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>SOTS.JK</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C563" s="2" t="n">
-        <v>15.87</v>
+        <v>17.46</v>
       </c>
       <c r="D563" s="2" t="n">
         <v>5.56</v>
       </c>
       <c r="E563" s="3" t="n">
-        <v>133</v>
+        <v>645</v>
       </c>
       <c r="F563" s="3" t="n">
-        <v>146</v>
+        <v>740</v>
       </c>
       <c r="G563" s="3" t="n">
-        <v>133</v>
+        <v>665</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>SOTS.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C564" s="2" t="n">
-        <v>17.46</v>
+        <v>15.87</v>
       </c>
       <c r="D564" s="2" t="n">
         <v>5.56</v>
       </c>
       <c r="E564" s="3" t="n">
-        <v>645</v>
+        <v>133</v>
       </c>
       <c r="F564" s="3" t="n">
-        <v>740</v>
+        <v>146</v>
       </c>
       <c r="G564" s="3" t="n">
-        <v>665</v>
+        <v>133</v>
       </c>
     </row>
     <row r="565">
@@ -15832,55 +15842,55 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>PPRI.JK</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C571" s="2" t="n">
-        <v>11.58</v>
+        <v>22.81</v>
       </c>
       <c r="D571" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E571" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>171</v>
       </c>
       <c r="F571" s="3" t="n">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="G571" s="3" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>PPRI.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C572" s="2" t="n">
-        <v>22.81</v>
+        <v>11.58</v>
       </c>
       <c r="D572" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E572" s="3" t="n">
-        <v>171</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F572" s="3" t="n">
-        <v>210</v>
+        <v>106</v>
       </c>
       <c r="G572" s="3" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
     </row>
     <row r="573">
@@ -16156,55 +16166,55 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>BIPP.JK</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C583" s="2" t="n">
-        <v>17.5</v>
+        <v>13.33</v>
       </c>
       <c r="D583" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E583" s="3" t="n">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="F583" s="3" t="n">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="G583" s="3" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>BIPP.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C584" s="2" t="n">
-        <v>13.33</v>
+        <v>17.5</v>
       </c>
       <c r="D584" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E584" s="3" t="n">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="F584" s="3" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="G584" s="3" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
     </row>
     <row r="585">
@@ -16318,55 +16328,55 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>BWPT.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C589" s="2" t="n">
-        <v>10.78</v>
+        <v>15.69</v>
       </c>
       <c r="D589" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E589" s="3" t="n">
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="F589" s="3" t="n">
-        <v>113</v>
+        <v>236</v>
       </c>
       <c r="G589" s="3" t="n">
-        <v>107</v>
+        <v>214</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>BWPT.JK</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C590" s="2" t="n">
-        <v>15.69</v>
+        <v>10.78</v>
       </c>
       <c r="D590" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E590" s="3" t="n">
-        <v>230</v>
+        <v>104</v>
       </c>
       <c r="F590" s="3" t="n">
-        <v>236</v>
+        <v>113</v>
       </c>
       <c r="G590" s="3" t="n">
-        <v>214</v>
+        <v>107</v>
       </c>
     </row>
     <row r="591">
@@ -16480,55 +16490,55 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>PURA.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C595" s="2" t="n">
-        <v>14.29</v>
+        <v>22.22</v>
       </c>
       <c r="D595" s="2" t="n">
         <v>4.76</v>
       </c>
       <c r="E595" s="3" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F595" s="3" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="G595" s="3" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>PURA.JK</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C596" s="2" t="n">
-        <v>22.22</v>
+        <v>14.29</v>
       </c>
       <c r="D596" s="2" t="n">
         <v>4.76</v>
       </c>
       <c r="E596" s="3" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="F596" s="3" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G596" s="3" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
     </row>
     <row r="597">
@@ -16642,55 +16652,55 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>NASA.JK</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C601" s="2" t="n">
-        <v>11.63</v>
+        <v>20.93</v>
       </c>
       <c r="D601" s="2" t="n">
         <v>4.65</v>
       </c>
       <c r="E601" s="3" t="n">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="F601" s="3" t="n">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="G601" s="3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>NASA.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C602" s="2" t="n">
-        <v>20.93</v>
+        <v>11.63</v>
       </c>
       <c r="D602" s="2" t="n">
         <v>4.65</v>
       </c>
       <c r="E602" s="3" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="F602" s="3" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="G602" s="3" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
     </row>
     <row r="603">
@@ -16723,25 +16733,25 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C604" s="2" t="n">
-        <v>12.21</v>
+        <v>10.69</v>
       </c>
       <c r="D604" s="2" t="n">
         <v>4.58</v>
       </c>
       <c r="E604" s="3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F604" s="3" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G604" s="3" t="n">
         <v>274</v>
@@ -16750,25 +16760,25 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C605" s="2" t="n">
-        <v>10.69</v>
+        <v>12.21</v>
       </c>
       <c r="D605" s="2" t="n">
         <v>4.58</v>
       </c>
       <c r="E605" s="3" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F605" s="3" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G605" s="3" t="n">
         <v>274</v>
@@ -16885,55 +16895,55 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>BBYB.JK</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C610" s="2" t="n">
-        <v>20.49</v>
+        <v>10.53</v>
       </c>
       <c r="D610" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E610" s="3" t="n">
-        <v>2470</v>
+        <v>266</v>
       </c>
       <c r="F610" s="3" t="n">
-        <v>2940</v>
+        <v>294</v>
       </c>
       <c r="G610" s="3" t="n">
-        <v>2550</v>
+        <v>278</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>BBYB.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C611" s="2" t="n">
-        <v>10.53</v>
+        <v>20.49</v>
       </c>
       <c r="D611" s="2" t="n">
         <v>4.51</v>
       </c>
       <c r="E611" s="3" t="n">
-        <v>266</v>
+        <v>2470</v>
       </c>
       <c r="F611" s="3" t="n">
-        <v>294</v>
+        <v>2940</v>
       </c>
       <c r="G611" s="3" t="n">
-        <v>278</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="612">
@@ -17101,55 +17111,55 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>ARII.JK</t>
+          <t>POLI.JK</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C618" s="2" t="n">
-        <v>10.06</v>
+        <v>20.88</v>
       </c>
       <c r="D618" s="2" t="n">
         <v>4.4</v>
       </c>
       <c r="E618" s="3" t="n">
-        <v>324</v>
+        <v>895</v>
       </c>
       <c r="F618" s="3" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="G618" s="3" t="n">
-        <v>332</v>
+        <v>950</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>POLI.JK</t>
+          <t>ARII.JK</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C619" s="2" t="n">
-        <v>20.88</v>
+        <v>10.06</v>
       </c>
       <c r="D619" s="2" t="n">
         <v>4.4</v>
       </c>
       <c r="E619" s="3" t="n">
-        <v>895</v>
+        <v>324</v>
       </c>
       <c r="F619" s="3" t="n">
-        <v>1100</v>
+        <v>350</v>
       </c>
       <c r="G619" s="3" t="n">
-        <v>950</v>
+        <v>332</v>
       </c>
     </row>
     <row r="620">
@@ -17317,25 +17327,25 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>OPMS.JK</t>
+          <t>SEMA.JK</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C626" s="2" t="n">
-        <v>19.66</v>
+        <v>14.53</v>
       </c>
       <c r="D626" s="2" t="n">
         <v>4.27</v>
       </c>
       <c r="E626" s="3" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F626" s="3" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G626" s="3" t="n">
         <v>122</v>
@@ -17344,25 +17354,25 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>SEMA.JK</t>
+          <t>OPMS.JK</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C627" s="2" t="n">
-        <v>14.53</v>
+        <v>19.66</v>
       </c>
       <c r="D627" s="2" t="n">
         <v>4.27</v>
       </c>
       <c r="E627" s="3" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F627" s="3" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G627" s="3" t="n">
         <v>122</v>
@@ -17533,28 +17543,28 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C634" s="2" t="n">
-        <v>10.67</v>
+        <v>15</v>
       </c>
       <c r="D634" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E634" s="3" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="F634" s="3" t="n">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="G634" s="3" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
     </row>
     <row r="635">
@@ -17587,28 +17597,28 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C636" s="2" t="n">
-        <v>15</v>
+        <v>10.67</v>
       </c>
       <c r="D636" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E636" s="3" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="F636" s="3" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="G636" s="3" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="637">
@@ -17641,55 +17651,55 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>MPRO.JK</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C638" s="2" t="n">
-        <v>21.78</v>
+        <v>20</v>
       </c>
       <c r="D638" s="2" t="n">
         <v>3.96</v>
       </c>
       <c r="E638" s="3" t="n">
-        <v>102</v>
+        <v>16650</v>
       </c>
       <c r="F638" s="3" t="n">
-        <v>123</v>
+        <v>16650</v>
       </c>
       <c r="G638" s="3" t="n">
-        <v>105</v>
+        <v>14425</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>MPRO.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C639" s="2" t="n">
-        <v>20</v>
+        <v>21.78</v>
       </c>
       <c r="D639" s="2" t="n">
         <v>3.96</v>
       </c>
       <c r="E639" s="3" t="n">
-        <v>16650</v>
+        <v>102</v>
       </c>
       <c r="F639" s="3" t="n">
-        <v>16650</v>
+        <v>123</v>
       </c>
       <c r="G639" s="3" t="n">
-        <v>14425</v>
+        <v>105</v>
       </c>
     </row>
     <row r="640">
@@ -18073,55 +18083,55 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>MPIX.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C654" s="2" t="n">
-        <v>12.07</v>
+        <v>15.52</v>
       </c>
       <c r="D654" s="2" t="n">
         <v>3.45</v>
       </c>
       <c r="E654" s="3" t="n">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="F654" s="3" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="G654" s="3" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>MPIX.JK</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C655" s="2" t="n">
-        <v>15.52</v>
+        <v>12.07</v>
       </c>
       <c r="D655" s="2" t="n">
         <v>3.45</v>
       </c>
       <c r="E655" s="3" t="n">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="F655" s="3" t="n">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="G655" s="3" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="656">
@@ -18154,55 +18164,55 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>GUNA.JK</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C657" s="2" t="n">
-        <v>12.45</v>
+        <v>10.23</v>
       </c>
       <c r="D657" s="2" t="n">
         <v>3.41</v>
       </c>
       <c r="E657" s="3" t="n">
-        <v>545</v>
+        <v>178</v>
       </c>
       <c r="F657" s="3" t="n">
-        <v>560</v>
+        <v>194</v>
       </c>
       <c r="G657" s="3" t="n">
-        <v>515</v>
+        <v>182</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>GUNA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C658" s="2" t="n">
-        <v>10.23</v>
+        <v>12.45</v>
       </c>
       <c r="D658" s="2" t="n">
         <v>3.41</v>
       </c>
       <c r="E658" s="3" t="n">
-        <v>178</v>
+        <v>545</v>
       </c>
       <c r="F658" s="3" t="n">
-        <v>194</v>
+        <v>560</v>
       </c>
       <c r="G658" s="3" t="n">
-        <v>182</v>
+        <v>515</v>
       </c>
     </row>
     <row r="659">
@@ -18262,55 +18272,55 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>TNCA.JK</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C661" s="2" t="n">
-        <v>17.51</v>
+        <v>11.24</v>
       </c>
       <c r="D661" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E661" s="3" t="n">
-        <v>3180</v>
+        <v>180</v>
       </c>
       <c r="F661" s="3" t="n">
-        <v>3490</v>
+        <v>198</v>
       </c>
       <c r="G661" s="3" t="n">
-        <v>3070</v>
+        <v>184</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>TNCA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C662" s="2" t="n">
-        <v>11.24</v>
+        <v>17.51</v>
       </c>
       <c r="D662" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E662" s="3" t="n">
-        <v>180</v>
+        <v>3180</v>
       </c>
       <c r="F662" s="3" t="n">
-        <v>198</v>
+        <v>3490</v>
       </c>
       <c r="G662" s="3" t="n">
-        <v>184</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="663">
@@ -18424,28 +18434,28 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C667" s="2" t="n">
-        <v>10.66</v>
+        <v>19.4</v>
       </c>
       <c r="D667" s="2" t="n">
         <v>3.28</v>
       </c>
       <c r="E667" s="3" t="n">
-        <v>246</v>
+        <v>1670</v>
       </c>
       <c r="F667" s="3" t="n">
-        <v>270</v>
+        <v>2000</v>
       </c>
       <c r="G667" s="3" t="n">
-        <v>252</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="668">
@@ -18478,28 +18488,28 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C669" s="2" t="n">
-        <v>19.4</v>
+        <v>10.66</v>
       </c>
       <c r="D669" s="2" t="n">
         <v>3.28</v>
       </c>
       <c r="E669" s="3" t="n">
-        <v>1670</v>
+        <v>246</v>
       </c>
       <c r="F669" s="3" t="n">
-        <v>2000</v>
+        <v>270</v>
       </c>
       <c r="G669" s="3" t="n">
-        <v>1730</v>
+        <v>252</v>
       </c>
     </row>
     <row r="670">
@@ -18532,109 +18542,109 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C671" s="2" t="n">
-        <v>19.35</v>
+        <v>11.83</v>
       </c>
       <c r="D671" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E671" s="3" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F671" s="3" t="n">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="G671" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C672" s="2" t="n">
-        <v>11.83</v>
+        <v>19.35</v>
       </c>
       <c r="D672" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E672" s="3" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F672" s="3" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="G672" s="3" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C673" s="2" t="n">
-        <v>23.66</v>
+        <v>15.48</v>
       </c>
       <c r="D673" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E673" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>850</v>
       </c>
       <c r="F673" s="3" t="n">
-        <v>460</v>
+        <v>895</v>
       </c>
       <c r="G673" s="3" t="n">
-        <v>384</v>
+        <v>800</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C674" s="2" t="n">
-        <v>15.48</v>
+        <v>23.66</v>
       </c>
       <c r="D674" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E674" s="3" t="n">
-        <v>850</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F674" s="3" t="n">
-        <v>895</v>
+        <v>460</v>
       </c>
       <c r="G674" s="3" t="n">
-        <v>800</v>
+        <v>384</v>
       </c>
     </row>
     <row r="675">
@@ -18775,55 +18785,55 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C680" s="2" t="n">
-        <v>14.71</v>
+        <v>17.65</v>
       </c>
       <c r="D680" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E680" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="F680" s="3" t="n">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="G680" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C681" s="2" t="n">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
       <c r="D681" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E681" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="F681" s="3" t="n">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="G681" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
     </row>
     <row r="682">
@@ -18856,55 +18866,55 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>PBID.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C683" s="2" t="n">
-        <v>10.68</v>
+        <v>11.63</v>
       </c>
       <c r="D683" s="2" t="n">
         <v>2.91</v>
       </c>
       <c r="E683" s="3" t="n">
-        <v>515</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F683" s="3" t="n">
-        <v>570</v>
+        <v>192</v>
       </c>
       <c r="G683" s="3" t="n">
-        <v>530</v>
+        <v>177</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>PBID.JK</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C684" s="2" t="n">
-        <v>11.63</v>
+        <v>10.68</v>
       </c>
       <c r="D684" s="2" t="n">
         <v>2.91</v>
       </c>
       <c r="E684" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>515</v>
       </c>
       <c r="F684" s="3" t="n">
-        <v>192</v>
+        <v>570</v>
       </c>
       <c r="G684" s="3" t="n">
-        <v>177</v>
+        <v>530</v>
       </c>
     </row>
     <row r="685">
@@ -18991,55 +19001,55 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C688" s="2" t="n">
-        <v>12.15</v>
+        <v>11.89</v>
       </c>
       <c r="D688" s="2" t="n">
         <v>2.8</v>
       </c>
       <c r="E688" s="3" t="n">
-        <v>109</v>
+        <v>286.4117805325255</v>
       </c>
       <c r="F688" s="3" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="G688" s="3" t="n">
-        <v>110</v>
+        <v>294</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C689" s="2" t="n">
-        <v>11.89</v>
+        <v>12.15</v>
       </c>
       <c r="D689" s="2" t="n">
         <v>2.8</v>
       </c>
       <c r="E689" s="3" t="n">
-        <v>286.4117805325255</v>
+        <v>109</v>
       </c>
       <c r="F689" s="3" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="G689" s="3" t="n">
-        <v>294</v>
+        <v>110</v>
       </c>
     </row>
     <row r="690">
@@ -19180,163 +19190,163 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C695" s="2" t="n">
-        <v>10.39</v>
+        <v>14.58</v>
       </c>
       <c r="D695" s="2" t="n">
         <v>2.6</v>
       </c>
       <c r="E695" s="3" t="n">
-        <v>72.38636016845703</v>
+        <v>1065</v>
       </c>
       <c r="F695" s="3" t="n">
-        <v>85</v>
+        <v>1100</v>
       </c>
       <c r="G695" s="3" t="n">
-        <v>79</v>
+        <v>985</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C696" s="2" t="n">
-        <v>14.58</v>
+        <v>10.39</v>
       </c>
       <c r="D696" s="2" t="n">
         <v>2.6</v>
       </c>
       <c r="E696" s="3" t="n">
-        <v>1065</v>
+        <v>72.38636016845703</v>
       </c>
       <c r="F696" s="3" t="n">
-        <v>1100</v>
+        <v>85</v>
       </c>
       <c r="G696" s="3" t="n">
-        <v>985</v>
+        <v>79</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C697" s="2" t="n">
-        <v>17.95</v>
+        <v>17.09</v>
       </c>
       <c r="D697" s="2" t="n">
         <v>2.56</v>
       </c>
       <c r="E697" s="3" t="n">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="F697" s="3" t="n">
-        <v>92</v>
+        <v>274</v>
       </c>
       <c r="G697" s="3" t="n">
-        <v>80</v>
+        <v>240</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C698" s="2" t="n">
-        <v>17.09</v>
+        <v>17.95</v>
       </c>
       <c r="D698" s="2" t="n">
         <v>2.56</v>
       </c>
       <c r="E698" s="3" t="n">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="F698" s="3" t="n">
-        <v>274</v>
+        <v>92</v>
       </c>
       <c r="G698" s="3" t="n">
-        <v>240</v>
+        <v>80</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>LAND.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C699" s="2" t="n">
-        <v>10.13</v>
+        <v>25</v>
       </c>
       <c r="D699" s="2" t="n">
         <v>2.53</v>
       </c>
       <c r="E699" s="3" t="n">
-        <v>78</v>
+        <v>1975</v>
       </c>
       <c r="F699" s="3" t="n">
-        <v>87</v>
+        <v>1975</v>
       </c>
       <c r="G699" s="3" t="n">
-        <v>81</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>LAND.JK</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C700" s="2" t="n">
-        <v>25</v>
+        <v>10.13</v>
       </c>
       <c r="D700" s="2" t="n">
         <v>2.53</v>
       </c>
       <c r="E700" s="3" t="n">
-        <v>1975</v>
+        <v>78</v>
       </c>
       <c r="F700" s="3" t="n">
-        <v>1975</v>
+        <v>87</v>
       </c>
       <c r="G700" s="3" t="n">
-        <v>1620</v>
+        <v>81</v>
       </c>
     </row>
     <row r="701">
@@ -19450,55 +19460,55 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>LABA.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C705" s="2" t="n">
-        <v>14.73</v>
+        <v>17.44</v>
       </c>
       <c r="D705" s="2" t="n">
         <v>2.33</v>
       </c>
       <c r="E705" s="3" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="F705" s="3" t="n">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="G705" s="3" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>LABA.JK</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C706" s="2" t="n">
-        <v>17.44</v>
+        <v>14.73</v>
       </c>
       <c r="D706" s="2" t="n">
         <v>2.33</v>
       </c>
       <c r="E706" s="3" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="F706" s="3" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="G706" s="3" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
     </row>
     <row r="707">
@@ -19585,55 +19595,55 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>INAI.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C710" s="2" t="n">
-        <v>13.48</v>
+        <v>12.36</v>
       </c>
       <c r="D710" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E710" s="3" t="n">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F710" s="3" t="n">
-        <v>202</v>
+        <v>100</v>
       </c>
       <c r="G710" s="3" t="n">
-        <v>182</v>
+        <v>91</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>INAI.JK</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C711" s="2" t="n">
-        <v>12.36</v>
+        <v>13.48</v>
       </c>
       <c r="D711" s="2" t="n">
         <v>2.25</v>
       </c>
       <c r="E711" s="3" t="n">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="F711" s="3" t="n">
-        <v>100</v>
+        <v>202</v>
       </c>
       <c r="G711" s="3" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
     </row>
     <row r="712">
@@ -19855,25 +19865,25 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C720" s="2" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D720" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E720" s="3" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F720" s="3" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="G720" s="3" t="n">
         <v>204</v>
@@ -19882,25 +19892,25 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C721" s="2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D721" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E721" s="3" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F721" s="3" t="n">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="G721" s="3" t="n">
         <v>204</v>
@@ -20017,25 +20027,25 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DOSS.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C726" s="2" t="n">
-        <v>19.38</v>
+        <v>15.62</v>
       </c>
       <c r="D726" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="E726" s="3" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="F726" s="3" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G726" s="3" t="n">
         <v>163</v>
@@ -20044,25 +20054,25 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>DOSS.JK</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C727" s="2" t="n">
-        <v>15.62</v>
+        <v>19.38</v>
       </c>
       <c r="D727" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="E727" s="3" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F727" s="3" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G727" s="3" t="n">
         <v>163</v>
@@ -20366,55 +20376,55 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>LAND.JK</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C739" s="2" t="n">
-        <v>11.83</v>
+        <v>11.29</v>
       </c>
       <c r="D739" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E739" s="3" t="n">
-        <v>181.15625</v>
+        <v>62</v>
       </c>
       <c r="F739" s="3" t="n">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="G739" s="3" t="n">
-        <v>189</v>
+        <v>63</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>LAND.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C740" s="2" t="n">
-        <v>11.29</v>
+        <v>11.83</v>
       </c>
       <c r="D740" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E740" s="3" t="n">
-        <v>62</v>
+        <v>181.15625</v>
       </c>
       <c r="F740" s="3" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="G740" s="3" t="n">
-        <v>63</v>
+        <v>189</v>
       </c>
     </row>
     <row r="741">
@@ -20555,55 +20565,55 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>PYFA.JK</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C746" s="2" t="n">
-        <v>24.4</v>
+        <v>13.77</v>
       </c>
       <c r="D746" s="2" t="n">
         <v>1.45</v>
       </c>
       <c r="E746" s="3" t="n">
-        <v>480</v>
+        <v>296</v>
       </c>
       <c r="F746" s="3" t="n">
-        <v>515</v>
+        <v>314</v>
       </c>
       <c r="G746" s="3" t="n">
-        <v>420</v>
+        <v>280</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>PYFA.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C747" s="2" t="n">
-        <v>13.77</v>
+        <v>24.4</v>
       </c>
       <c r="D747" s="2" t="n">
         <v>1.45</v>
       </c>
       <c r="E747" s="3" t="n">
-        <v>296</v>
+        <v>480</v>
       </c>
       <c r="F747" s="3" t="n">
-        <v>314</v>
+        <v>515</v>
       </c>
       <c r="G747" s="3" t="n">
-        <v>280</v>
+        <v>420</v>
       </c>
     </row>
     <row r="748">
@@ -21095,82 +21105,82 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>PORT.JK</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C766" s="2" t="n">
-        <v>10.17</v>
+        <v>16.38</v>
       </c>
       <c r="D766" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E766" s="3" t="n">
-        <v>177</v>
+        <v>1015</v>
       </c>
       <c r="F766" s="3" t="n">
-        <v>195</v>
+        <v>1030</v>
       </c>
       <c r="G766" s="3" t="n">
-        <v>178</v>
+        <v>890</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>PORT.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C767" s="2" t="n">
-        <v>16.38</v>
+        <v>20</v>
       </c>
       <c r="D767" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E767" s="3" t="n">
-        <v>1015</v>
+        <v>406</v>
       </c>
       <c r="F767" s="3" t="n">
-        <v>1030</v>
+        <v>432</v>
       </c>
       <c r="G767" s="3" t="n">
-        <v>890</v>
+        <v>362</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C768" s="2" t="n">
-        <v>20</v>
+        <v>10.17</v>
       </c>
       <c r="D768" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E768" s="3" t="n">
-        <v>406</v>
+        <v>177</v>
       </c>
       <c r="F768" s="3" t="n">
-        <v>432</v>
+        <v>195</v>
       </c>
       <c r="G768" s="3" t="n">
-        <v>362</v>
+        <v>178</v>
       </c>
     </row>
     <row r="769">
@@ -21203,55 +21213,55 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C770" s="2" t="n">
-        <v>11.43</v>
+        <v>11.96</v>
       </c>
       <c r="D770" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="E770" s="3" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F770" s="3" t="n">
         <v>468</v>
       </c>
       <c r="G770" s="3" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C771" s="2" t="n">
-        <v>11.96</v>
+        <v>11.43</v>
       </c>
       <c r="D771" s="2" t="n">
         <v>0.48</v>
       </c>
       <c r="E771" s="3" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F771" s="3" t="n">
         <v>468</v>
       </c>
       <c r="G771" s="3" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="772">
@@ -21311,433 +21321,433 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>AISA.JK</t>
+          <t>RELI.JK</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C774" s="2" t="n">
-        <v>12.9</v>
+        <v>14.29</v>
       </c>
       <c r="D774" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E774" s="3" t="n">
-        <v>128</v>
+        <v>520</v>
       </c>
       <c r="F774" s="3" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="G774" s="3" t="n">
-        <v>124</v>
+        <v>525</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>RELI.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C775" s="2" t="n">
-        <v>14.29</v>
+        <v>27.33</v>
       </c>
       <c r="D775" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E775" s="3" t="n">
-        <v>520</v>
+        <v>152</v>
       </c>
       <c r="F775" s="3" t="n">
-        <v>600</v>
+        <v>191</v>
       </c>
       <c r="G775" s="3" t="n">
-        <v>525</v>
+        <v>150</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>BEKS.JK</t>
+          <t>PDES.JK</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C776" s="2" t="n">
-        <v>11.11</v>
+        <v>18.01</v>
       </c>
       <c r="D776" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E776" s="3" t="n">
-        <v>38</v>
+        <v>424</v>
       </c>
       <c r="F776" s="3" t="n">
-        <v>40</v>
+        <v>498</v>
       </c>
       <c r="G776" s="3" t="n">
-        <v>36</v>
+        <v>422</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>AISA.JK</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C777" s="2" t="n">
-        <v>12.38</v>
+        <v>12.9</v>
       </c>
       <c r="D777" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E777" s="3" t="n">
-        <v>91.91489410400391</v>
+        <v>128</v>
       </c>
       <c r="F777" s="3" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="G777" s="3" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>MPRO.JK</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C778" s="2" t="n">
-        <v>12.78</v>
+        <v>19.95</v>
       </c>
       <c r="D778" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E778" s="3" t="n">
-        <v>2640</v>
+        <v>11750</v>
       </c>
       <c r="F778" s="3" t="n">
-        <v>3000</v>
+        <v>11875</v>
       </c>
       <c r="G778" s="3" t="n">
-        <v>2660</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>KREN.JK</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C779" s="2" t="n">
-        <v>17.65</v>
+        <v>10.53</v>
       </c>
       <c r="D779" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E779" s="3" t="n">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="F779" s="3" t="n">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="G779" s="3" t="n">
-        <v>170</v>
+        <v>19</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>TAXI.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C780" s="2" t="n">
-        <v>11.11</v>
+        <v>12.87</v>
       </c>
       <c r="D780" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E780" s="3" t="n">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="F780" s="3" t="n">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="G780" s="3" t="n">
-        <v>18</v>
+        <v>101</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>BTEK.JK</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C781" s="2" t="n">
-        <v>27.33</v>
+        <v>14.29</v>
       </c>
       <c r="D781" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E781" s="3" t="n">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="F781" s="3" t="n">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="G781" s="3" t="n">
-        <v>150</v>
+        <v>14</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>PDES.JK</t>
+          <t>BEKS.JK</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C782" s="2" t="n">
-        <v>18.01</v>
+        <v>11.11</v>
       </c>
       <c r="D782" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E782" s="3" t="n">
-        <v>424</v>
+        <v>38</v>
       </c>
       <c r="F782" s="3" t="n">
-        <v>498</v>
+        <v>40</v>
       </c>
       <c r="G782" s="3" t="n">
-        <v>422</v>
+        <v>36</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>ISEA.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C783" s="2" t="n">
-        <v>11.25</v>
+        <v>10.91</v>
       </c>
       <c r="D783" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E783" s="3" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="F783" s="3" t="n">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="G783" s="3" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>SAFE.JK</t>
+          <t>KREN.JK</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C784" s="2" t="n">
-        <v>12.41</v>
+        <v>26.32</v>
       </c>
       <c r="D784" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E784" s="3" t="n">
-        <v>810</v>
+        <v>19</v>
       </c>
       <c r="F784" s="3" t="n">
-        <v>815</v>
+        <v>24</v>
       </c>
       <c r="G784" s="3" t="n">
-        <v>725</v>
+        <v>19</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>FISH.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C785" s="2" t="n">
-        <v>13.89</v>
+        <v>12.78</v>
       </c>
       <c r="D785" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E785" s="3" t="n">
-        <v>760</v>
+        <v>2640</v>
       </c>
       <c r="F785" s="3" t="n">
-        <v>820</v>
+        <v>3000</v>
       </c>
       <c r="G785" s="3" t="n">
-        <v>720</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C786" s="2" t="n">
-        <v>17.5</v>
+        <v>28.48</v>
       </c>
       <c r="D786" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E786" s="3" t="n">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="F786" s="3" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G786" s="3" t="n">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>KKES.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C787" s="2" t="n">
-        <v>11.43</v>
+        <v>17.65</v>
       </c>
       <c r="D787" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E787" s="3" t="n">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="F787" s="3" t="n">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="G787" s="3" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C788" s="2" t="n">
-        <v>10.76</v>
+        <v>10.26</v>
       </c>
       <c r="D788" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E788" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>79</v>
       </c>
       <c r="F788" s="3" t="n">
-        <v>3500</v>
+        <v>86</v>
       </c>
       <c r="G788" s="3" t="n">
-        <v>3160</v>
+        <v>78</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>TAXI.JK</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C789" s="2" t="n">
-        <v>12.87</v>
+        <v>11.11</v>
       </c>
       <c r="D789" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E789" s="3" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="F789" s="3" t="n">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="G789" s="3" t="n">
-        <v>101</v>
+        <v>18</v>
       </c>
     </row>
     <row r="790">
@@ -21770,190 +21780,190 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>SAFE.JK</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C791" s="2" t="n">
-        <v>10.26</v>
+        <v>12.41</v>
       </c>
       <c r="D791" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E791" s="3" t="n">
-        <v>79</v>
+        <v>810</v>
       </c>
       <c r="F791" s="3" t="n">
-        <v>86</v>
+        <v>815</v>
       </c>
       <c r="G791" s="3" t="n">
-        <v>78</v>
+        <v>725</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>BTEK.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C792" s="2" t="n">
-        <v>14.29</v>
+        <v>10.76</v>
       </c>
       <c r="D792" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E792" s="3" t="n">
-        <v>14</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F792" s="3" t="n">
-        <v>16</v>
+        <v>3500</v>
       </c>
       <c r="G792" s="3" t="n">
-        <v>14</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>KREN.JK</t>
+          <t>ISEA.JK</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C793" s="2" t="n">
-        <v>26.32</v>
+        <v>11.25</v>
       </c>
       <c r="D793" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E793" s="3" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="F793" s="3" t="n">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="G793" s="3" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>MPRO.JK</t>
+          <t>KKES.JK</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C794" s="2" t="n">
-        <v>19.95</v>
+        <v>11.43</v>
       </c>
       <c r="D794" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E794" s="3" t="n">
-        <v>11750</v>
+        <v>75</v>
       </c>
       <c r="F794" s="3" t="n">
-        <v>11875</v>
+        <v>78</v>
       </c>
       <c r="G794" s="3" t="n">
-        <v>9900</v>
+        <v>70</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>KREN.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C795" s="2" t="n">
-        <v>10.53</v>
+        <v>12.38</v>
       </c>
       <c r="D795" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E795" s="3" t="n">
-        <v>19</v>
+        <v>91.91489410400391</v>
       </c>
       <c r="F795" s="3" t="n">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="G795" s="3" t="n">
-        <v>19</v>
+        <v>105</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>FISH.JK</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C796" s="2" t="n">
-        <v>10.91</v>
+        <v>13.89</v>
       </c>
       <c r="D796" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E796" s="3" t="n">
-        <v>165</v>
+        <v>760</v>
       </c>
       <c r="F796" s="3" t="n">
-        <v>183</v>
+        <v>820</v>
       </c>
       <c r="G796" s="3" t="n">
-        <v>165</v>
+        <v>720</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C797" s="2" t="n">
-        <v>28.48</v>
+        <v>17.5</v>
       </c>
       <c r="D797" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E797" s="3" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F797" s="3" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G797" s="3" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="798">
@@ -23039,12 +23049,12 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C838" s="2" t="n">
@@ -23054,67 +23064,67 @@
         <v>-2.53</v>
       </c>
       <c r="E838" s="3" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="F838" s="3" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="G838" s="3" t="n">
-        <v>77</v>
+        <v>154</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C839" s="2" t="n">
-        <v>15.19</v>
+        <v>19.62</v>
       </c>
       <c r="D839" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E839" s="3" t="n">
-        <v>160</v>
+        <v>910</v>
       </c>
       <c r="F839" s="3" t="n">
-        <v>182</v>
+        <v>945</v>
       </c>
       <c r="G839" s="3" t="n">
-        <v>154</v>
+        <v>770</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C840" s="2" t="n">
-        <v>19.62</v>
+        <v>15.19</v>
       </c>
       <c r="D840" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E840" s="3" t="n">
-        <v>910</v>
+        <v>80</v>
       </c>
       <c r="F840" s="3" t="n">
-        <v>945</v>
+        <v>91</v>
       </c>
       <c r="G840" s="3" t="n">
-        <v>770</v>
+        <v>77</v>
       </c>
     </row>
     <row r="841">
@@ -23228,55 +23238,55 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>POLA.JK</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C845" s="2" t="n">
-        <v>17.36</v>
+        <v>12.04</v>
       </c>
       <c r="D845" s="2" t="n">
         <v>-2.78</v>
       </c>
       <c r="E845" s="3" t="n">
-        <v>720</v>
+        <v>110</v>
       </c>
       <c r="F845" s="3" t="n">
-        <v>845</v>
+        <v>121</v>
       </c>
       <c r="G845" s="3" t="n">
-        <v>700</v>
+        <v>105</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>POLA.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C846" s="2" t="n">
-        <v>12.04</v>
+        <v>17.36</v>
       </c>
       <c r="D846" s="2" t="n">
         <v>-2.78</v>
       </c>
       <c r="E846" s="3" t="n">
-        <v>110</v>
+        <v>720</v>
       </c>
       <c r="F846" s="3" t="n">
-        <v>121</v>
+        <v>845</v>
       </c>
       <c r="G846" s="3" t="n">
-        <v>105</v>
+        <v>700</v>
       </c>
     </row>
     <row r="847">
@@ -23930,16 +23940,16 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C871" s="2" t="n">
-        <v>20.24</v>
+        <v>15.48</v>
       </c>
       <c r="D871" s="2" t="n">
         <v>-4.76</v>
@@ -23948,7 +23958,7 @@
         <v>84</v>
       </c>
       <c r="F871" s="3" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G871" s="3" t="n">
         <v>80</v>
@@ -23957,16 +23967,16 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C872" s="2" t="n">
-        <v>15.48</v>
+        <v>20.24</v>
       </c>
       <c r="D872" s="2" t="n">
         <v>-4.76</v>
@@ -23975,7 +23985,7 @@
         <v>84</v>
       </c>
       <c r="F872" s="3" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G872" s="3" t="n">
         <v>80</v>
@@ -24038,55 +24048,55 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>POLA.JK</t>
+          <t>NASA.JK</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C875" s="2" t="n">
-        <v>13.33</v>
+        <v>17.5</v>
       </c>
       <c r="D875" s="2" t="n">
         <v>-5</v>
       </c>
       <c r="E875" s="3" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F875" s="3" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G875" s="3" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>NASA.JK</t>
+          <t>POLA.JK</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C876" s="2" t="n">
-        <v>17.5</v>
+        <v>13.33</v>
       </c>
       <c r="D876" s="2" t="n">
         <v>-5</v>
       </c>
       <c r="E876" s="3" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="F876" s="3" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G876" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="877">
@@ -24173,55 +24183,55 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C880" s="2" t="n">
-        <v>23.53</v>
+        <v>12.63</v>
       </c>
       <c r="D880" s="2" t="n">
         <v>-5.15</v>
       </c>
       <c r="E880" s="3" t="n">
-        <v>700</v>
+        <v>19500</v>
       </c>
       <c r="F880" s="3" t="n">
-        <v>840</v>
+        <v>21850</v>
       </c>
       <c r="G880" s="3" t="n">
-        <v>645</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C881" s="2" t="n">
-        <v>12.63</v>
+        <v>23.53</v>
       </c>
       <c r="D881" s="2" t="n">
         <v>-5.15</v>
       </c>
       <c r="E881" s="3" t="n">
-        <v>19500</v>
+        <v>700</v>
       </c>
       <c r="F881" s="3" t="n">
-        <v>21850</v>
+        <v>840</v>
       </c>
       <c r="G881" s="3" t="n">
-        <v>18400</v>
+        <v>645</v>
       </c>
     </row>
     <row r="882">
@@ -24254,55 +24264,55 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C883" s="2" t="n">
-        <v>21.24</v>
+        <v>13.58</v>
       </c>
       <c r="D883" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E883" s="3" t="n">
-        <v>1827.910536399762</v>
+        <v>162</v>
       </c>
       <c r="F883" s="3" t="n">
-        <v>1855</v>
+        <v>184</v>
       </c>
       <c r="G883" s="3" t="n">
-        <v>1445</v>
+        <v>153</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C884" s="2" t="n">
-        <v>13.58</v>
+        <v>21.24</v>
       </c>
       <c r="D884" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E884" s="3" t="n">
-        <v>162</v>
+        <v>1827.910536399762</v>
       </c>
       <c r="F884" s="3" t="n">
-        <v>184</v>
+        <v>1855</v>
       </c>
       <c r="G884" s="3" t="n">
-        <v>153</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="885">
@@ -24767,12 +24777,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>BEKS.JK</t>
+          <t>HADE.JK</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C902" s="2" t="n">
@@ -24782,7 +24792,7 @@
         <v>-6.9</v>
       </c>
       <c r="E902" s="3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F902" s="3" t="n">
         <v>34</v>
@@ -24794,12 +24804,12 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>HADE.JK</t>
+          <t>BEKS.JK</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C903" s="2" t="n">
@@ -24809,7 +24819,7 @@
         <v>-6.9</v>
       </c>
       <c r="E903" s="3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F903" s="3" t="n">
         <v>34</v>
@@ -26414,28 +26424,28 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C963" s="2" t="n">
-        <v>24.79</v>
+        <v>25</v>
       </c>
       <c r="D963" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E963" s="3" t="n">
-        <v>1510</v>
+        <v>165</v>
       </c>
       <c r="F963" s="3" t="n">
-        <v>1510</v>
+        <v>210</v>
       </c>
       <c r="G963" s="3" t="n">
-        <v>1030</v>
+        <v>143</v>
       </c>
     </row>
     <row r="964">
@@ -26468,80 +26478,80 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C965" s="2" t="n">
-        <v>25</v>
+        <v>24.79</v>
       </c>
       <c r="D965" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E965" s="3" t="n">
-        <v>165</v>
+        <v>1510</v>
       </c>
       <c r="F965" s="3" t="n">
-        <v>210</v>
+        <v>1510</v>
       </c>
       <c r="G965" s="3" t="n">
-        <v>143</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>CCSI.JK</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C966" s="2" t="n">
-        <v>18.44</v>
+        <v>19.15</v>
       </c>
       <c r="D966" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E966" s="3" t="inlineStr"/>
+      <c r="E966" s="3" t="n">
+        <v>525</v>
+      </c>
       <c r="F966" s="3" t="n">
-        <v>167</v>
+        <v>560</v>
       </c>
       <c r="G966" s="3" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>CCSI.JK</t>
+          <t>LCKM.JK</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C967" s="2" t="n">
-        <v>19.15</v>
+        <v>18.44</v>
       </c>
       <c r="D967" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E967" s="3" t="n">
-        <v>525</v>
-      </c>
+      <c r="E967" s="3" t="inlineStr"/>
       <c r="F967" s="3" t="n">
-        <v>560</v>
+        <v>167</v>
       </c>
       <c r="G967" s="3" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
     </row>
     <row r="968">
@@ -26628,55 +26638,55 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>INTD.JK</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C971" s="2" t="n">
-        <v>13.57</v>
+        <v>12.5</v>
       </c>
       <c r="D971" s="2" t="n">
         <v>-15</v>
       </c>
       <c r="E971" s="3" t="n">
-        <v>3010</v>
+        <v>320</v>
       </c>
       <c r="F971" s="3" t="n">
-        <v>3180</v>
+        <v>360</v>
       </c>
       <c r="G971" s="3" t="n">
-        <v>2380</v>
+        <v>272</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>INTD.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C972" s="2" t="n">
-        <v>12.5</v>
+        <v>13.57</v>
       </c>
       <c r="D972" s="2" t="n">
         <v>-15</v>
       </c>
       <c r="E972" s="3" t="n">
-        <v>320</v>
+        <v>3010</v>
       </c>
       <c r="F972" s="3" t="n">
-        <v>360</v>
+        <v>3180</v>
       </c>
       <c r="G972" s="3" t="n">
-        <v>272</v>
+        <v>2380</v>
       </c>
     </row>
   </sheetData>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -1129,39 +1129,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ANDI.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>30</v>
+        <v>1200</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>36</v>
+        <v>1375</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>35</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -1171,78 +1171,78 @@
         <v>25</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1190</v>
+        <v>432</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1200</v>
+        <v>520</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1200</v>
+        <v>520</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>ANDI.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>432</v>
+        <v>30</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>520</v>
+        <v>36</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>520</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>MLPT.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>119</v>
+        <v>1425</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>155</v>
+        <v>1625</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>145</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>PTSP.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1252,51 +1252,51 @@
         <v>25</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3310</v>
+        <v>1680</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3700</v>
+        <v>2250</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3700</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>3680</v>
+        <v>165</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4500</v>
+        <v>202</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1306,24 +1306,24 @@
         <v>25</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>290</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>350</v>
+        <v>545</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>350</v>
+        <v>545</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EKAD.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1333,24 +1333,24 @@
         <v>25</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>300</v>
+        <v>153.7625885009766</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BIKE.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1360,24 +1360,24 @@
         <v>25</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>755</v>
+        <v>1150</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>775</v>
+        <v>1225</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>775</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAFE.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1387,24 +1387,24 @@
         <v>25</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>550</v>
+        <v>1190</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>615</v>
+        <v>1200</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>615</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MLPT.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1414,24 +1414,24 @@
         <v>25</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1425</v>
+        <v>505</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1625</v>
+        <v>505</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1625</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>EKAD.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1441,24 +1441,24 @@
         <v>25</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>5000</v>
+        <v>300</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5025</v>
+        <v>300</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5025</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1468,24 +1468,24 @@
         <v>25</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1200</v>
+        <v>605</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1375</v>
+        <v>775</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1375</v>
+        <v>775</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PTSP.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1495,51 +1495,51 @@
         <v>25</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1680</v>
+        <v>434</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2250</v>
+        <v>515</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2250</v>
+        <v>515</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>165</v>
+        <v>3310</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>202</v>
+        <v>3700</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>200</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1549,13 +1549,13 @@
         <v>25</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>414.3801616703698</v>
+        <v>290</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>545</v>
+        <v>350</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>545</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42">
@@ -1588,12 +1588,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PTSP.JK</t>
+          <t>SAFE.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -1603,24 +1603,24 @@
         <v>25</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1470</v>
+        <v>550</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1800</v>
+        <v>615</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1800</v>
+        <v>615</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>BIKE.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -1630,51 +1630,51 @@
         <v>25</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1150</v>
+        <v>755</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1225</v>
+        <v>775</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1225</v>
+        <v>775</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>153.7625885009766</v>
+        <v>119</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>290</v>
+        <v>155</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>290</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>BLTZ.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -1684,13 +1684,13 @@
         <v>25</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>434</v>
+        <v>3040</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>515</v>
+        <v>3600</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>515</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="47">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -1711,24 +1711,24 @@
         <v>25</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>3040</v>
+        <v>3680</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>3600</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -1738,24 +1738,24 @@
         <v>25</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>505</v>
+        <v>5000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>505</v>
+        <v>5025</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>505</v>
+        <v>5025</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>PTSP.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -1765,24 +1765,24 @@
         <v>25</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>605</v>
+        <v>1470</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>775</v>
+        <v>1800</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>775</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ALDO.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -1792,13 +1792,13 @@
         <v>24.92</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1565</v>
+        <v>3210</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1955</v>
+        <v>4010</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1955</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="51">
@@ -1858,12 +1858,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>ALDO.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -1873,24 +1873,24 @@
         <v>24.92</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>3210</v>
+        <v>1565</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>4010</v>
+        <v>1955</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>4010</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -1900,24 +1900,24 @@
         <v>24.9</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1445</v>
+        <v>2580</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1605</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -1927,13 +1927,13 @@
         <v>24.9</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>2580</v>
+        <v>1445</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>3210</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="56">
@@ -1966,12 +1966,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -1981,24 +1981,24 @@
         <v>24.88</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>2170</v>
+        <v>1170</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>2510</v>
+        <v>1255</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>2510</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -2008,13 +2008,13 @@
         <v>24.88</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1170</v>
+        <v>2170</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1255</v>
+        <v>2510</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1255</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="59">
@@ -2101,55 +2101,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>SEMA.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>29.7</v>
+        <v>24.85</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>167</v>
+        <v>372</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>214</v>
+        <v>412</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>206</v>
+        <v>412</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEMA.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>24.85</v>
+        <v>29.7</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>24.85</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>372</v>
+        <v>167</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>412</v>
+        <v>214</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>412</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64">
@@ -2209,12 +2209,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PGLI.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -2224,24 +2224,24 @@
         <v>24.81</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2600</v>
+        <v>300</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>3220</v>
+        <v>332</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>3220</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PGLI.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -2251,24 +2251,24 @@
         <v>24.81</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>300</v>
+        <v>3220</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>332</v>
+        <v>3220</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>332</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -2278,7 +2278,7 @@
         <v>24.81</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>3220</v>
+        <v>2600</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>3220</v>
@@ -2290,12 +2290,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IFSH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -2305,24 +2305,24 @@
         <v>24.8</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1555</v>
+        <v>3070</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>1560</v>
+        <v>3070</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1560</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>IFSH.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -2332,24 +2332,24 @@
         <v>24.8</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>3070</v>
+        <v>1555</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>3070</v>
+        <v>1560</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>3070</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>NASI.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -2359,24 +2359,24 @@
         <v>24.79</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2580</v>
+        <v>262</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2970</v>
+        <v>292</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2970</v>
+        <v>292</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NASI.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -2386,13 +2386,13 @@
         <v>24.79</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>262</v>
+        <v>2580</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>292</v>
+        <v>2970</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>292</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="73">
@@ -2425,12 +2425,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BIKE.JK</t>
+          <t>BABY.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -2440,24 +2440,24 @@
         <v>24.77</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2270</v>
+        <v>226</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2670</v>
+        <v>272</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2670</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BABY.JK</t>
+          <t>BIKE.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -2467,24 +2467,24 @@
         <v>24.77</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>226</v>
+        <v>2270</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>272</v>
+        <v>2670</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>272</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>ASLI.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -2494,7 +2494,7 @@
         <v>24.76</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="F76" s="3" t="n">
         <v>262</v>
@@ -2506,12 +2506,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -2521,24 +2521,24 @@
         <v>24.76</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>525</v>
+        <v>214</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TFCO.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -2548,24 +2548,24 @@
         <v>24.76</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>1060</v>
+        <v>525</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>1285</v>
+        <v>655</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>1285</v>
+        <v>655</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ASLI.JK</t>
+          <t>TFCO.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -2575,13 +2575,13 @@
         <v>24.76</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>228</v>
+        <v>1060</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>262</v>
+        <v>1285</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>262</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="80">
@@ -2776,12 +2776,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>BLTZ.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -2791,24 +2791,24 @@
         <v>24.68</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>760</v>
+        <v>2330</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>960</v>
+        <v>2880</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>960</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -2818,13 +2818,13 @@
         <v>24.68</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2330</v>
+        <v>760</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2880</v>
+        <v>960</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>2880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="89">
@@ -3127,12 +3127,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BELI.JK</t>
+          <t>SAPX.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -3142,7 +3142,7 @@
         <v>24.54</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>406</v>
@@ -3154,12 +3154,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SAPX.JK</t>
+          <t>BELI.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -3169,7 +3169,7 @@
         <v>24.54</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>406</v>
@@ -3854,55 +3854,55 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>KOKA.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>30.71</v>
+        <v>24.6</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>21.43</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>143</v>
+        <v>690</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>183</v>
+        <v>785</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>170</v>
+        <v>765</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>24.6</v>
+        <v>30.71</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>21.43</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>690</v>
+        <v>143</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>785</v>
+        <v>183</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>765</v>
+        <v>170</v>
       </c>
     </row>
     <row r="129">
@@ -3962,55 +3962,55 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>22.22</v>
+        <v>22.92</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>20.83</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>730</v>
+        <v>290</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>880</v>
+        <v>354</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>870</v>
+        <v>348</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>22.92</v>
+        <v>22.22</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>20.83</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>290</v>
+        <v>730</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>354</v>
+        <v>880</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>348</v>
+        <v>870</v>
       </c>
     </row>
     <row r="133">
@@ -4259,55 +4259,55 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>20</v>
+        <v>24.85</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>20</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>6550</v>
+        <v>910</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>7800</v>
+        <v>1030</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>7800</v>
+        <v>990</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>24.85</v>
+        <v>20</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>20</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>910</v>
+        <v>6550</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>1030</v>
+        <v>7800</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>990</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="144">
@@ -5069,55 +5069,55 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>29.09</v>
+        <v>22.31</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>18.18</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>123</v>
+        <v>615</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>142</v>
+        <v>740</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>130</v>
+        <v>715</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>22.31</v>
+        <v>29.09</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>18.18</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>615</v>
+        <v>123</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>740</v>
+        <v>142</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>715</v>
+        <v>130</v>
       </c>
     </row>
     <row r="174">
@@ -6392,55 +6392,55 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MBSS.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="D221" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>3940</v>
+        <v>78</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>4600</v>
+        <v>98</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>4600</v>
+        <v>92</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>MBSS.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="D222" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>78</v>
+        <v>3940</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>98</v>
+        <v>4600</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>92</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="223">
@@ -6797,109 +6797,109 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MDIA.JK</t>
+          <t>ERAA.JK</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>30.77</v>
+        <v>17.31</v>
       </c>
       <c r="D236" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>106</v>
+        <v>515</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>136</v>
+        <v>610</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>119</v>
+        <v>595</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>VICI.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>19.07</v>
+        <v>21.4</v>
       </c>
       <c r="D237" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E237" s="3" t="n">
-        <v>1080</v>
+        <v>2200</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>1280</v>
+        <v>2610</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>1230</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ERAA.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>17.31</v>
+        <v>19.07</v>
       </c>
       <c r="D238" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>515</v>
+        <v>1080</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>610</v>
+        <v>1280</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>595</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>MDIA.JK</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>21.4</v>
+        <v>30.77</v>
       </c>
       <c r="D239" s="2" t="n">
         <v>14.42</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>2200</v>
+        <v>106</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>2610</v>
+        <v>136</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>2460</v>
+        <v>119</v>
       </c>
     </row>
     <row r="240">
@@ -7337,163 +7337,163 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ELIT.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C256" s="2" t="n">
-        <v>13.79</v>
+        <v>15.17</v>
       </c>
       <c r="D256" s="2" t="n">
         <v>13.79</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>236</v>
+        <v>2800</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>264</v>
+        <v>3340</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>264</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>ELIT.JK</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C257" s="2" t="n">
-        <v>15.17</v>
+        <v>13.79</v>
       </c>
       <c r="D257" s="2" t="n">
         <v>13.79</v>
       </c>
       <c r="E257" s="3" t="n">
-        <v>2800</v>
+        <v>236</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>3340</v>
+        <v>264</v>
       </c>
       <c r="G257" s="3" t="n">
-        <v>3300</v>
+        <v>264</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C258" s="2" t="n">
-        <v>14.88</v>
+        <v>24.9</v>
       </c>
       <c r="D258" s="2" t="n">
         <v>13.69</v>
       </c>
       <c r="E258" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>2990</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>386</v>
+        <v>3010</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>382</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C259" s="2" t="n">
-        <v>24.9</v>
+        <v>14.88</v>
       </c>
       <c r="D259" s="2" t="n">
         <v>13.69</v>
       </c>
       <c r="E259" s="3" t="n">
-        <v>2990</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>3010</v>
+        <v>386</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>2740</v>
+        <v>382</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C260" s="2" t="n">
-        <v>20</v>
+        <v>17.27</v>
       </c>
       <c r="D260" s="2" t="n">
         <v>13.64</v>
       </c>
       <c r="E260" s="3" t="n">
-        <v>220</v>
+        <v>550</v>
       </c>
       <c r="F260" s="3" t="n">
-        <v>264</v>
+        <v>645</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C261" s="2" t="n">
-        <v>17.27</v>
+        <v>20</v>
       </c>
       <c r="D261" s="2" t="n">
         <v>13.64</v>
       </c>
       <c r="E261" s="3" t="n">
-        <v>550</v>
+        <v>220</v>
       </c>
       <c r="F261" s="3" t="n">
-        <v>645</v>
+        <v>264</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>625</v>
+        <v>250</v>
       </c>
     </row>
     <row r="262">
@@ -7553,55 +7553,55 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ASGR.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C264" s="2" t="n">
-        <v>19.37</v>
+        <v>23.42</v>
       </c>
       <c r="D264" s="2" t="n">
         <v>13.51</v>
       </c>
       <c r="E264" s="3" t="n">
-        <v>2291.120024181548</v>
+        <v>228</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>2650</v>
+        <v>274</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>2520</v>
+        <v>252</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>ASGR.JK</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C265" s="2" t="n">
-        <v>23.42</v>
+        <v>19.37</v>
       </c>
       <c r="D265" s="2" t="n">
         <v>13.51</v>
       </c>
       <c r="E265" s="3" t="n">
-        <v>228</v>
+        <v>2291.120024181548</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>274</v>
+        <v>2650</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>252</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="266">
@@ -8228,55 +8228,55 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>20.31</v>
+        <v>14.06</v>
       </c>
       <c r="D289" s="2" t="n">
         <v>12.5</v>
       </c>
       <c r="E289" s="3" t="n">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="F289" s="3" t="n">
-        <v>308</v>
+        <v>146</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>288</v>
+        <v>144</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>14.06</v>
+        <v>20.31</v>
       </c>
       <c r="D290" s="2" t="n">
         <v>12.5</v>
       </c>
       <c r="E290" s="3" t="n">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="F290" s="3" t="n">
-        <v>146</v>
+        <v>308</v>
       </c>
       <c r="G290" s="3" t="n">
-        <v>144</v>
+        <v>288</v>
       </c>
     </row>
     <row r="291">
@@ -8309,55 +8309,55 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>14.49</v>
+        <v>12.32</v>
       </c>
       <c r="D292" s="2" t="n">
         <v>12.32</v>
       </c>
       <c r="E292" s="3" t="n">
-        <v>138</v>
+        <v>690</v>
       </c>
       <c r="F292" s="3" t="n">
-        <v>158</v>
+        <v>775</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>155</v>
+        <v>775</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>12.32</v>
+        <v>14.49</v>
       </c>
       <c r="D293" s="2" t="n">
         <v>12.32</v>
       </c>
       <c r="E293" s="3" t="n">
-        <v>690</v>
+        <v>138</v>
       </c>
       <c r="F293" s="3" t="n">
-        <v>775</v>
+        <v>158</v>
       </c>
       <c r="G293" s="3" t="n">
-        <v>775</v>
+        <v>155</v>
       </c>
     </row>
     <row r="294">
@@ -8660,55 +8660,55 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>CBPE.JK</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C305" s="2" t="n">
-        <v>20.62</v>
+        <v>23.76</v>
       </c>
       <c r="D305" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="E305" s="3" t="n">
-        <v>160</v>
+        <v>525</v>
       </c>
       <c r="F305" s="3" t="n">
-        <v>193</v>
+        <v>625</v>
       </c>
       <c r="G305" s="3" t="n">
-        <v>179</v>
+        <v>565</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CBPE.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>23.76</v>
+        <v>20.62</v>
       </c>
       <c r="D306" s="2" t="n">
         <v>11.88</v>
       </c>
       <c r="E306" s="3" t="n">
-        <v>525</v>
+        <v>160</v>
       </c>
       <c r="F306" s="3" t="n">
-        <v>625</v>
+        <v>193</v>
       </c>
       <c r="G306" s="3" t="n">
-        <v>565</v>
+        <v>179</v>
       </c>
     </row>
     <row r="307">
@@ -8822,25 +8822,25 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>UNIQ.JK</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>21.71</v>
+        <v>13.95</v>
       </c>
       <c r="D311" s="2" t="n">
         <v>11.63</v>
       </c>
       <c r="E311" s="3" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F311" s="3" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="G311" s="3" t="n">
         <v>144</v>
@@ -8849,25 +8849,25 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>UNIQ.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>13.95</v>
+        <v>21.71</v>
       </c>
       <c r="D312" s="2" t="n">
         <v>11.63</v>
       </c>
       <c r="E312" s="3" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F312" s="3" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G312" s="3" t="n">
         <v>144</v>
@@ -9038,55 +9038,55 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VTNY.JK</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>12.38</v>
+        <v>13.92</v>
       </c>
       <c r="D319" s="2" t="n">
         <v>11.39</v>
       </c>
       <c r="E319" s="3" t="n">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="F319" s="3" t="n">
-        <v>454</v>
+        <v>90</v>
       </c>
       <c r="G319" s="3" t="n">
-        <v>450</v>
+        <v>88</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>VTNY.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>13.92</v>
+        <v>12.38</v>
       </c>
       <c r="D320" s="2" t="n">
         <v>11.39</v>
       </c>
       <c r="E320" s="3" t="n">
-        <v>78</v>
+        <v>406</v>
       </c>
       <c r="F320" s="3" t="n">
-        <v>90</v>
+        <v>454</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>88</v>
+        <v>450</v>
       </c>
     </row>
     <row r="321">
@@ -9362,28 +9362,28 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>PCAR.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>12.35</v>
+        <v>12.5</v>
       </c>
       <c r="D331" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E331" s="3" t="n">
-        <v>81</v>
+        <v>720</v>
       </c>
       <c r="F331" s="3" t="n">
-        <v>91</v>
+        <v>810</v>
       </c>
       <c r="G331" s="3" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
     </row>
     <row r="332">
@@ -9443,82 +9443,82 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>PCAR.JK</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C334" s="2" t="n">
-        <v>12.5</v>
+        <v>12.35</v>
       </c>
       <c r="D334" s="2" t="n">
         <v>11.11</v>
       </c>
       <c r="E334" s="3" t="n">
-        <v>720</v>
+        <v>81</v>
       </c>
       <c r="F334" s="3" t="n">
-        <v>810</v>
+        <v>91</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C335" s="2" t="n">
-        <v>12.67</v>
+        <v>19</v>
       </c>
       <c r="D335" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E335" s="3" t="n">
-        <v>1515</v>
+        <v>500</v>
       </c>
       <c r="F335" s="3" t="n">
-        <v>1690</v>
+        <v>595</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>1665</v>
+        <v>555</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C336" s="2" t="n">
-        <v>19</v>
+        <v>12.67</v>
       </c>
       <c r="D336" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E336" s="3" t="n">
-        <v>500</v>
+        <v>1515</v>
       </c>
       <c r="F336" s="3" t="n">
-        <v>595</v>
+        <v>1690</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>555</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="337">
@@ -9686,55 +9686,55 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>18.07</v>
+        <v>21.69</v>
       </c>
       <c r="D343" s="2" t="n">
         <v>10.84</v>
       </c>
       <c r="E343" s="3" t="n">
-        <v>332</v>
+        <v>87</v>
       </c>
       <c r="F343" s="3" t="n">
-        <v>392</v>
+        <v>101</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>368</v>
+        <v>92</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>21.69</v>
+        <v>18.07</v>
       </c>
       <c r="D344" s="2" t="n">
         <v>10.84</v>
       </c>
       <c r="E344" s="3" t="n">
-        <v>87</v>
+        <v>332</v>
       </c>
       <c r="F344" s="3" t="n">
-        <v>101</v>
+        <v>392</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>92</v>
+        <v>368</v>
       </c>
     </row>
     <row r="345">
@@ -10037,55 +10037,55 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>10.38</v>
+        <v>22.64</v>
       </c>
       <c r="D356" s="2" t="n">
         <v>10.38</v>
       </c>
       <c r="E356" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>106</v>
       </c>
       <c r="F356" s="3" t="n">
-        <v>585</v>
+        <v>130</v>
       </c>
       <c r="G356" s="3" t="n">
-        <v>585</v>
+        <v>117</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>22.64</v>
+        <v>10.38</v>
       </c>
       <c r="D357" s="2" t="n">
         <v>10.38</v>
       </c>
       <c r="E357" s="3" t="n">
-        <v>106</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F357" s="3" t="n">
-        <v>130</v>
+        <v>585</v>
       </c>
       <c r="G357" s="3" t="n">
-        <v>117</v>
+        <v>585</v>
       </c>
     </row>
     <row r="358">
@@ -10361,25 +10361,25 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>21.1</v>
+        <v>10.09</v>
       </c>
       <c r="D368" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E368" s="3" t="n">
-        <v>495.4545288085938</v>
+        <v>535</v>
       </c>
       <c r="F368" s="3" t="n">
-        <v>660</v>
+        <v>600</v>
       </c>
       <c r="G368" s="3" t="n">
         <v>600</v>
@@ -10388,25 +10388,25 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>10.09</v>
+        <v>21.1</v>
       </c>
       <c r="D369" s="2" t="n">
         <v>10.09</v>
       </c>
       <c r="E369" s="3" t="n">
-        <v>535</v>
+        <v>495.4545288085938</v>
       </c>
       <c r="F369" s="3" t="n">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="G369" s="3" t="n">
         <v>600</v>
@@ -10442,34 +10442,34 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>TKIM.JK</t>
+          <t>PPRO.JK</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
-        <v>10.77</v>
+        <v>30</v>
       </c>
       <c r="D371" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E371" s="3" t="n">
-        <v>6850</v>
+        <v>23</v>
       </c>
       <c r="F371" s="3" t="n">
-        <v>7200</v>
+        <v>26</v>
       </c>
       <c r="G371" s="3" t="n">
-        <v>7150</v>
+        <v>22</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>APEX.JK</t>
+          <t>TKIM.JK</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10478,19 +10478,19 @@
         </is>
       </c>
       <c r="C372" s="2" t="n">
-        <v>12.67</v>
+        <v>10.77</v>
       </c>
       <c r="D372" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E372" s="3" t="n">
-        <v>150</v>
+        <v>6850</v>
       </c>
       <c r="F372" s="3" t="n">
-        <v>169</v>
+        <v>7200</v>
       </c>
       <c r="G372" s="3" t="n">
-        <v>165</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="373">
@@ -10523,28 +10523,28 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>PPRO.JK</t>
+          <t>APEX.JK</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
-        <v>30</v>
+        <v>12.67</v>
       </c>
       <c r="D374" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E374" s="3" t="n">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="F374" s="3" t="n">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="G374" s="3" t="n">
-        <v>22</v>
+        <v>165</v>
       </c>
     </row>
     <row r="375">
@@ -10928,55 +10928,55 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>TOBA.JK</t>
+          <t>BKDP.JK</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>15.78</v>
+        <v>27.41</v>
       </c>
       <c r="D389" s="2" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="E389" s="3" t="n">
-        <v>492</v>
+        <v>135</v>
       </c>
       <c r="F389" s="3" t="n">
-        <v>565</v>
+        <v>172</v>
       </c>
       <c r="G389" s="3" t="n">
-        <v>535</v>
+        <v>148</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>TOBA.JK</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>27.41</v>
+        <v>15.78</v>
       </c>
       <c r="D390" s="2" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="E390" s="3" t="n">
-        <v>135</v>
+        <v>492</v>
       </c>
       <c r="F390" s="3" t="n">
-        <v>172</v>
+        <v>565</v>
       </c>
       <c r="G390" s="3" t="n">
-        <v>148</v>
+        <v>535</v>
       </c>
     </row>
     <row r="391">
@@ -11144,55 +11144,55 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>PGLI.JK</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>11.72</v>
+        <v>11.46</v>
       </c>
       <c r="D397" s="2" t="n">
         <v>9.380000000000001</v>
       </c>
       <c r="E397" s="3" t="n">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="F397" s="3" t="n">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="G397" s="3" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>PGLI.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>11.46</v>
+        <v>11.72</v>
       </c>
       <c r="D398" s="2" t="n">
         <v>9.380000000000001</v>
       </c>
       <c r="E398" s="3" t="n">
-        <v>191</v>
+        <v>128</v>
       </c>
       <c r="F398" s="3" t="n">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="G398" s="3" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
     </row>
     <row r="399">
@@ -11225,25 +11225,25 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>EKAD.JK</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
-        <v>11.4</v>
+        <v>20.73</v>
       </c>
       <c r="D400" s="2" t="n">
         <v>9.33</v>
       </c>
       <c r="E400" s="3" t="n">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="F400" s="3" t="n">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="G400" s="3" t="n">
         <v>422</v>
@@ -11252,25 +11252,25 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>EKAD.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
-        <v>20.73</v>
+        <v>11.4</v>
       </c>
       <c r="D401" s="2" t="n">
         <v>9.33</v>
       </c>
       <c r="E401" s="3" t="n">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="F401" s="3" t="n">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="G401" s="3" t="n">
         <v>422</v>
@@ -11495,55 +11495,55 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>11.11</v>
+        <v>22.73</v>
       </c>
       <c r="D410" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E410" s="3" t="n">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="F410" s="3" t="n">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="G410" s="3" t="n">
-        <v>108</v>
+        <v>192</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>22.73</v>
+        <v>11.11</v>
       </c>
       <c r="D411" s="2" t="n">
         <v>9.09</v>
       </c>
       <c r="E411" s="3" t="n">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="F411" s="3" t="n">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="G411" s="3" t="n">
-        <v>192</v>
+        <v>108</v>
       </c>
     </row>
     <row r="412">
@@ -11711,25 +11711,25 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>20.33</v>
+        <v>13.82</v>
       </c>
       <c r="D418" s="2" t="n">
         <v>8.94</v>
       </c>
       <c r="E418" s="3" t="n">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="F418" s="3" t="n">
-        <v>740</v>
+        <v>700</v>
       </c>
       <c r="G418" s="3" t="n">
         <v>670</v>
@@ -11738,25 +11738,25 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>13.82</v>
+        <v>20.33</v>
       </c>
       <c r="D419" s="2" t="n">
         <v>8.94</v>
       </c>
       <c r="E419" s="3" t="n">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="F419" s="3" t="n">
-        <v>700</v>
+        <v>740</v>
       </c>
       <c r="G419" s="3" t="n">
         <v>670</v>
@@ -11927,109 +11927,109 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>WINS.JK</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>15.2</v>
+        <v>15.79</v>
       </c>
       <c r="D426" s="2" t="n">
         <v>8.77</v>
       </c>
       <c r="E426" s="3" t="n">
-        <v>364</v>
+        <v>580</v>
       </c>
       <c r="F426" s="3" t="n">
-        <v>394</v>
+        <v>660</v>
       </c>
       <c r="G426" s="3" t="n">
-        <v>372</v>
+        <v>620</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>WINS.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>15.79</v>
+        <v>15.2</v>
       </c>
       <c r="D427" s="2" t="n">
         <v>8.77</v>
       </c>
       <c r="E427" s="3" t="n">
-        <v>580</v>
+        <v>364</v>
       </c>
       <c r="F427" s="3" t="n">
-        <v>660</v>
+        <v>394</v>
       </c>
       <c r="G427" s="3" t="n">
-        <v>620</v>
+        <v>372</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>IKAI.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>21.74</v>
+        <v>10.14</v>
       </c>
       <c r="D428" s="2" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E428" s="3" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="F428" s="3" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G428" s="3" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>IKAI.JK</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>10.14</v>
+        <v>21.74</v>
       </c>
       <c r="D429" s="2" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E429" s="3" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="F429" s="3" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G429" s="3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="430">
@@ -12170,55 +12170,55 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>10.17</v>
+        <v>16.1</v>
       </c>
       <c r="D435" s="2" t="n">
         <v>8.470000000000001</v>
       </c>
       <c r="E435" s="3" t="n">
-        <v>248</v>
+        <v>120</v>
       </c>
       <c r="F435" s="3" t="n">
-        <v>260</v>
+        <v>137</v>
       </c>
       <c r="G435" s="3" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C436" s="2" t="n">
-        <v>16.1</v>
+        <v>10.17</v>
       </c>
       <c r="D436" s="2" t="n">
         <v>8.470000000000001</v>
       </c>
       <c r="E436" s="3" t="n">
-        <v>120</v>
+        <v>248</v>
       </c>
       <c r="F436" s="3" t="n">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="G436" s="3" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="437">
@@ -12332,82 +12332,82 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C441" s="2" t="n">
-        <v>12.12</v>
+        <v>10.19</v>
       </c>
       <c r="D441" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E441" s="3" t="n">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="F441" s="3" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="G441" s="3" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>HGII.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C442" s="2" t="n">
-        <v>27.27</v>
+        <v>19.05</v>
       </c>
       <c r="D442" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E442" s="3" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="F442" s="3" t="n">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="G442" s="3" t="n">
-        <v>143</v>
+        <v>182</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>HGII.JK</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C443" s="2" t="n">
-        <v>11.67</v>
+        <v>27.27</v>
       </c>
       <c r="D443" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E443" s="3" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="F443" s="3" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="G443" s="3" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="444">
@@ -12440,82 +12440,82 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>SSTM.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C445" s="2" t="n">
-        <v>22.92</v>
+        <v>12.12</v>
       </c>
       <c r="D445" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E445" s="3" t="n">
-        <v>555</v>
+        <v>133</v>
       </c>
       <c r="F445" s="3" t="n">
-        <v>590</v>
+        <v>148</v>
       </c>
       <c r="G445" s="3" t="n">
-        <v>520</v>
+        <v>143</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C446" s="2" t="n">
-        <v>10.19</v>
+        <v>11.67</v>
       </c>
       <c r="D446" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E446" s="3" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F446" s="3" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G446" s="3" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>SSTM.JK</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C447" s="2" t="n">
-        <v>19.05</v>
+        <v>22.92</v>
       </c>
       <c r="D447" s="2" t="n">
         <v>8.33</v>
       </c>
       <c r="E447" s="3" t="n">
-        <v>169</v>
+        <v>555</v>
       </c>
       <c r="F447" s="3" t="n">
-        <v>200</v>
+        <v>590</v>
       </c>
       <c r="G447" s="3" t="n">
-        <v>182</v>
+        <v>520</v>
       </c>
     </row>
     <row r="448">
@@ -12899,25 +12899,25 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C462" s="2" t="n">
-        <v>13.33</v>
+        <v>20</v>
       </c>
       <c r="D462" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E462" s="3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F462" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G462" s="3" t="n">
         <v>81</v>
@@ -12926,25 +12926,25 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C463" s="2" t="n">
-        <v>20</v>
+        <v>13.33</v>
       </c>
       <c r="D463" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E463" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F463" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G463" s="3" t="n">
         <v>81</v>
@@ -13223,82 +13223,82 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>ASLI.JK</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C474" s="2" t="n">
-        <v>16.35</v>
+        <v>20.51</v>
       </c>
       <c r="D474" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E474" s="3" t="n">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="F474" s="3" t="n">
-        <v>121</v>
+        <v>282</v>
       </c>
       <c r="G474" s="3" t="n">
-        <v>112</v>
+        <v>252</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>LPPS.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C475" s="2" t="n">
-        <v>15.38</v>
+        <v>16.35</v>
       </c>
       <c r="D475" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E475" s="3" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="F475" s="3" t="n">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="G475" s="3" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>ASLI.JK</t>
+          <t>LPPS.JK</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C476" s="2" t="n">
-        <v>20.51</v>
+        <v>15.38</v>
       </c>
       <c r="D476" s="2" t="n">
         <v>7.69</v>
       </c>
       <c r="E476" s="3" t="n">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="F476" s="3" t="n">
-        <v>282</v>
+        <v>90</v>
       </c>
       <c r="G476" s="3" t="n">
-        <v>252</v>
+        <v>84</v>
       </c>
     </row>
     <row r="477">
@@ -13331,55 +13331,55 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>MPIX.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C478" s="2" t="n">
-        <v>13.56</v>
+        <v>12.98</v>
       </c>
       <c r="D478" s="2" t="n">
         <v>7.63</v>
       </c>
       <c r="E478" s="3" t="n">
-        <v>118</v>
+        <v>264</v>
       </c>
       <c r="F478" s="3" t="n">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="G478" s="3" t="n">
-        <v>127</v>
+        <v>282</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>MPIX.JK</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C479" s="2" t="n">
-        <v>12.98</v>
+        <v>13.56</v>
       </c>
       <c r="D479" s="2" t="n">
         <v>7.63</v>
       </c>
       <c r="E479" s="3" t="n">
-        <v>264</v>
+        <v>118</v>
       </c>
       <c r="F479" s="3" t="n">
-        <v>296</v>
+        <v>134</v>
       </c>
       <c r="G479" s="3" t="n">
-        <v>282</v>
+        <v>127</v>
       </c>
     </row>
     <row r="480">
@@ -13412,109 +13412,109 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C481" s="2" t="n">
-        <v>16.46</v>
+        <v>11.03</v>
       </c>
       <c r="D481" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E481" s="3" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F481" s="3" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="G481" s="3" t="n">
-        <v>85</v>
+        <v>156</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C482" s="2" t="n">
-        <v>11.03</v>
+        <v>16.46</v>
       </c>
       <c r="D482" s="2" t="n">
         <v>7.59</v>
       </c>
       <c r="E482" s="3" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="F482" s="3" t="n">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="G482" s="3" t="n">
-        <v>156</v>
+        <v>85</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>WAPO.JK</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C483" s="2" t="n">
-        <v>18.01</v>
+        <v>18.18</v>
       </c>
       <c r="D483" s="2" t="n">
         <v>7.58</v>
       </c>
       <c r="E483" s="3" t="n">
-        <v>2220</v>
+        <v>143</v>
       </c>
       <c r="F483" s="3" t="n">
-        <v>2490</v>
+        <v>156</v>
       </c>
       <c r="G483" s="3" t="n">
-        <v>2270</v>
+        <v>142</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>WAPO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C484" s="2" t="n">
-        <v>18.18</v>
+        <v>18.01</v>
       </c>
       <c r="D484" s="2" t="n">
         <v>7.58</v>
       </c>
       <c r="E484" s="3" t="n">
-        <v>143</v>
+        <v>2220</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>156</v>
+        <v>2490</v>
       </c>
       <c r="G484" s="3" t="n">
-        <v>142</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="485">
@@ -13709,55 +13709,55 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>AKPI.JK</t>
+          <t>PSKT.JK</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C492" s="2" t="n">
-        <v>20.91</v>
+        <v>10.91</v>
       </c>
       <c r="D492" s="2" t="n">
         <v>7.27</v>
       </c>
       <c r="E492" s="3" t="n">
-        <v>550</v>
+        <v>222</v>
       </c>
       <c r="F492" s="3" t="n">
-        <v>665</v>
+        <v>244</v>
       </c>
       <c r="G492" s="3" t="n">
-        <v>590</v>
+        <v>236</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>PSKT.JK</t>
+          <t>AKPI.JK</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C493" s="2" t="n">
-        <v>10.91</v>
+        <v>20.91</v>
       </c>
       <c r="D493" s="2" t="n">
         <v>7.27</v>
       </c>
       <c r="E493" s="3" t="n">
-        <v>222</v>
+        <v>550</v>
       </c>
       <c r="F493" s="3" t="n">
-        <v>244</v>
+        <v>665</v>
       </c>
       <c r="G493" s="3" t="n">
-        <v>236</v>
+        <v>590</v>
       </c>
     </row>
     <row r="494">
@@ -13923,55 +13923,55 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>FIRE.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C500" s="2" t="n">
-        <v>22.32</v>
+        <v>22.86</v>
       </c>
       <c r="D500" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E500" s="3" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="F500" s="3" t="n">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="G500" s="3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>FIRE.JK</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C501" s="2" t="n">
-        <v>22.86</v>
+        <v>22.32</v>
       </c>
       <c r="D501" s="2" t="n">
         <v>7.14</v>
       </c>
       <c r="E501" s="3" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="F501" s="3" t="n">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="G501" s="3" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="502">
@@ -14193,55 +14193,55 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>IFSH.JK</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C510" s="2" t="n">
-        <v>17.44</v>
+        <v>16.28</v>
       </c>
       <c r="D510" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E510" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>2210</v>
       </c>
       <c r="F510" s="3" t="n">
-        <v>101</v>
+        <v>2500</v>
       </c>
       <c r="G510" s="3" t="n">
-        <v>92</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>IFSH.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C511" s="2" t="n">
-        <v>16.28</v>
+        <v>17.44</v>
       </c>
       <c r="D511" s="2" t="n">
         <v>6.98</v>
       </c>
       <c r="E511" s="3" t="n">
-        <v>2210</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F511" s="3" t="n">
-        <v>2500</v>
+        <v>101</v>
       </c>
       <c r="G511" s="3" t="n">
-        <v>2300</v>
+        <v>92</v>
       </c>
     </row>
     <row r="512">
@@ -14382,55 +14382,55 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>PTSP.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C517" s="2" t="n">
-        <v>24.92</v>
+        <v>24.86</v>
       </c>
       <c r="D517" s="2" t="n">
         <v>6.91</v>
       </c>
       <c r="E517" s="3" t="n">
-        <v>1850</v>
+        <v>2260</v>
       </c>
       <c r="F517" s="3" t="n">
-        <v>2080</v>
+        <v>2260</v>
       </c>
       <c r="G517" s="3" t="n">
-        <v>1780</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PTSP.JK</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C518" s="2" t="n">
-        <v>24.86</v>
+        <v>24.92</v>
       </c>
       <c r="D518" s="2" t="n">
         <v>6.91</v>
       </c>
       <c r="E518" s="3" t="n">
-        <v>2260</v>
+        <v>1850</v>
       </c>
       <c r="F518" s="3" t="n">
-        <v>2260</v>
+        <v>2080</v>
       </c>
       <c r="G518" s="3" t="n">
-        <v>1935</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="519">
@@ -14625,55 +14625,55 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C526" s="2" t="n">
-        <v>25.84</v>
+        <v>20.73</v>
       </c>
       <c r="D526" s="2" t="n">
         <v>6.74</v>
       </c>
       <c r="E526" s="3" t="n">
-        <v>91</v>
+        <v>396</v>
       </c>
       <c r="F526" s="3" t="n">
-        <v>112</v>
+        <v>466</v>
       </c>
       <c r="G526" s="3" t="n">
-        <v>95</v>
+        <v>412</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C527" s="2" t="n">
-        <v>20.73</v>
+        <v>25.84</v>
       </c>
       <c r="D527" s="2" t="n">
         <v>6.74</v>
       </c>
       <c r="E527" s="3" t="n">
-        <v>396</v>
+        <v>91</v>
       </c>
       <c r="F527" s="3" t="n">
-        <v>466</v>
+        <v>112</v>
       </c>
       <c r="G527" s="3" t="n">
-        <v>412</v>
+        <v>95</v>
       </c>
     </row>
     <row r="528">
@@ -14733,106 +14733,106 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>ISEA.JK</t>
+          <t>PTSN.JK</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C530" s="2" t="n">
-        <v>25.33</v>
+        <v>11.11</v>
       </c>
       <c r="D530" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E530" s="3" t="n">
-        <v>77</v>
+        <v>452</v>
       </c>
       <c r="F530" s="3" t="n">
-        <v>94</v>
+        <v>500</v>
       </c>
       <c r="G530" s="3" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C531" s="2" t="n">
-        <v>23.33</v>
+        <v>16</v>
       </c>
       <c r="D531" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E531" s="3" t="n">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="F531" s="3" t="n">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="G531" s="3" t="n">
-        <v>128</v>
+        <v>80</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>PTSN.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C532" s="2" t="n">
-        <v>11.11</v>
+        <v>23.33</v>
       </c>
       <c r="D532" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E532" s="3" t="n">
-        <v>452</v>
+        <v>119</v>
       </c>
       <c r="F532" s="3" t="n">
-        <v>500</v>
+        <v>148</v>
       </c>
       <c r="G532" s="3" t="n">
-        <v>480</v>
+        <v>128</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ISEA.JK</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C533" s="2" t="n">
-        <v>16</v>
+        <v>25.33</v>
       </c>
       <c r="D533" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="E533" s="3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F533" s="3" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G533" s="3" t="n">
         <v>80</v>
@@ -14895,109 +14895,109 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>NAIK.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C536" s="2" t="n">
-        <v>11.96</v>
+        <v>23.29</v>
       </c>
       <c r="D536" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E536" s="3" t="n">
-        <v>92</v>
+        <v>3000</v>
       </c>
       <c r="F536" s="3" t="n">
-        <v>103</v>
+        <v>3970</v>
       </c>
       <c r="G536" s="3" t="n">
-        <v>98</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>NAIK.JK</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C537" s="2" t="n">
-        <v>23.29</v>
+        <v>11.96</v>
       </c>
       <c r="D537" s="2" t="n">
         <v>6.52</v>
       </c>
       <c r="E537" s="3" t="n">
-        <v>3000</v>
+        <v>92</v>
       </c>
       <c r="F537" s="3" t="n">
-        <v>3970</v>
+        <v>103</v>
       </c>
       <c r="G537" s="3" t="n">
-        <v>3430</v>
+        <v>98</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>KKES.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C538" s="2" t="n">
-        <v>10.39</v>
+        <v>20.13</v>
       </c>
       <c r="D538" s="2" t="n">
         <v>6.49</v>
       </c>
       <c r="E538" s="3" t="n">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="F538" s="3" t="n">
-        <v>85</v>
+        <v>370</v>
       </c>
       <c r="G538" s="3" t="n">
-        <v>82</v>
+        <v>328</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KKES.JK</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C539" s="2" t="n">
-        <v>20.13</v>
+        <v>10.39</v>
       </c>
       <c r="D539" s="2" t="n">
         <v>6.49</v>
       </c>
       <c r="E539" s="3" t="n">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="F539" s="3" t="n">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="G539" s="3" t="n">
-        <v>328</v>
+        <v>82</v>
       </c>
     </row>
     <row r="540">
@@ -15111,25 +15111,25 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C544" s="2" t="n">
-        <v>17.46</v>
+        <v>11.9</v>
       </c>
       <c r="D544" s="2" t="n">
         <v>6.35</v>
       </c>
       <c r="E544" s="3" t="n">
-        <v>127.4960645988806</v>
+        <v>127</v>
       </c>
       <c r="F544" s="3" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G544" s="3" t="n">
         <v>134</v>
@@ -15138,25 +15138,25 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>SRSN.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C545" s="2" t="n">
-        <v>11.9</v>
+        <v>17.46</v>
       </c>
       <c r="D545" s="2" t="n">
         <v>6.35</v>
       </c>
       <c r="E545" s="3" t="n">
-        <v>127</v>
+        <v>127.4960645988806</v>
       </c>
       <c r="F545" s="3" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G545" s="3" t="n">
         <v>134</v>
@@ -15435,55 +15435,55 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C556" s="2" t="n">
-        <v>10.43</v>
+        <v>14.78</v>
       </c>
       <c r="D556" s="2" t="n">
         <v>6.09</v>
       </c>
       <c r="E556" s="3" t="n">
-        <v>117</v>
+        <v>232</v>
       </c>
       <c r="F556" s="3" t="n">
-        <v>127</v>
+        <v>264</v>
       </c>
       <c r="G556" s="3" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C557" s="2" t="n">
-        <v>14.78</v>
+        <v>10.43</v>
       </c>
       <c r="D557" s="2" t="n">
         <v>6.09</v>
       </c>
       <c r="E557" s="3" t="n">
-        <v>232</v>
+        <v>117</v>
       </c>
       <c r="F557" s="3" t="n">
-        <v>264</v>
+        <v>127</v>
       </c>
       <c r="G557" s="3" t="n">
-        <v>244</v>
+        <v>122</v>
       </c>
     </row>
     <row r="558">
@@ -15570,109 +15570,109 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C561" s="2" t="n">
-        <v>10.53</v>
+        <v>12.03</v>
       </c>
       <c r="D561" s="2" t="n">
         <v>6.02</v>
       </c>
       <c r="E561" s="3" t="n">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="F561" s="3" t="n">
-        <v>147</v>
+        <v>298</v>
       </c>
       <c r="G561" s="3" t="n">
-        <v>141</v>
+        <v>282</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C562" s="2" t="n">
-        <v>12.03</v>
+        <v>10.53</v>
       </c>
       <c r="D562" s="2" t="n">
         <v>6.02</v>
       </c>
       <c r="E562" s="3" t="n">
-        <v>268</v>
+        <v>133</v>
       </c>
       <c r="F562" s="3" t="n">
-        <v>298</v>
+        <v>147</v>
       </c>
       <c r="G562" s="3" t="n">
-        <v>282</v>
+        <v>141</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>DAAZ.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C563" s="2" t="n">
-        <v>21.63</v>
+        <v>11.92</v>
       </c>
       <c r="D563" s="2" t="n">
         <v>5.96</v>
       </c>
       <c r="E563" s="3" t="n">
-        <v>1615</v>
+        <v>151</v>
       </c>
       <c r="F563" s="3" t="n">
-        <v>1940</v>
+        <v>169</v>
       </c>
       <c r="G563" s="3" t="n">
-        <v>1690</v>
+        <v>160</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>DAAZ.JK</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C564" s="2" t="n">
-        <v>11.92</v>
+        <v>21.63</v>
       </c>
       <c r="D564" s="2" t="n">
         <v>5.96</v>
       </c>
       <c r="E564" s="3" t="n">
-        <v>151</v>
+        <v>1615</v>
       </c>
       <c r="F564" s="3" t="n">
-        <v>169</v>
+        <v>1940</v>
       </c>
       <c r="G564" s="3" t="n">
-        <v>160</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="565">
@@ -15732,28 +15732,28 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>ISSP.JK</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C567" s="2" t="n">
-        <v>15.69</v>
+        <v>11.31</v>
       </c>
       <c r="D567" s="2" t="n">
         <v>5.88</v>
       </c>
       <c r="E567" s="3" t="n">
-        <v>103</v>
+        <v>448</v>
       </c>
       <c r="F567" s="3" t="n">
-        <v>118</v>
+        <v>492</v>
       </c>
       <c r="G567" s="3" t="n">
-        <v>108</v>
+        <v>468</v>
       </c>
     </row>
     <row r="568">
@@ -15786,28 +15786,28 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>ISSP.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C569" s="2" t="n">
-        <v>11.31</v>
+        <v>15.69</v>
       </c>
       <c r="D569" s="2" t="n">
         <v>5.88</v>
       </c>
       <c r="E569" s="3" t="n">
-        <v>448</v>
+        <v>103</v>
       </c>
       <c r="F569" s="3" t="n">
-        <v>492</v>
+        <v>118</v>
       </c>
       <c r="G569" s="3" t="n">
-        <v>468</v>
+        <v>108</v>
       </c>
     </row>
     <row r="570">
@@ -16083,25 +16083,25 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>GGRP.JK</t>
+          <t>MITI.JK</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C580" s="2" t="n">
-        <v>10.29</v>
+        <v>15.43</v>
       </c>
       <c r="D580" s="2" t="n">
         <v>5.71</v>
       </c>
       <c r="E580" s="3" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="F580" s="3" t="n">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="G580" s="3" t="n">
         <v>370</v>
@@ -16137,25 +16137,25 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>MITI.JK</t>
+          <t>GGRP.JK</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C582" s="2" t="n">
-        <v>15.43</v>
+        <v>10.29</v>
       </c>
       <c r="D582" s="2" t="n">
         <v>5.71</v>
       </c>
       <c r="E582" s="3" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F582" s="3" t="n">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="G582" s="3" t="n">
         <v>370</v>
@@ -16299,55 +16299,55 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>SWID.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C588" s="2" t="n">
-        <v>17.76</v>
+        <v>12.15</v>
       </c>
       <c r="D588" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E588" s="3" t="n">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="F588" s="3" t="n">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="G588" s="3" t="n">
-        <v>113</v>
+        <v>226</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>KOKA.JK</t>
+          <t>SWID.JK</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C589" s="2" t="n">
-        <v>12.15</v>
+        <v>17.76</v>
       </c>
       <c r="D589" s="2" t="n">
         <v>5.61</v>
       </c>
       <c r="E589" s="3" t="n">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="F589" s="3" t="n">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="G589" s="3" t="n">
-        <v>226</v>
+        <v>113</v>
       </c>
     </row>
     <row r="590">
@@ -16569,82 +16569,82 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>FITT.JK</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C598" s="2" t="n">
-        <v>14.74</v>
+        <v>12.44</v>
       </c>
       <c r="D598" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E598" s="3" t="n">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="F598" s="3" t="n">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="G598" s="3" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>FITT.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C599" s="2" t="n">
-        <v>12.44</v>
+        <v>11.58</v>
       </c>
       <c r="D599" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E599" s="3" t="n">
-        <v>424</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F599" s="3" t="n">
-        <v>470</v>
+        <v>106</v>
       </c>
       <c r="G599" s="3" t="n">
-        <v>440</v>
+        <v>100</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C600" s="2" t="n">
-        <v>11.58</v>
+        <v>14.74</v>
       </c>
       <c r="D600" s="2" t="n">
         <v>5.26</v>
       </c>
       <c r="E600" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>430</v>
       </c>
       <c r="F600" s="3" t="n">
-        <v>106</v>
+        <v>436</v>
       </c>
       <c r="G600" s="3" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="601">
@@ -16920,55 +16920,55 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>BIPP.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C611" s="2" t="n">
-        <v>13.33</v>
+        <v>17.5</v>
       </c>
       <c r="D611" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E611" s="3" t="n">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="F611" s="3" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="G611" s="3" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>BIPP.JK</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C612" s="2" t="n">
-        <v>17.5</v>
+        <v>13.33</v>
       </c>
       <c r="D612" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E612" s="3" t="n">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="F612" s="3" t="n">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="G612" s="3" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
     </row>
     <row r="613">
@@ -17001,55 +17001,55 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>BBSS.JK</t>
+          <t>MGNA.JK</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C614" s="2" t="n">
-        <v>15.84</v>
+        <v>10.89</v>
       </c>
       <c r="D614" s="2" t="n">
         <v>4.95</v>
       </c>
       <c r="E614" s="3" t="n">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="F614" s="3" t="n">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="G614" s="3" t="n">
-        <v>106</v>
+        <v>212</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>MGNA.JK</t>
+          <t>BBSS.JK</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C615" s="2" t="n">
-        <v>10.89</v>
+        <v>15.84</v>
       </c>
       <c r="D615" s="2" t="n">
         <v>4.95</v>
       </c>
       <c r="E615" s="3" t="n">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="F615" s="3" t="n">
-        <v>224</v>
+        <v>117</v>
       </c>
       <c r="G615" s="3" t="n">
-        <v>212</v>
+        <v>106</v>
       </c>
     </row>
     <row r="616">
@@ -17244,55 +17244,55 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>PURA.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C623" s="2" t="n">
-        <v>14.29</v>
+        <v>22.22</v>
       </c>
       <c r="D623" s="2" t="n">
         <v>4.76</v>
       </c>
       <c r="E623" s="3" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F623" s="3" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="G623" s="3" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>PURA.JK</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C624" s="2" t="n">
-        <v>22.22</v>
+        <v>14.29</v>
       </c>
       <c r="D624" s="2" t="n">
         <v>4.76</v>
       </c>
       <c r="E624" s="3" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="F624" s="3" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G624" s="3" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
     </row>
     <row r="625">
@@ -17487,25 +17487,25 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C632" s="2" t="n">
-        <v>12.21</v>
+        <v>10.69</v>
       </c>
       <c r="D632" s="2" t="n">
         <v>4.58</v>
       </c>
       <c r="E632" s="3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F632" s="3" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G632" s="3" t="n">
         <v>274</v>
@@ -17514,25 +17514,25 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C633" s="2" t="n">
-        <v>10.69</v>
+        <v>12.21</v>
       </c>
       <c r="D633" s="2" t="n">
         <v>4.58</v>
       </c>
       <c r="E633" s="3" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F633" s="3" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G633" s="3" t="n">
         <v>274</v>
@@ -17595,55 +17595,55 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>BIPI.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C636" s="2" t="n">
-        <v>10.97</v>
+        <v>19.77</v>
       </c>
       <c r="D636" s="2" t="n">
         <v>4.52</v>
       </c>
       <c r="E636" s="3" t="n">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="F636" s="3" t="n">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="G636" s="3" t="n">
-        <v>162</v>
+        <v>185</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C637" s="2" t="n">
-        <v>19.77</v>
+        <v>10.97</v>
       </c>
       <c r="D637" s="2" t="n">
         <v>4.52</v>
       </c>
       <c r="E637" s="3" t="n">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="F637" s="3" t="n">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="G637" s="3" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="638">
@@ -18297,79 +18297,79 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C662" s="2" t="n">
-        <v>10.67</v>
+        <v>15</v>
       </c>
       <c r="D662" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E662" s="3" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="F662" s="3" t="n">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="G662" s="3" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C663" s="2" t="n">
-        <v>15</v>
+        <v>17.33</v>
       </c>
       <c r="D663" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E663" s="3" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="F663" s="3" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="G663" s="3" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C664" s="2" t="n">
-        <v>17.33</v>
+        <v>10.67</v>
       </c>
       <c r="D664" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E664" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F664" s="3" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G664" s="3" t="n">
         <v>78</v>
@@ -18835,55 +18835,55 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>MPIX.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C682" s="2" t="n">
-        <v>12.07</v>
+        <v>15.52</v>
       </c>
       <c r="D682" s="2" t="n">
         <v>3.45</v>
       </c>
       <c r="E682" s="3" t="n">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="F682" s="3" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="G682" s="3" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>MPIX.JK</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C683" s="2" t="n">
-        <v>15.52</v>
+        <v>12.07</v>
       </c>
       <c r="D683" s="2" t="n">
         <v>3.45</v>
       </c>
       <c r="E683" s="3" t="n">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="F683" s="3" t="n">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="G683" s="3" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="684">
@@ -18916,55 +18916,55 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>GUNA.JK</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C685" s="2" t="n">
-        <v>12.45</v>
+        <v>10.23</v>
       </c>
       <c r="D685" s="2" t="n">
         <v>3.41</v>
       </c>
       <c r="E685" s="3" t="n">
-        <v>545</v>
+        <v>178</v>
       </c>
       <c r="F685" s="3" t="n">
-        <v>560</v>
+        <v>194</v>
       </c>
       <c r="G685" s="3" t="n">
-        <v>515</v>
+        <v>182</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>GUNA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C686" s="2" t="n">
-        <v>10.23</v>
+        <v>12.45</v>
       </c>
       <c r="D686" s="2" t="n">
         <v>3.41</v>
       </c>
       <c r="E686" s="3" t="n">
-        <v>178</v>
+        <v>545</v>
       </c>
       <c r="F686" s="3" t="n">
-        <v>194</v>
+        <v>560</v>
       </c>
       <c r="G686" s="3" t="n">
-        <v>182</v>
+        <v>515</v>
       </c>
     </row>
     <row r="687">
@@ -19024,55 +19024,55 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>TNCA.JK</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C689" s="2" t="n">
-        <v>17.51</v>
+        <v>11.24</v>
       </c>
       <c r="D689" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E689" s="3" t="n">
-        <v>3180</v>
+        <v>180</v>
       </c>
       <c r="F689" s="3" t="n">
-        <v>3490</v>
+        <v>198</v>
       </c>
       <c r="G689" s="3" t="n">
-        <v>3070</v>
+        <v>184</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>TNCA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C690" s="2" t="n">
-        <v>11.24</v>
+        <v>17.51</v>
       </c>
       <c r="D690" s="2" t="n">
         <v>3.37</v>
       </c>
       <c r="E690" s="3" t="n">
-        <v>180</v>
+        <v>3180</v>
       </c>
       <c r="F690" s="3" t="n">
-        <v>198</v>
+        <v>3490</v>
       </c>
       <c r="G690" s="3" t="n">
-        <v>184</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="691">
@@ -19213,55 +19213,55 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C696" s="2" t="n">
-        <v>17.21</v>
+        <v>19.4</v>
       </c>
       <c r="D696" s="2" t="n">
         <v>3.28</v>
       </c>
       <c r="E696" s="3" t="n">
-        <v>615</v>
+        <v>1670</v>
       </c>
       <c r="F696" s="3" t="n">
-        <v>715</v>
+        <v>2000</v>
       </c>
       <c r="G696" s="3" t="n">
-        <v>630</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C697" s="2" t="n">
-        <v>19.4</v>
+        <v>17.21</v>
       </c>
       <c r="D697" s="2" t="n">
         <v>3.28</v>
       </c>
       <c r="E697" s="3" t="n">
-        <v>1670</v>
+        <v>615</v>
       </c>
       <c r="F697" s="3" t="n">
-        <v>2000</v>
+        <v>715</v>
       </c>
       <c r="G697" s="3" t="n">
-        <v>1730</v>
+        <v>630</v>
       </c>
     </row>
     <row r="698">
@@ -19321,109 +19321,109 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C700" s="2" t="n">
-        <v>11.83</v>
+        <v>15.48</v>
       </c>
       <c r="D700" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E700" s="3" t="n">
-        <v>95</v>
+        <v>850</v>
       </c>
       <c r="F700" s="3" t="n">
-        <v>104</v>
+        <v>895</v>
       </c>
       <c r="G700" s="3" t="n">
-        <v>96</v>
+        <v>800</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>TRUE.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C701" s="2" t="n">
-        <v>19.35</v>
+        <v>23.66</v>
       </c>
       <c r="D701" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E701" s="3" t="n">
-        <v>70</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F701" s="3" t="n">
-        <v>74</v>
+        <v>460</v>
       </c>
       <c r="G701" s="3" t="n">
-        <v>64</v>
+        <v>384</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C702" s="2" t="n">
-        <v>15.48</v>
+        <v>11.83</v>
       </c>
       <c r="D702" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E702" s="3" t="n">
-        <v>850</v>
+        <v>95</v>
       </c>
       <c r="F702" s="3" t="n">
-        <v>895</v>
+        <v>104</v>
       </c>
       <c r="G702" s="3" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>TRUE.JK</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C703" s="2" t="n">
-        <v>23.66</v>
+        <v>19.35</v>
       </c>
       <c r="D703" s="2" t="n">
         <v>3.23</v>
       </c>
       <c r="E703" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>70</v>
       </c>
       <c r="F703" s="3" t="n">
-        <v>460</v>
+        <v>74</v>
       </c>
       <c r="G703" s="3" t="n">
-        <v>384</v>
+        <v>64</v>
       </c>
     </row>
     <row r="704">
@@ -19483,25 +19483,25 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>VRNA.JK</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C706" s="2" t="n">
-        <v>34.34</v>
+        <v>26.26</v>
       </c>
       <c r="D706" s="2" t="n">
         <v>3.03</v>
       </c>
       <c r="E706" s="3" t="n">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="F706" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G706" s="3" t="n">
         <v>102</v>
@@ -19510,25 +19510,25 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>VRNA.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C707" s="2" t="n">
-        <v>26.26</v>
+        <v>34.34</v>
       </c>
       <c r="D707" s="2" t="n">
         <v>3.03</v>
       </c>
       <c r="E707" s="3" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F707" s="3" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G707" s="3" t="n">
         <v>102</v>
@@ -19564,55 +19564,55 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C709" s="2" t="n">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
       <c r="D709" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E709" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="F709" s="3" t="n">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="G709" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C710" s="2" t="n">
-        <v>14.71</v>
+        <v>17.65</v>
       </c>
       <c r="D710" s="2" t="n">
         <v>2.94</v>
       </c>
       <c r="E710" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="F710" s="3" t="n">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="G710" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
     </row>
     <row r="711">
@@ -19645,55 +19645,55 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>PBID.JK</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C712" s="2" t="n">
-        <v>11.63</v>
+        <v>10.68</v>
       </c>
       <c r="D712" s="2" t="n">
         <v>2.91</v>
       </c>
       <c r="E712" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>515</v>
       </c>
       <c r="F712" s="3" t="n">
-        <v>192</v>
+        <v>570</v>
       </c>
       <c r="G712" s="3" t="n">
-        <v>177</v>
+        <v>530</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>PBID.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C713" s="2" t="n">
-        <v>10.68</v>
+        <v>11.63</v>
       </c>
       <c r="D713" s="2" t="n">
         <v>2.91</v>
       </c>
       <c r="E713" s="3" t="n">
-        <v>515</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F713" s="3" t="n">
-        <v>570</v>
+        <v>192</v>
       </c>
       <c r="G713" s="3" t="n">
-        <v>530</v>
+        <v>177</v>
       </c>
     </row>
     <row r="714">
@@ -19834,28 +19834,28 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>PTSP.JK</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C719" s="2" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="D719" s="2" t="n">
         <v>2.78</v>
       </c>
       <c r="E719" s="3" t="n">
-        <v>5200</v>
+        <v>2270</v>
       </c>
       <c r="F719" s="3" t="n">
-        <v>5450</v>
+        <v>2700</v>
       </c>
       <c r="G719" s="3" t="n">
-        <v>4800</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="720">
@@ -19888,28 +19888,28 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>PTSP.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C721" s="2" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="D721" s="2" t="n">
         <v>2.78</v>
       </c>
       <c r="E721" s="3" t="n">
-        <v>2270</v>
+        <v>5200</v>
       </c>
       <c r="F721" s="3" t="n">
-        <v>2700</v>
+        <v>5450</v>
       </c>
       <c r="G721" s="3" t="n">
-        <v>2220</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="722">
@@ -20050,109 +20050,109 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C727" s="2" t="n">
-        <v>17.95</v>
+        <v>17.09</v>
       </c>
       <c r="D727" s="2" t="n">
         <v>2.56</v>
       </c>
       <c r="E727" s="3" t="n">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="F727" s="3" t="n">
-        <v>92</v>
+        <v>274</v>
       </c>
       <c r="G727" s="3" t="n">
-        <v>80</v>
+        <v>240</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C728" s="2" t="n">
-        <v>17.09</v>
+        <v>17.95</v>
       </c>
       <c r="D728" s="2" t="n">
         <v>2.56</v>
       </c>
       <c r="E728" s="3" t="n">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="F728" s="3" t="n">
-        <v>274</v>
+        <v>92</v>
       </c>
       <c r="G728" s="3" t="n">
-        <v>240</v>
+        <v>80</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>LAND.JK</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C729" s="2" t="n">
-        <v>25</v>
+        <v>10.13</v>
       </c>
       <c r="D729" s="2" t="n">
         <v>2.53</v>
       </c>
       <c r="E729" s="3" t="n">
-        <v>1975</v>
+        <v>78</v>
       </c>
       <c r="F729" s="3" t="n">
-        <v>1975</v>
+        <v>87</v>
       </c>
       <c r="G729" s="3" t="n">
-        <v>1620</v>
+        <v>81</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>LAND.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C730" s="2" t="n">
-        <v>10.13</v>
+        <v>25</v>
       </c>
       <c r="D730" s="2" t="n">
         <v>2.53</v>
       </c>
       <c r="E730" s="3" t="n">
-        <v>78</v>
+        <v>1975</v>
       </c>
       <c r="F730" s="3" t="n">
-        <v>87</v>
+        <v>1975</v>
       </c>
       <c r="G730" s="3" t="n">
-        <v>81</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="731">
@@ -20347,55 +20347,55 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C738" s="2" t="n">
-        <v>15.21</v>
+        <v>20.69</v>
       </c>
       <c r="D738" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="E738" s="3" t="n">
-        <v>1085</v>
+        <v>99</v>
       </c>
       <c r="F738" s="3" t="n">
-        <v>1250</v>
+        <v>105</v>
       </c>
       <c r="G738" s="3" t="n">
-        <v>1110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C739" s="2" t="n">
-        <v>20.69</v>
+        <v>15.21</v>
       </c>
       <c r="D739" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="E739" s="3" t="n">
-        <v>99</v>
+        <v>1085</v>
       </c>
       <c r="F739" s="3" t="n">
-        <v>105</v>
+        <v>1250</v>
       </c>
       <c r="G739" s="3" t="n">
-        <v>89</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="740">
@@ -21209,109 +21209,109 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>LAND.JK</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C770" s="2" t="n">
-        <v>11.83</v>
+        <v>11.29</v>
       </c>
       <c r="D770" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E770" s="3" t="n">
-        <v>181.15625</v>
+        <v>62</v>
       </c>
       <c r="F770" s="3" t="n">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="G770" s="3" t="n">
-        <v>189</v>
+        <v>63</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>LAND.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C771" s="2" t="n">
-        <v>11.29</v>
+        <v>11.83</v>
       </c>
       <c r="D771" s="2" t="n">
         <v>1.61</v>
       </c>
       <c r="E771" s="3" t="n">
-        <v>62</v>
+        <v>181.15625</v>
       </c>
       <c r="F771" s="3" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="G771" s="3" t="n">
-        <v>63</v>
+        <v>189</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>TFAS.JK</t>
+          <t>MCAS.JK</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C772" s="2" t="n">
-        <v>11.79</v>
+        <v>16.92</v>
       </c>
       <c r="D772" s="2" t="n">
         <v>1.54</v>
       </c>
       <c r="E772" s="3" t="n">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="F772" s="3" t="n">
-        <v>218</v>
+        <v>304</v>
       </c>
       <c r="G772" s="3" t="n">
-        <v>198</v>
+        <v>264</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>MCAS.JK</t>
+          <t>TFAS.JK</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C773" s="2" t="n">
-        <v>16.92</v>
+        <v>11.79</v>
       </c>
       <c r="D773" s="2" t="n">
         <v>1.54</v>
       </c>
       <c r="E773" s="3" t="n">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="F773" s="3" t="n">
-        <v>304</v>
+        <v>218</v>
       </c>
       <c r="G773" s="3" t="n">
-        <v>264</v>
+        <v>198</v>
       </c>
     </row>
     <row r="774">
@@ -21398,55 +21398,55 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>PYFA.JK</t>
+          <t>STAR.JK</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C777" s="2" t="n">
-        <v>13.77</v>
+        <v>24.4</v>
       </c>
       <c r="D777" s="2" t="n">
         <v>1.45</v>
       </c>
       <c r="E777" s="3" t="n">
-        <v>296</v>
+        <v>480</v>
       </c>
       <c r="F777" s="3" t="n">
-        <v>314</v>
+        <v>515</v>
       </c>
       <c r="G777" s="3" t="n">
-        <v>280</v>
+        <v>420</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>STAR.JK</t>
+          <t>PYFA.JK</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C778" s="2" t="n">
-        <v>24.4</v>
+        <v>13.77</v>
       </c>
       <c r="D778" s="2" t="n">
         <v>1.45</v>
       </c>
       <c r="E778" s="3" t="n">
-        <v>480</v>
+        <v>296</v>
       </c>
       <c r="F778" s="3" t="n">
-        <v>515</v>
+        <v>314</v>
       </c>
       <c r="G778" s="3" t="n">
-        <v>420</v>
+        <v>280</v>
       </c>
     </row>
     <row r="779">
@@ -21533,109 +21533,109 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C782" s="2" t="n">
-        <v>19.87</v>
+        <v>15.38</v>
       </c>
       <c r="D782" s="2" t="n">
         <v>1.28</v>
       </c>
       <c r="E782" s="3" t="n">
-        <v>8125</v>
+        <v>79</v>
       </c>
       <c r="F782" s="3" t="n">
-        <v>9350</v>
+        <v>90</v>
       </c>
       <c r="G782" s="3" t="n">
-        <v>7900</v>
+        <v>79</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C783" s="2" t="n">
-        <v>15.38</v>
+        <v>19.87</v>
       </c>
       <c r="D783" s="2" t="n">
         <v>1.28</v>
       </c>
       <c r="E783" s="3" t="n">
-        <v>79</v>
+        <v>8125</v>
       </c>
       <c r="F783" s="3" t="n">
-        <v>90</v>
+        <v>9350</v>
       </c>
       <c r="G783" s="3" t="n">
-        <v>79</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>LPPS.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C784" s="2" t="n">
-        <v>10.13</v>
+        <v>15.94</v>
       </c>
       <c r="D784" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="E784" s="3" t="n">
-        <v>79</v>
+        <v>13800</v>
       </c>
       <c r="F784" s="3" t="n">
-        <v>87</v>
+        <v>16000</v>
       </c>
       <c r="G784" s="3" t="n">
-        <v>80</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>LPPS.JK</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C785" s="2" t="n">
-        <v>15.94</v>
+        <v>10.13</v>
       </c>
       <c r="D785" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="E785" s="3" t="n">
-        <v>13800</v>
+        <v>79</v>
       </c>
       <c r="F785" s="3" t="n">
-        <v>16000</v>
+        <v>87</v>
       </c>
       <c r="G785" s="3" t="n">
-        <v>13975</v>
+        <v>80</v>
       </c>
     </row>
     <row r="786">
@@ -21965,82 +21965,82 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PORT.JK</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C798" s="2" t="n">
-        <v>20</v>
+        <v>16.38</v>
       </c>
       <c r="D798" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E798" s="3" t="n">
-        <v>406</v>
+        <v>1015</v>
       </c>
       <c r="F798" s="3" t="n">
-        <v>432</v>
+        <v>1030</v>
       </c>
       <c r="G798" s="3" t="n">
-        <v>362</v>
+        <v>890</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>PORT.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C799" s="2" t="n">
-        <v>16.38</v>
+        <v>10.17</v>
       </c>
       <c r="D799" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E799" s="3" t="n">
-        <v>1015</v>
+        <v>177</v>
       </c>
       <c r="F799" s="3" t="n">
-        <v>1030</v>
+        <v>195</v>
       </c>
       <c r="G799" s="3" t="n">
-        <v>890</v>
+        <v>178</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C800" s="2" t="n">
-        <v>10.17</v>
+        <v>20</v>
       </c>
       <c r="D800" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E800" s="3" t="n">
-        <v>177</v>
+        <v>406</v>
       </c>
       <c r="F800" s="3" t="n">
-        <v>195</v>
+        <v>432</v>
       </c>
       <c r="G800" s="3" t="n">
-        <v>178</v>
+        <v>362</v>
       </c>
     </row>
     <row r="801">
@@ -22154,82 +22154,82 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>RELI.JK</t>
+          <t>KREN.JK</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C805" s="2" t="n">
-        <v>14.29</v>
+        <v>26.32</v>
       </c>
       <c r="D805" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E805" s="3" t="n">
-        <v>520</v>
+        <v>19</v>
       </c>
       <c r="F805" s="3" t="n">
-        <v>600</v>
+        <v>24</v>
       </c>
       <c r="G805" s="3" t="n">
-        <v>525</v>
+        <v>19</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C806" s="2" t="n">
-        <v>12.38</v>
+        <v>10.91</v>
       </c>
       <c r="D806" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E806" s="3" t="n">
-        <v>91.91489410400391</v>
+        <v>165</v>
       </c>
       <c r="F806" s="3" t="n">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="G806" s="3" t="n">
-        <v>105</v>
+        <v>165</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>KREN.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C807" s="2" t="n">
-        <v>26.32</v>
+        <v>27.33</v>
       </c>
       <c r="D807" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E807" s="3" t="n">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="F807" s="3" t="n">
-        <v>24</v>
+        <v>191</v>
       </c>
       <c r="G807" s="3" t="n">
-        <v>19</v>
+        <v>150</v>
       </c>
     </row>
     <row r="808">
@@ -22262,88 +22262,88 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>KKES.JK</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C809" s="2" t="n">
-        <v>10.76</v>
+        <v>11.43</v>
       </c>
       <c r="D809" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E809" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>75</v>
       </c>
       <c r="F809" s="3" t="n">
-        <v>3500</v>
+        <v>78</v>
       </c>
       <c r="G809" s="3" t="n">
-        <v>3160</v>
+        <v>70</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>PDES.JK</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C810" s="2" t="n">
-        <v>12.87</v>
+        <v>18.01</v>
       </c>
       <c r="D810" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E810" s="3" t="n">
-        <v>93</v>
+        <v>424</v>
       </c>
       <c r="F810" s="3" t="n">
-        <v>114</v>
+        <v>498</v>
       </c>
       <c r="G810" s="3" t="n">
-        <v>101</v>
+        <v>422</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>BEKS.JK</t>
+          <t>RELI.JK</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C811" s="2" t="n">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
       <c r="D811" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E811" s="3" t="n">
-        <v>38</v>
+        <v>520</v>
       </c>
       <c r="F811" s="3" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="G811" s="3" t="n">
-        <v>36</v>
+        <v>525</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>MPRO.JK</t>
+          <t>IKAN.JK</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -22352,383 +22352,385 @@
         </is>
       </c>
       <c r="C812" s="2" t="n">
-        <v>19.95</v>
+        <v>10.26</v>
       </c>
       <c r="D812" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E812" s="3" t="inlineStr"/>
+      <c r="E812" s="3" t="n">
+        <v>79</v>
+      </c>
       <c r="F812" s="3" t="n">
-        <v>11875</v>
+        <v>86</v>
       </c>
       <c r="G812" s="3" t="n">
-        <v>9900</v>
+        <v>78</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>IKAN.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C813" s="2" t="n">
-        <v>10.26</v>
+        <v>10.76</v>
       </c>
       <c r="D813" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E813" s="3" t="n">
-        <v>79</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F813" s="3" t="n">
-        <v>86</v>
+        <v>3500</v>
       </c>
       <c r="G813" s="3" t="n">
-        <v>78</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>KKES.JK</t>
+          <t>AISA.JK</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C814" s="2" t="n">
-        <v>11.43</v>
+        <v>12.9</v>
       </c>
       <c r="D814" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E814" s="3" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="F814" s="3" t="n">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="G814" s="3" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>SAFE.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C815" s="2" t="n">
-        <v>12.41</v>
+        <v>28.48</v>
       </c>
       <c r="D815" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E815" s="3" t="n">
-        <v>810</v>
+        <v>152</v>
       </c>
       <c r="F815" s="3" t="n">
-        <v>815</v>
+        <v>194</v>
       </c>
       <c r="G815" s="3" t="n">
-        <v>725</v>
+        <v>151</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>FISH.JK</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C816" s="2" t="n">
-        <v>10.91</v>
+        <v>13.89</v>
       </c>
       <c r="D816" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E816" s="3" t="n">
-        <v>165</v>
+        <v>760</v>
       </c>
       <c r="F816" s="3" t="n">
-        <v>183</v>
+        <v>820</v>
       </c>
       <c r="G816" s="3" t="n">
-        <v>165</v>
+        <v>720</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>ISEA.JK</t>
+          <t>STRK.JK</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C817" s="2" t="n">
-        <v>11.25</v>
+        <v>10.61</v>
       </c>
       <c r="D817" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E817" s="3" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F817" s="3" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="G817" s="3" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C818" s="2" t="n">
-        <v>28.48</v>
+        <v>12.38</v>
       </c>
       <c r="D818" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E818" s="3" t="n">
-        <v>152</v>
+        <v>91.91489410400391</v>
       </c>
       <c r="F818" s="3" t="n">
-        <v>194</v>
+        <v>118</v>
       </c>
       <c r="G818" s="3" t="n">
-        <v>151</v>
+        <v>105</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BTEK.JK</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C819" s="2" t="n">
-        <v>12.78</v>
+        <v>28.57</v>
       </c>
       <c r="D819" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E819" s="3" t="n">
-        <v>2640</v>
+        <v>17</v>
       </c>
       <c r="F819" s="3" t="n">
-        <v>3000</v>
+        <v>18</v>
       </c>
       <c r="G819" s="3" t="n">
-        <v>2660</v>
+        <v>14</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>TAXI.JK</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C820" s="2" t="n">
-        <v>17.65</v>
+        <v>11.11</v>
       </c>
       <c r="D820" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E820" s="3" t="n">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="F820" s="3" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="G820" s="3" t="n">
-        <v>170</v>
+        <v>18</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>AISA.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C821" s="2" t="n">
-        <v>12.9</v>
+        <v>17.65</v>
       </c>
       <c r="D821" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E821" s="3" t="n">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="F821" s="3" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="G821" s="3" t="n">
-        <v>124</v>
+        <v>170</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>TAXI.JK</t>
+          <t>BTEK.JK</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C822" s="2" t="n">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
       <c r="D822" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E822" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F822" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G822" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>BTEK.JK</t>
+          <t>ISEA.JK</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C823" s="2" t="n">
-        <v>28.57</v>
+        <v>11.25</v>
       </c>
       <c r="D823" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E823" s="3" t="n">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="F823" s="3" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="G823" s="3" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>BTEK.JK</t>
+          <t>SAFE.JK</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C824" s="2" t="n">
-        <v>14.29</v>
+        <v>12.41</v>
       </c>
       <c r="D824" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E824" s="3" t="n">
-        <v>14</v>
+        <v>810</v>
       </c>
       <c r="F824" s="3" t="n">
-        <v>16</v>
+        <v>815</v>
       </c>
       <c r="G824" s="3" t="n">
-        <v>14</v>
+        <v>725</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>KREN.JK</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C825" s="2" t="n">
-        <v>27.33</v>
+        <v>10.53</v>
       </c>
       <c r="D825" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E825" s="3" t="n">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="F825" s="3" t="n">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="G825" s="3" t="n">
-        <v>150</v>
+        <v>19</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>ANDI.JK</t>
+          <t>BEKS.JK</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C826" s="2" t="n">
-        <v>20</v>
+        <v>11.11</v>
       </c>
       <c r="D826" s="2" t="n">
         <v>0</v>
@@ -22737,118 +22739,116 @@
         <v>38</v>
       </c>
       <c r="F826" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G826" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>STRK.JK</t>
+          <t>ANDI.JK</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C827" s="2" t="n">
-        <v>10.61</v>
+        <v>20</v>
       </c>
       <c r="D827" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E827" s="3" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F827" s="3" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G827" s="3" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>KREN.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C828" s="2" t="n">
-        <v>10.53</v>
+        <v>12.87</v>
       </c>
       <c r="D828" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E828" s="3" t="n">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="F828" s="3" t="n">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="G828" s="3" t="n">
-        <v>19</v>
+        <v>101</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>PDES.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C829" s="2" t="n">
-        <v>18.01</v>
+        <v>12.78</v>
       </c>
       <c r="D829" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E829" s="3" t="n">
-        <v>424</v>
+        <v>2640</v>
       </c>
       <c r="F829" s="3" t="n">
-        <v>498</v>
+        <v>3000</v>
       </c>
       <c r="G829" s="3" t="n">
-        <v>422</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>FISH.JK</t>
+          <t>MPRO.JK</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C830" s="2" t="n">
-        <v>13.89</v>
+        <v>19.95</v>
       </c>
       <c r="D830" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E830" s="3" t="n">
-        <v>760</v>
-      </c>
+      <c r="E830" s="3" t="inlineStr"/>
       <c r="F830" s="3" t="n">
-        <v>820</v>
+        <v>11875</v>
       </c>
       <c r="G830" s="3" t="n">
-        <v>720</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="831">
@@ -23961,66 +23961,66 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>YPAS.JK</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C872" s="2" t="n">
-        <v>15.19</v>
+        <v>19.62</v>
       </c>
       <c r="D872" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E872" s="3" t="n">
-        <v>160</v>
+        <v>910</v>
       </c>
       <c r="F872" s="3" t="n">
-        <v>182</v>
+        <v>945</v>
       </c>
       <c r="G872" s="3" t="n">
-        <v>154</v>
+        <v>770</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>YPAS.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C873" s="2" t="n">
-        <v>19.62</v>
+        <v>15.19</v>
       </c>
       <c r="D873" s="2" t="n">
         <v>-2.53</v>
       </c>
       <c r="E873" s="3" t="n">
-        <v>910</v>
+        <v>80</v>
       </c>
       <c r="F873" s="3" t="n">
-        <v>945</v>
+        <v>91</v>
       </c>
       <c r="G873" s="3" t="n">
-        <v>770</v>
+        <v>77</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C874" s="2" t="n">
@@ -24030,13 +24030,13 @@
         <v>-2.53</v>
       </c>
       <c r="E874" s="3" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="F874" s="3" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="G874" s="3" t="n">
-        <v>77</v>
+        <v>154</v>
       </c>
     </row>
     <row r="875">
@@ -24636,55 +24636,55 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C897" s="2" t="n">
-        <v>19.31</v>
+        <v>10.9</v>
       </c>
       <c r="D897" s="2" t="n">
         <v>-4.14</v>
       </c>
       <c r="E897" s="3" t="n">
-        <v>149</v>
+        <v>2670</v>
       </c>
       <c r="F897" s="3" t="n">
-        <v>173</v>
+        <v>2950</v>
       </c>
       <c r="G897" s="3" t="n">
-        <v>139</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C898" s="2" t="n">
-        <v>18.05</v>
+        <v>19.31</v>
       </c>
       <c r="D898" s="2" t="n">
         <v>-4.14</v>
       </c>
       <c r="E898" s="3" t="n">
-        <v>2700</v>
+        <v>149</v>
       </c>
       <c r="F898" s="3" t="n">
-        <v>3140</v>
+        <v>173</v>
       </c>
       <c r="G898" s="3" t="n">
-        <v>2550</v>
+        <v>139</v>
       </c>
     </row>
     <row r="899">
@@ -24695,20 +24695,20 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C899" s="2" t="n">
-        <v>10.9</v>
+        <v>18.05</v>
       </c>
       <c r="D899" s="2" t="n">
         <v>-4.14</v>
       </c>
       <c r="E899" s="3" t="n">
-        <v>2670</v>
+        <v>2700</v>
       </c>
       <c r="F899" s="3" t="n">
-        <v>2950</v>
+        <v>3140</v>
       </c>
       <c r="G899" s="3" t="n">
         <v>2550</v>
@@ -25041,55 +25041,55 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>NASA.JK</t>
+          <t>POLA.JK</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C912" s="2" t="n">
-        <v>17.5</v>
+        <v>13.33</v>
       </c>
       <c r="D912" s="2" t="n">
         <v>-5</v>
       </c>
       <c r="E912" s="3" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="F912" s="3" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G912" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>POLA.JK</t>
+          <t>NASA.JK</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C913" s="2" t="n">
-        <v>13.33</v>
+        <v>17.5</v>
       </c>
       <c r="D913" s="2" t="n">
         <v>-5</v>
       </c>
       <c r="E913" s="3" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F913" s="3" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G913" s="3" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="914">
@@ -25311,55 +25311,55 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C922" s="2" t="n">
-        <v>13.58</v>
+        <v>21.24</v>
       </c>
       <c r="D922" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E922" s="3" t="n">
-        <v>162</v>
+        <v>1827.910536399762</v>
       </c>
       <c r="F922" s="3" t="n">
-        <v>184</v>
+        <v>1855</v>
       </c>
       <c r="G922" s="3" t="n">
-        <v>153</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C923" s="2" t="n">
-        <v>21.24</v>
+        <v>13.58</v>
       </c>
       <c r="D923" s="2" t="n">
         <v>-5.56</v>
       </c>
       <c r="E923" s="3" t="n">
-        <v>1827.910536399762</v>
+        <v>162</v>
       </c>
       <c r="F923" s="3" t="n">
-        <v>1855</v>
+        <v>184</v>
       </c>
       <c r="G923" s="3" t="n">
-        <v>1445</v>
+        <v>153</v>
       </c>
     </row>
     <row r="924">
@@ -25716,55 +25716,55 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C937" s="2" t="n">
-        <v>14.94</v>
+        <v>14.79</v>
       </c>
       <c r="D937" s="2" t="n">
         <v>-6.51</v>
       </c>
       <c r="E937" s="3" t="n">
-        <v>2610</v>
+        <v>178</v>
       </c>
       <c r="F937" s="3" t="n">
-        <v>3000</v>
+        <v>194</v>
       </c>
       <c r="G937" s="3" t="n">
-        <v>2440</v>
+        <v>158</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C938" s="2" t="n">
-        <v>14.79</v>
+        <v>14.94</v>
       </c>
       <c r="D938" s="2" t="n">
         <v>-6.51</v>
       </c>
       <c r="E938" s="3" t="n">
-        <v>178</v>
+        <v>2610</v>
       </c>
       <c r="F938" s="3" t="n">
-        <v>194</v>
+        <v>3000</v>
       </c>
       <c r="G938" s="3" t="n">
-        <v>158</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="939">
@@ -25932,28 +25932,28 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>PTSN.JK</t>
+          <t>BEKS.JK</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C945" s="2" t="n">
-        <v>10.34</v>
+        <v>17.24</v>
       </c>
       <c r="D945" s="2" t="n">
         <v>-6.9</v>
       </c>
       <c r="E945" s="3" t="n">
-        <v>408</v>
+        <v>34</v>
       </c>
       <c r="F945" s="3" t="n">
-        <v>448</v>
+        <v>34</v>
       </c>
       <c r="G945" s="3" t="n">
-        <v>378</v>
+        <v>27</v>
       </c>
     </row>
     <row r="946">
@@ -25986,28 +25986,28 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>BEKS.JK</t>
+          <t>PTSN.JK</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C947" s="2" t="n">
-        <v>17.24</v>
+        <v>10.34</v>
       </c>
       <c r="D947" s="2" t="n">
         <v>-6.9</v>
       </c>
       <c r="E947" s="3" t="n">
-        <v>34</v>
+        <v>408</v>
       </c>
       <c r="F947" s="3" t="n">
-        <v>34</v>
+        <v>448</v>
       </c>
       <c r="G947" s="3" t="n">
-        <v>27</v>
+        <v>378</v>
       </c>
     </row>
     <row r="948">
@@ -27039,55 +27039,55 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>DMMX.JK</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C986" s="2" t="n">
-        <v>16.35</v>
+        <v>25</v>
       </c>
       <c r="D986" s="2" t="n">
         <v>-12.5</v>
       </c>
       <c r="E986" s="3" t="n">
-        <v>91</v>
+        <v>258</v>
       </c>
       <c r="F986" s="3" t="n">
-        <v>121</v>
+        <v>270</v>
       </c>
       <c r="G986" s="3" t="n">
-        <v>91</v>
+        <v>189</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>DMMX.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C987" s="2" t="n">
-        <v>25</v>
+        <v>16.35</v>
       </c>
       <c r="D987" s="2" t="n">
         <v>-12.5</v>
       </c>
       <c r="E987" s="3" t="n">
-        <v>258</v>
+        <v>91</v>
       </c>
       <c r="F987" s="3" t="n">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c r="G987" s="3" t="n">
-        <v>189</v>
+        <v>91</v>
       </c>
     </row>
     <row r="988">
@@ -27606,188 +27606,188 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C1007" s="2" t="n">
-        <v>14.86</v>
+        <v>15.94</v>
       </c>
       <c r="D1007" s="2" t="n">
         <v>-14.86</v>
       </c>
       <c r="E1007" s="3" t="n">
-        <v>296</v>
+        <v>2760</v>
       </c>
       <c r="F1007" s="3" t="n">
-        <v>340</v>
+        <v>3200</v>
       </c>
       <c r="G1007" s="3" t="n">
-        <v>252</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C1008" s="2" t="n">
-        <v>15.94</v>
+        <v>14.86</v>
       </c>
       <c r="D1008" s="2" t="n">
         <v>-14.86</v>
       </c>
       <c r="E1008" s="3" t="n">
-        <v>2760</v>
+        <v>296</v>
       </c>
       <c r="F1008" s="3" t="n">
-        <v>3200</v>
+        <v>340</v>
       </c>
       <c r="G1008" s="3" t="n">
-        <v>2350</v>
+        <v>252</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>AGAR.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C1009" s="2" t="n">
-        <v>24.79</v>
+        <v>25</v>
       </c>
       <c r="D1009" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E1009" s="3" t="n">
-        <v>1510</v>
+        <v>165</v>
       </c>
       <c r="F1009" s="3" t="n">
-        <v>1510</v>
+        <v>210</v>
       </c>
       <c r="G1009" s="3" t="n">
-        <v>1030</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>AGAR.JK</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C1010" s="2" t="n">
-        <v>14.05</v>
+        <v>24.79</v>
       </c>
       <c r="D1010" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E1010" s="3" t="n">
-        <v>115</v>
+        <v>1510</v>
       </c>
       <c r="F1010" s="3" t="n">
-        <v>138</v>
+        <v>1510</v>
       </c>
       <c r="G1010" s="3" t="n">
-        <v>103</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C1011" s="2" t="n">
-        <v>25</v>
+        <v>14.05</v>
       </c>
       <c r="D1011" s="2" t="n">
         <v>-14.88</v>
       </c>
       <c r="E1011" s="3" t="n">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="F1011" s="3" t="n">
-        <v>210</v>
+        <v>138</v>
       </c>
       <c r="G1011" s="3" t="n">
-        <v>143</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>CCSI.JK</t>
+          <t>LCKM.JK</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C1012" s="2" t="n">
-        <v>19.15</v>
+        <v>18.44</v>
       </c>
       <c r="D1012" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E1012" s="3" t="n">
-        <v>525</v>
-      </c>
+      <c r="E1012" s="3" t="inlineStr"/>
       <c r="F1012" s="3" t="n">
-        <v>560</v>
+        <v>167</v>
       </c>
       <c r="G1012" s="3" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>CCSI.JK</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C1013" s="2" t="n">
-        <v>18.44</v>
+        <v>19.15</v>
       </c>
       <c r="D1013" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E1013" s="3" t="inlineStr"/>
+      <c r="E1013" s="3" t="n">
+        <v>525</v>
+      </c>
       <c r="F1013" s="3" t="n">
-        <v>167</v>
+        <v>560</v>
       </c>
       <c r="G1013" s="3" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1014">
